--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G20">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G33">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G155">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G166">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G205">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G207">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G220">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O223">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="P223">
-        <v>6.06</v>
+        <v>4.36</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36697,16 +36697,16 @@
         <v>0</v>
       </c>
       <c r="AA223">
+        <v>0</v>
+      </c>
+      <c r="AB223">
+        <v>0</v>
+      </c>
+      <c r="AC223">
+        <v>2.15</v>
+      </c>
+      <c r="AD223">
         <v>1.62</v>
-      </c>
-      <c r="AB223">
-        <v>2.15</v>
-      </c>
-      <c r="AC223">
-        <v>0</v>
-      </c>
-      <c r="AD223">
-        <v>0</v>
       </c>
       <c r="AE223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="O224">
-        <v>4.36</v>
+        <v>3.62</v>
       </c>
       <c r="P224">
-        <v>4.36</v>
+        <v>3.23</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36860,16 +36860,16 @@
         <v>0</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC224">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD224">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="O225">
-        <v>3.62</v>
+        <v>3.41</v>
       </c>
       <c r="P225">
-        <v>3.23</v>
+        <v>2.86</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37023,10 +37023,10 @@
         <v>0</v>
       </c>
       <c r="AA225">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AB225">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.69</v>
+        <v>1.6</v>
       </c>
       <c r="O226">
-        <v>3.41</v>
+        <v>4.42</v>
       </c>
       <c r="P226">
-        <v>2.86</v>
+        <v>6.06</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37186,10 +37186,10 @@
         <v>0</v>
       </c>
       <c r="AA226">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AB226">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC226">
         <v>0</v>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G270">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G279">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G280">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G282">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G284">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU301"/>
+  <dimension ref="A1:AU302"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G8">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G15">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G22">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G67">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G155">
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G167">
@@ -27651,7 +27651,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,22 +28303,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G184">
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:00</t>
+          <t>2026-10-25 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G187">
@@ -30906,27 +30906,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G188">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>2026-10-25 12:30:00</t>
+          <t>2026-10-25 12:15:00</t>
         </is>
       </c>
     </row>
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O189">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="P189">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31161,10 +31161,10 @@
         <v>0</v>
       </c>
       <c r="AC189">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD189">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="O190">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="P190">
-        <v>7.48</v>
+        <v>4.4</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31324,10 +31324,10 @@
         <v>0</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE190">
         <v>0</v>
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>3.38</v>
+        <v>1.36</v>
       </c>
       <c r="O191">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="P191">
-        <v>2.05</v>
+        <v>7.48</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB191">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31726,22 +31726,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,22 +31889,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O194">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="P194">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O196">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P196">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB196">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-10-25 12:45:00</t>
+          <t>2026-10-25 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="O200">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="P200">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -32954,10 +32954,10 @@
         <v>0</v>
       </c>
       <c r="AC200">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD200">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE200">
         <v>0</v>
@@ -33025,12 +33025,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33117,10 +33117,10 @@
         <v>0</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE201">
         <v>0</v>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-10-25 13:00:00</t>
+          <t>2026-10-25 12:45:00</t>
         </is>
       </c>
     </row>
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,22 +33519,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,22 +34171,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O208">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P208">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34334,22 +34334,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34497,22 +34497,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O212">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P212">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,22 +35638,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,22 +36290,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G221">
@@ -36448,12 +36448,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="G222">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-10-25 13:15:00</t>
+          <t>2026-10-25 13:00:00</t>
         </is>
       </c>
     </row>
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O223">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="P223">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36703,10 +36703,10 @@
         <v>0</v>
       </c>
       <c r="AC223">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD223">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="O224">
-        <v>3.62</v>
+        <v>4.36</v>
       </c>
       <c r="P224">
-        <v>3.23</v>
+        <v>4.36</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36860,16 +36860,16 @@
         <v>0</v>
       </c>
       <c r="AA224">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB224">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="O225">
-        <v>3.41</v>
+        <v>3.62</v>
       </c>
       <c r="P225">
-        <v>2.86</v>
+        <v>3.23</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37023,10 +37023,10 @@
         <v>0</v>
       </c>
       <c r="AA225">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB225">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="O226">
-        <v>4.42</v>
+        <v>3.41</v>
       </c>
       <c r="P226">
-        <v>6.06</v>
+        <v>2.86</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37186,10 +37186,10 @@
         <v>0</v>
       </c>
       <c r="AA226">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AB226">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC226">
         <v>0</v>
@@ -37263,12 +37263,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>3.03</v>
+        <v>1.6</v>
       </c>
       <c r="O227">
-        <v>3.51</v>
+        <v>4.42</v>
       </c>
       <c r="P227">
-        <v>2.5</v>
+        <v>6.06</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB227">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AC227">
         <v>0</v>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-10-25 13:30:00</t>
+          <t>2026-10-25 13:15:00</t>
         </is>
       </c>
     </row>
@@ -37431,22 +37431,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G228">
@@ -37469,17 +37469,17 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37512,10 +37512,10 @@
         <v>0</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC228">
         <v>0</v>
@@ -37594,22 +37594,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G229">
@@ -37632,7 +37632,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,22 +37920,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,22 +38083,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G233">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G235">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O237">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="P237">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -38985,10 +38985,10 @@
         <v>0</v>
       </c>
       <c r="AC237">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD237">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE237">
         <v>0</v>
@@ -39056,12 +39056,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39148,10 +39148,10 @@
         <v>0</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE238">
         <v>0</v>
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-10-25 14:00:00</t>
+          <t>2026-10-25 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O242">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P242">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O245">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="P245">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB245">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40360,27 +40360,27 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-10-25 14:15:00</t>
+          <t>2026-10-25 14:00:00</t>
         </is>
       </c>
     </row>
@@ -40523,27 +40523,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G247">
@@ -40674,7 +40674,7 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>2026-10-25 14:30:00</t>
+          <t>2026-10-25 14:15:00</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O248">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P248">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G250">
@@ -41175,12 +41175,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G251">
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-10-25 14:45:00</t>
+          <t>2026-10-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -41338,27 +41338,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G252">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-10-25 15:00:00</t>
+          <t>2026-10-25 14:45:00</t>
         </is>
       </c>
     </row>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,22 +41669,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="O258">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P258">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -42402,10 +42402,10 @@
         <v>0</v>
       </c>
       <c r="AA258">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB258">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC258">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>4.28</v>
+        <v>6.67</v>
       </c>
       <c r="O259">
-        <v>3.65</v>
+        <v>4.38</v>
       </c>
       <c r="P259">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42565,10 +42565,10 @@
         <v>0</v>
       </c>
       <c r="AA259">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB259">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC259">
         <v>0</v>
@@ -42642,27 +42642,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42728,10 +42728,10 @@
         <v>0</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC260">
         <v>0</v>
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-10-25 15:15:00</t>
+          <t>2026-10-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G263">
@@ -43294,27 +43294,27 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-10-25 15:30:00</t>
+          <t>2026-10-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -43625,22 +43625,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G266">
@@ -43783,27 +43783,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-10-25 16:00:00</t>
+          <t>2026-10-25 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45087,12 +45087,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="O275">
-        <v>4.78</v>
+        <v>3.9</v>
       </c>
       <c r="P275">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45179,10 +45179,10 @@
         <v>0</v>
       </c>
       <c r="AC275">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD275">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE275">
         <v>0</v>
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-10-25 16:45:00</t>
+          <t>2026-10-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>4.68</v>
+        <v>1.58</v>
       </c>
       <c r="O276">
-        <v>3.91</v>
+        <v>4.78</v>
       </c>
       <c r="P276">
-        <v>1.83</v>
+        <v>5.75</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45336,16 +45336,16 @@
         <v>0</v>
       </c>
       <c r="AA276">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB276">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE276">
         <v>0</v>
@@ -45413,27 +45413,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45499,10 +45499,10 @@
         <v>0</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC277">
         <v>0</v>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-10-25 17:00:00</t>
+          <t>2026-10-25 16:45:00</t>
         </is>
       </c>
     </row>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G278">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G279">
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G281">
@@ -46722,22 +46722,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G285">
@@ -46880,27 +46880,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,22 +47211,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O288">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="P288">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G293">
@@ -48184,27 +48184,27 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-10-25 18:00:00</t>
+          <t>2026-10-25 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48352,7 +48352,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G295">
@@ -48510,12 +48510,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-10-25 18:15:00</t>
+          <t>2026-10-25 18:00:00</t>
         </is>
       </c>
     </row>
@@ -48673,12 +48673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G297">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-10-25 18:30:00</t>
+          <t>2026-10-25 18:15:00</t>
         </is>
       </c>
     </row>
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-25 20:00:00</t>
+          <t>2026-10-25 18:30:00</t>
         </is>
       </c>
     </row>
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G299">
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G300">
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-10-25 20:30:00</t>
+          <t>2026-10-25 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,156 +49325,319 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="G301">
+        <v>0</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>0</v>
+      </c>
+      <c r="L301">
+        <v>0</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N301">
+        <v>0</v>
+      </c>
+      <c r="O301">
+        <v>0</v>
+      </c>
+      <c r="P301">
+        <v>0</v>
+      </c>
+      <c r="Q301">
+        <v>0</v>
+      </c>
+      <c r="R301">
+        <v>0</v>
+      </c>
+      <c r="S301">
+        <v>0</v>
+      </c>
+      <c r="T301">
+        <v>0</v>
+      </c>
+      <c r="U301">
+        <v>0</v>
+      </c>
+      <c r="V301">
+        <v>0</v>
+      </c>
+      <c r="W301">
+        <v>0</v>
+      </c>
+      <c r="X301">
+        <v>0</v>
+      </c>
+      <c r="Y301">
+        <v>0</v>
+      </c>
+      <c r="Z301">
+        <v>0</v>
+      </c>
+      <c r="AA301">
+        <v>0</v>
+      </c>
+      <c r="AB301">
+        <v>0</v>
+      </c>
+      <c r="AC301">
+        <v>0</v>
+      </c>
+      <c r="AD301">
+        <v>0</v>
+      </c>
+      <c r="AE301">
+        <v>0</v>
+      </c>
+      <c r="AF301">
+        <v>0</v>
+      </c>
+      <c r="AG301">
+        <v>0</v>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ301">
+        <v>0</v>
+      </c>
+      <c r="AK301">
+        <v>0</v>
+      </c>
+      <c r="AL301">
+        <v>0</v>
+      </c>
+      <c r="AM301">
+        <v>-1</v>
+      </c>
+      <c r="AN301">
+        <v>-1</v>
+      </c>
+      <c r="AO301">
+        <v>-1</v>
+      </c>
+      <c r="AP301">
+        <v>-1</v>
+      </c>
+      <c r="AQ301">
+        <v>0</v>
+      </c>
+      <c r="AR301">
+        <v>0</v>
+      </c>
+      <c r="AS301">
+        <v>0</v>
+      </c>
+      <c r="AT301">
+        <v>0</v>
+      </c>
+      <c r="AU301" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="D302" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
+      <c r="E302" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
+      <c r="F302" t="inlineStr">
         <is>
           <t>LA Galaxy</t>
         </is>
       </c>
-      <c r="G301">
-        <v>0</v>
-      </c>
-      <c r="H301">
-        <v>0</v>
-      </c>
-      <c r="I301">
-        <v>0</v>
-      </c>
-      <c r="J301">
-        <v>0</v>
-      </c>
-      <c r="K301">
-        <v>0</v>
-      </c>
-      <c r="L301">
-        <v>0</v>
-      </c>
-      <c r="M301" t="inlineStr">
+      <c r="G302">
+        <v>0</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>0</v>
+      </c>
+      <c r="M302" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N301">
-        <v>0</v>
-      </c>
-      <c r="O301">
-        <v>0</v>
-      </c>
-      <c r="P301">
-        <v>0</v>
-      </c>
-      <c r="Q301">
-        <v>0</v>
-      </c>
-      <c r="R301">
-        <v>0</v>
-      </c>
-      <c r="S301">
-        <v>0</v>
-      </c>
-      <c r="T301">
-        <v>0</v>
-      </c>
-      <c r="U301">
-        <v>0</v>
-      </c>
-      <c r="V301">
-        <v>0</v>
-      </c>
-      <c r="W301">
-        <v>0</v>
-      </c>
-      <c r="X301">
-        <v>0</v>
-      </c>
-      <c r="Y301">
-        <v>0</v>
-      </c>
-      <c r="Z301">
-        <v>0</v>
-      </c>
-      <c r="AA301">
-        <v>0</v>
-      </c>
-      <c r="AB301">
-        <v>0</v>
-      </c>
-      <c r="AC301">
-        <v>0</v>
-      </c>
-      <c r="AD301">
-        <v>0</v>
-      </c>
-      <c r="AE301">
-        <v>0</v>
-      </c>
-      <c r="AF301">
-        <v>0</v>
-      </c>
-      <c r="AG301">
-        <v>0</v>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI301" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ301">
-        <v>0</v>
-      </c>
-      <c r="AK301">
-        <v>0</v>
-      </c>
-      <c r="AL301">
-        <v>0</v>
-      </c>
-      <c r="AM301">
-        <v>-1</v>
-      </c>
-      <c r="AN301">
-        <v>-1</v>
-      </c>
-      <c r="AO301">
-        <v>-1</v>
-      </c>
-      <c r="AP301">
-        <v>-1</v>
-      </c>
-      <c r="AQ301">
-        <v>0</v>
-      </c>
-      <c r="AR301">
-        <v>0</v>
-      </c>
-      <c r="AS301">
-        <v>0</v>
-      </c>
-      <c r="AT301">
-        <v>0</v>
-      </c>
-      <c r="AU301" t="inlineStr">
+      <c r="N302">
+        <v>0</v>
+      </c>
+      <c r="O302">
+        <v>0</v>
+      </c>
+      <c r="P302">
+        <v>0</v>
+      </c>
+      <c r="Q302">
+        <v>0</v>
+      </c>
+      <c r="R302">
+        <v>0</v>
+      </c>
+      <c r="S302">
+        <v>0</v>
+      </c>
+      <c r="T302">
+        <v>0</v>
+      </c>
+      <c r="U302">
+        <v>0</v>
+      </c>
+      <c r="V302">
+        <v>0</v>
+      </c>
+      <c r="W302">
+        <v>0</v>
+      </c>
+      <c r="X302">
+        <v>0</v>
+      </c>
+      <c r="Y302">
+        <v>0</v>
+      </c>
+      <c r="Z302">
+        <v>0</v>
+      </c>
+      <c r="AA302">
+        <v>0</v>
+      </c>
+      <c r="AB302">
+        <v>0</v>
+      </c>
+      <c r="AC302">
+        <v>0</v>
+      </c>
+      <c r="AD302">
+        <v>0</v>
+      </c>
+      <c r="AE302">
+        <v>0</v>
+      </c>
+      <c r="AF302">
+        <v>0</v>
+      </c>
+      <c r="AG302">
+        <v>0</v>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ302">
+        <v>0</v>
+      </c>
+      <c r="AK302">
+        <v>0</v>
+      </c>
+      <c r="AL302">
+        <v>0</v>
+      </c>
+      <c r="AM302">
+        <v>-1</v>
+      </c>
+      <c r="AN302">
+        <v>-1</v>
+      </c>
+      <c r="AO302">
+        <v>-1</v>
+      </c>
+      <c r="AP302">
+        <v>-1</v>
+      </c>
+      <c r="AQ302">
+        <v>0</v>
+      </c>
+      <c r="AR302">
+        <v>0</v>
+      </c>
+      <c r="AS302">
+        <v>0</v>
+      </c>
+      <c r="AT302">
+        <v>0</v>
+      </c>
+      <c r="AU302" t="inlineStr">
         <is>
           <t>2026-10-25 22:00:00</t>
         </is>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G8">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G110">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36697,10 +36697,10 @@
         <v>0</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC223">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.69</v>
+        <v>1.6</v>
       </c>
       <c r="O226">
-        <v>3.41</v>
+        <v>4.42</v>
       </c>
       <c r="P226">
-        <v>2.86</v>
+        <v>6.06</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37186,10 +37186,10 @@
         <v>0</v>
       </c>
       <c r="AA226">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AB226">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="O227">
-        <v>4.42</v>
+        <v>3.41</v>
       </c>
       <c r="P227">
-        <v>6.06</v>
+        <v>2.86</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AB227">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC227">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30509,10 +30509,10 @@
         <v>0</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE185">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34095,10 +34095,10 @@
         <v>0</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE207">
         <v>0</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36051,10 +36051,10 @@
         <v>0</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q231">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q176">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41261,10 +41261,10 @@
         <v>0</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC251">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43386,10 +43386,10 @@
         <v>0</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE264">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P298">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q298">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC139">
         <v>0</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23168,10 +23168,10 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC140">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39637,10 +39637,10 @@
         <v>0</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE241">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q300">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G160">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G167">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G174">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G175">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G183">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>7.18</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49580,10 +49580,10 @@
         <v>0</v>
       </c>
       <c r="AC302">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD302">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE302">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="O125">
-        <v>4.36</v>
+        <v>3.84</v>
       </c>
       <c r="P125">
-        <v>4.42</v>
+        <v>2.65</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>5.07</v>
+        <v>2.11</v>
       </c>
       <c r="O126">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="P126">
-        <v>1.71</v>
+        <v>3.43</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="O127">
-        <v>3.84</v>
+        <v>4.36</v>
       </c>
       <c r="P127">
-        <v>2.65</v>
+        <v>4.42</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.11</v>
+        <v>5.07</v>
       </c>
       <c r="O128">
-        <v>4.01</v>
+        <v>4.26</v>
       </c>
       <c r="P128">
-        <v>3.43</v>
+        <v>1.71</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB128">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G174">
@@ -28955,22 +28955,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O176">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P176">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29118,22 +29118,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O177">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P177">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>7.18</v>
+        <v>0</v>
       </c>
       <c r="O184">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P184">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O185">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="P185">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30509,10 +30509,10 @@
         <v>0</v>
       </c>
       <c r="AC185">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD185">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE185">
         <v>0</v>
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.19</v>
+        <v>7.18</v>
       </c>
       <c r="O186">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="P186">
-        <v>3.18</v>
+        <v>1.41</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:00</t>
+          <t>2026-10-25 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="O187">
-        <v>3.65</v>
+        <v>5.51</v>
       </c>
       <c r="P187">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,16 +30829,16 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB187">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE187">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:00</t>
+          <t>2026-10-25 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31069,27 +31069,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>2026-10-25 12:30:00</t>
+          <t>2026-10-25 12:15:00</t>
         </is>
       </c>
     </row>
@@ -31232,12 +31232,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O190">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="P190">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31324,10 +31324,10 @@
         <v>0</v>
       </c>
       <c r="AC190">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD190">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE190">
         <v>0</v>
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-10-25 12:30:00</t>
+          <t>2026-10-25 12:15:00</t>
         </is>
       </c>
     </row>
@@ -31400,22 +31400,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O191">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P191">
-        <v>7.48</v>
+        <v>0</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>3.38</v>
+        <v>1.62</v>
       </c>
       <c r="O192">
-        <v>3.38</v>
+        <v>4.45</v>
       </c>
       <c r="P192">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,16 +31644,16 @@
         <v>0</v>
       </c>
       <c r="AA192">
+        <v>0</v>
+      </c>
+      <c r="AB192">
+        <v>0</v>
+      </c>
+      <c r="AC192">
         <v>1.9</v>
       </c>
-      <c r="AB192">
-        <v>1.87</v>
-      </c>
-      <c r="AC192">
-        <v>0</v>
-      </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE192">
         <v>0</v>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31889,22 +31889,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>6.33</v>
+        <v>3.38</v>
       </c>
       <c r="O194">
-        <v>4.76</v>
+        <v>3.38</v>
       </c>
       <c r="P194">
-        <v>1.41</v>
+        <v>2.05</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O195">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="P195">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32215,22 +32215,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.42</v>
+        <v>6.33</v>
       </c>
       <c r="O196">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="P196">
-        <v>5.57</v>
+        <v>1.41</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="O197">
-        <v>3.67</v>
+        <v>4.92</v>
       </c>
       <c r="P197">
-        <v>3.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB197">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32785,10 +32785,10 @@
         <v>0</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC199">
         <v>0</v>
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-10-25 12:45:00</t>
+          <t>2026-10-25 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-10-25 12:45:00</t>
+          <t>2026-10-25 12:30:00</t>
         </is>
       </c>
     </row>
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="O201">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="P201">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33117,10 +33117,10 @@
         <v>0</v>
       </c>
       <c r="AC201">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD201">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE201">
         <v>0</v>
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O202">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P202">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-10-25 13:00:00</t>
+          <t>2026-10-25 12:45:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33443,10 +33443,10 @@
         <v>0</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE203">
         <v>0</v>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-10-25 13:00:00</t>
+          <t>2026-10-25 12:45:00</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O205">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P205">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O206">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P206">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="O207">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="P207">
-        <v>3.69</v>
+        <v>2.84</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34095,10 +34095,10 @@
         <v>0</v>
       </c>
       <c r="AC207">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD207">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="O208">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="P208">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34334,22 +34334,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>6.17</v>
+        <v>1.83</v>
       </c>
       <c r="O209">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P209">
-        <v>1.48</v>
+        <v>3.69</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34421,10 +34421,10 @@
         <v>0</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE209">
         <v>0</v>
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34823,22 +34823,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O213">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P213">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,22 +35801,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O218">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P218">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35964,22 +35964,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O219">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P219">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36051,10 +36051,10 @@
         <v>0</v>
       </c>
       <c r="AC219">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD219">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.79</v>
+        <v>3.83</v>
       </c>
       <c r="O220">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="P220">
-        <v>3.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="O221">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="P221">
-        <v>3.61</v>
+        <v>3.95</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36377,10 +36377,10 @@
         <v>0</v>
       </c>
       <c r="AC221">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD221">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE221">
         <v>0</v>
@@ -36453,22 +36453,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="O222">
-        <v>4.55</v>
+        <v>4.21</v>
       </c>
       <c r="P222">
-        <v>7.55</v>
+        <v>3.56</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36611,27 +36611,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="O223">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="P223">
-        <v>2.93</v>
+        <v>3.61</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36697,10 +36697,10 @@
         <v>0</v>
       </c>
       <c r="AA223">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB223">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC223">
         <v>0</v>
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-10-25 13:15:00</t>
+          <t>2026-10-25 13:00:00</t>
         </is>
       </c>
     </row>
@@ -36774,12 +36774,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="O224">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="P224">
-        <v>4.36</v>
+        <v>7.55</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36866,10 +36866,10 @@
         <v>0</v>
       </c>
       <c r="AC224">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD224">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE224">
         <v>0</v>
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-10-25 13:15:00</t>
+          <t>2026-10-25 13:00:00</t>
         </is>
       </c>
     </row>
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="O225">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="P225">
-        <v>3.23</v>
+        <v>2.93</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37023,10 +37023,10 @@
         <v>0</v>
       </c>
       <c r="AA225">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB225">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AC225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O226">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="P226">
-        <v>6.06</v>
+        <v>4.36</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37186,16 +37186,16 @@
         <v>0</v>
       </c>
       <c r="AA226">
+        <v>0</v>
+      </c>
+      <c r="AB226">
+        <v>0</v>
+      </c>
+      <c r="AC226">
+        <v>2.15</v>
+      </c>
+      <c r="AD226">
         <v>1.62</v>
-      </c>
-      <c r="AB226">
-        <v>2.15</v>
-      </c>
-      <c r="AC226">
-        <v>0</v>
-      </c>
-      <c r="AD226">
-        <v>0</v>
       </c>
       <c r="AE226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="O227">
-        <v>3.41</v>
+        <v>3.62</v>
       </c>
       <c r="P227">
-        <v>2.86</v>
+        <v>3.23</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB227">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC227">
         <v>0</v>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>3.03</v>
+        <v>1.6</v>
       </c>
       <c r="O228">
-        <v>3.51</v>
+        <v>4.42</v>
       </c>
       <c r="P228">
-        <v>2.5</v>
+        <v>6.06</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37512,10 +37512,10 @@
         <v>0</v>
       </c>
       <c r="AA228">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB228">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AC228">
         <v>0</v>
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-10-25 13:30:00</t>
+          <t>2026-10-25 13:15:00</t>
         </is>
       </c>
     </row>
@@ -37589,27 +37589,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G229">
@@ -37632,17 +37632,17 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37675,10 +37675,10 @@
         <v>0</v>
       </c>
       <c r="AA229">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB229">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC229">
         <v>0</v>
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-10-25 13:30:00</t>
+          <t>2026-10-25 13:15:00</t>
         </is>
       </c>
     </row>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O230">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P230">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37838,10 +37838,10 @@
         <v>0</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC230">
         <v>0</v>
@@ -37920,22 +37920,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G231">
@@ -37958,17 +37958,17 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N231">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O231">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P231">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38083,22 +38083,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38409,22 +38409,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O238">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="P238">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39148,10 +39148,10 @@
         <v>0</v>
       </c>
       <c r="AC238">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD238">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE238">
         <v>0</v>
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G239">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-10-25 14:00:00</t>
+          <t>2026-10-25 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39382,12 +39382,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39474,10 +39474,10 @@
         <v>0</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE240">
         <v>0</v>
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-10-25 14:00:00</t>
+          <t>2026-10-25 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O241">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P241">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39637,10 +39637,10 @@
         <v>0</v>
       </c>
       <c r="AC241">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD241">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE241">
         <v>0</v>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>3.15</v>
+        <v>1.28</v>
       </c>
       <c r="O243">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="P243">
-        <v>2.12</v>
+        <v>7.5</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -39963,10 +39963,10 @@
         <v>0</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE243">
         <v>0</v>
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O244">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P244">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O245">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P245">
-        <v>2.52</v>
+        <v>2.12</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>7.7</v>
+        <v>2.48</v>
       </c>
       <c r="O246">
-        <v>4.53</v>
+        <v>3.6</v>
       </c>
       <c r="P246">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB246">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40523,27 +40523,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40674,7 +40674,7 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>2026-10-25 14:15:00</t>
+          <t>2026-10-25 14:00:00</t>
         </is>
       </c>
     </row>
@@ -40686,12 +40686,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.51</v>
+        <v>7.7</v>
       </c>
       <c r="O248">
-        <v>4.59</v>
+        <v>4.53</v>
       </c>
       <c r="P248">
-        <v>6.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40772,10 +40772,10 @@
         <v>0</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC248">
         <v>0</v>
@@ -40837,7 +40837,7 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>2026-10-25 14:30:00</t>
+          <t>2026-10-25 14:00:00</t>
         </is>
       </c>
     </row>
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O249">
-        <v>3.48</v>
+        <v>4.59</v>
       </c>
       <c r="P249">
-        <v>4.24</v>
+        <v>6.24</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O251">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P251">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41261,10 +41261,10 @@
         <v>0</v>
       </c>
       <c r="AA251">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB251">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC251">
         <v>0</v>
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB252">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-10-25 14:45:00</t>
+          <t>2026-10-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -41501,27 +41501,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G253">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-10-25 15:00:00</t>
+          <t>2026-10-25 14:45:00</t>
         </is>
       </c>
     </row>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,22 +41832,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="O259">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P259">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42565,10 +42565,10 @@
         <v>0</v>
       </c>
       <c r="AA259">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB259">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>4.28</v>
+        <v>6.67</v>
       </c>
       <c r="O260">
-        <v>3.65</v>
+        <v>4.38</v>
       </c>
       <c r="P260">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42728,10 +42728,10 @@
         <v>0</v>
       </c>
       <c r="AA260">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB260">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC260">
         <v>0</v>
@@ -42805,27 +42805,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.53</v>
+        <v>4.28</v>
       </c>
       <c r="O261">
-        <v>4.72</v>
+        <v>3.65</v>
       </c>
       <c r="P261">
-        <v>5.49</v>
+        <v>1.91</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42891,10 +42891,10 @@
         <v>0</v>
       </c>
       <c r="AA261">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB261">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC261">
         <v>0</v>
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-10-25 15:15:00</t>
+          <t>2026-10-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -42973,22 +42973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O263">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P263">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>1.32</v>
+        <v>2.56</v>
       </c>
       <c r="O264">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="P264">
-        <v>8.800000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43386,10 +43386,10 @@
         <v>0</v>
       </c>
       <c r="AC264">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD264">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE264">
         <v>0</v>
@@ -43457,27 +43457,27 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43549,10 +43549,10 @@
         <v>0</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE265">
         <v>0</v>
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-10-25 15:30:00</t>
+          <t>2026-10-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G266">
@@ -43788,22 +43788,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G267">
@@ -43946,27 +43946,27 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-10-25 16:00:00</t>
+          <t>2026-10-25 15:30:00</t>
         </is>
       </c>
     </row>
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G270">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O272">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P272">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>4.66</v>
+        <v>1.68</v>
       </c>
       <c r="O273">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P273">
-        <v>1.58</v>
+        <v>4.89</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -47043,27 +47043,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47206,27 +47206,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O289">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="P289">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47532,7 +47532,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47700,22 +47700,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,22 +47863,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G292">
@@ -48026,7 +48026,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48184,27 +48184,27 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 18:00:00</t>
         </is>
       </c>
     </row>
@@ -48352,7 +48352,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48510,12 +48510,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O296">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P296">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-10-25 18:00:00</t>
+          <t>2026-10-25 18:15:00</t>
         </is>
       </c>
     </row>
@@ -48673,12 +48673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P297">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-10-25 18:15:00</t>
+          <t>2026-10-25 18:30:00</t>
         </is>
       </c>
     </row>
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O298">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P298">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-25 18:30:00</t>
+          <t>2026-10-25 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49167,22 +49167,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O300">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P300">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q300">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G184">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G185">

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC136">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q263">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU302"/>
+  <dimension ref="A1:AU304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,55 +644,55 @@
         <v>3.65</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.15</v>
+        <v>1.13</v>
       </c>
       <c r="O120">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="P120">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.13</v>
+        <v>2.15</v>
       </c>
       <c r="O121">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="P121">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G184">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G185">
@@ -37920,22 +37920,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G231">
@@ -37958,7 +37958,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N231">
@@ -38083,22 +38083,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G232">
@@ -38121,7 +38121,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O233">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P233">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38409,22 +38409,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38572,22 +38572,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G237">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G238">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O240">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="P240">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39474,10 +39474,10 @@
         <v>0</v>
       </c>
       <c r="AC240">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD240">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE240">
         <v>0</v>
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39637,10 +39637,10 @@
         <v>0</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE241">
         <v>0</v>
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-10-25 14:00:00</t>
+          <t>2026-10-25 13:30:00</t>
         </is>
       </c>
     </row>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O243">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P243">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -39963,10 +39963,10 @@
         <v>0</v>
       </c>
       <c r="AC243">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD243">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE243">
         <v>0</v>
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40126,10 +40126,10 @@
         <v>0</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE244">
         <v>0</v>
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O245">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P245">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="O246">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P246">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="O247">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P247">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="O248">
-        <v>4.53</v>
+        <v>3.28</v>
       </c>
       <c r="P248">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40772,10 +40772,10 @@
         <v>0</v>
       </c>
       <c r="AA248">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB248">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC248">
         <v>0</v>
@@ -40849,12 +40849,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.51</v>
+        <v>7.7</v>
       </c>
       <c r="O249">
-        <v>4.59</v>
+        <v>4.53</v>
       </c>
       <c r="P249">
-        <v>6.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-10-25 14:30:00</t>
+          <t>2026-10-25 14:00:00</t>
         </is>
       </c>
     </row>
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O250">
-        <v>3.48</v>
+        <v>4.59</v>
       </c>
       <c r="P250">
-        <v>4.24</v>
+        <v>6.24</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O252">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P252">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB252">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-10-25 14:45:00</t>
+          <t>2026-10-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -41664,27 +41664,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-10-25 15:00:00</t>
+          <t>2026-10-25 14:45:00</t>
         </is>
       </c>
     </row>
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="O260">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P260">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42728,10 +42728,10 @@
         <v>0</v>
       </c>
       <c r="AA260">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB260">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>4.28</v>
+        <v>6.67</v>
       </c>
       <c r="O261">
-        <v>3.65</v>
+        <v>4.38</v>
       </c>
       <c r="P261">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42891,10 +42891,10 @@
         <v>0</v>
       </c>
       <c r="AA261">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB261">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC261">
         <v>0</v>
@@ -42968,27 +42968,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>1.53</v>
+        <v>4.28</v>
       </c>
       <c r="O262">
-        <v>4.72</v>
+        <v>3.65</v>
       </c>
       <c r="P262">
-        <v>5.49</v>
+        <v>1.91</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43054,10 +43054,10 @@
         <v>0</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC262">
         <v>0</v>
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-10-25 15:15:00</t>
+          <t>2026-10-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -43136,22 +43136,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>4.76</v>
+        <v>1.53</v>
       </c>
       <c r="O263">
-        <v>4</v>
+        <v>4.72</v>
       </c>
       <c r="P263">
-        <v>1.63</v>
+        <v>5.49</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.56</v>
+        <v>4.76</v>
       </c>
       <c r="O264">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P264">
-        <v>2.33</v>
+        <v>1.63</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>1.32</v>
+        <v>2.56</v>
       </c>
       <c r="O265">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="P265">
-        <v>8.800000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43549,10 +43549,10 @@
         <v>0</v>
       </c>
       <c r="AC265">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD265">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE265">
         <v>0</v>
@@ -43620,27 +43620,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -43712,10 +43712,10 @@
         <v>0</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE266">
         <v>0</v>
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-10-25 15:30:00</t>
+          <t>2026-10-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G267">
@@ -43951,22 +43951,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G268">
@@ -44109,27 +44109,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-10-25 16:00:00</t>
+          <t>2026-10-25 15:30:00</t>
         </is>
       </c>
     </row>
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G271">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O273">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P273">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45092,22 +45092,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="O275">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P275">
-        <v>2.88</v>
+        <v>4.89</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45250,27 +45250,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,14 +45297,14 @@
         </is>
       </c>
       <c r="N276">
+        <v>4.66</v>
+      </c>
+      <c r="O276">
+        <v>3.82</v>
+      </c>
+      <c r="P276">
         <v>1.58</v>
       </c>
-      <c r="O276">
-        <v>4.78</v>
-      </c>
-      <c r="P276">
-        <v>5.75</v>
-      </c>
       <c r="Q276">
         <v>0</v>
       </c>
@@ -45342,10 +45342,10 @@
         <v>0</v>
       </c>
       <c r="AC276">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD276">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE276">
         <v>0</v>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-10-25 16:45:00</t>
+          <t>2026-10-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -45413,12 +45413,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>4.68</v>
+        <v>2.28</v>
       </c>
       <c r="O277">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="P277">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45499,10 +45499,10 @@
         <v>0</v>
       </c>
       <c r="AA277">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB277">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC277">
         <v>0</v>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-10-25 16:45:00</t>
+          <t>2026-10-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -45576,27 +45576,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45668,10 +45668,10 @@
         <v>0</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE278">
         <v>0</v>
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-10-25 17:00:00</t>
+          <t>2026-10-25 16:45:00</t>
         </is>
       </c>
     </row>
@@ -45739,27 +45739,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45825,10 +45825,10 @@
         <v>0</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC279">
         <v>0</v>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-10-25 17:00:00</t>
+          <t>2026-10-25 16:45:00</t>
         </is>
       </c>
     </row>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G281">
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G282">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G284">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,22 +46885,22 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G286">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G288">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G290">
@@ -47695,27 +47695,27 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G291">
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47858,27 +47858,27 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G292">
@@ -48009,7 +48009,7 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>2026-10-25 17:30:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O293">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="P293">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-10-25 18:00:00</t>
+          <t>2026-10-25 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48347,27 +48347,27 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.08</v>
+        <v>1.18</v>
       </c>
       <c r="O295">
-        <v>3.45</v>
+        <v>8.35</v>
       </c>
       <c r="P295">
-        <v>2.94</v>
+        <v>16</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-10-25 18:00:00</t>
+          <t>2026-10-25 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48510,12 +48510,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-10-25 18:15:00</t>
+          <t>2026-10-25 18:00:00</t>
         </is>
       </c>
     </row>
@@ -48673,12 +48673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O297">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P297">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-10-25 18:30:00</t>
+          <t>2026-10-25 18:00:00</t>
         </is>
       </c>
     </row>
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-25 20:00:00</t>
+          <t>2026-10-25 18:15:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="O299">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P299">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-25 20:00:00</t>
+          <t>2026-10-25 18:30:00</t>
         </is>
       </c>
     </row>
@@ -49167,22 +49167,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G300">
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-10-25 20:30:00</t>
+          <t>2026-10-25 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49488,156 +49488,482 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="G302">
+        <v>0</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>0</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N302">
+        <v>0</v>
+      </c>
+      <c r="O302">
+        <v>0</v>
+      </c>
+      <c r="P302">
+        <v>0</v>
+      </c>
+      <c r="Q302">
+        <v>0</v>
+      </c>
+      <c r="R302">
+        <v>0</v>
+      </c>
+      <c r="S302">
+        <v>0</v>
+      </c>
+      <c r="T302">
+        <v>0</v>
+      </c>
+      <c r="U302">
+        <v>0</v>
+      </c>
+      <c r="V302">
+        <v>0</v>
+      </c>
+      <c r="W302">
+        <v>0</v>
+      </c>
+      <c r="X302">
+        <v>0</v>
+      </c>
+      <c r="Y302">
+        <v>0</v>
+      </c>
+      <c r="Z302">
+        <v>0</v>
+      </c>
+      <c r="AA302">
+        <v>0</v>
+      </c>
+      <c r="AB302">
+        <v>0</v>
+      </c>
+      <c r="AC302">
+        <v>0</v>
+      </c>
+      <c r="AD302">
+        <v>0</v>
+      </c>
+      <c r="AE302">
+        <v>0</v>
+      </c>
+      <c r="AF302">
+        <v>0</v>
+      </c>
+      <c r="AG302">
+        <v>0</v>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ302">
+        <v>0</v>
+      </c>
+      <c r="AK302">
+        <v>0</v>
+      </c>
+      <c r="AL302">
+        <v>0</v>
+      </c>
+      <c r="AM302">
+        <v>-1</v>
+      </c>
+      <c r="AN302">
+        <v>-1</v>
+      </c>
+      <c r="AO302">
+        <v>-1</v>
+      </c>
+      <c r="AP302">
+        <v>-1</v>
+      </c>
+      <c r="AQ302">
+        <v>0</v>
+      </c>
+      <c r="AR302">
+        <v>0</v>
+      </c>
+      <c r="AS302">
+        <v>0</v>
+      </c>
+      <c r="AT302">
+        <v>0</v>
+      </c>
+      <c r="AU302" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303">
+        <v>0</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>0</v>
+      </c>
+      <c r="L303">
+        <v>0</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N303">
+        <v>0</v>
+      </c>
+      <c r="O303">
+        <v>0</v>
+      </c>
+      <c r="P303">
+        <v>0</v>
+      </c>
+      <c r="Q303">
+        <v>0</v>
+      </c>
+      <c r="R303">
+        <v>0</v>
+      </c>
+      <c r="S303">
+        <v>0</v>
+      </c>
+      <c r="T303">
+        <v>0</v>
+      </c>
+      <c r="U303">
+        <v>0</v>
+      </c>
+      <c r="V303">
+        <v>0</v>
+      </c>
+      <c r="W303">
+        <v>0</v>
+      </c>
+      <c r="X303">
+        <v>0</v>
+      </c>
+      <c r="Y303">
+        <v>0</v>
+      </c>
+      <c r="Z303">
+        <v>0</v>
+      </c>
+      <c r="AA303">
+        <v>0</v>
+      </c>
+      <c r="AB303">
+        <v>0</v>
+      </c>
+      <c r="AC303">
+        <v>0</v>
+      </c>
+      <c r="AD303">
+        <v>0</v>
+      </c>
+      <c r="AE303">
+        <v>0</v>
+      </c>
+      <c r="AF303">
+        <v>0</v>
+      </c>
+      <c r="AG303">
+        <v>0</v>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ303">
+        <v>0</v>
+      </c>
+      <c r="AK303">
+        <v>0</v>
+      </c>
+      <c r="AL303">
+        <v>0</v>
+      </c>
+      <c r="AM303">
+        <v>-1</v>
+      </c>
+      <c r="AN303">
+        <v>-1</v>
+      </c>
+      <c r="AO303">
+        <v>-1</v>
+      </c>
+      <c r="AP303">
+        <v>-1</v>
+      </c>
+      <c r="AQ303">
+        <v>0</v>
+      </c>
+      <c r="AR303">
+        <v>0</v>
+      </c>
+      <c r="AS303">
+        <v>0</v>
+      </c>
+      <c r="AT303">
+        <v>0</v>
+      </c>
+      <c r="AU303" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C304" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
+      <c r="D304" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
+      <c r="E304" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
+      <c r="F304" t="inlineStr">
         <is>
           <t>LA Galaxy</t>
         </is>
       </c>
-      <c r="G302">
-        <v>0</v>
-      </c>
-      <c r="H302">
-        <v>0</v>
-      </c>
-      <c r="I302">
-        <v>0</v>
-      </c>
-      <c r="J302">
-        <v>0</v>
-      </c>
-      <c r="K302">
-        <v>0</v>
-      </c>
-      <c r="L302">
-        <v>0</v>
-      </c>
-      <c r="M302" t="inlineStr">
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>0</v>
+      </c>
+      <c r="L304">
+        <v>0</v>
+      </c>
+      <c r="M304" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N302">
+      <c r="N304">
         <v>1.54</v>
       </c>
-      <c r="O302">
+      <c r="O304">
         <v>4.9</v>
       </c>
-      <c r="P302">
+      <c r="P304">
         <v>5.58</v>
       </c>
-      <c r="Q302">
-        <v>0</v>
-      </c>
-      <c r="R302">
-        <v>0</v>
-      </c>
-      <c r="S302">
-        <v>0</v>
-      </c>
-      <c r="T302">
-        <v>0</v>
-      </c>
-      <c r="U302">
-        <v>0</v>
-      </c>
-      <c r="V302">
-        <v>0</v>
-      </c>
-      <c r="W302">
-        <v>0</v>
-      </c>
-      <c r="X302">
-        <v>0</v>
-      </c>
-      <c r="Y302">
-        <v>0</v>
-      </c>
-      <c r="Z302">
-        <v>0</v>
-      </c>
-      <c r="AA302">
-        <v>0</v>
-      </c>
-      <c r="AB302">
-        <v>0</v>
-      </c>
-      <c r="AC302">
+      <c r="Q304">
+        <v>0</v>
+      </c>
+      <c r="R304">
+        <v>0</v>
+      </c>
+      <c r="S304">
+        <v>0</v>
+      </c>
+      <c r="T304">
+        <v>0</v>
+      </c>
+      <c r="U304">
+        <v>0</v>
+      </c>
+      <c r="V304">
+        <v>0</v>
+      </c>
+      <c r="W304">
+        <v>0</v>
+      </c>
+      <c r="X304">
+        <v>0</v>
+      </c>
+      <c r="Y304">
+        <v>0</v>
+      </c>
+      <c r="Z304">
+        <v>0</v>
+      </c>
+      <c r="AA304">
+        <v>0</v>
+      </c>
+      <c r="AB304">
+        <v>0</v>
+      </c>
+      <c r="AC304">
         <v>1.95</v>
       </c>
-      <c r="AD302">
+      <c r="AD304">
         <v>1.73</v>
       </c>
-      <c r="AE302">
-        <v>0</v>
-      </c>
-      <c r="AF302">
-        <v>0</v>
-      </c>
-      <c r="AG302">
-        <v>0</v>
-      </c>
-      <c r="AH302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ302">
-        <v>0</v>
-      </c>
-      <c r="AK302">
-        <v>0</v>
-      </c>
-      <c r="AL302">
-        <v>0</v>
-      </c>
-      <c r="AM302">
-        <v>-1</v>
-      </c>
-      <c r="AN302">
-        <v>-1</v>
-      </c>
-      <c r="AO302">
-        <v>-1</v>
-      </c>
-      <c r="AP302">
-        <v>-1</v>
-      </c>
-      <c r="AQ302">
-        <v>0</v>
-      </c>
-      <c r="AR302">
-        <v>0</v>
-      </c>
-      <c r="AS302">
-        <v>0</v>
-      </c>
-      <c r="AT302">
-        <v>0</v>
-      </c>
-      <c r="AU302" t="inlineStr">
+      <c r="AE304">
+        <v>0</v>
+      </c>
+      <c r="AF304">
+        <v>0</v>
+      </c>
+      <c r="AG304">
+        <v>0</v>
+      </c>
+      <c r="AH304" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI304" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ304">
+        <v>0</v>
+      </c>
+      <c r="AK304">
+        <v>0</v>
+      </c>
+      <c r="AL304">
+        <v>0</v>
+      </c>
+      <c r="AM304">
+        <v>-1</v>
+      </c>
+      <c r="AN304">
+        <v>-1</v>
+      </c>
+      <c r="AO304">
+        <v>-1</v>
+      </c>
+      <c r="AP304">
+        <v>-1</v>
+      </c>
+      <c r="AQ304">
+        <v>0</v>
+      </c>
+      <c r="AR304">
+        <v>0</v>
+      </c>
+      <c r="AS304">
+        <v>0</v>
+      </c>
+      <c r="AT304">
+        <v>0</v>
+      </c>
+      <c r="AU304" t="inlineStr">
         <is>
           <t>2026-10-25 22:00:00</t>
         </is>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>5.1</v>
+        <v>1.72</v>
       </c>
       <c r="O9">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P9">
+        <v>3.91</v>
+      </c>
+      <c r="Q9">
+        <v>2.29</v>
+      </c>
+      <c r="R9">
+        <v>2.29</v>
+      </c>
+      <c r="S9">
+        <v>1.24</v>
+      </c>
+      <c r="T9">
+        <v>3.38</v>
+      </c>
+      <c r="U9">
+        <v>2.38</v>
+      </c>
+      <c r="V9">
         <v>1.53</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AB9">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.72</v>
+        <v>5.1</v>
       </c>
       <c r="O10">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>3.91</v>
+        <v>1.53</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,34 +2111,34 @@
         <v>3.77</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
         <v>1.81</v>
@@ -2147,19 +2147,19 @@
         <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>3.94</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA18">
         <v>1.79</v>
@@ -3288,19 +3288,19 @@
         <v>1.98</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>1.99</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,34 +3578,34 @@
         <v>2.82</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA20">
         <v>1.93</v>
@@ -3614,19 +3614,19 @@
         <v>1.83</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G70">
@@ -13195,55 +13195,55 @@
         <v>1.03</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="O126">
-        <v>4.01</v>
+        <v>4.36</v>
       </c>
       <c r="P126">
-        <v>3.43</v>
+        <v>4.42</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB126">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.79</v>
+        <v>5.07</v>
       </c>
       <c r="O127">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="P127">
-        <v>4.42</v>
+        <v>1.71</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>5.07</v>
+        <v>2.11</v>
       </c>
       <c r="O128">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="P128">
-        <v>1.71</v>
+        <v>3.43</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G155">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="G167">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G172">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q240">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>3.44</v>
+      </c>
+      <c r="O18">
+        <v>3.2</v>
+      </c>
+      <c r="P18">
+        <v>1.99</v>
+      </c>
+      <c r="Q18">
+        <v>4.33</v>
+      </c>
+      <c r="R18">
+        <v>2.1</v>
+      </c>
+      <c r="S18">
+        <v>1.36</v>
+      </c>
+      <c r="T18">
+        <v>2.88</v>
+      </c>
+      <c r="U18">
+        <v>2.88</v>
+      </c>
+      <c r="V18">
+        <v>1.36</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.26</v>
+      </c>
+      <c r="Z18">
+        <v>3.2</v>
+      </c>
+      <c r="AA18">
+        <v>1.98</v>
+      </c>
+      <c r="AB18">
         <v>1.76</v>
       </c>
-      <c r="O18">
-        <v>3.52</v>
-      </c>
-      <c r="P18">
-        <v>3.94</v>
-      </c>
-      <c r="Q18">
-        <v>2.3</v>
-      </c>
-      <c r="R18">
-        <v>2.25</v>
-      </c>
-      <c r="S18">
-        <v>1.3</v>
-      </c>
-      <c r="T18">
-        <v>3.2</v>
-      </c>
-      <c r="U18">
-        <v>2.75</v>
-      </c>
-      <c r="V18">
-        <v>1.4</v>
-      </c>
-      <c r="W18">
-        <v>1.1</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.27</v>
-      </c>
-      <c r="Z18">
-        <v>3.64</v>
-      </c>
-      <c r="AA18">
+      <c r="AC18">
+        <v>3.34</v>
+      </c>
+      <c r="AD18">
+        <v>1.24</v>
+      </c>
+      <c r="AE18">
+        <v>1.05</v>
+      </c>
+      <c r="AF18">
         <v>1.79</v>
       </c>
-      <c r="AB18">
-        <v>1.98</v>
-      </c>
-      <c r="AC18">
-        <v>3.07</v>
-      </c>
-      <c r="AD18">
-        <v>1.35</v>
-      </c>
-      <c r="AE18">
-        <v>1.13</v>
-      </c>
-      <c r="AF18">
-        <v>1.7</v>
-      </c>
       <c r="AG18">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.44</v>
+        <v>2.29</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P19">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="Q19">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
         <v>2.1</v>
@@ -3433,37 +3433,37 @@
         <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA19">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB19">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AC19">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.29</v>
+        <v>1.76</v>
       </c>
       <c r="O20">
-        <v>3.18</v>
+        <v>3.52</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>3.94</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AD20">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>1.92</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>3.4</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>2.85</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>3.64</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>2.34</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>2.27</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>2.44</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11402,40 +11402,40 @@
         <v>7.9</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC68">
         <v>2.05</v>
@@ -11444,13 +11444,13 @@
         <v>1.7</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>1.67</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13847,55 +13847,55 @@
         <v>1.47</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,55 +14173,55 @@
         <v>2.68</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,55 +14499,55 @@
         <v>2.08</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="O88">
         <v>3.8</v>
       </c>
       <c r="P88">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="O89">
         <v>3.8</v>
       </c>
       <c r="P89">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15314,34 +15314,34 @@
         <v>4.45</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA92">
         <v>1.61</v>
@@ -15350,19 +15350,19 @@
         <v>2.15</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,40 +15803,40 @@
         <v>1.64</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC95">
         <v>1.93</v>
@@ -15845,13 +15845,13 @@
         <v>1.87</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,55 +15966,55 @@
         <v>3.69</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16292,55 +16292,55 @@
         <v>3.78</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16618,55 +16618,55 @@
         <v>3.35</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,55 +16781,55 @@
         <v>2.72</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>7</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>1.69</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>1.96</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18900,55 +18900,55 @@
         <v>4.4</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19063,55 +19063,55 @@
         <v>5.18</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,55 +19389,55 @@
         <v>4.23</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,55 +19552,55 @@
         <v>3.23</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19715,55 +19715,55 @@
         <v>2.97</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>11</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>2.7</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20367,55 +20367,55 @@
         <v>3.79</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20530,34 +20530,34 @@
         <v>6.27</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA124">
         <v>1.53</v>
@@ -20566,19 +20566,19 @@
         <v>2.3</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20693,55 +20693,55 @@
         <v>2.65</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>4.42</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>5.07</v>
+        <v>2.11</v>
       </c>
       <c r="O127">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="P127">
-        <v>1.71</v>
+        <v>3.43</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.11</v>
+        <v>5.07</v>
       </c>
       <c r="O128">
-        <v>4.01</v>
+        <v>4.26</v>
       </c>
       <c r="P128">
-        <v>3.43</v>
+        <v>1.71</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA128">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB128">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21508,34 +21508,34 @@
         <v>3.39</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AA130">
         <v>1.65</v>
@@ -21544,19 +21544,19 @@
         <v>2.1</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21671,55 +21671,55 @@
         <v>2.79</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21997,55 +21997,55 @@
         <v>2.73</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22160,55 +22160,55 @@
         <v>19</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22649,55 +22649,55 @@
         <v>2.15</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23301,55 +23301,55 @@
         <v>3.95</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T141">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U141">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V141">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W141">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y141">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z141">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD141">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE141">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF141">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG141">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK141">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23627,55 +23627,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="O144">
-        <v>3.55</v>
+        <v>4.53</v>
       </c>
       <c r="P144">
-        <v>3.75</v>
+        <v>5.04</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA144">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB144">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="O145">
-        <v>4.53</v>
+        <v>3.55</v>
       </c>
       <c r="P145">
-        <v>5.04</v>
+        <v>3.75</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U145">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V145">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC145">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AD145">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF145">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24116,55 +24116,55 @@
         <v>3.29</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V146">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z146">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF146">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG146">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK146">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24442,40 +24442,40 @@
         <v>2.16</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S148">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U148">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V148">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W148">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X148">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z148">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC148">
         <v>1.82</v>
@@ -24484,13 +24484,13 @@
         <v>1.88</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF148">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK148">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X162">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -29332,55 +29332,55 @@
         <v>2.2</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T178">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U178">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V178">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W178">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X178">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG178">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK178">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29495,55 +29495,55 @@
         <v>2.9</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G184">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G185">
@@ -30799,40 +30799,40 @@
         <v>6.9</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC187">
         <v>1.92</v>
@@ -30841,13 +30841,13 @@
         <v>1.88</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32266,55 +32266,55 @@
         <v>1.41</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -34059,55 +34059,55 @@
         <v>2.84</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T207">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y207">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z207">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA207">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34222,55 +34222,55 @@
         <v>2.93</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T208">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U208">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V208">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W208">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X208">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA208">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB208">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC208">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD208">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE208">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF208">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG208">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK208">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34385,40 +34385,40 @@
         <v>3.69</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V209">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W209">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X209">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC209">
         <v>1.98</v>
@@ -34427,13 +34427,13 @@
         <v>1.83</v>
       </c>
       <c r="AE209">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK209">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34548,55 +34548,55 @@
         <v>3.4</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T210">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V210">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W210">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y210">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z210">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG210">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK210">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Q212">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R212">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S212">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T212">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U212">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V212">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W212">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X212">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z212">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC212">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD212">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE212">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF212">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG212">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK212">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>3.83</v>
+        <v>1.68</v>
       </c>
       <c r="O220">
+        <v>4.29</v>
+      </c>
+      <c r="P220">
+        <v>3.95</v>
+      </c>
+      <c r="Q220">
+        <v>2.02</v>
+      </c>
+      <c r="R220">
+        <v>2.51</v>
+      </c>
+      <c r="S220">
+        <v>1.17</v>
+      </c>
+      <c r="T220">
         <v>4.5</v>
       </c>
-      <c r="P220">
-        <v>1.68</v>
-      </c>
-      <c r="Q220">
-        <v>0</v>
-      </c>
-      <c r="R220">
-        <v>0</v>
-      </c>
-      <c r="S220">
-        <v>0</v>
-      </c>
-      <c r="T220">
-        <v>0</v>
-      </c>
       <c r="U220">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V220">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W220">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X220">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z220">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC220">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD220">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG220">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK220">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="O221">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="P221">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T221">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="U221">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V221">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W221">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X221">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y221">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z221">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA221">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB221">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC221">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD221">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG221">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK221">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="O222">
-        <v>4.21</v>
+        <v>3.83</v>
       </c>
       <c r="P222">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S222">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T222">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U222">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V222">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W222">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X222">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y222">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z222">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA222">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB222">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC222">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD222">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE222">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF222">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG222">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK222">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.86</v>
+        <v>3.83</v>
       </c>
       <c r="O223">
-        <v>3.83</v>
+        <v>4.5</v>
       </c>
       <c r="P223">
-        <v>3.61</v>
+        <v>1.68</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q286">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>1.83</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>3.77</v>
       </c>
       <c r="Q10">
-        <v>4.8</v>
+        <v>2.42</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="Z10">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="AA10">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB10">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>2.93</v>
+        <v>3.46</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.13</v>
+        <v>1.77</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>5.1</v>
+      </c>
+      <c r="O11">
+        <v>3.9</v>
+      </c>
+      <c r="P11">
+        <v>1.53</v>
+      </c>
+      <c r="Q11">
+        <v>4.8</v>
+      </c>
+      <c r="R11">
+        <v>2.3</v>
+      </c>
+      <c r="S11">
+        <v>1.31</v>
+      </c>
+      <c r="T11">
+        <v>3.2</v>
+      </c>
+      <c r="U11">
+        <v>2.63</v>
+      </c>
+      <c r="V11">
+        <v>1.44</v>
+      </c>
+      <c r="W11">
+        <v>1.1</v>
+      </c>
+      <c r="X11">
+        <v>1.04</v>
+      </c>
+      <c r="Y11">
+        <v>1.21</v>
+      </c>
+      <c r="Z11">
+        <v>3.58</v>
+      </c>
+      <c r="AA11">
         <v>1.83</v>
       </c>
-      <c r="O11">
-        <v>3.4</v>
-      </c>
-      <c r="P11">
-        <v>3.77</v>
-      </c>
-      <c r="Q11">
-        <v>2.42</v>
-      </c>
-      <c r="R11">
-        <v>2.1</v>
-      </c>
-      <c r="S11">
-        <v>1.36</v>
-      </c>
-      <c r="T11">
-        <v>2.88</v>
-      </c>
-      <c r="U11">
-        <v>2.76</v>
-      </c>
-      <c r="V11">
-        <v>1.35</v>
-      </c>
-      <c r="W11">
+      <c r="AB11">
+        <v>1.93</v>
+      </c>
+      <c r="AC11">
+        <v>2.93</v>
+      </c>
+      <c r="AD11">
+        <v>1.38</v>
+      </c>
+      <c r="AE11">
         <v>1.07</v>
       </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1.32</v>
-      </c>
-      <c r="Z11">
-        <v>3.25</v>
-      </c>
-      <c r="AA11">
-        <v>1.81</v>
-      </c>
-      <c r="AB11">
-        <v>1.95</v>
-      </c>
-      <c r="AC11">
-        <v>3.46</v>
-      </c>
-      <c r="AD11">
-        <v>1.29</v>
-      </c>
-      <c r="AE11">
-        <v>1.06</v>
-      </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G32">
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.52</v>
+        <v>4.68</v>
       </c>
       <c r="R32">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AA32">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G33">
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>4.68</v>
+        <v>3.52</v>
       </c>
       <c r="R33">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB33">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.09</v>
+        <v>2.19</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="Q87">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="R87">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U87">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V87">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z87">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA87">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AB87">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AC87">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AD87">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AE87">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AF87">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG87">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.19</v>
+        <v>3.09</v>
       </c>
       <c r="O89">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P89">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q89">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="R89">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S89">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V89">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="W89">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA89">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AB89">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AC89">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AD89">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AE89">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AF89">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG89">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK89">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
+        <v>2.15</v>
+      </c>
+      <c r="O120">
+        <v>3.6</v>
+      </c>
+      <c r="P120">
+        <v>2.7</v>
+      </c>
+      <c r="Q120">
+        <v>2.7</v>
+      </c>
+      <c r="R120">
+        <v>2.5</v>
+      </c>
+      <c r="S120">
+        <v>1.22</v>
+      </c>
+      <c r="T120">
+        <v>3.75</v>
+      </c>
+      <c r="U120">
+        <v>2.1</v>
+      </c>
+      <c r="V120">
+        <v>1.62</v>
+      </c>
+      <c r="W120">
+        <v>1.18</v>
+      </c>
+      <c r="X120">
+        <v>1.02</v>
+      </c>
+      <c r="Y120">
         <v>1.13</v>
       </c>
-      <c r="O120">
-        <v>7.5</v>
-      </c>
-      <c r="P120">
-        <v>11</v>
-      </c>
-      <c r="Q120">
-        <v>1.48</v>
-      </c>
-      <c r="R120">
-        <v>3.48</v>
-      </c>
-      <c r="S120">
-        <v>1.13</v>
-      </c>
-      <c r="T120">
-        <v>5</v>
-      </c>
-      <c r="U120">
-        <v>1.7</v>
-      </c>
-      <c r="V120">
-        <v>2.1</v>
-      </c>
-      <c r="W120">
-        <v>1.3</v>
-      </c>
-      <c r="X120">
-        <v>1</v>
-      </c>
-      <c r="Y120">
-        <v>1.02</v>
-      </c>
       <c r="Z120">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AA120">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AB120">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC120">
+        <v>2.12</v>
+      </c>
+      <c r="AD120">
+        <v>1.62</v>
+      </c>
+      <c r="AE120">
+        <v>1.22</v>
+      </c>
+      <c r="AF120">
+        <v>1.4</v>
+      </c>
+      <c r="AG120">
+        <v>2.7</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>1.22</v>
+      </c>
+      <c r="AK120">
         <v>1.57</v>
-      </c>
-      <c r="AD120">
-        <v>2.26</v>
-      </c>
-      <c r="AE120">
-        <v>1.57</v>
-      </c>
-      <c r="AF120">
-        <v>1.5</v>
-      </c>
-      <c r="AG120">
-        <v>2.45</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.06</v>
-      </c>
-      <c r="AK120">
-        <v>4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.15</v>
+        <v>1.13</v>
       </c>
       <c r="O121">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="P121">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="Q121">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="R121">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="S121">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T121">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U121">
+        <v>1.7</v>
+      </c>
+      <c r="V121">
         <v>2.1</v>
       </c>
-      <c r="V121">
-        <v>1.62</v>
-      </c>
       <c r="W121">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X121">
+        <v>1</v>
+      </c>
+      <c r="Y121">
         <v>1.02</v>
       </c>
-      <c r="Y121">
-        <v>1.13</v>
-      </c>
       <c r="Z121">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AA121">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AB121">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="AC121">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="AD121">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AE121">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AF121">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG121">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK121">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,31 +20684,31 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.65</v>
+        <v>2.11</v>
       </c>
       <c r="O125">
-        <v>3.84</v>
+        <v>4.01</v>
       </c>
       <c r="P125">
-        <v>2.65</v>
+        <v>3.43</v>
       </c>
       <c r="Q125">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="R125">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="S125">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T125">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U125">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="V125">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W125">
         <v>1.11</v>
@@ -20717,31 +20717,31 @@
         <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z125">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AA125">
+        <v>1.55</v>
+      </c>
+      <c r="AB125">
+        <v>2.3</v>
+      </c>
+      <c r="AC125">
+        <v>2.5</v>
+      </c>
+      <c r="AD125">
         <v>1.57</v>
       </c>
-      <c r="AB125">
-        <v>2.25</v>
-      </c>
-      <c r="AC125">
-        <v>2.43</v>
-      </c>
-      <c r="AD125">
-        <v>1.48</v>
-      </c>
       <c r="AE125">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF125">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG125">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK125">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.79</v>
+        <v>5.07</v>
       </c>
       <c r="O126">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="P126">
-        <v>4.42</v>
+        <v>1.71</v>
       </c>
       <c r="Q126">
-        <v>2.19</v>
+        <v>4.33</v>
       </c>
       <c r="R126">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S126">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="T126">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="U126">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="V126">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W126">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X126">
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z126">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA126">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB126">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC126">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AD126">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AE126">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF126">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG126">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AK126">
-        <v>1.99</v>
+        <v>1.17</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="O127">
-        <v>4.01</v>
+        <v>4.36</v>
       </c>
       <c r="P127">
-        <v>3.43</v>
+        <v>4.42</v>
       </c>
       <c r="Q127">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="R127">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="S127">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T127">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U127">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="V127">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="W127">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z127">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA127">
+        <v>1.5</v>
+      </c>
+      <c r="AB127">
+        <v>2.4</v>
+      </c>
+      <c r="AC127">
+        <v>2.41</v>
+      </c>
+      <c r="AD127">
         <v>1.55</v>
       </c>
-      <c r="AB127">
-        <v>2.3</v>
-      </c>
-      <c r="AC127">
-        <v>2.5</v>
-      </c>
-      <c r="AD127">
-        <v>1.57</v>
-      </c>
       <c r="AE127">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF127">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG127">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK127">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>5.07</v>
+        <v>2.65</v>
       </c>
       <c r="O128">
-        <v>4.26</v>
+        <v>3.84</v>
       </c>
       <c r="P128">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="Q128">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R128">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S128">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T128">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U128">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V128">
         <v>1.5</v>
       </c>
       <c r="W128">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z128">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AA128">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB128">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC128">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AD128">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE128">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF128">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG128">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="O144">
-        <v>4.53</v>
+        <v>3.55</v>
       </c>
       <c r="P144">
-        <v>5.04</v>
+        <v>3.75</v>
       </c>
       <c r="Q144">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="R144">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S144">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="T144">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="U144">
-        <v>2.19</v>
+        <v>2.95</v>
       </c>
       <c r="V144">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W144">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X144">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y144">
+        <v>1.25</v>
+      </c>
+      <c r="Z144">
+        <v>3.44</v>
+      </c>
+      <c r="AA144">
+        <v>1.85</v>
+      </c>
+      <c r="AB144">
+        <v>1.85</v>
+      </c>
+      <c r="AC144">
+        <v>3</v>
+      </c>
+      <c r="AD144">
+        <v>1.32</v>
+      </c>
+      <c r="AE144">
         <v>1.07</v>
       </c>
-      <c r="Z144">
-        <v>5.8</v>
-      </c>
-      <c r="AA144">
-        <v>1.4</v>
-      </c>
-      <c r="AB144">
-        <v>2.88</v>
-      </c>
-      <c r="AC144">
-        <v>2.1</v>
-      </c>
-      <c r="AD144">
-        <v>1.66</v>
-      </c>
-      <c r="AE144">
-        <v>1.3</v>
-      </c>
       <c r="AF144">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG144">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="O145">
-        <v>3.55</v>
+        <v>4.53</v>
       </c>
       <c r="P145">
-        <v>3.75</v>
+        <v>5.04</v>
       </c>
       <c r="Q145">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="R145">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S145">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="T145">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="U145">
-        <v>2.95</v>
+        <v>2.19</v>
       </c>
       <c r="V145">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="W145">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Z145">
-        <v>3.44</v>
+        <v>5.8</v>
       </c>
       <c r="AA145">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB145">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="AC145">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AD145">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="AE145">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AF145">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG145">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,22 +28303,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G174">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,22 +29118,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="O178">
+        <v>3.5</v>
+      </c>
+      <c r="P178">
+        <v>2.9</v>
+      </c>
+      <c r="Q178">
+        <v>2.92</v>
+      </c>
+      <c r="R178">
+        <v>2.25</v>
+      </c>
+      <c r="S178">
+        <v>1.32</v>
+      </c>
+      <c r="T178">
         <v>3.3</v>
       </c>
-      <c r="P178">
-        <v>2.2</v>
-      </c>
-      <c r="Q178">
-        <v>3.01</v>
-      </c>
-      <c r="R178">
-        <v>2.22</v>
-      </c>
-      <c r="S178">
-        <v>1.25</v>
-      </c>
-      <c r="T178">
-        <v>3.5</v>
-      </c>
       <c r="U178">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="V178">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W178">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X178">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y178">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z178">
-        <v>4.51</v>
+        <v>3.92</v>
       </c>
       <c r="AA178">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB178">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC178">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD178">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE178">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF178">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG178">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK178">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O179">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P179">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q179">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R179">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S179">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T179">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U179">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V179">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W179">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X179">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y179">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z179">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA179">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB179">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC179">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD179">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE179">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF179">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG179">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK179">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>7.18</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>7.18</v>
+        <v>1.34</v>
       </c>
       <c r="O186">
-        <v>4.33</v>
+        <v>5.51</v>
       </c>
       <c r="P186">
-        <v>1.41</v>
+        <v>6.9</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.34</v>
+        <v>2.19</v>
       </c>
       <c r="O187">
-        <v>5.51</v>
+        <v>3.7</v>
       </c>
       <c r="P187">
-        <v>6.9</v>
+        <v>3.18</v>
       </c>
       <c r="Q187">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="R187">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S187">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T187">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U187">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V187">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W187">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y187">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z187">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA187">
-        <v>1.31</v>
+        <v>1.93</v>
       </c>
       <c r="AB187">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC187">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD187">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE187">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF187">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG187">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK187">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-10-25 12:00:00</t>
+          <t>2026-10-25 12:15:00</t>
         </is>
       </c>
     </row>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="O188">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P188">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O189">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P189">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB189">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31232,27 +31232,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U190">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V190">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X190">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y190">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z190">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG190">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK190">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-10-25 12:15:00</t>
+          <t>2026-10-25 12:30:00</t>
         </is>
       </c>
     </row>
@@ -31400,22 +31400,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="O191">
-        <v>3.1</v>
+        <v>4.45</v>
       </c>
       <c r="P191">
-        <v>2.37</v>
+        <v>4.4</v>
       </c>
       <c r="Q191">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S191">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T191">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U191">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V191">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W191">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y191">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z191">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA191">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB191">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC191">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD191">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="AE191">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF191">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG191">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK191">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="O192">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="P192">
-        <v>4.4</v>
+        <v>7.48</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31650,10 +31650,10 @@
         <v>0</v>
       </c>
       <c r="AC192">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD192">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE192">
         <v>0</v>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.36</v>
+        <v>3.38</v>
       </c>
       <c r="O193">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="P193">
-        <v>7.48</v>
+        <v>2.05</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O194">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P194">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB194">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32215,22 +32215,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>6.33</v>
+        <v>1.41</v>
       </c>
       <c r="O196">
-        <v>4.76</v>
+        <v>4.92</v>
       </c>
       <c r="P196">
-        <v>1.41</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q196">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R196">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S196">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T196">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U196">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V196">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W196">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y196">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z196">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA196">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB196">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC196">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD196">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE196">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF196">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG196">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK196">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O197">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="P197">
-        <v>9.949999999999999</v>
+        <v>5.57</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.42</v>
+        <v>1.98</v>
       </c>
       <c r="O198">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="P198">
-        <v>5.57</v>
+        <v>3.94</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32622,10 +32622,10 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC198">
         <v>0</v>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O199">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P199">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32785,10 +32785,10 @@
         <v>0</v>
       </c>
       <c r="AA199">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB199">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC199">
         <v>0</v>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-10-25 12:30:00</t>
+          <t>2026-10-25 12:45:00</t>
         </is>
       </c>
     </row>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33280,10 +33280,10 @@
         <v>0</v>
       </c>
       <c r="AC202">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD202">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE202">
         <v>0</v>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>6.84</v>
+        <v>1.87</v>
       </c>
       <c r="O203">
-        <v>5.33</v>
+        <v>3.6</v>
       </c>
       <c r="P203">
-        <v>1.41</v>
+        <v>3.42</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33443,10 +33443,10 @@
         <v>0</v>
       </c>
       <c r="AC203">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD203">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE203">
         <v>0</v>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-10-25 12:45:00</t>
+          <t>2026-10-25 13:00:00</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O204">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P204">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33682,7 +33682,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R206">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U206">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V206">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W206">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X206">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z206">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA206">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB206">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC206">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD206">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE206">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF206">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG206">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK206">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="O207">
-        <v>3.76</v>
+        <v>3.63</v>
       </c>
       <c r="P207">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="Q207">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="R207">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S207">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="T207">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U207">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="V207">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="W207">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X207">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y207">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z207">
-        <v>5.65</v>
+        <v>4.25</v>
       </c>
       <c r="AA207">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AB207">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="AC207">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AD207">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AE207">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AF207">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG207">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK207">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34497,22 +34497,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.04</v>
+        <v>6.17</v>
       </c>
       <c r="O210">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="P210">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="Q210">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R210">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S210">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T210">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U210">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V210">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W210">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X210">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y210">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z210">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA210">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB210">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC210">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD210">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE210">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF210">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG210">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK210">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34660,22 +34660,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>6.17</v>
+        <v>15</v>
       </c>
       <c r="O211">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="P211">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U211">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V211">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W211">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z211">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG211">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34823,22 +34823,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O212">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P212">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Q212">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R212">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S212">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T212">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U212">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V212">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W212">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X212">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y212">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z212">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA212">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB212">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC212">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD212">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE212">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF212">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG212">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK212">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O215">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P215">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,22 +35964,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V219">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z219">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK219">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="O220">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="P220">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q220">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="R220">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="S220">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="T220">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="U220">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="V220">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="W220">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X220">
         <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z220">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="AA220">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB220">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AC220">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD220">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AE220">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF220">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG220">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK220">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.79</v>
+        <v>3.83</v>
       </c>
       <c r="O221">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="P221">
-        <v>3.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q221">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="R221">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="S221">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T221">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="U221">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V221">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="W221">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X221">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y221">
         <v>1.03</v>
       </c>
       <c r="Z221">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="AA221">
+        <v>1.17</v>
+      </c>
+      <c r="AB221">
+        <v>3.96</v>
+      </c>
+      <c r="AC221">
+        <v>1.52</v>
+      </c>
+      <c r="AD221">
+        <v>2.24</v>
+      </c>
+      <c r="AE221">
+        <v>1.59</v>
+      </c>
+      <c r="AF221">
         <v>1.25</v>
       </c>
-      <c r="AB221">
-        <v>3.28</v>
-      </c>
-      <c r="AC221">
-        <v>1.73</v>
-      </c>
-      <c r="AD221">
-        <v>2.02</v>
-      </c>
-      <c r="AE221">
-        <v>1.41</v>
-      </c>
-      <c r="AF221">
-        <v>1.3</v>
-      </c>
       <c r="AG221">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.17</v>
+        <v>2.1</v>
       </c>
       <c r="AK221">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36616,22 +36616,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>3.83</v>
+        <v>1.37</v>
       </c>
       <c r="O223">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P223">
-        <v>1.68</v>
+        <v>7.55</v>
       </c>
       <c r="Q223">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R223">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S223">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T223">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U223">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V223">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W223">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y223">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z223">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA223">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB223">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AC223">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD223">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AE223">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF223">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG223">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK223">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36774,12 +36774,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.37</v>
+        <v>2.32</v>
       </c>
       <c r="O224">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="P224">
-        <v>7.55</v>
+        <v>2.93</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36860,10 +36860,10 @@
         <v>0</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC224">
         <v>0</v>
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-10-25 13:00:00</t>
+          <t>2026-10-25 13:15:00</t>
         </is>
       </c>
     </row>
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="O225">
-        <v>3.1</v>
+        <v>4.36</v>
       </c>
       <c r="P225">
-        <v>2.93</v>
+        <v>4.36</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37023,16 +37023,16 @@
         <v>0</v>
       </c>
       <c r="AA225">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB225">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="O226">
-        <v>4.36</v>
+        <v>3.62</v>
       </c>
       <c r="P226">
-        <v>4.36</v>
+        <v>3.23</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37186,16 +37186,16 @@
         <v>0</v>
       </c>
       <c r="AA226">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB226">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC226">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD226">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="O227">
-        <v>3.62</v>
+        <v>4.42</v>
       </c>
       <c r="P227">
-        <v>3.23</v>
+        <v>6.06</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB227">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="O228">
-        <v>4.42</v>
+        <v>3.41</v>
       </c>
       <c r="P228">
-        <v>6.06</v>
+        <v>2.86</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37512,10 +37512,10 @@
         <v>0</v>
       </c>
       <c r="AA228">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AB228">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC228">
         <v>0</v>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="O229">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="P229">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37675,10 +37675,10 @@
         <v>0</v>
       </c>
       <c r="AA229">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB229">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC229">
         <v>0</v>
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-10-25 13:15:00</t>
+          <t>2026-10-25 13:30:00</t>
         </is>
       </c>
     </row>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O230">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="P230">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37838,10 +37838,10 @@
         <v>0</v>
       </c>
       <c r="AA230">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB230">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC230">
         <v>0</v>
@@ -37920,22 +37920,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G231">
@@ -37958,7 +37958,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N231">
@@ -38083,22 +38083,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G232">
@@ -38121,7 +38121,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38409,22 +38409,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O234">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P234">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38572,22 +38572,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>1.65</v>
+        <v>2.98</v>
       </c>
       <c r="O237">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="P237">
-        <v>4.62</v>
+        <v>2.21</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="O238">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P238">
-        <v>2.21</v>
+        <v>3.06</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="O239">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P239">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O240">
-        <v>3.18</v>
+        <v>6.65</v>
       </c>
       <c r="P240">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39474,10 +39474,10 @@
         <v>0</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE240">
         <v>0</v>
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O241">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="P241">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39637,10 +39637,10 @@
         <v>0</v>
       </c>
       <c r="AC241">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD241">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE241">
         <v>0</v>
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-10-25 13:30:00</t>
+          <t>2026-10-25 14:00:00</t>
         </is>
       </c>
     </row>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -39963,10 +39963,10 @@
         <v>0</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE243">
         <v>0</v>
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O244">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P244">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40126,10 +40126,10 @@
         <v>0</v>
       </c>
       <c r="AC244">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD244">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE244">
         <v>0</v>
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="O246">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P246">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O247">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P247">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="O248">
-        <v>3.28</v>
+        <v>4.53</v>
       </c>
       <c r="P248">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40772,10 +40772,10 @@
         <v>0</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC248">
         <v>0</v>
@@ -40849,12 +40849,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>7.7</v>
+        <v>1.51</v>
       </c>
       <c r="O249">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="P249">
-        <v>1.5</v>
+        <v>6.24</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB249">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-10-25 14:00:00</t>
+          <t>2026-10-25 14:30:00</t>
         </is>
       </c>
     </row>
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O250">
-        <v>4.59</v>
+        <v>3.48</v>
       </c>
       <c r="P250">
-        <v>6.24</v>
+        <v>4.24</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O251">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P251">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB252">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O253">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P253">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB253">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-10-25 14:30:00</t>
+          <t>2026-10-25 14:45:00</t>
         </is>
       </c>
     </row>
@@ -41664,27 +41664,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-10-25 14:45:00</t>
+          <t>2026-10-25 15:00:00</t>
         </is>
       </c>
     </row>
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42728,10 +42728,10 @@
         <v>0</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>6.67</v>
+        <v>4.28</v>
       </c>
       <c r="O261">
-        <v>4.38</v>
+        <v>3.65</v>
       </c>
       <c r="P261">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42891,10 +42891,10 @@
         <v>0</v>
       </c>
       <c r="AA261">
+        <v>1.92</v>
+      </c>
+      <c r="AB261">
         <v>1.88</v>
-      </c>
-      <c r="AB261">
-        <v>1.98</v>
       </c>
       <c r="AC261">
         <v>0</v>
@@ -42968,27 +42968,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>4.28</v>
+        <v>1.53</v>
       </c>
       <c r="O262">
-        <v>3.65</v>
+        <v>4.72</v>
       </c>
       <c r="P262">
-        <v>1.91</v>
+        <v>5.49</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43054,10 +43054,10 @@
         <v>0</v>
       </c>
       <c r="AA262">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB262">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC262">
         <v>0</v>
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-10-25 15:00:00</t>
+          <t>2026-10-25 15:15:00</t>
         </is>
       </c>
     </row>
@@ -43136,22 +43136,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>1.53</v>
+        <v>4.76</v>
       </c>
       <c r="O263">
-        <v>4.72</v>
+        <v>4</v>
       </c>
       <c r="P263">
-        <v>5.49</v>
+        <v>1.63</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>4.76</v>
+        <v>2.56</v>
       </c>
       <c r="O264">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P264">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.56</v>
+        <v>1.32</v>
       </c>
       <c r="O265">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="P265">
-        <v>2.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43549,10 +43549,10 @@
         <v>0</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE265">
         <v>0</v>
@@ -43620,27 +43620,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O266">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="P266">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -43712,10 +43712,10 @@
         <v>0</v>
       </c>
       <c r="AC266">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD266">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE266">
         <v>0</v>
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-10-25 15:15:00</t>
+          <t>2026-10-25 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G267">
@@ -43951,22 +43951,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G268">
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-10-25 15:30:00</t>
+          <t>2026-10-25 16:00:00</t>
         </is>
       </c>
     </row>
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G271">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.68</v>
+        <v>4.66</v>
       </c>
       <c r="O275">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="P275">
-        <v>4.89</v>
+        <v>1.58</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45255,22 +45255,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>4.66</v>
+        <v>2.28</v>
       </c>
       <c r="O276">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="P276">
-        <v>1.58</v>
+        <v>2.88</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45413,12 +45413,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="O277">
-        <v>3.9</v>
+        <v>4.78</v>
       </c>
       <c r="P277">
-        <v>2.88</v>
+        <v>5.75</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45505,10 +45505,10 @@
         <v>0</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE277">
         <v>0</v>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-10-25 16:00:00</t>
+          <t>2026-10-25 16:45:00</t>
         </is>
       </c>
     </row>
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.58</v>
+        <v>4.68</v>
       </c>
       <c r="O278">
-        <v>4.78</v>
+        <v>3.91</v>
       </c>
       <c r="P278">
-        <v>5.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45662,16 +45662,16 @@
         <v>0</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC278">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD278">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE278">
         <v>0</v>
@@ -45739,27 +45739,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O279">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P279">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45825,10 +45825,10 @@
         <v>0</v>
       </c>
       <c r="AA279">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB279">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC279">
         <v>0</v>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-10-25 16:45:00</t>
+          <t>2026-10-25 17:00:00</t>
         </is>
       </c>
     </row>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G282">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.44</v>
+        <v>8.25</v>
       </c>
       <c r="O284">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="P284">
-        <v>5.49</v>
+        <v>1.27</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>8.25</v>
+        <v>2.95</v>
       </c>
       <c r="O285">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="P285">
-        <v>1.27</v>
+        <v>2.04</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O286">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P286">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G287">

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O88">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P88">
-        <v>3.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q88">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="R88">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V88">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W88">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="AA88">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AB88">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AC88">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AD88">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE88">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF88">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG88">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK88">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
+        <v>2.12</v>
+      </c>
+      <c r="O89">
+        <v>3.8</v>
+      </c>
+      <c r="P89">
         <v>3.09</v>
       </c>
-      <c r="O89">
-        <v>3.9</v>
-      </c>
-      <c r="P89">
-        <v>2.08</v>
-      </c>
       <c r="Q89">
-        <v>3.28</v>
+        <v>2.79</v>
       </c>
       <c r="R89">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U89">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
-        <v>5.7</v>
+        <v>4.35</v>
       </c>
       <c r="AA89">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AB89">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AC89">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD89">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AE89">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF89">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,34 +21010,34 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="O127">
-        <v>4.36</v>
+        <v>3.84</v>
       </c>
       <c r="P127">
-        <v>4.42</v>
+        <v>2.65</v>
       </c>
       <c r="Q127">
-        <v>2.19</v>
+        <v>3.1</v>
       </c>
       <c r="R127">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="S127">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T127">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U127">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="V127">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W127">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21046,22 +21046,22 @@
         <v>1.15</v>
       </c>
       <c r="Z127">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA127">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB127">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC127">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AD127">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE127">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF127">
         <v>1.5</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="O128">
-        <v>3.84</v>
+        <v>4.36</v>
       </c>
       <c r="P128">
-        <v>2.65</v>
+        <v>4.42</v>
       </c>
       <c r="Q128">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="R128">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="S128">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T128">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U128">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V128">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W128">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X128">
         <v>1.01</v>
@@ -21209,22 +21209,22 @@
         <v>1.15</v>
       </c>
       <c r="Z128">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA128">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB128">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC128">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AD128">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AE128">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF128">
         <v>1.5</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK128">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G155">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G160">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G170">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G184">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45825,10 +45825,10 @@
         <v>0</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC279">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.29</v>
+        <v>1.76</v>
       </c>
       <c r="O19">
-        <v>3.18</v>
+        <v>3.52</v>
       </c>
       <c r="P19">
-        <v>2.82</v>
+        <v>3.94</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z19">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="AA19">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB19">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AD19">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="O20">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="P20">
-        <v>3.94</v>
+        <v>2.82</v>
       </c>
       <c r="Q20">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
+        <v>1.29</v>
+      </c>
+      <c r="Z20">
+        <v>3.45</v>
+      </c>
+      <c r="AA20">
+        <v>1.93</v>
+      </c>
+      <c r="AB20">
+        <v>1.83</v>
+      </c>
+      <c r="AC20">
+        <v>3.14</v>
+      </c>
+      <c r="AD20">
         <v>1.27</v>
       </c>
-      <c r="Z20">
-        <v>3.64</v>
-      </c>
-      <c r="AA20">
-        <v>1.79</v>
-      </c>
-      <c r="AB20">
-        <v>1.98</v>
-      </c>
-      <c r="AC20">
-        <v>3.07</v>
-      </c>
-      <c r="AD20">
-        <v>1.35</v>
-      </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>3.95</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -10424,34 +10424,34 @@
         <v>2.79</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA62">
         <v>1.98</v>
@@ -10460,19 +10460,19 @@
         <v>1.83</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
+        <v>2.12</v>
+      </c>
+      <c r="O88">
+        <v>3.8</v>
+      </c>
+      <c r="P88">
         <v>3.09</v>
       </c>
-      <c r="O88">
-        <v>3.9</v>
-      </c>
-      <c r="P88">
-        <v>2.08</v>
-      </c>
       <c r="Q88">
-        <v>3.28</v>
+        <v>2.79</v>
       </c>
       <c r="R88">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="V88">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>5.7</v>
+        <v>4.35</v>
       </c>
       <c r="AA88">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AB88">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AC88">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD88">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AE88">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O89">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P89">
-        <v>3.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q89">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="R89">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S89">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="AA89">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AB89">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AC89">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AD89">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE89">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF89">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG89">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK89">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -18411,55 +18411,55 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18574,55 +18574,55 @@
         <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18737,55 +18737,55 @@
         <v>3.14</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19226,55 +19226,55 @@
         <v>2.79</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.15</v>
+        <v>1.13</v>
       </c>
       <c r="O120">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="P120">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="Q120">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="R120">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="S120">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T120">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U120">
+        <v>1.7</v>
+      </c>
+      <c r="V120">
         <v>2.1</v>
       </c>
-      <c r="V120">
-        <v>1.62</v>
-      </c>
       <c r="W120">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X120">
+        <v>1</v>
+      </c>
+      <c r="Y120">
         <v>1.02</v>
       </c>
-      <c r="Y120">
-        <v>1.13</v>
-      </c>
       <c r="Z120">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AA120">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AB120">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="AC120">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="AD120">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AE120">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AF120">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG120">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK120">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
+        <v>2.15</v>
+      </c>
+      <c r="O121">
+        <v>3.6</v>
+      </c>
+      <c r="P121">
+        <v>2.7</v>
+      </c>
+      <c r="Q121">
+        <v>2.7</v>
+      </c>
+      <c r="R121">
+        <v>2.5</v>
+      </c>
+      <c r="S121">
+        <v>1.22</v>
+      </c>
+      <c r="T121">
+        <v>3.75</v>
+      </c>
+      <c r="U121">
+        <v>2.1</v>
+      </c>
+      <c r="V121">
+        <v>1.62</v>
+      </c>
+      <c r="W121">
+        <v>1.18</v>
+      </c>
+      <c r="X121">
+        <v>1.02</v>
+      </c>
+      <c r="Y121">
         <v>1.13</v>
       </c>
-      <c r="O121">
-        <v>7.5</v>
-      </c>
-      <c r="P121">
-        <v>11</v>
-      </c>
-      <c r="Q121">
-        <v>1.48</v>
-      </c>
-      <c r="R121">
-        <v>3.48</v>
-      </c>
-      <c r="S121">
-        <v>1.13</v>
-      </c>
-      <c r="T121">
-        <v>5</v>
-      </c>
-      <c r="U121">
-        <v>1.7</v>
-      </c>
-      <c r="V121">
-        <v>2.1</v>
-      </c>
-      <c r="W121">
-        <v>1.3</v>
-      </c>
-      <c r="X121">
-        <v>1</v>
-      </c>
-      <c r="Y121">
-        <v>1.02</v>
-      </c>
       <c r="Z121">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AA121">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AB121">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC121">
+        <v>2.12</v>
+      </c>
+      <c r="AD121">
+        <v>1.62</v>
+      </c>
+      <c r="AE121">
+        <v>1.22</v>
+      </c>
+      <c r="AF121">
+        <v>1.4</v>
+      </c>
+      <c r="AG121">
+        <v>2.7</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <v>1.22</v>
+      </c>
+      <c r="AK121">
         <v>1.57</v>
-      </c>
-      <c r="AD121">
-        <v>2.26</v>
-      </c>
-      <c r="AE121">
-        <v>1.57</v>
-      </c>
-      <c r="AF121">
-        <v>1.5</v>
-      </c>
-      <c r="AG121">
-        <v>2.45</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.06</v>
-      </c>
-      <c r="AK121">
-        <v>4</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>7.12</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22486,34 +22486,34 @@
         <v>2.35</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA136">
         <v>2</v>
@@ -22522,19 +22522,19 @@
         <v>1.77</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22975,34 +22975,34 @@
         <v>3.2</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA139">
         <v>1.8</v>
@@ -23011,19 +23011,19 @@
         <v>1.96</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23464,55 +23464,55 @@
         <v>0</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G155">
@@ -30473,55 +30473,55 @@
         <v>1.41</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -36667,55 +36667,55 @@
         <v>7.55</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.65</v>
+        <v>2.98</v>
       </c>
       <c r="O236">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="P236">
-        <v>4.62</v>
+        <v>2.21</v>
       </c>
       <c r="Q236">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R236">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S236">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T236">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U236">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V236">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W236">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X236">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z236">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC236">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD236">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE236">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF236">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG236">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK236">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="O237">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P237">
-        <v>2.21</v>
+        <v>3.06</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="O238">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P238">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="O239">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P239">
-        <v>3.25</v>
+        <v>4.62</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39438,40 +39438,40 @@
         <v>1.33</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AC240">
         <v>1.6</v>
@@ -39480,13 +39480,13 @@
         <v>2.2</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40579,55 +40579,55 @@
         <v>2.52</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -42535,55 +42535,55 @@
         <v>0</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X259">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE259">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q293">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q32">
         <v>4.68</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q33">
         <v>3.52</v>
@@ -9609,55 +9609,55 @@
         <v>2.39</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.62</v>
+        <v>2.49</v>
       </c>
       <c r="O66">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P66">
-        <v>4.78</v>
+        <v>2.52</v>
       </c>
       <c r="Q66">
-        <v>2.21</v>
+        <v>3.18</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T66">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="U66">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="V66">
         <v>1.33</v>
       </c>
       <c r="W66">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z66">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA66">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AB66">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC66">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AD66">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK66">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.49</v>
+        <v>1.62</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="P67">
-        <v>2.52</v>
+        <v>4.78</v>
       </c>
       <c r="Q67">
-        <v>3.18</v>
+        <v>2.21</v>
       </c>
       <c r="R67">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="U67">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="V67">
         <v>1.33</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z67">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AA67">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AB67">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC67">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AD67">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AG67">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q111">
-        <v>2.98</v>
+        <v>3.53</v>
       </c>
       <c r="R111">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S111">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T111">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U111">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V111">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
+        <v>1.2</v>
+      </c>
+      <c r="Z111">
+        <v>3.7</v>
+      </c>
+      <c r="AA111">
+        <v>1.72</v>
+      </c>
+      <c r="AB111">
+        <v>1.95</v>
+      </c>
+      <c r="AC111">
+        <v>2.78</v>
+      </c>
+      <c r="AD111">
+        <v>1.34</v>
+      </c>
+      <c r="AE111">
+        <v>1.1</v>
+      </c>
+      <c r="AF111">
+        <v>1.59</v>
+      </c>
+      <c r="AG111">
+        <v>2.17</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.22</v>
+      </c>
+      <c r="AK111">
         <v>1.32</v>
-      </c>
-      <c r="Z111">
-        <v>2.88</v>
-      </c>
-      <c r="AA111">
-        <v>2.07</v>
-      </c>
-      <c r="AB111">
-        <v>1.72</v>
-      </c>
-      <c r="AC111">
-        <v>3.82</v>
-      </c>
-      <c r="AD111">
-        <v>1.18</v>
-      </c>
-      <c r="AE111">
-        <v>1.02</v>
-      </c>
-      <c r="AF111">
-        <v>1.82</v>
-      </c>
-      <c r="AG111">
-        <v>1.85</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.3</v>
-      </c>
-      <c r="AK111">
-        <v>1.53</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>3.53</v>
+        <v>2.98</v>
       </c>
       <c r="R112">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S112">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U112">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V112">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W112">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z112">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA112">
+        <v>2.07</v>
+      </c>
+      <c r="AB112">
         <v>1.72</v>
       </c>
-      <c r="AB112">
-        <v>1.95</v>
-      </c>
       <c r="AC112">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="AD112">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF112">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AG112">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O118">
-        <v>3.92</v>
+        <v>4.18</v>
       </c>
       <c r="P118">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="Q118">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="R118">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="S118">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T118">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="U118">
+        <v>1.75</v>
+      </c>
+      <c r="V118">
         <v>1.95</v>
       </c>
-      <c r="V118">
-        <v>1.77</v>
-      </c>
       <c r="W118">
+        <v>1.25</v>
+      </c>
+      <c r="X118">
+        <v>1.01</v>
+      </c>
+      <c r="Y118">
+        <v>1.03</v>
+      </c>
+      <c r="Z118">
+        <v>7.4</v>
+      </c>
+      <c r="AA118">
+        <v>1.24</v>
+      </c>
+      <c r="AB118">
+        <v>3.34</v>
+      </c>
+      <c r="AC118">
+        <v>1.72</v>
+      </c>
+      <c r="AD118">
+        <v>2.06</v>
+      </c>
+      <c r="AE118">
+        <v>1.42</v>
+      </c>
+      <c r="AF118">
+        <v>1.3</v>
+      </c>
+      <c r="AG118">
+        <v>3.3</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
         <v>1.2</v>
       </c>
-      <c r="X118">
-        <v>1.02</v>
-      </c>
-      <c r="Y118">
-        <v>1.08</v>
-      </c>
-      <c r="Z118">
-        <v>5.55</v>
-      </c>
-      <c r="AA118">
-        <v>1.4</v>
-      </c>
-      <c r="AB118">
-        <v>2.88</v>
-      </c>
-      <c r="AC118">
-        <v>1.99</v>
-      </c>
-      <c r="AD118">
+      <c r="AK118">
         <v>1.79</v>
-      </c>
-      <c r="AE118">
-        <v>1.33</v>
-      </c>
-      <c r="AF118">
-        <v>1.36</v>
-      </c>
-      <c r="AG118">
-        <v>2.84</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.21</v>
-      </c>
-      <c r="AK118">
-        <v>1.6</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O119">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="P119">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="Q119">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="R119">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="S119">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T119">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="U119">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="V119">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="W119">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X119">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z119">
-        <v>7.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA119">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AB119">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AC119">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AD119">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AE119">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF119">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG119">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK119">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>5.07</v>
+        <v>1.79</v>
       </c>
       <c r="O126">
-        <v>4.26</v>
+        <v>4.36</v>
       </c>
       <c r="P126">
-        <v>1.71</v>
+        <v>4.42</v>
       </c>
       <c r="Q126">
-        <v>4.33</v>
+        <v>2.19</v>
       </c>
       <c r="R126">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="S126">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="T126">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="U126">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="V126">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W126">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X126">
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z126">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA126">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AB126">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC126">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AD126">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AE126">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF126">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG126">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AK126">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.79</v>
+        <v>5.07</v>
       </c>
       <c r="O128">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="P128">
-        <v>4.42</v>
+        <v>1.71</v>
       </c>
       <c r="Q128">
-        <v>2.19</v>
+        <v>4.33</v>
       </c>
       <c r="R128">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S128">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="T128">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="U128">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="V128">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W128">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X128">
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z128">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA128">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB128">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC128">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AD128">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AE128">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF128">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG128">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AK128">
-        <v>1.99</v>
+        <v>1.17</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21375,10 +21375,10 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="O139">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P139">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q139">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R139">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S139">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T139">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U139">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V139">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W139">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y139">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z139">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AA139">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB139">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AC139">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD139">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE139">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF139">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG139">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK139">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>3.4</v>
+        <v>1.99</v>
       </c>
       <c r="O140">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P140">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA140">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB140">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="G160">
@@ -26561,55 +26561,55 @@
         <v>1.18</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,43 +30790,43 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="O187">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P187">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA187">
         <v>1.93</v>
@@ -30835,19 +30835,19 @@
         <v>1.87</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,43 +30953,43 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="O188">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P188">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AA188">
         <v>1.93</v>
@@ -30998,19 +30998,19 @@
         <v>1.87</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T189">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U189">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V189">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X189">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z189">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC189">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD189">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE189">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG189">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK189">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="O191">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="P191">
-        <v>4.4</v>
+        <v>7.48</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC191">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AD191">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
+        <v>1.62</v>
+      </c>
+      <c r="O192">
+        <v>4.45</v>
+      </c>
+      <c r="P192">
+        <v>4.4</v>
+      </c>
+      <c r="Q192">
+        <v>2.05</v>
+      </c>
+      <c r="R192">
+        <v>2.6</v>
+      </c>
+      <c r="S192">
+        <v>1.18</v>
+      </c>
+      <c r="T192">
+        <v>4.33</v>
+      </c>
+      <c r="U192">
+        <v>1.9</v>
+      </c>
+      <c r="V192">
+        <v>1.77</v>
+      </c>
+      <c r="W192">
+        <v>1.2</v>
+      </c>
+      <c r="X192">
+        <v>1.01</v>
+      </c>
+      <c r="Y192">
+        <v>1.11</v>
+      </c>
+      <c r="Z192">
+        <v>6.77</v>
+      </c>
+      <c r="AA192">
         <v>1.36</v>
       </c>
-      <c r="O192">
-        <v>5</v>
-      </c>
-      <c r="P192">
-        <v>7.48</v>
-      </c>
-      <c r="Q192">
-        <v>0</v>
-      </c>
-      <c r="R192">
-        <v>0</v>
-      </c>
-      <c r="S192">
-        <v>0</v>
-      </c>
-      <c r="T192">
-        <v>0</v>
-      </c>
-      <c r="U192">
-        <v>0</v>
-      </c>
-      <c r="V192">
-        <v>0</v>
-      </c>
-      <c r="W192">
-        <v>0</v>
-      </c>
-      <c r="X192">
-        <v>0</v>
-      </c>
-      <c r="Y192">
-        <v>0</v>
-      </c>
-      <c r="Z192">
-        <v>0</v>
-      </c>
-      <c r="AA192">
-        <v>0</v>
-      </c>
       <c r="AB192">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC192">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE192">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG192">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK192">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31777,34 +31777,34 @@
         <v>2.05</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA193">
         <v>1.9</v>
@@ -31813,19 +31813,19 @@
         <v>1.87</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32266,55 +32266,55 @@
         <v>9.949999999999999</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32429,55 +32429,55 @@
         <v>5.57</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32592,34 +32592,34 @@
         <v>3.94</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA198">
         <v>1.96</v>
@@ -32628,19 +32628,19 @@
         <v>1.84</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33244,40 +33244,40 @@
         <v>1.41</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T202">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U202">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V202">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W202">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X202">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z202">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC202">
         <v>1.9</v>
@@ -33286,13 +33286,13 @@
         <v>1.9</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG202">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK202">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33407,55 +33407,55 @@
         <v>3.42</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="O206">
-        <v>3.76</v>
+        <v>3.63</v>
       </c>
       <c r="P206">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="Q206">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="R206">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S206">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="T206">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U206">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="V206">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="W206">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X206">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y206">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z206">
-        <v>5.65</v>
+        <v>4.25</v>
       </c>
       <c r="AA206">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AB206">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="AC206">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AD206">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AE206">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AF206">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG206">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK206">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="O207">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="P207">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q207">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="R207">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S207">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T207">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="U207">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V207">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W207">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X207">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z207">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA207">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB207">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="AC207">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AD207">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE207">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF207">
         <v>1.57</v>
       </c>
       <c r="AG207">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK207">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,80 +34213,80 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="O208">
-        <v>3.54</v>
+        <v>4.15</v>
       </c>
       <c r="P208">
-        <v>2.93</v>
+        <v>3.69</v>
       </c>
       <c r="Q208">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="R208">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="S208">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T208">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="U208">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="V208">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="W208">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
+        <v>1.06</v>
+      </c>
+      <c r="Z208">
+        <v>6.8</v>
+      </c>
+      <c r="AA208">
+        <v>1.33</v>
+      </c>
+      <c r="AB208">
+        <v>2.83</v>
+      </c>
+      <c r="AC208">
+        <v>1.98</v>
+      </c>
+      <c r="AD208">
+        <v>1.83</v>
+      </c>
+      <c r="AE208">
+        <v>1.31</v>
+      </c>
+      <c r="AF208">
+        <v>1.36</v>
+      </c>
+      <c r="AG208">
+        <v>2.8</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ208">
         <v>1.24</v>
       </c>
-      <c r="Z208">
-        <v>3.8</v>
-      </c>
-      <c r="AA208">
-        <v>1.8</v>
-      </c>
-      <c r="AB208">
-        <v>2.03</v>
-      </c>
-      <c r="AC208">
-        <v>2.92</v>
-      </c>
-      <c r="AD208">
-        <v>1.41</v>
-      </c>
-      <c r="AE208">
-        <v>1.16</v>
-      </c>
-      <c r="AF208">
-        <v>1.57</v>
-      </c>
-      <c r="AG208">
-        <v>2.25</v>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ208">
-        <v>1.28</v>
-      </c>
       <c r="AK208">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="O209">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="P209">
-        <v>3.69</v>
+        <v>2.84</v>
       </c>
       <c r="Q209">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="R209">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S209">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T209">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U209">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V209">
+        <v>1.74</v>
+      </c>
+      <c r="W209">
+        <v>1.13</v>
+      </c>
+      <c r="X209">
+        <v>1.02</v>
+      </c>
+      <c r="Y209">
+        <v>1.08</v>
+      </c>
+      <c r="Z209">
+        <v>5.65</v>
+      </c>
+      <c r="AA209">
+        <v>1.39</v>
+      </c>
+      <c r="AB209">
+        <v>2.75</v>
+      </c>
+      <c r="AC209">
+        <v>2.07</v>
+      </c>
+      <c r="AD209">
         <v>1.78</v>
       </c>
-      <c r="W209">
-        <v>1.17</v>
-      </c>
-      <c r="X209">
-        <v>1.01</v>
-      </c>
-      <c r="Y209">
-        <v>1.06</v>
-      </c>
-      <c r="Z209">
-        <v>6.8</v>
-      </c>
-      <c r="AA209">
+      <c r="AE209">
         <v>1.33</v>
       </c>
-      <c r="AB209">
-        <v>2.83</v>
-      </c>
-      <c r="AC209">
-        <v>1.98</v>
-      </c>
-      <c r="AD209">
-        <v>1.83</v>
-      </c>
-      <c r="AE209">
-        <v>1.31</v>
-      </c>
       <c r="AF209">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG209">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>1.24</v>
       </c>
       <c r="AK209">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34548,55 +34548,55 @@
         <v>1.48</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T210">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V210">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W210">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y210">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z210">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG210">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK210">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35200,55 +35200,55 @@
         <v>2.8</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S216">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T216">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V216">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W216">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X216">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z216">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD216">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG216">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK216">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.79</v>
+        <v>3.83</v>
       </c>
       <c r="O220">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="P220">
-        <v>3.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q220">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="R220">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="S220">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T220">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="U220">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V220">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="W220">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X220">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y220">
         <v>1.03</v>
       </c>
       <c r="Z220">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="AA220">
+        <v>1.17</v>
+      </c>
+      <c r="AB220">
+        <v>3.96</v>
+      </c>
+      <c r="AC220">
+        <v>1.52</v>
+      </c>
+      <c r="AD220">
+        <v>2.24</v>
+      </c>
+      <c r="AE220">
+        <v>1.59</v>
+      </c>
+      <c r="AF220">
         <v>1.25</v>
       </c>
-      <c r="AB220">
-        <v>3.28</v>
-      </c>
-      <c r="AC220">
-        <v>1.73</v>
-      </c>
-      <c r="AD220">
-        <v>2.02</v>
-      </c>
-      <c r="AE220">
-        <v>1.41</v>
-      </c>
-      <c r="AF220">
-        <v>1.3</v>
-      </c>
       <c r="AG220">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.17</v>
+        <v>2.1</v>
       </c>
       <c r="AK220">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
+        <v>1.86</v>
+      </c>
+      <c r="O221">
         <v>3.83</v>
       </c>
-      <c r="O221">
-        <v>4.5</v>
-      </c>
       <c r="P221">
-        <v>1.68</v>
+        <v>3.61</v>
       </c>
       <c r="Q221">
+        <v>2.18</v>
+      </c>
+      <c r="R221">
+        <v>2.54</v>
+      </c>
+      <c r="S221">
+        <v>1.22</v>
+      </c>
+      <c r="T221">
         <v>3.75</v>
       </c>
-      <c r="R221">
-        <v>2.76</v>
-      </c>
-      <c r="S221">
-        <v>1.15</v>
-      </c>
-      <c r="T221">
+      <c r="U221">
+        <v>2.25</v>
+      </c>
+      <c r="V221">
+        <v>1.57</v>
+      </c>
+      <c r="W221">
+        <v>1.14</v>
+      </c>
+      <c r="X221">
+        <v>1.01</v>
+      </c>
+      <c r="Y221">
+        <v>1.1</v>
+      </c>
+      <c r="Z221">
         <v>5</v>
       </c>
-      <c r="U221">
-        <v>1.67</v>
-      </c>
-      <c r="V221">
-        <v>2.1</v>
-      </c>
-      <c r="W221">
-        <v>1.3</v>
-      </c>
-      <c r="X221">
-        <v>1</v>
-      </c>
-      <c r="Y221">
-        <v>1.03</v>
-      </c>
-      <c r="Z221">
-        <v>8.4</v>
-      </c>
       <c r="AA221">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AB221">
-        <v>3.96</v>
+        <v>2.31</v>
       </c>
       <c r="AC221">
-        <v>1.52</v>
+        <v>2.23</v>
       </c>
       <c r="AD221">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="AE221">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="AF221">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AG221">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK221">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="O222">
-        <v>3.83</v>
+        <v>4.21</v>
       </c>
       <c r="P222">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="Q222">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R222">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="S222">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T222">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="U222">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="V222">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="W222">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="X222">
         <v>1.01</v>
       </c>
       <c r="Y222">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z222">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="AA222">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AB222">
-        <v>2.31</v>
+        <v>3.28</v>
       </c>
       <c r="AC222">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="AD222">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="AE222">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AF222">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG222">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK222">
         <v>1.91</v>
@@ -36830,34 +36830,34 @@
         <v>2.93</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA224">
         <v>2.05</v>
@@ -36866,19 +36866,19 @@
         <v>1.68</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36993,40 +36993,40 @@
         <v>4.36</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC225">
         <v>2.15</v>
@@ -37035,13 +37035,13 @@
         <v>1.62</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,34 +37156,34 @@
         <v>3.23</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T226">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U226">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V226">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA226">
         <v>1.75</v>
@@ -37192,19 +37192,19 @@
         <v>1.95</v>
       </c>
       <c r="AC226">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD226">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG226">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK226">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37319,34 +37319,34 @@
         <v>6.06</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S227">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T227">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U227">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V227">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W227">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z227">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA227">
         <v>1.62</v>
@@ -37355,19 +37355,19 @@
         <v>2.15</v>
       </c>
       <c r="AC227">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD227">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK227">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37482,34 +37482,34 @@
         <v>2.86</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA228">
         <v>2.02</v>
@@ -37518,19 +37518,19 @@
         <v>1.78</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37645,34 +37645,34 @@
         <v>2.5</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA229">
         <v>2</v>
@@ -37681,19 +37681,19 @@
         <v>1.73</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -38297,55 +38297,55 @@
         <v>2.55</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38460,55 +38460,55 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,80 +38777,80 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.98</v>
+        <v>2.06</v>
       </c>
       <c r="O236">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P236">
-        <v>2.21</v>
+        <v>3.25</v>
       </c>
       <c r="Q236">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="R236">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="S236">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T236">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="U236">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V236">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W236">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X236">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y236">
+        <v>1.33</v>
+      </c>
+      <c r="Z236">
+        <v>2.83</v>
+      </c>
+      <c r="AA236">
+        <v>2.2</v>
+      </c>
+      <c r="AB236">
+        <v>1.64</v>
+      </c>
+      <c r="AC236">
+        <v>3.7</v>
+      </c>
+      <c r="AD236">
+        <v>1.2</v>
+      </c>
+      <c r="AE236">
+        <v>1.04</v>
+      </c>
+      <c r="AF236">
+        <v>1.83</v>
+      </c>
+      <c r="AG236">
+        <v>1.84</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ236">
         <v>1.26</v>
       </c>
-      <c r="Z236">
-        <v>3.2</v>
-      </c>
-      <c r="AA236">
-        <v>1.9</v>
-      </c>
-      <c r="AB236">
-        <v>1.77</v>
-      </c>
-      <c r="AC236">
-        <v>3.28</v>
-      </c>
-      <c r="AD236">
-        <v>1.25</v>
-      </c>
-      <c r="AE236">
-        <v>1.05</v>
-      </c>
-      <c r="AF236">
-        <v>1.74</v>
-      </c>
-      <c r="AG236">
-        <v>1.94</v>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ236">
-        <v>1.22</v>
-      </c>
       <c r="AK236">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,80 +38940,80 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="O237">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P237">
-        <v>3.06</v>
+        <v>2.21</v>
       </c>
       <c r="Q237">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R237">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S237">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T237">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U237">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V237">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W237">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X237">
         <v>1.01</v>
       </c>
       <c r="Y237">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z237">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA237">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB237">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC237">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD237">
+        <v>1.25</v>
+      </c>
+      <c r="AE237">
+        <v>1.05</v>
+      </c>
+      <c r="AF237">
+        <v>1.74</v>
+      </c>
+      <c r="AG237">
+        <v>1.94</v>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ237">
         <v>1.22</v>
       </c>
-      <c r="AE237">
-        <v>1.04</v>
-      </c>
-      <c r="AF237">
-        <v>1.78</v>
-      </c>
-      <c r="AG237">
-        <v>1.89</v>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ237">
-        <v>1.29</v>
-      </c>
       <c r="AK237">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="O238">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P238">
-        <v>3.25</v>
+        <v>4.62</v>
       </c>
       <c r="Q238">
-        <v>2.82</v>
+        <v>2.15</v>
       </c>
       <c r="R238">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="S238">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T238">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="U238">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V238">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W238">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X238">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y238">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z238">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AA238">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB238">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC238">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AD238">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE238">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF238">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AG238">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK238">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="O239">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P239">
-        <v>4.62</v>
+        <v>3.06</v>
       </c>
       <c r="Q239">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R239">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="S239">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T239">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="U239">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V239">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W239">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X239">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y239">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z239">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA239">
         <v>2.05</v>
       </c>
       <c r="AB239">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC239">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD239">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE239">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF239">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AG239">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK239">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39592,64 +39592,64 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q241">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R241">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S241">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T241">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U241">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V241">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X241">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y241">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z241">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AA241">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB241">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE241">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF241">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG241">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK241">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39927,40 +39927,40 @@
         <v>7.5</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R243">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S243">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T243">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V243">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W243">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X243">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z243">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="AA243">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB243">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC243">
         <v>1.93</v>
@@ -39969,13 +39969,13 @@
         <v>1.82</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG243">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK243">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40416,55 +40416,55 @@
         <v>2.54</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X246">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40742,34 +40742,34 @@
         <v>1.5</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA248">
         <v>1.82</v>
@@ -40778,19 +40778,19 @@
         <v>1.88</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40905,55 +40905,55 @@
         <v>6.24</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V249">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W249">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z249">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK249">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41068,55 +41068,55 @@
         <v>4.24</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T250">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U250">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V250">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X250">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y250">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z250">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA250">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB250">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC250">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD250">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK250">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,64 +41222,64 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41394,34 +41394,34 @@
         <v>3.02</v>
       </c>
       <c r="Q252">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R252">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S252">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T252">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U252">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V252">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W252">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X252">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y252">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z252">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA252">
         <v>1.87</v>
@@ -41430,19 +41430,19 @@
         <v>1.82</v>
       </c>
       <c r="AC252">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD252">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE252">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF252">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG252">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK252">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41557,55 +41557,55 @@
         <v>4.43</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42200,64 +42200,64 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42698,34 +42698,34 @@
         <v>1.53</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA260">
         <v>1.88</v>
@@ -42734,19 +42734,19 @@
         <v>1.98</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42861,34 +42861,34 @@
         <v>1.91</v>
       </c>
       <c r="Q261">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R261">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S261">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T261">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U261">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V261">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W261">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X261">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y261">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z261">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AA261">
         <v>1.92</v>
@@ -42897,19 +42897,19 @@
         <v>1.88</v>
       </c>
       <c r="AC261">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD261">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE261">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF261">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG261">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AK261">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43024,55 +43024,55 @@
         <v>5.49</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43187,55 +43187,55 @@
         <v>1.63</v>
       </c>
       <c r="Q263">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T263">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U263">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V263">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y263">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z263">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC263">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD263">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE263">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF263">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG263">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK263">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43350,55 +43350,55 @@
         <v>2.33</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43513,40 +43513,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC265">
         <v>2.05</v>
@@ -43555,13 +43555,13 @@
         <v>1.66</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G271">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G273">
@@ -44980,55 +44980,55 @@
         <v>4.89</v>
       </c>
       <c r="Q274">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R274">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S274">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T274">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U274">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V274">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W274">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X274">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y274">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z274">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC274">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD274">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE274">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF274">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG274">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK274">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45143,55 +45143,55 @@
         <v>1.58</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45306,55 +45306,55 @@
         <v>2.88</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45469,40 +45469,40 @@
         <v>5.75</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AC277">
         <v>2.05</v>
@@ -45511,13 +45511,13 @@
         <v>1.7</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45632,34 +45632,34 @@
         <v>1.83</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z278">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA278">
         <v>1.85</v>
@@ -45668,19 +45668,19 @@
         <v>1.85</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O279">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P279">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45825,10 +45825,10 @@
         <v>0</v>
       </c>
       <c r="AA279">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB279">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46314,10 +46314,10 @@
         <v>0</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC282">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46640,10 +46640,10 @@
         <v>0</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC284">
         <v>0</v>
@@ -46803,10 +46803,10 @@
         <v>0</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC285">
         <v>0</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -46966,10 +46966,10 @@
         <v>0</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC286">
         <v>0</v>
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G292">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q294">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R294">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S294">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T294">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U294">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V294">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W294">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X294">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y294">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z294">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA294">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB294">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC294">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD294">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE294">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF294">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG294">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK294">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48403,55 +48403,55 @@
         <v>16</v>
       </c>
       <c r="Q295">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R295">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S295">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T295">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U295">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V295">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W295">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X295">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y295">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z295">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA295">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB295">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC295">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD295">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE295">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF295">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG295">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK295">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48729,55 +48729,55 @@
         <v>2.94</v>
       </c>
       <c r="Q297">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R297">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T297">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U297">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V297">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W297">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X297">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y297">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z297">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA297">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB297">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC297">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD297">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE297">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF297">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG297">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK297">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49055,55 +49055,55 @@
         <v>3.3</v>
       </c>
       <c r="Q299">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R299">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S299">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T299">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U299">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V299">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W299">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X299">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y299">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z299">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC299">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD299">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE299">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF299">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG299">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK299">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q300">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R300">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S300">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T300">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U300">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V300">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W300">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X300">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y300">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z300">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC300">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD300">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE300">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF300">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG300">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK300">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL300">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="O19">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="P19">
-        <v>3.94</v>
+        <v>2.82</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
+        <v>1.29</v>
+      </c>
+      <c r="Z19">
+        <v>3.45</v>
+      </c>
+      <c r="AA19">
+        <v>1.93</v>
+      </c>
+      <c r="AB19">
+        <v>1.83</v>
+      </c>
+      <c r="AC19">
+        <v>3.14</v>
+      </c>
+      <c r="AD19">
         <v>1.27</v>
       </c>
-      <c r="Z19">
-        <v>3.64</v>
-      </c>
-      <c r="AA19">
-        <v>1.79</v>
-      </c>
-      <c r="AB19">
-        <v>1.98</v>
-      </c>
-      <c r="AC19">
-        <v>3.07</v>
-      </c>
-      <c r="AD19">
-        <v>1.35</v>
-      </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.29</v>
+        <v>1.76</v>
       </c>
       <c r="O20">
-        <v>3.18</v>
+        <v>3.52</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>3.94</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AD20">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G40">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="G52">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="O87">
         <v>3.8</v>
       </c>
       <c r="P87">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="Q87">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="R87">
         <v>2.4</v>
@@ -14511,22 +14511,22 @@
         <v>3.8</v>
       </c>
       <c r="U87">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V87">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA87">
         <v>1.58</v>
@@ -14535,19 +14535,19 @@
         <v>2.36</v>
       </c>
       <c r="AC87">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD87">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE87">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF87">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG87">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O88">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P88">
-        <v>3.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q88">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="R88">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V88">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W88">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="AA88">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AB88">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AC88">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AD88">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE88">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF88">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG88">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK88">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.09</v>
+        <v>2.19</v>
       </c>
       <c r="O89">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P89">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="Q89">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="R89">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U89">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA89">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AB89">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AC89">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AD89">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AE89">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG89">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O111">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P111">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>3.53</v>
+        <v>2.98</v>
       </c>
       <c r="R111">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S111">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T111">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U111">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W111">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z111">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA111">
+        <v>2.07</v>
+      </c>
+      <c r="AB111">
         <v>1.72</v>
       </c>
-      <c r="AB111">
-        <v>1.95</v>
-      </c>
       <c r="AC111">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="AD111">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF111">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AG111">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,80 +18565,80 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>2.98</v>
+        <v>3.53</v>
       </c>
       <c r="R112">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U112">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V112">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
+        <v>1.2</v>
+      </c>
+      <c r="Z112">
+        <v>3.7</v>
+      </c>
+      <c r="AA112">
+        <v>1.72</v>
+      </c>
+      <c r="AB112">
+        <v>1.95</v>
+      </c>
+      <c r="AC112">
+        <v>2.78</v>
+      </c>
+      <c r="AD112">
+        <v>1.34</v>
+      </c>
+      <c r="AE112">
+        <v>1.1</v>
+      </c>
+      <c r="AF112">
+        <v>1.59</v>
+      </c>
+      <c r="AG112">
+        <v>2.17</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>1.22</v>
+      </c>
+      <c r="AK112">
         <v>1.32</v>
-      </c>
-      <c r="Z112">
-        <v>2.88</v>
-      </c>
-      <c r="AA112">
-        <v>2.07</v>
-      </c>
-      <c r="AB112">
-        <v>1.72</v>
-      </c>
-      <c r="AC112">
-        <v>3.82</v>
-      </c>
-      <c r="AD112">
-        <v>1.18</v>
-      </c>
-      <c r="AE112">
-        <v>1.02</v>
-      </c>
-      <c r="AF112">
-        <v>1.82</v>
-      </c>
-      <c r="AG112">
-        <v>1.85</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.3</v>
-      </c>
-      <c r="AK112">
-        <v>1.53</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.65</v>
+        <v>5.07</v>
       </c>
       <c r="O127">
-        <v>3.84</v>
+        <v>4.26</v>
       </c>
       <c r="P127">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q127">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R127">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T127">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U127">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V127">
         <v>1.5</v>
       </c>
       <c r="W127">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z127">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="AA127">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB127">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC127">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AD127">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE127">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF127">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG127">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK127">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>5.07</v>
+        <v>2.65</v>
       </c>
       <c r="O128">
-        <v>4.26</v>
+        <v>3.84</v>
       </c>
       <c r="P128">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="Q128">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R128">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S128">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T128">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U128">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V128">
         <v>1.5</v>
       </c>
       <c r="W128">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z128">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AA128">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB128">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC128">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AD128">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE128">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF128">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG128">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,43 +30790,43 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="O187">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P187">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="Q187">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="R187">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S187">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T187">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U187">
         <v>2.63</v>
       </c>
       <c r="V187">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W187">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y187">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z187">
-        <v>3.56</v>
+        <v>4.04</v>
       </c>
       <c r="AA187">
         <v>1.93</v>
@@ -30835,19 +30835,19 @@
         <v>1.87</v>
       </c>
       <c r="AC187">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AD187">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE187">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF187">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK187">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,43 +30953,43 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="O188">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P188">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="Q188">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="R188">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S188">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T188">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U188">
         <v>2.63</v>
       </c>
       <c r="V188">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W188">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X188">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z188">
-        <v>4.04</v>
+        <v>3.56</v>
       </c>
       <c r="AA188">
         <v>1.93</v>
@@ -30998,19 +30998,19 @@
         <v>1.87</v>
       </c>
       <c r="AC188">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AD188">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE188">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF188">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG188">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK188">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
+        <v>1.62</v>
+      </c>
+      <c r="O191">
+        <v>4.45</v>
+      </c>
+      <c r="P191">
+        <v>4.4</v>
+      </c>
+      <c r="Q191">
+        <v>2.05</v>
+      </c>
+      <c r="R191">
+        <v>2.6</v>
+      </c>
+      <c r="S191">
+        <v>1.18</v>
+      </c>
+      <c r="T191">
+        <v>4.33</v>
+      </c>
+      <c r="U191">
+        <v>1.9</v>
+      </c>
+      <c r="V191">
+        <v>1.77</v>
+      </c>
+      <c r="W191">
+        <v>1.2</v>
+      </c>
+      <c r="X191">
+        <v>1.01</v>
+      </c>
+      <c r="Y191">
+        <v>1.11</v>
+      </c>
+      <c r="Z191">
+        <v>6.77</v>
+      </c>
+      <c r="AA191">
         <v>1.36</v>
       </c>
-      <c r="O191">
-        <v>5</v>
-      </c>
-      <c r="P191">
-        <v>7.48</v>
-      </c>
-      <c r="Q191">
-        <v>1.93</v>
-      </c>
-      <c r="R191">
-        <v>2.75</v>
-      </c>
-      <c r="S191">
-        <v>1.22</v>
-      </c>
-      <c r="T191">
-        <v>4.5</v>
-      </c>
-      <c r="U191">
-        <v>1.99</v>
-      </c>
-      <c r="V191">
-        <v>1.7</v>
-      </c>
-      <c r="W191">
-        <v>1.17</v>
-      </c>
-      <c r="X191">
-        <v>1.02</v>
-      </c>
-      <c r="Y191">
-        <v>1.1</v>
-      </c>
-      <c r="Z191">
-        <v>5.75</v>
-      </c>
-      <c r="AA191">
-        <v>1.4</v>
-      </c>
       <c r="AB191">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC191">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AD191">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AE191">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF191">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG191">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK191">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="O192">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="P192">
-        <v>4.4</v>
+        <v>7.48</v>
       </c>
       <c r="Q192">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="R192">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S192">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T192">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U192">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="V192">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W192">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X192">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z192">
-        <v>6.77</v>
+        <v>5.75</v>
       </c>
       <c r="AA192">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB192">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC192">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AD192">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AE192">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF192">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG192">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK192">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="O227">
-        <v>4.42</v>
+        <v>3.41</v>
       </c>
       <c r="P227">
-        <v>6.06</v>
+        <v>2.86</v>
       </c>
       <c r="Q227">
-        <v>2.04</v>
+        <v>3.68</v>
       </c>
       <c r="R227">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S227">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T227">
-        <v>3.84</v>
+        <v>2.72</v>
       </c>
       <c r="U227">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="V227">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="W227">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X227">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y227">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z227">
-        <v>4.75</v>
+        <v>3.14</v>
       </c>
       <c r="AA227">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AB227">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC227">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD227">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AE227">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF227">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG227">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK227">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.69</v>
+        <v>1.6</v>
       </c>
       <c r="O228">
-        <v>3.41</v>
+        <v>4.42</v>
       </c>
       <c r="P228">
-        <v>2.86</v>
+        <v>6.06</v>
       </c>
       <c r="Q228">
-        <v>3.68</v>
+        <v>2.04</v>
       </c>
       <c r="R228">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S228">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T228">
-        <v>2.72</v>
+        <v>3.84</v>
       </c>
       <c r="U228">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="V228">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="W228">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X228">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z228">
-        <v>3.14</v>
+        <v>4.75</v>
       </c>
       <c r="AA228">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AB228">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC228">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD228">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AE228">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF228">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG228">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK228">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>6.67</v>
+        <v>4.28</v>
       </c>
       <c r="O260">
-        <v>4.38</v>
+        <v>3.65</v>
       </c>
       <c r="P260">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="Q260">
-        <v>5.8</v>
+        <v>3.69</v>
       </c>
       <c r="R260">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="S260">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T260">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="U260">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V260">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W260">
         <v>1.07</v>
       </c>
       <c r="X260">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y260">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="Z260">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="AA260">
+        <v>1.92</v>
+      </c>
+      <c r="AB260">
         <v>1.88</v>
       </c>
-      <c r="AB260">
-        <v>1.98</v>
-      </c>
       <c r="AC260">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="AD260">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE260">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF260">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG260">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
+        <v>1.77</v>
+      </c>
+      <c r="AK260">
         <v>1.2</v>
-      </c>
-      <c r="AK260">
-        <v>1.11</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,65 +42852,65 @@
         </is>
       </c>
       <c r="N261">
-        <v>4.28</v>
+        <v>6.67</v>
       </c>
       <c r="O261">
-        <v>3.65</v>
+        <v>4.38</v>
       </c>
       <c r="P261">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="Q261">
-        <v>3.69</v>
+        <v>5.8</v>
       </c>
       <c r="R261">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="S261">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T261">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U261">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V261">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W261">
         <v>1.07</v>
       </c>
       <c r="X261">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y261">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z261">
-        <v>2.86</v>
+        <v>3.42</v>
       </c>
       <c r="AA261">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB261">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC261">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="AD261">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AE261">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF261">
+        <v>1.91</v>
+      </c>
+      <c r="AG261">
         <v>1.8</v>
       </c>
-      <c r="AG261">
-        <v>1.84</v>
-      </c>
       <c r="AH261" t="inlineStr">
         <is>
           <t>[]</t>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="AK261">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AL261">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="P2">
-        <v>3.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q2">
         <v>2.68</v>
@@ -650,10 +650,10 @@
         <v>2.23</v>
       </c>
       <c r="S2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U2">
         <v>2.52</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G15">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G22">
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O32">
         <v>3.6</v>
@@ -5534,22 +5534,22 @@
         <v>1.75</v>
       </c>
       <c r="Q32">
-        <v>4.68</v>
+        <v>4.5</v>
       </c>
       <c r="R32">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="U32">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
         <v>1.07</v>
@@ -5558,28 +5558,28 @@
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
         <v>2.1</v>
@@ -5598,7 +5598,7 @@
         <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T33">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V33">
         <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD33">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
         <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG33">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="O35">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q35">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S35">
         <v>1.42</v>
@@ -6071,7 +6071,7 @@
         <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK35">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -6355,19 +6355,19 @@
         <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="U37">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -6376,7 +6376,7 @@
         <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="AA37">
         <v>2.01</v>
@@ -6385,7 +6385,7 @@
         <v>1.69</v>
       </c>
       <c r="AC37">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="AD37">
         <v>1.21</v>
@@ -6397,7 +6397,7 @@
         <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
         <v>1.73</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="G56">
@@ -9935,13 +9935,13 @@
         <v>2.27</v>
       </c>
       <c r="Q59">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="R59">
         <v>2.5</v>
       </c>
       <c r="S59">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T59">
         <v>3.4</v>
@@ -9962,13 +9962,13 @@
         <v>1.12</v>
       </c>
       <c r="Z59">
-        <v>5.16</v>
+        <v>4.8</v>
       </c>
       <c r="AA59">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AB59">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AC59">
         <v>2.34</v>
@@ -9983,7 +9983,7 @@
         <v>1.44</v>
       </c>
       <c r="AG59">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK59">
         <v>1.4</v>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="O60">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="Q60">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="R60">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S60">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U60">
         <v>2.12</v>
       </c>
       <c r="V60">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W60">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10125,7 +10125,7 @@
         <v>1.12</v>
       </c>
       <c r="Z60">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="AA60">
         <v>1.48</v>
@@ -10137,7 +10137,7 @@
         <v>2.27</v>
       </c>
       <c r="AD60">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE60">
         <v>1.24</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK60">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P62">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q62">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R62">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
         <v>1.36</v>
@@ -10454,10 +10454,10 @@
         <v>2.97</v>
       </c>
       <c r="AA62">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC62">
         <v>3.34</v>
@@ -10472,7 +10472,7 @@
         <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="O66">
+        <v>3.2</v>
+      </c>
+      <c r="P66">
+        <v>2.6</v>
+      </c>
+      <c r="Q66">
         <v>3.1</v>
       </c>
-      <c r="P66">
-        <v>2.52</v>
-      </c>
-      <c r="Q66">
-        <v>3.18</v>
-      </c>
       <c r="R66">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T66">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U66">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V66">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W66">
+        <v>1.07</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
+        <v>1.28</v>
+      </c>
+      <c r="Z66">
+        <v>3.08</v>
+      </c>
+      <c r="AA66">
+        <v>1.94</v>
+      </c>
+      <c r="AB66">
+        <v>1.85</v>
+      </c>
+      <c r="AC66">
+        <v>3.34</v>
+      </c>
+      <c r="AD66">
+        <v>1.24</v>
+      </c>
+      <c r="AE66">
         <v>1.05</v>
       </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.32</v>
-      </c>
-      <c r="Z66">
-        <v>2.88</v>
-      </c>
-      <c r="AA66">
-        <v>2.06</v>
-      </c>
-      <c r="AB66">
-        <v>1.65</v>
-      </c>
-      <c r="AC66">
-        <v>3.68</v>
-      </c>
-      <c r="AD66">
-        <v>1.2</v>
-      </c>
-      <c r="AE66">
-        <v>1.03</v>
-      </c>
       <c r="AF66">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG66">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="O67">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="P67">
-        <v>4.78</v>
+        <v>5.25</v>
       </c>
       <c r="Q67">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S67">
         <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="U67">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V67">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y67">
+        <v>1.24</v>
+      </c>
+      <c r="Z67">
+        <v>3.34</v>
+      </c>
+      <c r="AA67">
+        <v>1.9</v>
+      </c>
+      <c r="AB67">
+        <v>1.9</v>
+      </c>
+      <c r="AC67">
+        <v>3.14</v>
+      </c>
+      <c r="AD67">
         <v>1.27</v>
       </c>
-      <c r="Z67">
-        <v>3.14</v>
-      </c>
-      <c r="AA67">
-        <v>1.93</v>
-      </c>
-      <c r="AB67">
-        <v>1.75</v>
-      </c>
-      <c r="AC67">
-        <v>3.34</v>
-      </c>
-      <c r="AD67">
-        <v>1.24</v>
-      </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG67">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="O68">
-        <v>5.56</v>
+        <v>5.35</v>
       </c>
       <c r="P68">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="Q68">
         <v>1.77</v>
@@ -11408,22 +11408,22 @@
         <v>2.56</v>
       </c>
       <c r="S68">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U68">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V68">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W68">
         <v>1.17</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
         <v>1.1</v>
@@ -11432,22 +11432,22 @@
         <v>6.5</v>
       </c>
       <c r="AA68">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB68">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AC68">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AD68">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE68">
         <v>1.27</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG68">
         <v>2.2</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK68">
         <v>3.1</v>
@@ -12211,10 +12211,10 @@
         <v>2.1</v>
       </c>
       <c r="O73">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P73">
-        <v>3.2</v>
+        <v>3.77</v>
       </c>
       <c r="Q73">
         <v>2.7</v>
@@ -12223,16 +12223,16 @@
         <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T73">
         <v>2.93</v>
       </c>
       <c r="U73">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="V73">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W73">
         <v>1.04</v>
@@ -12247,16 +12247,16 @@
         <v>3.51</v>
       </c>
       <c r="AA73">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB73">
         <v>1.8</v>
       </c>
       <c r="AC73">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="AD73">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE73">
         <v>1.08</v>
@@ -12265,7 +12265,7 @@
         <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK73">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.79</v>
+        <v>3.55</v>
       </c>
       <c r="O74">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P74">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P78">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q78">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="R78">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U78">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V78">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W78">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z78">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA78">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB78">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC78">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AD78">
         <v>1.57</v>
       </c>
       <c r="AE78">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF78">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG78">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.21</v>
+        <v>2.17</v>
       </c>
       <c r="AK78">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13198,7 +13198,7 @@
         <v>14</v>
       </c>
       <c r="R79">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="S79">
         <v>1.14</v>
@@ -13225,7 +13225,7 @@
         <v>8</v>
       </c>
       <c r="AA79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB79">
         <v>3.34</v>
@@ -13234,16 +13234,16 @@
         <v>1.7</v>
       </c>
       <c r="AD79">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AE79">
         <v>1.42</v>
       </c>
       <c r="AF79">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG79">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>3.53</v>
+        <v>2.98</v>
       </c>
       <c r="R112">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S112">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U112">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V112">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W112">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z112">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA112">
+        <v>2.07</v>
+      </c>
+      <c r="AB112">
         <v>1.72</v>
       </c>
-      <c r="AB112">
-        <v>1.95</v>
-      </c>
       <c r="AC112">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="AD112">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF112">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AG112">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,80 +18728,80 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q113">
-        <v>2.98</v>
+        <v>3.53</v>
       </c>
       <c r="R113">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S113">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U113">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V113">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
+        <v>1.2</v>
+      </c>
+      <c r="Z113">
+        <v>3.7</v>
+      </c>
+      <c r="AA113">
+        <v>1.72</v>
+      </c>
+      <c r="AB113">
+        <v>1.95</v>
+      </c>
+      <c r="AC113">
+        <v>2.78</v>
+      </c>
+      <c r="AD113">
+        <v>1.34</v>
+      </c>
+      <c r="AE113">
+        <v>1.1</v>
+      </c>
+      <c r="AF113">
+        <v>1.59</v>
+      </c>
+      <c r="AG113">
+        <v>2.17</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
+        <v>1.22</v>
+      </c>
+      <c r="AK113">
         <v>1.32</v>
-      </c>
-      <c r="Z113">
-        <v>2.88</v>
-      </c>
-      <c r="AA113">
-        <v>2.07</v>
-      </c>
-      <c r="AB113">
-        <v>1.72</v>
-      </c>
-      <c r="AC113">
-        <v>3.82</v>
-      </c>
-      <c r="AD113">
-        <v>1.18</v>
-      </c>
-      <c r="AE113">
-        <v>1.02</v>
-      </c>
-      <c r="AF113">
-        <v>1.82</v>
-      </c>
-      <c r="AG113">
-        <v>1.85</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.3</v>
-      </c>
-      <c r="AK113">
-        <v>1.53</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.65</v>
+        <v>5.07</v>
       </c>
       <c r="O127">
-        <v>3.84</v>
+        <v>4.26</v>
       </c>
       <c r="P127">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q127">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R127">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T127">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U127">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V127">
         <v>1.5</v>
       </c>
       <c r="W127">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z127">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="AA127">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB127">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC127">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AD127">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE127">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF127">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG127">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK127">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>5.07</v>
+        <v>2.65</v>
       </c>
       <c r="O128">
-        <v>4.26</v>
+        <v>3.84</v>
       </c>
       <c r="P128">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="Q128">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R128">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S128">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T128">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U128">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V128">
         <v>1.5</v>
       </c>
       <c r="W128">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z128">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AA128">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB128">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC128">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AD128">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE128">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF128">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG128">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q142">
         <v>5.51</v>
@@ -23509,10 +23509,10 @@
         <v>1.08</v>
       </c>
       <c r="AF142">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG142">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.8</v>
+        <v>2.69</v>
       </c>
       <c r="O226">
-        <v>4.36</v>
+        <v>3.41</v>
       </c>
       <c r="P226">
-        <v>4.36</v>
+        <v>2.86</v>
       </c>
       <c r="Q226">
-        <v>2.08</v>
+        <v>3.68</v>
       </c>
       <c r="R226">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="S226">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T226">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="U226">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="V226">
+        <v>1.36</v>
+      </c>
+      <c r="W226">
+        <v>1.05</v>
+      </c>
+      <c r="X226">
+        <v>1.02</v>
+      </c>
+      <c r="Y226">
+        <v>1.32</v>
+      </c>
+      <c r="Z226">
+        <v>3.14</v>
+      </c>
+      <c r="AA226">
+        <v>2.02</v>
+      </c>
+      <c r="AB226">
+        <v>1.78</v>
+      </c>
+      <c r="AC226">
+        <v>3.34</v>
+      </c>
+      <c r="AD226">
+        <v>1.27</v>
+      </c>
+      <c r="AE226">
+        <v>1.06</v>
+      </c>
+      <c r="AF226">
         <v>1.75</v>
       </c>
-      <c r="W226">
-        <v>1.2</v>
-      </c>
-      <c r="X226">
-        <v>1.01</v>
-      </c>
-      <c r="Y226">
-        <v>1.08</v>
-      </c>
-      <c r="Z226">
-        <v>6.5</v>
-      </c>
-      <c r="AA226">
-        <v>1.44</v>
-      </c>
-      <c r="AB226">
-        <v>2.72</v>
-      </c>
-      <c r="AC226">
-        <v>2.15</v>
-      </c>
-      <c r="AD226">
-        <v>1.62</v>
-      </c>
-      <c r="AE226">
-        <v>1.28</v>
-      </c>
-      <c r="AF226">
-        <v>1.44</v>
-      </c>
       <c r="AG226">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK226">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="O227">
-        <v>3.41</v>
+        <v>3.62</v>
       </c>
       <c r="P227">
-        <v>2.86</v>
+        <v>3.23</v>
       </c>
       <c r="Q227">
-        <v>3.68</v>
+        <v>2.5</v>
       </c>
       <c r="R227">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S227">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T227">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="U227">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="V227">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W227">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X227">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z227">
-        <v>3.14</v>
+        <v>4.05</v>
       </c>
       <c r="AA227">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB227">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC227">
-        <v>3.34</v>
+        <v>2.68</v>
       </c>
       <c r="AD227">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE227">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF227">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG227">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK227">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="O229">
-        <v>3.62</v>
+        <v>4.36</v>
       </c>
       <c r="P229">
-        <v>3.23</v>
+        <v>4.36</v>
       </c>
       <c r="Q229">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="R229">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="S229">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T229">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U229">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="V229">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W229">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z229">
-        <v>4.05</v>
+        <v>6.5</v>
       </c>
       <c r="AA229">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AB229">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="AC229">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="AD229">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AE229">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AF229">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG229">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK229">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,80 +39103,80 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="O238">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P238">
-        <v>3.06</v>
+        <v>2.21</v>
       </c>
       <c r="Q238">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R238">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S238">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T238">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U238">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V238">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W238">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X238">
         <v>1.01</v>
       </c>
       <c r="Y238">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z238">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA238">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB238">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC238">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD238">
+        <v>1.25</v>
+      </c>
+      <c r="AE238">
+        <v>1.05</v>
+      </c>
+      <c r="AF238">
+        <v>1.74</v>
+      </c>
+      <c r="AG238">
+        <v>1.94</v>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ238">
         <v>1.22</v>
       </c>
-      <c r="AE238">
-        <v>1.04</v>
-      </c>
-      <c r="AF238">
-        <v>1.78</v>
-      </c>
-      <c r="AG238">
-        <v>1.89</v>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ238">
-        <v>1.29</v>
-      </c>
       <c r="AK238">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,25 +39266,25 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.98</v>
+        <v>1.65</v>
       </c>
       <c r="O239">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="P239">
-        <v>2.21</v>
+        <v>4.62</v>
       </c>
       <c r="Q239">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R239">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S239">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T239">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U239">
         <v>2.88</v>
@@ -39296,34 +39296,34 @@
         <v>1.08</v>
       </c>
       <c r="X239">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y239">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z239">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA239">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB239">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC239">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD239">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE239">
         <v>1.05</v>
       </c>
       <c r="AF239">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AG239">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK239">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="O240">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P240">
-        <v>4.62</v>
+        <v>3.06</v>
       </c>
       <c r="Q240">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R240">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="S240">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T240">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="U240">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V240">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W240">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X240">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z240">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA240">
         <v>2.05</v>
       </c>
       <c r="AB240">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC240">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD240">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE240">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF240">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AG240">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK240">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,65 +43015,65 @@
         </is>
       </c>
       <c r="N262">
-        <v>4.28</v>
+        <v>6.67</v>
       </c>
       <c r="O262">
-        <v>3.65</v>
+        <v>4.38</v>
       </c>
       <c r="P262">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="Q262">
-        <v>3.69</v>
+        <v>5.8</v>
       </c>
       <c r="R262">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="S262">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T262">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U262">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V262">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W262">
         <v>1.07</v>
       </c>
       <c r="X262">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y262">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z262">
-        <v>2.86</v>
+        <v>3.42</v>
       </c>
       <c r="AA262">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB262">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC262">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="AD262">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AE262">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF262">
+        <v>1.91</v>
+      </c>
+      <c r="AG262">
         <v>1.8</v>
       </c>
-      <c r="AG262">
-        <v>1.84</v>
-      </c>
       <c r="AH262" t="inlineStr">
         <is>
           <t>[]</t>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="AK262">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>6.67</v>
+        <v>4.28</v>
       </c>
       <c r="O263">
-        <v>4.38</v>
+        <v>3.65</v>
       </c>
       <c r="P263">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="Q263">
-        <v>5.8</v>
+        <v>3.69</v>
       </c>
       <c r="R263">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="S263">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T263">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="U263">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V263">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W263">
         <v>1.07</v>
       </c>
       <c r="X263">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y263">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="Z263">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="AA263">
+        <v>1.92</v>
+      </c>
+      <c r="AB263">
         <v>1.88</v>
       </c>
-      <c r="AB263">
-        <v>1.98</v>
-      </c>
       <c r="AC263">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="AD263">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE263">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF263">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG263">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
+        <v>1.77</v>
+      </c>
+      <c r="AK263">
         <v>1.2</v>
-      </c>
-      <c r="AK263">
-        <v>1.11</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q271">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G6">
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="Q9">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA9">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB9">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AC9">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="Q10">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
         <v>2.1</v>
@@ -1957,7 +1957,7 @@
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="U10">
         <v>2.76</v>
@@ -1966,28 +1966,28 @@
         <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA10">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC10">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AD10">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE10">
         <v>1.06</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="O11">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>2.3</v>
@@ -2120,16 +2120,16 @@
         <v>1.31</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="V11">
         <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2141,16 +2141,16 @@
         <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC11">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
         <v>1.07</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,10 +3252,10 @@
         <v>1.99</v>
       </c>
       <c r="Q18">
-        <v>4.33</v>
+        <v>4.64</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S18">
         <v>1.36</v>
@@ -3264,10 +3264,10 @@
         <v>2.88</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
         <v>1.08</v>
@@ -3282,10 +3282,10 @@
         <v>3.2</v>
       </c>
       <c r="AA18">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
         <v>3.34</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AK18">
         <v>1.2</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="O19">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="P19">
-        <v>3.94</v>
+        <v>2.82</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V19">
         <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="AA19">
+        <v>1.88</v>
+      </c>
+      <c r="AB19">
         <v>1.79</v>
       </c>
-      <c r="AB19">
-        <v>1.98</v>
-      </c>
       <c r="AC19">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD20">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.09</v>
+        <v>3.55</v>
       </c>
       <c r="O25">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Q25">
         <v>4.65</v>
@@ -4399,7 +4399,7 @@
         <v>2.05</v>
       </c>
       <c r="S25">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
         <v>2.75</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q28">
         <v>2.77</v>
@@ -4912,10 +4912,10 @@
         <v>2.83</v>
       </c>
       <c r="AA28">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AB28">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC28">
         <v>3.58</v>
@@ -4930,7 +4930,7 @@
         <v>1.84</v>
       </c>
       <c r="AG28">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="O43">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="Q43">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="R43">
         <v>1.97</v>
@@ -7336,46 +7336,46 @@
         <v>1.42</v>
       </c>
       <c r="T43">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="U43">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="V43">
+        <v>1.36</v>
+      </c>
+      <c r="W43">
+        <v>1.05</v>
+      </c>
+      <c r="X43">
+        <v>1.04</v>
+      </c>
+      <c r="Y43">
         <v>1.33</v>
       </c>
-      <c r="W43">
-        <v>1.04</v>
-      </c>
-      <c r="X43">
+      <c r="Z43">
+        <v>3.1</v>
+      </c>
+      <c r="AA43">
+        <v>2.02</v>
+      </c>
+      <c r="AB43">
+        <v>1.7</v>
+      </c>
+      <c r="AC43">
+        <v>3.42</v>
+      </c>
+      <c r="AD43">
+        <v>1.23</v>
+      </c>
+      <c r="AE43">
         <v>1.05</v>
       </c>
-      <c r="Y43">
-        <v>1.34</v>
-      </c>
-      <c r="Z43">
-        <v>2.88</v>
-      </c>
-      <c r="AA43">
-        <v>2.16</v>
-      </c>
-      <c r="AB43">
-        <v>1.64</v>
-      </c>
-      <c r="AC43">
-        <v>3.82</v>
-      </c>
-      <c r="AD43">
-        <v>1.18</v>
-      </c>
-      <c r="AE43">
-        <v>1.03</v>
-      </c>
       <c r="AF43">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AK43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -10089,25 +10089,25 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P60">
         <v>2.62</v>
       </c>
       <c r="Q60">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="R60">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U60">
         <v>2.12</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK60">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -11106,7 +11106,7 @@
         <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB66">
         <v>1.85</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>4.75</v>
+        <v>5.7</v>
       </c>
       <c r="O83">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P83">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="Q83">
         <v>5.92</v>
@@ -13856,7 +13856,7 @@
         <v>1.14</v>
       </c>
       <c r="T83">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U83">
         <v>1.83</v>
@@ -13889,7 +13889,7 @@
         <v>2.11</v>
       </c>
       <c r="AE83">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AF83">
         <v>1.4</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="O92">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>4.45</v>
+        <v>3.68</v>
       </c>
       <c r="Q92">
         <v>2.11</v>
@@ -15323,40 +15323,40 @@
         <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U92">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="V92">
         <v>1.57</v>
       </c>
       <c r="W92">
+        <v>1.13</v>
+      </c>
+      <c r="X92">
+        <v>1.03</v>
+      </c>
+      <c r="Y92">
         <v>1.15</v>
       </c>
-      <c r="X92">
-        <v>1.02</v>
-      </c>
-      <c r="Y92">
-        <v>1.17</v>
-      </c>
       <c r="Z92">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA92">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB92">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AC92">
         <v>2.42</v>
       </c>
       <c r="AD92">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE92">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF92">
         <v>1.53</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK92">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17587,31 +17587,31 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="O106">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="P106">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q106">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R106">
         <v>2.2</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U106">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V106">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
         <v>1.09</v>
@@ -17620,16 +17620,16 @@
         <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA106">
         <v>1.81</v>
       </c>
       <c r="AB106">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC106">
         <v>2.85</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK106">
         <v>1.25</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,80 +18565,80 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>2.98</v>
+        <v>3.53</v>
       </c>
       <c r="R112">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U112">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V112">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
+        <v>1.2</v>
+      </c>
+      <c r="Z112">
+        <v>3.7</v>
+      </c>
+      <c r="AA112">
+        <v>1.72</v>
+      </c>
+      <c r="AB112">
+        <v>1.95</v>
+      </c>
+      <c r="AC112">
+        <v>2.78</v>
+      </c>
+      <c r="AD112">
+        <v>1.34</v>
+      </c>
+      <c r="AE112">
+        <v>1.1</v>
+      </c>
+      <c r="AF112">
+        <v>1.59</v>
+      </c>
+      <c r="AG112">
+        <v>2.17</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>1.22</v>
+      </c>
+      <c r="AK112">
         <v>1.32</v>
-      </c>
-      <c r="Z112">
-        <v>2.88</v>
-      </c>
-      <c r="AA112">
-        <v>2.07</v>
-      </c>
-      <c r="AB112">
-        <v>1.72</v>
-      </c>
-      <c r="AC112">
-        <v>3.82</v>
-      </c>
-      <c r="AD112">
-        <v>1.18</v>
-      </c>
-      <c r="AE112">
-        <v>1.02</v>
-      </c>
-      <c r="AF112">
-        <v>1.82</v>
-      </c>
-      <c r="AG112">
-        <v>1.85</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.3</v>
-      </c>
-      <c r="AK112">
-        <v>1.53</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>3.53</v>
+        <v>2.98</v>
       </c>
       <c r="R113">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S113">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T113">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U113">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V113">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA113">
+        <v>2.07</v>
+      </c>
+      <c r="AB113">
         <v>1.72</v>
       </c>
-      <c r="AB113">
-        <v>1.95</v>
-      </c>
       <c r="AC113">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="AD113">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF113">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AG113">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O114">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P114">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q114">
         <v>2.08</v>
@@ -18906,10 +18906,10 @@
         <v>2.49</v>
       </c>
       <c r="S114">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T114">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="U114">
         <v>2.5</v>
@@ -18927,13 +18927,13 @@
         <v>1.16</v>
       </c>
       <c r="Z114">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA114">
         <v>1.61</v>
       </c>
       <c r="AB114">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC114">
         <v>2.46</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="O115">
-        <v>4.46</v>
+        <v>4.33</v>
       </c>
       <c r="P115">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="Q115">
         <v>1.92</v>
@@ -19087,16 +19087,16 @@
         <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z115">
         <v>5.5</v>
       </c>
       <c r="AA115">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB115">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC115">
         <v>2.19</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="O118">
-        <v>4.18</v>
+        <v>4.05</v>
       </c>
       <c r="P118">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="Q118">
         <v>2.35</v>
@@ -19564,10 +19564,10 @@
         <v>5.2</v>
       </c>
       <c r="U118">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="V118">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="W118">
         <v>1.25</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O119">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P119">
-        <v>3.23</v>
+        <v>2.72</v>
       </c>
       <c r="Q119">
         <v>2.65</v>
@@ -19721,19 +19721,19 @@
         <v>2.46</v>
       </c>
       <c r="S119">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T119">
         <v>4</v>
       </c>
       <c r="U119">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V119">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W119">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X119">
         <v>1.02</v>
@@ -19748,13 +19748,13 @@
         <v>1.4</v>
       </c>
       <c r="AB119">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC119">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AD119">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE119">
         <v>1.33</v>
@@ -19779,7 +19779,7 @@
         <v>1.21</v>
       </c>
       <c r="AK119">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,22 +19869,22 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="O120">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="P120">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q120">
         <v>1.48</v>
       </c>
       <c r="R120">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="S120">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T120">
         <v>5</v>
@@ -19914,7 +19914,7 @@
         <v>4.1</v>
       </c>
       <c r="AC120">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AD120">
         <v>2.26</v>
@@ -19923,10 +19923,10 @@
         <v>1.57</v>
       </c>
       <c r="AF120">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG120">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK120">
         <v>4</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="O121">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P121">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="Q121">
         <v>2.7</v>
@@ -20068,19 +20068,19 @@
         <v>1.13</v>
       </c>
       <c r="Z121">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA121">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB121">
         <v>2.5</v>
       </c>
       <c r="AC121">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AD121">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE121">
         <v>1.22</v>
@@ -20204,7 +20204,7 @@
         <v>3.05</v>
       </c>
       <c r="Q122">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R122">
         <v>2</v>
@@ -20216,13 +20216,13 @@
         <v>2.65</v>
       </c>
       <c r="U122">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="V122">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X122">
         <v>1.03</v>
@@ -20234,7 +20234,7 @@
         <v>2.83</v>
       </c>
       <c r="AA122">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB122">
         <v>1.65</v>
@@ -20252,7 +20252,7 @@
         <v>1.82</v>
       </c>
       <c r="AG122">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK122">
         <v>1.52</v>
@@ -21345,55 +21345,55 @@
         <v>2.63</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -23292,52 +23292,52 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="O141">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P141">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q141">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R141">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S141">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T141">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="U141">
         <v>2.6</v>
       </c>
       <c r="V141">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W141">
         <v>1.04</v>
       </c>
       <c r="X141">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z141">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA141">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB141">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC141">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD141">
         <v>1.3</v>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK141">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23497,7 +23497,7 @@
         <v>1.8</v>
       </c>
       <c r="AB142">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC142">
         <v>2.92</v>
@@ -23509,10 +23509,10 @@
         <v>1.08</v>
       </c>
       <c r="AF142">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG142">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.17</v>
+        <v>2.16</v>
       </c>
       <c r="AK142">
         <v>1.09</v>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O143">
         <v>5.42</v>
@@ -23627,10 +23627,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q143">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="R143">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S143">
         <v>1.29</v>
@@ -23691,7 +23691,7 @@
         <v>1.13</v>
       </c>
       <c r="AK143">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23781,19 +23781,19 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="O144">
-        <v>3.55</v>
+        <v>3.37</v>
       </c>
       <c r="P144">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="Q144">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R144">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S144">
         <v>1.39</v>
@@ -23802,10 +23802,10 @@
         <v>2.86</v>
       </c>
       <c r="U144">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="V144">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W144">
         <v>1.08</v>
@@ -23820,10 +23820,10 @@
         <v>3.44</v>
       </c>
       <c r="AA144">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB144">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC144">
         <v>3</v>
@@ -23832,13 +23832,13 @@
         <v>1.32</v>
       </c>
       <c r="AE144">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF144">
         <v>1.75</v>
       </c>
       <c r="AG144">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="O145">
-        <v>4.53</v>
+        <v>4.3</v>
       </c>
       <c r="P145">
-        <v>5.04</v>
+        <v>3.9</v>
       </c>
       <c r="Q145">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="R145">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="S145">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T145">
         <v>4.5</v>
       </c>
       <c r="U145">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="V145">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W145">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X145">
         <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z145">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="AA145">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB145">
         <v>2.88</v>
       </c>
       <c r="AC145">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AD145">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AE145">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF145">
         <v>1.4</v>
       </c>
       <c r="AG145">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="O148">
-        <v>4.31</v>
+        <v>3.9</v>
       </c>
       <c r="P148">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q148">
         <v>2.85</v>
@@ -24472,13 +24472,13 @@
         <v>6.55</v>
       </c>
       <c r="AA148">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB148">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="AC148">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="AD148">
         <v>1.88</v>
@@ -24487,10 +24487,10 @@
         <v>1.33</v>
       </c>
       <c r="AF148">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AG148">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>1.25</v>
       </c>
       <c r="AK148">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -27702,55 +27702,55 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -30473,19 +30473,19 @@
         <v>1.41</v>
       </c>
       <c r="Q185">
-        <v>6.5</v>
+        <v>7.47</v>
       </c>
       <c r="R185">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S185">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T185">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U185">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V185">
         <v>1.5</v>
@@ -30497,31 +30497,31 @@
         <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z185">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA185">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB185">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AC185">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AD185">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE185">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF185">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AG185">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK185">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30627,22 +30627,22 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O186">
-        <v>5.51</v>
+        <v>5.75</v>
       </c>
       <c r="P186">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="Q186">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="R186">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="S186">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T186">
         <v>4.5</v>
@@ -30651,7 +30651,7 @@
         <v>1.85</v>
       </c>
       <c r="V186">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="W186">
         <v>1.22</v>
@@ -30675,10 +30675,10 @@
         <v>1.92</v>
       </c>
       <c r="AD186">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AE186">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF186">
         <v>1.55</v>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK186">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -32755,55 +32755,55 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T199">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V199">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W199">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X199">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z199">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC199">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD199">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG199">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK199">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>6.84</v>
+        <v>4.8</v>
       </c>
       <c r="O202">
-        <v>5.33</v>
+        <v>4.65</v>
       </c>
       <c r="P202">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="Q202">
         <v>4.03</v>
@@ -33274,16 +33274,16 @@
         <v>7</v>
       </c>
       <c r="AA202">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB202">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC202">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD202">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE202">
         <v>1.33</v>
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK202">
         <v>1.13</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="O203">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P203">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q203">
         <v>2.38</v>
@@ -33416,7 +33416,7 @@
         <v>1.25</v>
       </c>
       <c r="T203">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U203">
         <v>2.25</v>
@@ -33428,7 +33428,7 @@
         <v>1.15</v>
       </c>
       <c r="X203">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y203">
         <v>1.17</v>
@@ -33440,7 +33440,7 @@
         <v>1.57</v>
       </c>
       <c r="AB203">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AC203">
         <v>2.41</v>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="O206">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="P206">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q206">
         <v>2.59</v>
@@ -33908,7 +33908,7 @@
         <v>3.38</v>
       </c>
       <c r="U206">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V206">
         <v>1.53</v>
@@ -33917,7 +33917,7 @@
         <v>1.08</v>
       </c>
       <c r="X206">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
         <v>1.15</v>
@@ -33932,7 +33932,7 @@
         <v>2.22</v>
       </c>
       <c r="AC206">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD206">
         <v>1.48</v>
@@ -33960,7 +33960,7 @@
         <v>1.26</v>
       </c>
       <c r="AK206">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="O207">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P207">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="Q207">
         <v>2.88</v>
@@ -34068,7 +34068,7 @@
         <v>1.3</v>
       </c>
       <c r="T207">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U207">
         <v>2.38</v>
@@ -34089,19 +34089,19 @@
         <v>3.8</v>
       </c>
       <c r="AA207">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB207">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AC207">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AD207">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE207">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF207">
         <v>1.57</v>
@@ -34120,7 +34120,7 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK207">
         <v>1.57</v>
@@ -34213,25 +34213,25 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O208">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="P208">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="Q208">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R208">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="S208">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T208">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U208">
         <v>2.04</v>
@@ -34258,7 +34258,7 @@
         <v>2.83</v>
       </c>
       <c r="AC208">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD208">
         <v>1.83</v>
@@ -34267,7 +34267,7 @@
         <v>1.31</v>
       </c>
       <c r="AF208">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG208">
         <v>2.8</v>
@@ -34376,19 +34376,19 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O209">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="P209">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="Q209">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="R209">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="S209">
         <v>1.2</v>
@@ -34418,7 +34418,7 @@
         <v>1.39</v>
       </c>
       <c r="AB209">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC209">
         <v>2.07</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK209">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -35852,55 +35852,55 @@
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36169,19 +36169,19 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="O220">
-        <v>4.29</v>
+        <v>4.15</v>
       </c>
       <c r="P220">
-        <v>3.95</v>
+        <v>4.55</v>
       </c>
       <c r="Q220">
         <v>2.02</v>
       </c>
       <c r="R220">
-        <v>2.51</v>
+        <v>2.87</v>
       </c>
       <c r="S220">
         <v>1.17</v>
@@ -36193,10 +36193,10 @@
         <v>1.85</v>
       </c>
       <c r="V220">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W220">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X220">
         <v>1.01</v>
@@ -36211,13 +36211,13 @@
         <v>1.33</v>
       </c>
       <c r="AB220">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC220">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AD220">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AE220">
         <v>1.36</v>
@@ -36332,19 +36332,19 @@
         </is>
       </c>
       <c r="N221">
-        <v>3.83</v>
+        <v>4.23</v>
       </c>
       <c r="O221">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="P221">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
       </c>
       <c r="R221">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="S221">
         <v>1.15</v>
@@ -36353,37 +36353,37 @@
         <v>5</v>
       </c>
       <c r="U221">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V221">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="W221">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X221">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y221">
         <v>1.03</v>
       </c>
       <c r="Z221">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA221">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AB221">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AC221">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AD221">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AE221">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AF221">
         <v>1.25</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O222">
-        <v>4.21</v>
+        <v>3.85</v>
       </c>
       <c r="P222">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -36510,10 +36510,10 @@
         <v>2.7</v>
       </c>
       <c r="S222">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T222">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="U222">
         <v>1.73</v>
@@ -36537,7 +36537,7 @@
         <v>1.25</v>
       </c>
       <c r="AB222">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC222">
         <v>1.73</v>
@@ -36546,7 +36546,7 @@
         <v>2.02</v>
       </c>
       <c r="AE222">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AF222">
         <v>1.3</v>
@@ -36658,19 +36658,19 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="O223">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="P223">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="Q223">
         <v>2.18</v>
       </c>
       <c r="R223">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S223">
         <v>1.22</v>
@@ -36679,10 +36679,10 @@
         <v>3.75</v>
       </c>
       <c r="U223">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V223">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W223">
         <v>1.14</v>
@@ -36697,16 +36697,16 @@
         <v>5</v>
       </c>
       <c r="AA223">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB223">
         <v>2.31</v>
       </c>
       <c r="AC223">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AD223">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE223">
         <v>1.24</v>
@@ -36863,7 +36863,7 @@
         <v>1.61</v>
       </c>
       <c r="AB224">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC224">
         <v>2.46</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.69</v>
+        <v>1.6</v>
       </c>
       <c r="O226">
-        <v>3.41</v>
+        <v>4.42</v>
       </c>
       <c r="P226">
-        <v>2.86</v>
+        <v>6.06</v>
       </c>
       <c r="Q226">
-        <v>3.68</v>
+        <v>2.04</v>
       </c>
       <c r="R226">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S226">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T226">
-        <v>2.72</v>
+        <v>3.84</v>
       </c>
       <c r="U226">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="V226">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="W226">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X226">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z226">
-        <v>3.14</v>
+        <v>4.75</v>
       </c>
       <c r="AA226">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AB226">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC226">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD226">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AE226">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF226">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG226">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK226">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="O228">
-        <v>4.42</v>
+        <v>3.41</v>
       </c>
       <c r="P228">
-        <v>6.06</v>
+        <v>2.86</v>
       </c>
       <c r="Q228">
-        <v>2.04</v>
+        <v>3.68</v>
       </c>
       <c r="R228">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S228">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T228">
-        <v>3.84</v>
+        <v>2.72</v>
       </c>
       <c r="U228">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="V228">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="W228">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X228">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z228">
-        <v>4.75</v>
+        <v>3.14</v>
       </c>
       <c r="AA228">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AB228">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC228">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD228">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AE228">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF228">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG228">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK228">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37971,55 +37971,55 @@
         <v>15.5</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q235">
         <v>2.48</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,25 +39103,25 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.98</v>
+        <v>1.65</v>
       </c>
       <c r="O238">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="P238">
-        <v>2.21</v>
+        <v>4.62</v>
       </c>
       <c r="Q238">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R238">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S238">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T238">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U238">
         <v>2.88</v>
@@ -39133,34 +39133,34 @@
         <v>1.08</v>
       </c>
       <c r="X238">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y238">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z238">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA238">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB238">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC238">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD238">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE238">
         <v>1.05</v>
       </c>
       <c r="AF238">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AG238">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK238">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="O239">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P239">
-        <v>4.62</v>
+        <v>3.06</v>
       </c>
       <c r="Q239">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R239">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="S239">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T239">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="U239">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V239">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W239">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X239">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y239">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z239">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA239">
         <v>2.05</v>
       </c>
       <c r="AB239">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC239">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD239">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE239">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF239">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AG239">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK239">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,80 +39429,80 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="O240">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P240">
-        <v>3.06</v>
+        <v>2.21</v>
       </c>
       <c r="Q240">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R240">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S240">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T240">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U240">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V240">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W240">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X240">
         <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z240">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA240">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB240">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC240">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD240">
+        <v>1.25</v>
+      </c>
+      <c r="AE240">
+        <v>1.05</v>
+      </c>
+      <c r="AF240">
+        <v>1.74</v>
+      </c>
+      <c r="AG240">
+        <v>1.94</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ240">
         <v>1.22</v>
       </c>
-      <c r="AE240">
-        <v>1.04</v>
-      </c>
-      <c r="AF240">
-        <v>1.78</v>
-      </c>
-      <c r="AG240">
-        <v>1.89</v>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ240">
-        <v>1.29</v>
-      </c>
       <c r="AK240">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -44491,55 +44491,55 @@
         <v>3.78</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL271">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -4441,7 +4441,7 @@
         <v>1.88</v>
       </c>
       <c r="AG25">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5531,37 +5531,37 @@
         <v>3.6</v>
       </c>
       <c r="P32">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="Q32">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
         <v>2.44</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
         <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AA32">
         <v>1.71</v>
@@ -5573,7 +5573,7 @@
         <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
         <v>1.11</v>
@@ -5688,37 +5688,37 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O33">
         <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U33">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
         <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y33">
         <v>1.22</v>
@@ -5733,10 +5733,10 @@
         <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE33">
         <v>1.08</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="O35">
         <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q35">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="R35">
         <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U35">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6056,13 +6056,13 @@
         <v>2.19</v>
       </c>
       <c r="AB35">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AC35">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE35">
         <v>1.04</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK35">
         <v>1.67</v>
@@ -6186,25 +6186,25 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>4.18</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S36">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T36">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="U36">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="V36">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>1.04</v>
@@ -6234,7 +6234,7 @@
         <v>1.96</v>
       </c>
       <c r="AG36">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6355,10 +6355,10 @@
         <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U37">
         <v>2.88</v>
@@ -6376,16 +6376,16 @@
         <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="AA37">
         <v>2.01</v>
       </c>
       <c r="AB37">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC37">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AD37">
         <v>1.21</v>
@@ -6397,7 +6397,7 @@
         <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -7330,13 +7330,13 @@
         <v>4.2</v>
       </c>
       <c r="R43">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S43">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="U43">
         <v>2.82</v>
@@ -7351,7 +7351,7 @@
         <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
         <v>3.1</v>
@@ -7363,13 +7363,13 @@
         <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD43">
         <v>1.23</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
         <v>1.85</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>3.5</v>
       </c>
       <c r="AA57">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB57">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC57">
         <v>3</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9944,7 +9944,7 @@
         <v>1.24</v>
       </c>
       <c r="T59">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="U59">
         <v>2.2</v>
@@ -9971,7 +9971,7 @@
         <v>2.33</v>
       </c>
       <c r="AC59">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="AD59">
         <v>1.6</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
         <v>1.4</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O60">
         <v>3.68</v>
@@ -10107,10 +10107,10 @@
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U60">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V60">
         <v>1.6</v>
@@ -10122,10 +10122,10 @@
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA60">
         <v>1.48</v>
@@ -10134,19 +10134,19 @@
         <v>2.33</v>
       </c>
       <c r="AC60">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AD60">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AE60">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF60">
         <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>4</v>
       </c>
       <c r="O63">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
         <v>1.85</v>
@@ -11073,28 +11073,28 @@
         <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U66">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="V66">
         <v>1.36</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11106,10 +11106,10 @@
         <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC66">
         <v>3.34</v>
@@ -11124,7 +11124,7 @@
         <v>1.73</v>
       </c>
       <c r="AG66">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,22 +11239,22 @@
         <v>5.25</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R67">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S67">
+        <v>1.33</v>
+      </c>
+      <c r="T67">
+        <v>2.83</v>
+      </c>
+      <c r="U67">
+        <v>2.72</v>
+      </c>
+      <c r="V67">
         <v>1.36</v>
-      </c>
-      <c r="T67">
-        <v>2.88</v>
-      </c>
-      <c r="U67">
-        <v>2.75</v>
-      </c>
-      <c r="V67">
-        <v>1.4</v>
       </c>
       <c r="W67">
         <v>1.04</v>
@@ -11272,7 +11272,7 @@
         <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC67">
         <v>3.14</v>
@@ -11287,7 +11287,7 @@
         <v>1.91</v>
       </c>
       <c r="AG67">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK67">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11408,16 +11408,16 @@
         <v>2.56</v>
       </c>
       <c r="S68">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T68">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
         <v>2.2</v>
       </c>
       <c r="V68">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="W68">
         <v>1.17</v>
@@ -11429,7 +11429,7 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA68">
         <v>1.4</v>
@@ -11438,19 +11438,19 @@
         <v>2.66</v>
       </c>
       <c r="AC68">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AD68">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE68">
         <v>1.27</v>
       </c>
       <c r="AF68">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12386,25 +12386,25 @@
         <v>2.33</v>
       </c>
       <c r="S74">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U74">
         <v>2.25</v>
       </c>
       <c r="V74">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W74">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X74">
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z74">
         <v>4.5</v>
@@ -12425,7 +12425,7 @@
         <v>1.16</v>
       </c>
       <c r="AF74">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG74">
         <v>2.3</v>
@@ -12444,7 +12444,7 @@
         <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13032,10 +13032,10 @@
         <v>1.68</v>
       </c>
       <c r="Q78">
-        <v>4.45</v>
+        <v>3.79</v>
       </c>
       <c r="R78">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S78">
         <v>1.22</v>
@@ -13053,13 +13053,13 @@
         <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z78">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA78">
         <v>1.47</v>
@@ -13096,7 +13096,7 @@
         <v>2.17</v>
       </c>
       <c r="AK78">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14176,22 +14176,22 @@
         <v>2.69</v>
       </c>
       <c r="R85">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="S85">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U85">
         <v>1.91</v>
       </c>
       <c r="V85">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W85">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X85">
         <v>1.01</v>
@@ -14206,13 +14206,13 @@
         <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AC85">
         <v>1.86</v>
       </c>
       <c r="AD85">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AE85">
         <v>1.32</v>
@@ -14333,10 +14333,10 @@
         <v>4.33</v>
       </c>
       <c r="P86">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q86">
-        <v>4.44</v>
+        <v>3.95</v>
       </c>
       <c r="R86">
         <v>2.54</v>
@@ -14345,7 +14345,7 @@
         <v>1.2</v>
       </c>
       <c r="T86">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U86">
         <v>2.1</v>
@@ -14366,19 +14366,19 @@
         <v>6.17</v>
       </c>
       <c r="AA86">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AB86">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="AC86">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AD86">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AE86">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
         <v>1.44</v>
@@ -14499,7 +14499,7 @@
         <v>2.75</v>
       </c>
       <c r="Q87">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R87">
         <v>2.4</v>
@@ -14680,7 +14680,7 @@
         <v>1.67</v>
       </c>
       <c r="W88">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.02</v>
@@ -14698,7 +14698,7 @@
         <v>2.62</v>
       </c>
       <c r="AC88">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="AD88">
         <v>1.7</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AK88">
         <v>1.4</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O89">
         <v>3.78</v>
@@ -14837,13 +14837,13 @@
         <v>3.38</v>
       </c>
       <c r="U89">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W89">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
         <v>1.02</v>
@@ -14867,7 +14867,7 @@
         <v>1.47</v>
       </c>
       <c r="AE89">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF89">
         <v>1.49</v>
@@ -14988,22 +14988,22 @@
         <v>2.5</v>
       </c>
       <c r="Q90">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="R90">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S90">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U90">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="V90">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W90">
         <v>1.14</v>
@@ -15012,22 +15012,22 @@
         <v>1</v>
       </c>
       <c r="Y90">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA90">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB90">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC90">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AD90">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE90">
         <v>1.19</v>
@@ -15036,7 +15036,7 @@
         <v>1.44</v>
       </c>
       <c r="AG90">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>3.68</v>
       </c>
       <c r="Q92">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="R92">
         <v>2.38</v>
@@ -15350,13 +15350,13 @@
         <v>2.28</v>
       </c>
       <c r="AC92">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AD92">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE92">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF92">
         <v>1.53</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK92">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15637,7 +15637,7 @@
         <v>3.5</v>
       </c>
       <c r="P94">
-        <v>4.18</v>
+        <v>3.95</v>
       </c>
       <c r="Q94">
         <v>2.43</v>
@@ -15664,13 +15664,13 @@
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z94">
         <v>3.08</v>
       </c>
       <c r="AA94">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB94">
         <v>1.8</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15827,10 +15827,10 @@
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AA95">
         <v>1.33</v>
@@ -15845,13 +15845,13 @@
         <v>1.79</v>
       </c>
       <c r="AE95">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF95">
         <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15972,13 +15972,13 @@
         <v>1.97</v>
       </c>
       <c r="S96">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T96">
         <v>2.69</v>
       </c>
       <c r="U96">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="V96">
         <v>1.33</v>
@@ -15990,10 +15990,10 @@
         <v>1.04</v>
       </c>
       <c r="Y96">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z96">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AA96">
         <v>2.19</v>
@@ -16002,10 +16002,10 @@
         <v>1.65</v>
       </c>
       <c r="AC96">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="AD96">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE96">
         <v>1.03</v>
@@ -16286,7 +16286,7 @@
         <v>1.85</v>
       </c>
       <c r="O98">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P98">
         <v>4.05</v>
@@ -16304,13 +16304,13 @@
         <v>2.38</v>
       </c>
       <c r="U98">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="V98">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W98">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
         <v>1.04</v>
@@ -16319,13 +16319,13 @@
         <v>1.41</v>
       </c>
       <c r="Z98">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="AA98">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="AB98">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AC98">
         <v>4.65</v>
@@ -16334,7 +16334,7 @@
         <v>1.12</v>
       </c>
       <c r="AE98">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF98">
         <v>2.14</v>
@@ -16449,7 +16449,7 @@
         <v>1.48</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P99">
         <v>5.75</v>
@@ -16476,7 +16476,7 @@
         <v>1.05</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y99">
         <v>1.38</v>
@@ -16485,16 +16485,16 @@
         <v>2.76</v>
       </c>
       <c r="AA99">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AB99">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AC99">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AD99">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE99">
         <v>1.01</v>
@@ -16615,25 +16615,25 @@
         <v>3.51</v>
       </c>
       <c r="P100">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
       </c>
       <c r="R100">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S100">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U100">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V100">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W100">
         <v>1.06</v>
@@ -16648,10 +16648,10 @@
         <v>3.8</v>
       </c>
       <c r="AA100">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB100">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC100">
         <v>2.74</v>
@@ -16666,7 +16666,7 @@
         <v>1.62</v>
       </c>
       <c r="AG100">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="O101">
-        <v>3.61</v>
+        <v>3.27</v>
       </c>
       <c r="P101">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="Q101">
         <v>3.55</v>
@@ -16793,10 +16793,10 @@
         <v>3.32</v>
       </c>
       <c r="U101">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="V101">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W101">
         <v>1.12</v>
@@ -16959,19 +16959,19 @@
         <v>2.71</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W102">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z102">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="AA102">
         <v>1.86</v>
@@ -16989,7 +16989,7 @@
         <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG102">
         <v>1.92</v>
@@ -17008,7 +17008,7 @@
         <v>1.15</v>
       </c>
       <c r="AK102">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -18417,13 +18417,13 @@
         <v>1.99</v>
       </c>
       <c r="S111">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T111">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="U111">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="V111">
         <v>1.3</v>
@@ -18441,10 +18441,10 @@
         <v>2.81</v>
       </c>
       <c r="AA111">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB111">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC111">
         <v>3.7</v>
@@ -18459,7 +18459,7 @@
         <v>1.83</v>
       </c>
       <c r="AG111">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18574,16 +18574,16 @@
         <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="R112">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
         <v>1.28</v>
       </c>
       <c r="T112">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U112">
         <v>2.63</v>
@@ -18592,10 +18592,10 @@
         <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y112">
         <v>1.2</v>
@@ -18607,7 +18607,7 @@
         <v>1.72</v>
       </c>
       <c r="AB112">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC112">
         <v>2.78</v>
@@ -18622,7 +18622,7 @@
         <v>1.59</v>
       </c>
       <c r="AG112">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18737,16 +18737,16 @@
         <v>0</v>
       </c>
       <c r="Q113">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R113">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S113">
         <v>1.4</v>
       </c>
       <c r="T113">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U113">
         <v>3</v>
@@ -18755,7 +18755,7 @@
         <v>1.33</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X113">
         <v>1.01</v>
@@ -18767,7 +18767,7 @@
         <v>2.88</v>
       </c>
       <c r="AA113">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB113">
         <v>1.72</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK113">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18900,10 +18900,10 @@
         <v>4.1</v>
       </c>
       <c r="Q114">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R114">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="S114">
         <v>1.24</v>
@@ -18948,7 +18948,7 @@
         <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>1.2</v>
       </c>
       <c r="T115">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U115">
         <v>2.1</v>
@@ -19090,13 +19090,13 @@
         <v>1.11</v>
       </c>
       <c r="Z115">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA115">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB115">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AC115">
         <v>2.19</v>
@@ -19105,7 +19105,7 @@
         <v>1.7</v>
       </c>
       <c r="AE115">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF115">
         <v>1.55</v>
@@ -19386,7 +19386,7 @@
         <v>3.8</v>
       </c>
       <c r="P117">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -19425,7 +19425,7 @@
         <v>2.35</v>
       </c>
       <c r="AC117">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD117">
         <v>1.59</v>
@@ -19434,10 +19434,10 @@
         <v>1.19</v>
       </c>
       <c r="AF117">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG117">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19546,10 +19546,10 @@
         <v>1.98</v>
       </c>
       <c r="O118">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P118">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q118">
         <v>2.35</v>
@@ -19558,7 +19558,7 @@
         <v>2.62</v>
       </c>
       <c r="S118">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T118">
         <v>5.2</v>
@@ -19570,7 +19570,7 @@
         <v>2.01</v>
       </c>
       <c r="W118">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X118">
         <v>1.01</v>
@@ -19585,13 +19585,13 @@
         <v>1.24</v>
       </c>
       <c r="AB118">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AC118">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AD118">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AE118">
         <v>1.42</v>
@@ -19600,7 +19600,7 @@
         <v>1.3</v>
       </c>
       <c r="AG118">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>1.2</v>
       </c>
       <c r="AK118">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20204,7 +20204,7 @@
         <v>3.05</v>
       </c>
       <c r="Q122">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R122">
         <v>2</v>
@@ -20216,13 +20216,13 @@
         <v>2.65</v>
       </c>
       <c r="U122">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="V122">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W122">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
         <v>1.03</v>
@@ -20252,7 +20252,7 @@
         <v>1.82</v>
       </c>
       <c r="AG122">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
         <v>1.52</v>
@@ -20373,10 +20373,10 @@
         <v>2.3</v>
       </c>
       <c r="S123">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U123">
         <v>2.29</v>
@@ -20542,10 +20542,10 @@
         <v>3.7</v>
       </c>
       <c r="U124">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="V124">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W124">
         <v>1.13</v>
@@ -20554,7 +20554,7 @@
         <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z124">
         <v>5</v>
@@ -20566,7 +20566,7 @@
         <v>2.47</v>
       </c>
       <c r="AC124">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="AD124">
         <v>1.61</v>
@@ -20702,7 +20702,7 @@
         <v>1.27</v>
       </c>
       <c r="T125">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U125">
         <v>2.35</v>
@@ -20720,28 +20720,28 @@
         <v>1.14</v>
       </c>
       <c r="Z125">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA125">
         <v>1.5</v>
       </c>
       <c r="AB125">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AC125">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AD125">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE125">
         <v>1.19</v>
       </c>
       <c r="AF125">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG125">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK125">
         <v>1.75</v>
@@ -20856,25 +20856,25 @@
         <v>3.37</v>
       </c>
       <c r="Q126">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="R126">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="S126">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T126">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U126">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="V126">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W126">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X126">
         <v>1.01</v>
@@ -20883,28 +20883,28 @@
         <v>1.15</v>
       </c>
       <c r="Z126">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA126">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB126">
         <v>2.4</v>
       </c>
       <c r="AC126">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AD126">
         <v>1.55</v>
       </c>
       <c r="AE126">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF126">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG126">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK126">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21022,7 +21022,7 @@
         <v>4.75</v>
       </c>
       <c r="R127">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S127">
         <v>1.25</v>
@@ -21031,7 +21031,7 @@
         <v>3.6</v>
       </c>
       <c r="U127">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V127">
         <v>1.51</v>
@@ -21061,7 +21061,7 @@
         <v>1.44</v>
       </c>
       <c r="AE127">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF127">
         <v>1.6</v>
@@ -21188,10 +21188,10 @@
         <v>2.46</v>
       </c>
       <c r="S128">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T128">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U128">
         <v>2.4</v>
@@ -21203,7 +21203,7 @@
         <v>1.1</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
         <v>1.15</v>
@@ -21215,7 +21215,7 @@
         <v>1.69</v>
       </c>
       <c r="AB128">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AC128">
         <v>2.43</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK128">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21532,7 +21532,7 @@
         <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z130">
         <v>4.11</v>
@@ -21541,10 +21541,10 @@
         <v>1.76</v>
       </c>
       <c r="AB130">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC130">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="AD130">
         <v>1.37</v>
@@ -21677,10 +21677,10 @@
         <v>1.91</v>
       </c>
       <c r="S131">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T131">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U131">
         <v>3.6</v>
@@ -21692,7 +21692,7 @@
         <v>1.03</v>
       </c>
       <c r="X131">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y131">
         <v>1.42</v>
@@ -21701,7 +21701,7 @@
         <v>2.49</v>
       </c>
       <c r="AA131">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AB131">
         <v>1.52</v>
@@ -21716,7 +21716,7 @@
         <v>1.02</v>
       </c>
       <c r="AF131">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG131">
         <v>1.75</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK131">
         <v>1.47</v>
@@ -21834,10 +21834,10 @@
         <v>7.5</v>
       </c>
       <c r="Q132">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R132">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="S132">
         <v>1.2</v>
@@ -21846,10 +21846,10 @@
         <v>4</v>
       </c>
       <c r="U132">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V132">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W132">
         <v>1.13</v>
@@ -21858,31 +21858,31 @@
         <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z132">
         <v>5.4</v>
       </c>
       <c r="AA132">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB132">
         <v>2.52</v>
       </c>
       <c r="AC132">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AD132">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE132">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF132">
         <v>1.73</v>
       </c>
       <c r="AG132">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.14</v>
       </c>
       <c r="AK132">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21997,10 +21997,10 @@
         <v>2.77</v>
       </c>
       <c r="Q133">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="R133">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S133">
         <v>1.25</v>
@@ -22061,7 +22061,7 @@
         <v>1.38</v>
       </c>
       <c r="AK133">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22157,19 +22157,19 @@
         <v>8</v>
       </c>
       <c r="P134">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q134">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="R134">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="S134">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T134">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="U134">
         <v>2.15</v>
@@ -22196,13 +22196,13 @@
         <v>2.3</v>
       </c>
       <c r="AC134">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AD134">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE134">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF134">
         <v>2.8</v>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK134">
         <v>5.95</v>
@@ -22489,7 +22489,7 @@
         <v>3.5</v>
       </c>
       <c r="R136">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
         <v>1.37</v>
@@ -22498,19 +22498,19 @@
         <v>2.68</v>
       </c>
       <c r="U136">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V136">
         <v>1.4</v>
       </c>
       <c r="W136">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X136">
         <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z136">
         <v>3.08</v>
@@ -22519,13 +22519,13 @@
         <v>1.94</v>
       </c>
       <c r="AB136">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC136">
         <v>3.34</v>
       </c>
       <c r="AD136">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE136">
         <v>1.05</v>
@@ -22534,7 +22534,7 @@
         <v>1.74</v>
       </c>
       <c r="AG136">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22643,13 +22643,13 @@
         <v>3.1</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P137">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q137">
-        <v>3.66</v>
+        <v>3.18</v>
       </c>
       <c r="R137">
         <v>2.23</v>
@@ -22670,7 +22670,7 @@
         <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
         <v>1.16</v>
@@ -22679,10 +22679,10 @@
         <v>4.2</v>
       </c>
       <c r="AA137">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB137">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AC137">
         <v>2.41</v>
@@ -22691,7 +22691,7 @@
         <v>1.45</v>
       </c>
       <c r="AE137">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF137">
         <v>1.5</v>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.69</v>
+        <v>1.21</v>
       </c>
       <c r="AK137">
         <v>1.28</v>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O141">
         <v>3.45</v>
@@ -23301,13 +23301,13 @@
         <v>3.6</v>
       </c>
       <c r="Q141">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R141">
         <v>2.11</v>
       </c>
       <c r="S141">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T141">
         <v>2.82</v>
@@ -23316,13 +23316,13 @@
         <v>2.6</v>
       </c>
       <c r="V141">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W141">
         <v>1.04</v>
       </c>
       <c r="X141">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y141">
         <v>1.23</v>
@@ -23334,10 +23334,10 @@
         <v>1.86</v>
       </c>
       <c r="AB141">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC141">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="AD141">
         <v>1.3</v>
@@ -23494,7 +23494,7 @@
         <v>3.5</v>
       </c>
       <c r="AA142">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB142">
         <v>1.88</v>
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK142">
         <v>1.09</v>
@@ -23627,10 +23627,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q143">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="R143">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S143">
         <v>1.29</v>
@@ -23691,7 +23691,7 @@
         <v>1.13</v>
       </c>
       <c r="AK143">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23781,7 +23781,7 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O144">
         <v>3.37</v>
@@ -23790,7 +23790,7 @@
         <v>3.08</v>
       </c>
       <c r="Q144">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="R144">
         <v>2.1</v>
@@ -23799,7 +23799,7 @@
         <v>1.39</v>
       </c>
       <c r="T144">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="U144">
         <v>2.62</v>
@@ -23808,19 +23808,19 @@
         <v>1.44</v>
       </c>
       <c r="W144">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
         <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AA144">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB144">
         <v>1.98</v>
@@ -23832,10 +23832,10 @@
         <v>1.32</v>
       </c>
       <c r="AE144">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF144">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG144">
         <v>2.05</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK144">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23959,19 +23959,19 @@
         <v>2.37</v>
       </c>
       <c r="S145">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T145">
         <v>4.5</v>
       </c>
       <c r="U145">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="V145">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W145">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X145">
         <v>1.02</v>
@@ -23983,7 +23983,7 @@
         <v>6.05</v>
       </c>
       <c r="AA145">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB145">
         <v>2.88</v>
@@ -23995,7 +23995,7 @@
         <v>1.83</v>
       </c>
       <c r="AE145">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF145">
         <v>1.4</v>
@@ -24017,7 +24017,7 @@
         <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
         <v>1.8</v>
@@ -26591,13 +26591,13 @@
         <v>5.7</v>
       </c>
       <c r="AA161">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB161">
         <v>2.75</v>
       </c>
       <c r="AC161">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AD161">
         <v>1.77</v>
@@ -26609,7 +26609,7 @@
         <v>1.8</v>
       </c>
       <c r="AG161">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.08</v>
+        <v>4.56</v>
       </c>
       <c r="AK161">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.72</v>
+        <v>4.33</v>
       </c>
       <c r="O172">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P172">
-        <v>4.15</v>
+        <v>1.62</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S172">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T172">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U172">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V172">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W172">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X172">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y172">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z172">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC172">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD172">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG172">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK172">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="O173">
         <v>3.44</v>
       </c>
       <c r="P173">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -29003,7 +29003,7 @@
         <v>3.35</v>
       </c>
       <c r="P176">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29166,13 +29166,13 @@
         <v>3.3</v>
       </c>
       <c r="P177">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q177">
         <v>3.01</v>
       </c>
       <c r="R177">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S177">
         <v>1.26</v>
@@ -29184,7 +29184,7 @@
         <v>2.39</v>
       </c>
       <c r="V177">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W177">
         <v>1.13</v>
@@ -29199,7 +29199,7 @@
         <v>4.51</v>
       </c>
       <c r="AA177">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB177">
         <v>2.25</v>
@@ -29214,7 +29214,7 @@
         <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG177">
         <v>2.38</v>
@@ -30473,16 +30473,16 @@
         <v>1.41</v>
       </c>
       <c r="Q185">
-        <v>7.47</v>
+        <v>6.5</v>
       </c>
       <c r="R185">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S185">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T185">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="U185">
         <v>2.38</v>
@@ -30497,10 +30497,10 @@
         <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z185">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA185">
         <v>1.63</v>
@@ -30509,19 +30509,19 @@
         <v>2.17</v>
       </c>
       <c r="AC185">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AD185">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE185">
         <v>1.13</v>
       </c>
       <c r="AF185">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG185">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.16</v>
+        <v>2.9</v>
       </c>
       <c r="AK185">
         <v>1.04</v>
@@ -30636,10 +30636,10 @@
         <v>6.5</v>
       </c>
       <c r="Q186">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R186">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="S186">
         <v>1.18</v>
@@ -30651,7 +30651,7 @@
         <v>1.85</v>
       </c>
       <c r="V186">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="W186">
         <v>1.22</v>
@@ -30663,7 +30663,7 @@
         <v>1.06</v>
       </c>
       <c r="Z186">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="AA186">
         <v>1.31</v>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK186">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P187">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="Q187">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="R187">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S187">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T187">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U187">
         <v>2.63</v>
       </c>
       <c r="V187">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W187">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X187">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z187">
-        <v>4.04</v>
+        <v>3.56</v>
       </c>
       <c r="AA187">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB187">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC187">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AD187">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE187">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF187">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG187">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK187">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O188">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P188">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q188">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R188">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S188">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T188">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U188">
         <v>2.63</v>
       </c>
       <c r="V188">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W188">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z188">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA188">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB188">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AC188">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AD188">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE188">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF188">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG188">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK188">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31122,31 +31122,31 @@
         <v>3.4</v>
       </c>
       <c r="P189">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q189">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="R189">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S189">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T189">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="U189">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V189">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W189">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X189">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
         <v>1.27</v>
@@ -31155,13 +31155,13 @@
         <v>3.56</v>
       </c>
       <c r="AA189">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB189">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC189">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="AD189">
         <v>1.38</v>
@@ -31173,7 +31173,7 @@
         <v>1.62</v>
       </c>
       <c r="AG189">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AK189">
         <v>1.5</v>
@@ -31318,7 +31318,7 @@
         <v>3.08</v>
       </c>
       <c r="AA190">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB190">
         <v>1.77</v>
@@ -31333,10 +31333,10 @@
         <v>1.06</v>
       </c>
       <c r="AF190">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG190">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK190">
         <v>1.4</v>
@@ -31454,10 +31454,10 @@
         <v>2.01</v>
       </c>
       <c r="R191">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S191">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T191">
         <v>4.33</v>
@@ -31481,16 +31481,16 @@
         <v>6.4</v>
       </c>
       <c r="AA191">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB191">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC191">
+        <v>1.94</v>
+      </c>
+      <c r="AD191">
         <v>1.88</v>
-      </c>
-      <c r="AD191">
-        <v>1.86</v>
       </c>
       <c r="AE191">
         <v>1.33</v>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK191">
         <v>2.27</v>
@@ -31638,16 +31638,16 @@
         <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z192">
         <v>5.6</v>
       </c>
       <c r="AA192">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AB192">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AC192">
         <v>2.05</v>
@@ -31659,7 +31659,7 @@
         <v>1.26</v>
       </c>
       <c r="AF192">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG192">
         <v>2.39</v>
@@ -31777,55 +31777,55 @@
         <v>1.91</v>
       </c>
       <c r="Q193">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="R193">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S193">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T193">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="U193">
         <v>2.5</v>
       </c>
       <c r="V193">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W193">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X193">
         <v>1</v>
       </c>
       <c r="Y193">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z193">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA193">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB193">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC193">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD193">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE193">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF193">
         <v>1.65</v>
       </c>
       <c r="AG193">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK193">
         <v>1.25</v>
@@ -31964,7 +31964,7 @@
         <v>1.04</v>
       </c>
       <c r="Y194">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z194">
         <v>3.78</v>
@@ -32004,7 +32004,7 @@
         <v>1.31</v>
       </c>
       <c r="AK194">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32115,7 +32115,7 @@
         <v>3.56</v>
       </c>
       <c r="U195">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V195">
         <v>1.6</v>
@@ -32151,7 +32151,7 @@
         <v>1.62</v>
       </c>
       <c r="AG195">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O196">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="P196">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="Q196">
         <v>1.69</v>
@@ -32302,7 +32302,7 @@
         <v>2.28</v>
       </c>
       <c r="AC196">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD196">
         <v>1.42</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK196">
         <v>3.64</v>
@@ -32586,16 +32586,16 @@
         <v>1.95</v>
       </c>
       <c r="O198">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P198">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q198">
+        <v>2.45</v>
+      </c>
+      <c r="R198">
         <v>2.25</v>
-      </c>
-      <c r="R198">
-        <v>2.16</v>
       </c>
       <c r="S198">
         <v>1.37</v>
@@ -32610,34 +32610,34 @@
         <v>1.43</v>
       </c>
       <c r="W198">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X198">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y198">
         <v>1.25</v>
       </c>
       <c r="Z198">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA198">
         <v>1.8</v>
       </c>
       <c r="AB198">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC198">
         <v>3.2</v>
       </c>
       <c r="AD198">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE198">
         <v>1.08</v>
       </c>
       <c r="AF198">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG198">
         <v>1.97</v>
@@ -33416,7 +33416,7 @@
         <v>1.25</v>
       </c>
       <c r="T203">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U203">
         <v>2.25</v>
@@ -33564,7 +33564,7 @@
         <v>2.15</v>
       </c>
       <c r="O204">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P204">
         <v>3</v>
@@ -33579,7 +33579,7 @@
         <v>1.28</v>
       </c>
       <c r="T204">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U204">
         <v>2.4</v>
@@ -33600,10 +33600,10 @@
         <v>4.3</v>
       </c>
       <c r="AA204">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB204">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AC204">
         <v>2.38</v>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK204">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33902,10 +33902,10 @@
         <v>2.3</v>
       </c>
       <c r="S206">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T206">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="U206">
         <v>2.38</v>
@@ -33929,7 +33929,7 @@
         <v>1.67</v>
       </c>
       <c r="AB206">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AC206">
         <v>2.56</v>
@@ -34059,7 +34059,7 @@
         <v>2.75</v>
       </c>
       <c r="Q207">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="R207">
         <v>2.17</v>
@@ -34071,34 +34071,34 @@
         <v>3.25</v>
       </c>
       <c r="U207">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V207">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W207">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z207">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA207">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB207">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AC207">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD207">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE207">
         <v>1.12</v>
@@ -34123,7 +34123,7 @@
         <v>1.3</v>
       </c>
       <c r="AK207">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34246,10 +34246,10 @@
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z208">
-        <v>6.8</v>
+        <v>6.79</v>
       </c>
       <c r="AA208">
         <v>1.33</v>
@@ -34270,7 +34270,7 @@
         <v>1.4</v>
       </c>
       <c r="AG208">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>2.75</v>
       </c>
       <c r="R209">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S209">
         <v>1.2</v>
@@ -34400,25 +34400,25 @@
         <v>2</v>
       </c>
       <c r="V209">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W209">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X209">
         <v>1.02</v>
       </c>
       <c r="Y209">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z209">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA209">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB209">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC209">
         <v>2.07</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK209">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34542,10 +34542,10 @@
         <v>7.25</v>
       </c>
       <c r="O210">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="P210">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q210">
         <v>7</v>
@@ -34557,10 +34557,10 @@
         <v>1.3</v>
       </c>
       <c r="T210">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="U210">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="V210">
         <v>1.5</v>
@@ -34587,13 +34587,13 @@
         <v>2.52</v>
       </c>
       <c r="AD210">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AE210">
         <v>1.12</v>
       </c>
       <c r="AF210">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG210">
         <v>1.85</v>
@@ -35363,13 +35363,13 @@
         <v>2.86</v>
       </c>
       <c r="Q215">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="R215">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S215">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T215">
         <v>4.1</v>
@@ -35378,7 +35378,7 @@
         <v>2.13</v>
       </c>
       <c r="V215">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W215">
         <v>1.17</v>
@@ -35393,16 +35393,16 @@
         <v>5.75</v>
       </c>
       <c r="AA215">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB215">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC215">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD215">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE215">
         <v>1.24</v>
@@ -35689,43 +35689,43 @@
         <v>2.07</v>
       </c>
       <c r="Q217">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R217">
         <v>2.28</v>
       </c>
       <c r="S217">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T217">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U217">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="V217">
         <v>1.4</v>
       </c>
       <c r="W217">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X217">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y217">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z217">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA217">
         <v>1.75</v>
       </c>
       <c r="AB217">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC217">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD217">
         <v>1.33</v>
@@ -35750,7 +35750,7 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK217">
         <v>1.27</v>
@@ -36830,10 +36830,10 @@
         <v>7.55</v>
       </c>
       <c r="Q224">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R224">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S224">
         <v>1.32</v>
@@ -36863,7 +36863,7 @@
         <v>1.61</v>
       </c>
       <c r="AB224">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC224">
         <v>2.46</v>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK224">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,34 +36984,34 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="O225">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P225">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="Q225">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="R225">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S225">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T225">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U225">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V225">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W225">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X225">
         <v>1.01</v>
@@ -37020,16 +37020,16 @@
         <v>1.21</v>
       </c>
       <c r="Z225">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="AA225">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB225">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="AC225">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AD225">
         <v>1.34</v>
@@ -37057,7 +37057,7 @@
         <v>1.33</v>
       </c>
       <c r="AK225">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>1.62</v>
       </c>
       <c r="AB226">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC226">
         <v>2.61</v>
@@ -37310,34 +37310,34 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="O227">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P227">
-        <v>3.23</v>
+        <v>2.85</v>
       </c>
       <c r="Q227">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R227">
         <v>2.22</v>
       </c>
       <c r="S227">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T227">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U227">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="V227">
         <v>1.5</v>
       </c>
       <c r="W227">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X227">
         <v>1.01</v>
@@ -37349,13 +37349,13 @@
         <v>4.05</v>
       </c>
       <c r="AA227">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB227">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC227">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="AD227">
         <v>1.4</v>
@@ -37364,7 +37364,7 @@
         <v>1.12</v>
       </c>
       <c r="AF227">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG227">
         <v>2.23</v>
@@ -37383,7 +37383,7 @@
         <v>1.31</v>
       </c>
       <c r="AK227">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O228">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="P228">
-        <v>6.06</v>
+        <v>5.25</v>
       </c>
       <c r="Q228">
         <v>2.04</v>
@@ -37488,7 +37488,7 @@
         <v>2.5</v>
       </c>
       <c r="S228">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T228">
         <v>3.84</v>
@@ -37512,10 +37512,10 @@
         <v>4.75</v>
       </c>
       <c r="AA228">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB228">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AC228">
         <v>2.4</v>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK228">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37636,22 +37636,22 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O229">
-        <v>4.36</v>
+        <v>4.24</v>
       </c>
       <c r="P229">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="Q229">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R229">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="S229">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T229">
         <v>4</v>
@@ -37669,31 +37669,31 @@
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z229">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA229">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB229">
         <v>2.72</v>
       </c>
       <c r="AC229">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD229">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AE229">
         <v>1.28</v>
       </c>
       <c r="AF229">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG229">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="O230">
-        <v>3.41</v>
+        <v>3.26</v>
       </c>
       <c r="P230">
-        <v>2.86</v>
+        <v>2.23</v>
       </c>
       <c r="Q230">
         <v>3.68</v>
@@ -37826,22 +37826,22 @@
         <v>1.36</v>
       </c>
       <c r="W230">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X230">
         <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z230">
         <v>3.14</v>
       </c>
       <c r="AA230">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB230">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC230">
         <v>3.34</v>
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="O231">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="P231">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q231">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R231">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S231">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T231">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="U231">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="V231">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W231">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X231">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y231">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z231">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="AA231">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB231">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC231">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="AD231">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE231">
         <v>1.04</v>
       </c>
       <c r="AF231">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG231">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK231">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38137,52 +38137,52 @@
         <v>1.5</v>
       </c>
       <c r="R232">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="S232">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T232">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="U232">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="V232">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W232">
         <v>1.11</v>
       </c>
       <c r="X232">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y232">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z232">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="AA232">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB232">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC232">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD232">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE232">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF232">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="AG232">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>1.04</v>
       </c>
       <c r="AK232">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38460,55 +38460,55 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38617,10 +38617,10 @@
         <v>2.5</v>
       </c>
       <c r="O235">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P235">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q235">
         <v>3.1</v>
@@ -38629,10 +38629,10 @@
         <v>2.3</v>
       </c>
       <c r="S235">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T235">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="U235">
         <v>2.34</v>
@@ -38647,7 +38647,7 @@
         <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z235">
         <v>4</v>
@@ -38656,7 +38656,7 @@
         <v>1.7</v>
       </c>
       <c r="AB235">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC235">
         <v>2.56</v>
@@ -38671,7 +38671,7 @@
         <v>1.53</v>
       </c>
       <c r="AG235">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38777,28 +38777,28 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="O236">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P236">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q236">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="R236">
         <v>2.1</v>
       </c>
       <c r="S236">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T236">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U236">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V236">
         <v>1.36</v>
@@ -38807,19 +38807,19 @@
         <v>1.07</v>
       </c>
       <c r="X236">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z236">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
       <c r="AA236">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB236">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC236">
         <v>3.34</v>
@@ -38847,7 +38847,7 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK236">
         <v>1.75</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="O238">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P238">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q238">
         <v>2.82</v>
@@ -39142,7 +39142,7 @@
         <v>2.83</v>
       </c>
       <c r="AA238">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB238">
         <v>1.64</v>
@@ -39272,7 +39272,7 @@
         <v>3.5</v>
       </c>
       <c r="P239">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="Q239">
         <v>2.15</v>
@@ -39281,19 +39281,19 @@
         <v>2.11</v>
       </c>
       <c r="S239">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T239">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U239">
         <v>2.88</v>
       </c>
       <c r="V239">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W239">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X239">
         <v>1.02</v>
@@ -39308,7 +39308,7 @@
         <v>2.05</v>
       </c>
       <c r="AB239">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC239">
         <v>3.34</v>
@@ -39429,16 +39429,16 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O240">
         <v>3.1</v>
       </c>
       <c r="P240">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="Q240">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R240">
         <v>2.01</v>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK240">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O241">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P241">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q241">
         <v>4</v>
@@ -39610,16 +39610,16 @@
         <v>1.36</v>
       </c>
       <c r="T241">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="U241">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V241">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W241">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X241">
         <v>1.01</v>
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O243">
         <v>4.33</v>
@@ -39939,43 +39939,43 @@
         <v>3.5</v>
       </c>
       <c r="U243">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="V243">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W243">
         <v>1.11</v>
       </c>
       <c r="X243">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y243">
         <v>1.12</v>
       </c>
       <c r="Z243">
-        <v>4.54</v>
+        <v>4.47</v>
       </c>
       <c r="AA243">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AB243">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC243">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AD243">
         <v>1.52</v>
       </c>
       <c r="AE243">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF243">
         <v>1.67</v>
       </c>
       <c r="AG243">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK243">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40090,55 +40090,55 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="O245">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="P245">
-        <v>7.5</v>
+        <v>6.11</v>
       </c>
       <c r="Q245">
         <v>1.8</v>
@@ -40268,7 +40268,7 @@
         <v>2</v>
       </c>
       <c r="V245">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W245">
         <v>1.2</v>
@@ -40280,22 +40280,22 @@
         <v>1.08</v>
       </c>
       <c r="Z245">
-        <v>6.12</v>
+        <v>5.7</v>
       </c>
       <c r="AA245">
         <v>1.4</v>
       </c>
       <c r="AB245">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AC245">
         <v>1.93</v>
       </c>
       <c r="AD245">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AE245">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF245">
         <v>1.55</v>
@@ -40314,7 +40314,7 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK245">
         <v>2.88</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O246">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P246">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q246">
         <v>1.9</v>
@@ -40422,10 +40422,10 @@
         <v>2.45</v>
       </c>
       <c r="S246">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T246">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U246">
         <v>2.22</v>
@@ -40434,37 +40434,37 @@
         <v>1.56</v>
       </c>
       <c r="W246">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X246">
         <v>1.03</v>
       </c>
       <c r="Y246">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z246">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA246">
         <v>1.6</v>
       </c>
       <c r="AB246">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC246">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD246">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE246">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF246">
         <v>1.7</v>
       </c>
       <c r="AG246">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK246">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="O247">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P247">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40905,7 +40905,7 @@
         <v>2.52</v>
       </c>
       <c r="Q249">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="R249">
         <v>2.1</v>
@@ -40935,7 +40935,7 @@
         <v>3.28</v>
       </c>
       <c r="AA249">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB249">
         <v>1.85</v>
@@ -40953,7 +40953,7 @@
         <v>1.69</v>
       </c>
       <c r="AG249">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK249">
         <v>1.43</v>
@@ -41059,22 +41059,22 @@
         </is>
       </c>
       <c r="N250">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="O250">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="P250">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q250">
-        <v>5.61</v>
+        <v>7.5</v>
       </c>
       <c r="R250">
         <v>2.29</v>
       </c>
       <c r="S250">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T250">
         <v>2.9</v>
@@ -41083,7 +41083,7 @@
         <v>2.62</v>
       </c>
       <c r="V250">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W250">
         <v>1.1</v>
@@ -41098,16 +41098,16 @@
         <v>3.44</v>
       </c>
       <c r="AA250">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB250">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AC250">
         <v>2.82</v>
       </c>
       <c r="AD250">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE250">
         <v>1.09</v>
@@ -41222,31 +41222,31 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="O251">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="P251">
-        <v>6.24</v>
+        <v>5.4</v>
       </c>
       <c r="Q251">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="R251">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="S251">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T251">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="U251">
         <v>2.5</v>
       </c>
       <c r="V251">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W251">
         <v>1.13</v>
@@ -41255,19 +41255,19 @@
         <v>1.01</v>
       </c>
       <c r="Y251">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z251">
-        <v>4.33</v>
+        <v>4.18</v>
       </c>
       <c r="AA251">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB251">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC251">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AD251">
         <v>1.45</v>
@@ -41276,7 +41276,7 @@
         <v>1.17</v>
       </c>
       <c r="AF251">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG251">
         <v>1.95</v>
@@ -41292,7 +41292,7 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK251">
         <v>2.57</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="O252">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P252">
-        <v>4.24</v>
+        <v>4.6</v>
       </c>
       <c r="Q252">
         <v>2.2</v>
@@ -41400,10 +41400,10 @@
         <v>2.14</v>
       </c>
       <c r="S252">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T252">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U252">
         <v>2.88</v>
@@ -41427,13 +41427,13 @@
         <v>1.92</v>
       </c>
       <c r="AB252">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC252">
         <v>3.2</v>
       </c>
       <c r="AD252">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE252">
         <v>1.05</v>
@@ -41551,13 +41551,13 @@
         <v>1.69</v>
       </c>
       <c r="O253">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P253">
         <v>4.33</v>
       </c>
       <c r="Q253">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R253">
         <v>2.36</v>
@@ -41581,7 +41581,7 @@
         <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z253">
         <v>4.45</v>
@@ -41596,7 +41596,7 @@
         <v>2.55</v>
       </c>
       <c r="AD253">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE253">
         <v>1.13</v>
@@ -41605,7 +41605,7 @@
         <v>1.6</v>
       </c>
       <c r="AG253">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41711,31 +41711,31 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="O254">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P254">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q254">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R254">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S254">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T254">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="U254">
         <v>2.8</v>
       </c>
       <c r="V254">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W254">
         <v>1.08</v>
@@ -41744,25 +41744,25 @@
         <v>1.03</v>
       </c>
       <c r="Y254">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z254">
-        <v>3.46</v>
+        <v>3.08</v>
       </c>
       <c r="AA254">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB254">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC254">
-        <v>3.44</v>
+        <v>3.14</v>
       </c>
       <c r="AD254">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE254">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF254">
         <v>1.75</v>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK254">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41883,25 +41883,25 @@
         <v>4.43</v>
       </c>
       <c r="Q255">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R255">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S255">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T255">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U255">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V255">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W255">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X255">
         <v>1.01</v>
@@ -41913,10 +41913,10 @@
         <v>4.05</v>
       </c>
       <c r="AA255">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB255">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC255">
         <v>2.46</v>
@@ -41931,7 +41931,7 @@
         <v>1.63</v>
       </c>
       <c r="AG255">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK255">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42046,55 +42046,55 @@
         <v>2.97</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42203,61 +42203,61 @@
         <v>3.3</v>
       </c>
       <c r="O257">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P257">
         <v>1.95</v>
       </c>
       <c r="Q257">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="R257">
         <v>2.25</v>
       </c>
       <c r="S257">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T257">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U257">
         <v>2.63</v>
       </c>
       <c r="V257">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W257">
         <v>1.1</v>
       </c>
       <c r="X257">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y257">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z257">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="AA257">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB257">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC257">
         <v>2.83</v>
       </c>
       <c r="AD257">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE257">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF257">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG257">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42526,22 +42526,22 @@
         </is>
       </c>
       <c r="N259">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O259">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P259">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q259">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="R259">
         <v>2.18</v>
       </c>
       <c r="S259">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T259">
         <v>3.2</v>
@@ -42550,7 +42550,7 @@
         <v>2.67</v>
       </c>
       <c r="V259">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W259">
         <v>1.07</v>
@@ -42559,10 +42559,10 @@
         <v>1.01</v>
       </c>
       <c r="Y259">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z259">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA259">
         <v>1.82</v>
@@ -42596,7 +42596,7 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK259">
         <v>1.16</v>
@@ -43178,22 +43178,22 @@
         </is>
       </c>
       <c r="N263">
-        <v>6.67</v>
+        <v>5.5</v>
       </c>
       <c r="O263">
-        <v>4.38</v>
+        <v>4.12</v>
       </c>
       <c r="P263">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Q263">
         <v>5.8</v>
       </c>
       <c r="R263">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="S263">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T263">
         <v>3.04</v>
@@ -43211,16 +43211,16 @@
         <v>1.03</v>
       </c>
       <c r="Y263">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z263">
         <v>3.42</v>
       </c>
       <c r="AA263">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB263">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC263">
         <v>3.22</v>
@@ -43232,7 +43232,7 @@
         <v>1.12</v>
       </c>
       <c r="AF263">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG263">
         <v>1.8</v>
@@ -43248,7 +43248,7 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK263">
         <v>1.11</v>
@@ -43341,25 +43341,25 @@
         </is>
       </c>
       <c r="N264">
-        <v>4.28</v>
+        <v>3.6</v>
       </c>
       <c r="O264">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P264">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q264">
         <v>3.69</v>
       </c>
       <c r="R264">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S264">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T264">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U264">
         <v>2.9</v>
@@ -43371,22 +43371,22 @@
         <v>1.07</v>
       </c>
       <c r="X264">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y264">
         <v>1.35</v>
       </c>
       <c r="Z264">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="AA264">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AB264">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC264">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD264">
         <v>1.22</v>
@@ -43414,7 +43414,7 @@
         <v>1.77</v>
       </c>
       <c r="AK264">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43504,25 +43504,25 @@
         </is>
       </c>
       <c r="N265">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O265">
-        <v>4.72</v>
+        <v>4.2</v>
       </c>
       <c r="P265">
-        <v>5.49</v>
+        <v>5.3</v>
       </c>
       <c r="Q265">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R265">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="S265">
         <v>1.2</v>
       </c>
       <c r="T265">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U265">
         <v>2.1</v>
@@ -43531,7 +43531,7 @@
         <v>1.65</v>
       </c>
       <c r="W265">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X265">
         <v>1.02</v>
@@ -43540,25 +43540,25 @@
         <v>1.09</v>
       </c>
       <c r="Z265">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA265">
         <v>1.4</v>
       </c>
       <c r="AB265">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AC265">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AD265">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AE265">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF265">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG265">
         <v>2.38</v>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK265">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43667,22 +43667,22 @@
         </is>
       </c>
       <c r="N266">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="O266">
         <v>4</v>
       </c>
       <c r="P266">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Q266">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="R266">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S266">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T266">
         <v>3.4</v>
@@ -43697,7 +43697,7 @@
         <v>1.13</v>
       </c>
       <c r="X266">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y266">
         <v>1.16</v>
@@ -43709,13 +43709,13 @@
         <v>1.6</v>
       </c>
       <c r="AB266">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AC266">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AD266">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE266">
         <v>1.13</v>
@@ -43830,19 +43830,19 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O267">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P267">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="Q267">
         <v>3.1</v>
       </c>
       <c r="R267">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S267">
         <v>1.25</v>
@@ -43851,7 +43851,7 @@
         <v>3.3</v>
       </c>
       <c r="U267">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V267">
         <v>1.53</v>
@@ -43860,13 +43860,13 @@
         <v>1.12</v>
       </c>
       <c r="X267">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y267">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z267">
-        <v>4.48</v>
+        <v>4.15</v>
       </c>
       <c r="AA267">
         <v>1.65</v>
@@ -43884,7 +43884,7 @@
         <v>1.15</v>
       </c>
       <c r="AF267">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG267">
         <v>2.4</v>
@@ -43996,13 +43996,13 @@
         <v>1.32</v>
       </c>
       <c r="O268">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P268">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Q268">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R268">
         <v>2.7</v>
@@ -44020,37 +44020,37 @@
         <v>1.7</v>
       </c>
       <c r="W268">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X268">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y268">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z268">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AA268">
         <v>1.4</v>
       </c>
       <c r="AB268">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC268">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AD268">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE268">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF268">
         <v>1.73</v>
       </c>
       <c r="AG268">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44165,55 +44165,55 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44328,55 +44328,55 @@
         <v>0</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44482,19 +44482,19 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O271">
         <v>3.6</v>
       </c>
       <c r="P271">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q271">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="R271">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S271">
         <v>1.22</v>
@@ -44509,13 +44509,13 @@
         <v>1.68</v>
       </c>
       <c r="W271">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X271">
         <v>1.02</v>
       </c>
       <c r="Y271">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z271">
         <v>5.7</v>
@@ -44524,7 +44524,7 @@
         <v>1.36</v>
       </c>
       <c r="AB271">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC271">
         <v>1.99</v>
@@ -44533,10 +44533,10 @@
         <v>1.7</v>
       </c>
       <c r="AE271">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF271">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AG271">
         <v>2.8</v>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AK271">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>2.69</v>
       </c>
       <c r="AA272">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB272">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC272">
         <v>3.94</v>
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q274">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R274">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S274">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T274">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U274">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V274">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W274">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X274">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y274">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z274">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC274">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD274">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE274">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF274">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG274">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK274">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,58 +45460,58 @@
         </is>
       </c>
       <c r="N277">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O277">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P277">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q277">
-        <v>4.34</v>
+        <v>2.5</v>
       </c>
       <c r="R277">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S277">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="T277">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U277">
-        <v>4.25</v>
+        <v>3.76</v>
       </c>
       <c r="V277">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W277">
+        <v>1.01</v>
+      </c>
+      <c r="X277">
+        <v>1.13</v>
+      </c>
+      <c r="Y277">
+        <v>1.63</v>
+      </c>
+      <c r="Z277">
+        <v>2.24</v>
+      </c>
+      <c r="AA277">
+        <v>2.95</v>
+      </c>
+      <c r="AB277">
+        <v>1.36</v>
+      </c>
+      <c r="AC277">
+        <v>6</v>
+      </c>
+      <c r="AD277">
+        <v>1.06</v>
+      </c>
+      <c r="AE277">
         <v>1.03</v>
-      </c>
-      <c r="X277">
-        <v>1.08</v>
-      </c>
-      <c r="Y277">
-        <v>1.67</v>
-      </c>
-      <c r="Z277">
-        <v>2.04</v>
-      </c>
-      <c r="AA277">
-        <v>3.4</v>
-      </c>
-      <c r="AB277">
-        <v>1.33</v>
-      </c>
-      <c r="AC277">
-        <v>6.65</v>
-      </c>
-      <c r="AD277">
-        <v>1.05</v>
-      </c>
-      <c r="AE277">
-        <v>1.02</v>
       </c>
       <c r="AF277">
         <v>2.42</v>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AK277">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O278">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P278">
-        <v>4.89</v>
+        <v>4.15</v>
       </c>
       <c r="Q278">
         <v>2.3</v>
@@ -45662,13 +45662,13 @@
         <v>2.78</v>
       </c>
       <c r="AA278">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB278">
         <v>1.65</v>
       </c>
       <c r="AC278">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="AD278">
         <v>1.23</v>
@@ -45696,7 +45696,7 @@
         <v>1.26</v>
       </c>
       <c r="AK278">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45949,22 +45949,22 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O280">
         <v>3.9</v>
       </c>
       <c r="P280">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="Q280">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="R280">
         <v>2.39</v>
       </c>
       <c r="S280">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T280">
         <v>3.8</v>
@@ -45976,7 +45976,7 @@
         <v>1.62</v>
       </c>
       <c r="W280">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X280">
         <v>1.02</v>
@@ -45985,19 +45985,19 @@
         <v>1.15</v>
       </c>
       <c r="Z280">
-        <v>5.52</v>
+        <v>5.15</v>
       </c>
       <c r="AA280">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB280">
         <v>2.63</v>
       </c>
       <c r="AC280">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AD280">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE280">
         <v>1.25</v>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK280">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="O281">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="P281">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q281">
         <v>1.84</v>
@@ -46127,19 +46127,19 @@
         <v>2.71</v>
       </c>
       <c r="S281">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T281">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U281">
         <v>2</v>
       </c>
       <c r="V281">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W281">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X281">
         <v>1.01</v>
@@ -46157,10 +46157,10 @@
         <v>2.84</v>
       </c>
       <c r="AC281">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AD281">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE281">
         <v>1.33</v>
@@ -46169,7 +46169,7 @@
         <v>1.53</v>
       </c>
       <c r="AG281">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK281">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46275,16 +46275,16 @@
         </is>
       </c>
       <c r="N282">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="O282">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="P282">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="Q282">
-        <v>5.42</v>
+        <v>5.22</v>
       </c>
       <c r="R282">
         <v>2.26</v>
@@ -46296,7 +46296,7 @@
         <v>3.2</v>
       </c>
       <c r="U282">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="V282">
         <v>1.43</v>
@@ -46308,16 +46308,16 @@
         <v>1.01</v>
       </c>
       <c r="Y282">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z282">
-        <v>3.84</v>
+        <v>3.44</v>
       </c>
       <c r="AA282">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB282">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC282">
         <v>3</v>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.18</v>
+        <v>2.15</v>
       </c>
       <c r="AK282">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46640,10 +46640,10 @@
         <v>0</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC284">
         <v>0</v>
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="O286">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="P286">
-        <v>8.550000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA286">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB286">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O287">
         <v>4.3</v>
       </c>
       <c r="P287">
-        <v>5.49</v>
+        <v>5.32</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>8.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O288">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="P288">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O290">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P290">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47911,19 +47911,19 @@
         <v>5.05</v>
       </c>
       <c r="P292">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q292">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R292">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="S292">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T292">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="U292">
         <v>1.62</v>
@@ -47947,7 +47947,7 @@
         <v>1.14</v>
       </c>
       <c r="AB292">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AC292">
         <v>1.49</v>
@@ -47956,13 +47956,13 @@
         <v>2.4</v>
       </c>
       <c r="AE292">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF292">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AG292">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK292">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AL292">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="O2">
         <v>3.63</v>
       </c>
       <c r="P2">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q2">
         <v>2.68</v>
@@ -653,16 +653,16 @@
         <v>1.27</v>
       </c>
       <c r="T2">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -683,16 +683,16 @@
         <v>2.59</v>
       </c>
       <c r="AD2">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
         <v>1.6</v>
       </c>
       <c r="AG2">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.64</v>
+        <v>1.82</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q7">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="U7">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z7">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="AA7">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AB7">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AC7">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
+        <v>1.98</v>
+      </c>
+      <c r="AG7">
         <v>1.72</v>
       </c>
-      <c r="AG7">
-        <v>1.95</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.82</v>
+        <v>2.64</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>4.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="U8">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA8">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AB8">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>3.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD8">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AG8">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O21">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
         <v>1.26</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5555,13 +5555,13 @@
         <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AA32">
         <v>1.71</v>
@@ -5727,10 +5727,10 @@
         <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>2.88</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -8818,31 +8818,31 @@
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9120,22 +9120,22 @@
         <v>2.8</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -9144,22 +9144,22 @@
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9184,7 +9184,7 @@
         <v>0</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="O60">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
         <v>2.62</v>
@@ -10107,7 +10107,7 @@
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U60">
         <v>2.25</v>
@@ -10424,16 +10424,16 @@
         <v>2.75</v>
       </c>
       <c r="Q62">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T62">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U62">
         <v>2.85</v>
@@ -10442,7 +10442,7 @@
         <v>1.33</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X62">
         <v>1.02</v>
@@ -10454,10 +10454,10 @@
         <v>2.97</v>
       </c>
       <c r="AA62">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB62">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC62">
         <v>3.34</v>
@@ -10472,7 +10472,7 @@
         <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="O78">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P78">
         <v>1.68</v>
@@ -13053,7 +13053,7 @@
         <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
         <v>1.14</v>
@@ -13225,7 +13225,7 @@
         <v>8</v>
       </c>
       <c r="AA79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AB79">
         <v>3.34</v>
@@ -13234,10 +13234,10 @@
         <v>1.7</v>
       </c>
       <c r="AD79">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AE79">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AF79">
         <v>2.3</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>2.67</v>
       </c>
       <c r="Q85">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="R85">
         <v>2.49</v>
@@ -14381,7 +14381,7 @@
         <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG86">
         <v>2.5</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="O89">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P89">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -14831,10 +14831,10 @@
         <v>2.4</v>
       </c>
       <c r="S89">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="U89">
         <v>2.2</v>
@@ -14852,28 +14852,28 @@
         <v>1.15</v>
       </c>
       <c r="Z89">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA89">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB89">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AC89">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD89">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE89">
         <v>1.22</v>
       </c>
       <c r="AF89">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG89">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>1.64</v>
       </c>
       <c r="AB92">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC92">
         <v>2.41</v>
@@ -15673,7 +15673,7 @@
         <v>1.95</v>
       </c>
       <c r="AB94">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC94">
         <v>3.48</v>
@@ -16286,7 +16286,7 @@
         <v>1.85</v>
       </c>
       <c r="O98">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P98">
         <v>4.05</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="O99">
         <v>3.9</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="O103">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q103">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="R103">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="S103">
         <v>1.22</v>
       </c>
       <c r="T103">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V103">
         <v>1.67</v>
       </c>
       <c r="W103">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z103">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA103">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB103">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AC103">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AD103">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE103">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF103">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG103">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK103">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,19 +17261,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="O104">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P104">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q104">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R104">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="S104">
         <v>1.17</v>
@@ -17297,7 +17297,7 @@
         <v>1.07</v>
       </c>
       <c r="Z104">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="AA104">
         <v>1.43</v>
@@ -17309,16 +17309,16 @@
         <v>2.04</v>
       </c>
       <c r="AD104">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE104">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AF104">
         <v>1.43</v>
       </c>
       <c r="AG104">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>2.08</v>
       </c>
       <c r="AB111">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC111">
         <v>3.7</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="O115">
         <v>4.33</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O116">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="Q116">
         <v>2.97</v>
@@ -19256,7 +19256,7 @@
         <v>3.08</v>
       </c>
       <c r="AA116">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AB116">
         <v>1.72</v>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="O117">
         <v>3.8</v>
@@ -19558,7 +19558,7 @@
         <v>2.62</v>
       </c>
       <c r="S118">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T118">
         <v>5.2</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O123">
         <v>3.58</v>
       </c>
       <c r="P123">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q123">
         <v>2.34</v>
@@ -20865,7 +20865,7 @@
         <v>1.29</v>
       </c>
       <c r="T126">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U126">
         <v>2.33</v>
@@ -21197,7 +21197,7 @@
         <v>2.4</v>
       </c>
       <c r="V128">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W128">
         <v>1.1</v>
@@ -21215,7 +21215,7 @@
         <v>1.69</v>
       </c>
       <c r="AB128">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC128">
         <v>2.43</v>
@@ -21553,7 +21553,7 @@
         <v>1.11</v>
       </c>
       <c r="AF130">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG130">
         <v>2.19</v>
@@ -21831,13 +21831,13 @@
         <v>5.5</v>
       </c>
       <c r="P132">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q132">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R132">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="S132">
         <v>1.2</v>
@@ -21846,7 +21846,7 @@
         <v>4</v>
       </c>
       <c r="U132">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V132">
         <v>1.68</v>
@@ -21864,19 +21864,19 @@
         <v>5.4</v>
       </c>
       <c r="AA132">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB132">
         <v>2.52</v>
       </c>
       <c r="AC132">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AD132">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE132">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF132">
         <v>1.73</v>
@@ -22314,31 +22314,31 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="O135">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P135">
-        <v>7.12</v>
+        <v>6.25</v>
       </c>
       <c r="Q135">
         <v>1.77</v>
       </c>
       <c r="R135">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S135">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T135">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U135">
         <v>2.38</v>
       </c>
       <c r="V135">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W135">
         <v>1.07</v>
@@ -22350,7 +22350,7 @@
         <v>1.16</v>
       </c>
       <c r="Z135">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA135">
         <v>1.65</v>
@@ -22387,7 +22387,7 @@
         <v>1.1</v>
       </c>
       <c r="AK135">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="N137">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O137">
         <v>3.61</v>
@@ -22670,7 +22670,7 @@
         <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
         <v>1.16</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB139">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC139">
         <v>0</v>
@@ -23138,19 +23138,19 @@
         <v>3.2</v>
       </c>
       <c r="Q140">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="R140">
         <v>2.19</v>
       </c>
       <c r="S140">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T140">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="U140">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V140">
         <v>1.44</v>
@@ -23165,16 +23165,16 @@
         <v>1.19</v>
       </c>
       <c r="Z140">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA140">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB140">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AC140">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AD140">
         <v>1.38</v>
@@ -23186,7 +23186,7 @@
         <v>1.58</v>
       </c>
       <c r="AG140">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O146">
         <v>3.44</v>
@@ -27702,16 +27702,16 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R168">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S168">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T168">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U168">
         <v>2.38</v>
@@ -27732,13 +27732,13 @@
         <v>3.7</v>
       </c>
       <c r="AA168">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB168">
         <v>2.05</v>
       </c>
       <c r="AC168">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD168">
         <v>1.36</v>
@@ -27747,10 +27747,10 @@
         <v>1.13</v>
       </c>
       <c r="AF168">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AG168">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK168">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="O176">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="P176">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29160,10 +29160,10 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O177">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P177">
         <v>2.25</v>
@@ -29184,7 +29184,7 @@
         <v>2.39</v>
       </c>
       <c r="V177">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W177">
         <v>1.13</v>
@@ -29199,7 +29199,7 @@
         <v>4.51</v>
       </c>
       <c r="AA177">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB177">
         <v>2.25</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O178">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P178">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Q178">
         <v>2.92</v>
@@ -29347,16 +29347,16 @@
         <v>2.36</v>
       </c>
       <c r="V178">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W178">
         <v>1.06</v>
       </c>
       <c r="X178">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z178">
         <v>3.92</v>
@@ -29368,13 +29368,13 @@
         <v>2.05</v>
       </c>
       <c r="AC178">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="AD178">
         <v>1.4</v>
       </c>
       <c r="AE178">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF178">
         <v>1.57</v>
@@ -30476,7 +30476,7 @@
         <v>6.5</v>
       </c>
       <c r="R185">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S185">
         <v>1.28</v>
@@ -30518,10 +30518,10 @@
         <v>1.13</v>
       </c>
       <c r="AF185">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG185">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>7.5</v>
       </c>
       <c r="AA186">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB186">
         <v>2.92</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O187">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P187">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q187">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="R187">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="S187">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T187">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U187">
         <v>2.63</v>
       </c>
       <c r="V187">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W187">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y187">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z187">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="AA187">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB187">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AC187">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AD187">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE187">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF187">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK187">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O188">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P188">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="Q188">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="R188">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S188">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T188">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U188">
         <v>2.63</v>
       </c>
       <c r="V188">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W188">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X188">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z188">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="AA188">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB188">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC188">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AD188">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE188">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF188">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG188">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK188">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31116,19 +31116,19 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O189">
         <v>3.4</v>
       </c>
       <c r="P189">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="Q189">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R189">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S189">
         <v>1.33</v>
@@ -31137,7 +31137,7 @@
         <v>3.12</v>
       </c>
       <c r="U189">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V189">
         <v>1.44</v>
@@ -31161,13 +31161,13 @@
         <v>2</v>
       </c>
       <c r="AC189">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AD189">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE189">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF189">
         <v>1.62</v>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AK189">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31810,7 +31810,7 @@
         <v>1.78</v>
       </c>
       <c r="AB193">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC193">
         <v>2.83</v>
@@ -32420,19 +32420,19 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="O197">
         <v>4.5</v>
       </c>
       <c r="P197">
-        <v>5.57</v>
+        <v>4.8</v>
       </c>
       <c r="Q197">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R197">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="S197">
         <v>1.17</v>
@@ -32444,7 +32444,7 @@
         <v>2.08</v>
       </c>
       <c r="V197">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W197">
         <v>1.17</v>
@@ -32456,28 +32456,28 @@
         <v>1.11</v>
       </c>
       <c r="Z197">
-        <v>6.12</v>
+        <v>5.55</v>
       </c>
       <c r="AA197">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB197">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC197">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AD197">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE197">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF197">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG197">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK197">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32586,10 +32586,10 @@
         <v>1.95</v>
       </c>
       <c r="O198">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P198">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q198">
         <v>2.45</v>
@@ -32598,16 +32598,16 @@
         <v>2.25</v>
       </c>
       <c r="S198">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T198">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="U198">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="V198">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W198">
         <v>1.05</v>
@@ -32622,7 +32622,7 @@
         <v>3.42</v>
       </c>
       <c r="AA198">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB198">
         <v>1.89</v>
@@ -32634,10 +32634,10 @@
         <v>1.29</v>
       </c>
       <c r="AE198">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF198">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG198">
         <v>1.97</v>
@@ -32803,7 +32803,7 @@
         <v>1.78</v>
       </c>
       <c r="AG199">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -33238,10 +33238,10 @@
         <v>4.8</v>
       </c>
       <c r="O202">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="P202">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q202">
         <v>4.03</v>
@@ -33280,10 +33280,10 @@
         <v>2.88</v>
       </c>
       <c r="AC202">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AD202">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AE202">
         <v>1.33</v>
@@ -33440,7 +33440,7 @@
         <v>1.57</v>
       </c>
       <c r="AB203">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC203">
         <v>2.41</v>
@@ -33603,7 +33603,7 @@
         <v>1.6</v>
       </c>
       <c r="AB204">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC204">
         <v>2.38</v>
@@ -33766,7 +33766,7 @@
         <v>2.13</v>
       </c>
       <c r="AB205">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC205">
         <v>3.8</v>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AK205">
         <v>1.19</v>
@@ -35882,10 +35882,10 @@
         <v>3.58</v>
       </c>
       <c r="AA218">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB218">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC218">
         <v>2.83</v>
@@ -36863,7 +36863,7 @@
         <v>1.61</v>
       </c>
       <c r="AB224">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC224">
         <v>2.46</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="O227">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P227">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="Q227">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="R227">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S227">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="T227">
-        <v>3.28</v>
+        <v>2.72</v>
       </c>
       <c r="U227">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="V227">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W227">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X227">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y227">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z227">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA227">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AB227">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AC227">
-        <v>2.53</v>
+        <v>3.34</v>
       </c>
       <c r="AD227">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE227">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF227">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG227">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK227">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37515,7 +37515,7 @@
         <v>1.6</v>
       </c>
       <c r="AB228">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="AC228">
         <v>2.4</v>
@@ -37636,7 +37636,7 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="O229">
         <v>4.24</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,65 +37799,65 @@
         </is>
       </c>
       <c r="N230">
+        <v>2.09</v>
+      </c>
+      <c r="O230">
+        <v>3.6</v>
+      </c>
+      <c r="P230">
+        <v>3.25</v>
+      </c>
+      <c r="Q230">
         <v>2.7</v>
       </c>
-      <c r="O230">
-        <v>3.26</v>
-      </c>
-      <c r="P230">
+      <c r="R230">
+        <v>2.22</v>
+      </c>
+      <c r="S230">
+        <v>1.32</v>
+      </c>
+      <c r="T230">
+        <v>3.28</v>
+      </c>
+      <c r="U230">
+        <v>2.51</v>
+      </c>
+      <c r="V230">
+        <v>1.5</v>
+      </c>
+      <c r="W230">
+        <v>1.08</v>
+      </c>
+      <c r="X230">
+        <v>1.01</v>
+      </c>
+      <c r="Y230">
+        <v>1.19</v>
+      </c>
+      <c r="Z230">
+        <v>4.05</v>
+      </c>
+      <c r="AA230">
+        <v>1.65</v>
+      </c>
+      <c r="AB230">
+        <v>2.07</v>
+      </c>
+      <c r="AC230">
+        <v>2.53</v>
+      </c>
+      <c r="AD230">
+        <v>1.4</v>
+      </c>
+      <c r="AE230">
+        <v>1.12</v>
+      </c>
+      <c r="AF230">
+        <v>1.58</v>
+      </c>
+      <c r="AG230">
         <v>2.23</v>
       </c>
-      <c r="Q230">
-        <v>3.68</v>
-      </c>
-      <c r="R230">
-        <v>2.05</v>
-      </c>
-      <c r="S230">
-        <v>1.44</v>
-      </c>
-      <c r="T230">
-        <v>2.72</v>
-      </c>
-      <c r="U230">
-        <v>2.88</v>
-      </c>
-      <c r="V230">
-        <v>1.36</v>
-      </c>
-      <c r="W230">
-        <v>1.06</v>
-      </c>
-      <c r="X230">
-        <v>1.02</v>
-      </c>
-      <c r="Y230">
-        <v>1.3</v>
-      </c>
-      <c r="Z230">
-        <v>3.14</v>
-      </c>
-      <c r="AA230">
-        <v>2</v>
-      </c>
-      <c r="AB230">
-        <v>1.82</v>
-      </c>
-      <c r="AC230">
-        <v>3.34</v>
-      </c>
-      <c r="AD230">
-        <v>1.27</v>
-      </c>
-      <c r="AE230">
-        <v>1.06</v>
-      </c>
-      <c r="AF230">
-        <v>1.75</v>
-      </c>
-      <c r="AG230">
-        <v>1.95</v>
-      </c>
       <c r="AH230" t="inlineStr">
         <is>
           <t>[]</t>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK230">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38460,7 +38460,7 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>4.96</v>
+        <v>4.75</v>
       </c>
       <c r="R234">
         <v>2.1</v>
@@ -38620,7 +38620,7 @@
         <v>3.3</v>
       </c>
       <c r="P235">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q235">
         <v>3.1</v>
@@ -38635,7 +38635,7 @@
         <v>3.6</v>
       </c>
       <c r="U235">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="V235">
         <v>1.5</v>
@@ -38979,10 +38979,10 @@
         <v>4.4</v>
       </c>
       <c r="AA237">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB237">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AC237">
         <v>2.46</v>
@@ -39305,10 +39305,10 @@
         <v>3.04</v>
       </c>
       <c r="AA239">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB239">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC239">
         <v>3.34</v>
@@ -40123,7 +40123,7 @@
         <v>1.93</v>
       </c>
       <c r="AB244">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC244">
         <v>3.28</v>
@@ -40298,10 +40298,10 @@
         <v>1.29</v>
       </c>
       <c r="AF245">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG245">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>3.8</v>
       </c>
       <c r="O247">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="P247">
         <v>1.9</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="O248">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P248">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q248">
         <v>2.88</v>
@@ -40757,10 +40757,10 @@
         <v>2.3</v>
       </c>
       <c r="V248">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W248">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X248">
         <v>1.02</v>
@@ -40772,13 +40772,13 @@
         <v>4.6</v>
       </c>
       <c r="AA248">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB248">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AC248">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD248">
         <v>1.46</v>
@@ -40787,7 +40787,7 @@
         <v>1.15</v>
       </c>
       <c r="AF248">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG248">
         <v>2.45</v>
@@ -40803,7 +40803,7 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK248">
         <v>1.53</v>
@@ -41264,7 +41264,7 @@
         <v>1.7</v>
       </c>
       <c r="AB251">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC251">
         <v>2.75</v>
@@ -41557,7 +41557,7 @@
         <v>4.33</v>
       </c>
       <c r="Q253">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="R253">
         <v>2.36</v>
@@ -41590,7 +41590,7 @@
         <v>1.57</v>
       </c>
       <c r="AB253">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC253">
         <v>2.55</v>
@@ -41714,7 +41714,7 @@
         <v>2.43</v>
       </c>
       <c r="O254">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P254">
         <v>2.9</v>
@@ -42891,10 +42891,10 @@
         <v>0</v>
       </c>
       <c r="AA261">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB261">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC261">
         <v>0</v>
@@ -43024,7 +43024,7 @@
         <v>0</v>
       </c>
       <c r="Q262">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R262">
         <v>2.6</v>
@@ -43039,10 +43039,10 @@
         <v>2.08</v>
       </c>
       <c r="V262">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W262">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X262">
         <v>1.02</v>
@@ -43051,13 +43051,13 @@
         <v>1.11</v>
       </c>
       <c r="Z262">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA262">
         <v>1.4</v>
       </c>
       <c r="AB262">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC262">
         <v>2.25</v>
@@ -43066,13 +43066,13 @@
         <v>1.62</v>
       </c>
       <c r="AE262">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF262">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG262">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43670,10 +43670,10 @@
         <v>4.8</v>
       </c>
       <c r="O266">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P266">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q266">
         <v>5.5</v>
@@ -43709,7 +43709,7 @@
         <v>1.6</v>
       </c>
       <c r="AB266">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AC266">
         <v>2.56</v>
@@ -43999,7 +43999,7 @@
         <v>5.6</v>
       </c>
       <c r="P268">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q268">
         <v>1.67</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G269">
@@ -44165,13 +44165,13 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R269">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S269">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T269">
         <v>2.2</v>
@@ -44183,25 +44183,25 @@
         <v>1.2</v>
       </c>
       <c r="W269">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X269">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y269">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z269">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AA269">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB269">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC269">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AD269">
         <v>1.04</v>
@@ -44210,10 +44210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AG269">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AK269">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G270">
@@ -44328,43 +44328,43 @@
         <v>0</v>
       </c>
       <c r="Q270">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R270">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S270">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T270">
         <v>2.2</v>
       </c>
       <c r="U270">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V270">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X270">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y270">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z270">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AA270">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB270">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC270">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AD270">
         <v>1.04</v>
@@ -44373,10 +44373,10 @@
         <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AG270">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AK270">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44539,7 +44539,7 @@
         <v>1.29</v>
       </c>
       <c r="AG271">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44684,10 +44684,10 @@
         <v>2.69</v>
       </c>
       <c r="AA272">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB272">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC272">
         <v>3.94</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,80 +44971,80 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="O274">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P274">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="Q274">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R274">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S274">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T274">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="U274">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V274">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W274">
         <v>1.03</v>
       </c>
       <c r="X274">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y274">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z274">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="AA274">
+        <v>2.35</v>
+      </c>
+      <c r="AB274">
+        <v>1.53</v>
+      </c>
+      <c r="AC274">
+        <v>4.33</v>
+      </c>
+      <c r="AD274">
+        <v>1.14</v>
+      </c>
+      <c r="AE274">
+        <v>1.01</v>
+      </c>
+      <c r="AF274">
+        <v>2.21</v>
+      </c>
+      <c r="AG274">
+        <v>1.58</v>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ274">
+        <v>1.3</v>
+      </c>
+      <c r="AK274">
         <v>2.15</v>
-      </c>
-      <c r="AB274">
-        <v>1.62</v>
-      </c>
-      <c r="AC274">
-        <v>3.72</v>
-      </c>
-      <c r="AD274">
-        <v>1.2</v>
-      </c>
-      <c r="AE274">
-        <v>1.04</v>
-      </c>
-      <c r="AF274">
-        <v>2</v>
-      </c>
-      <c r="AG274">
-        <v>1.75</v>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ274">
-        <v>1.24</v>
-      </c>
-      <c r="AK274">
-        <v>1.83</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
+        <v>3.2</v>
+      </c>
+      <c r="O275">
+        <v>2.8</v>
+      </c>
+      <c r="P275">
+        <v>2.3</v>
+      </c>
+      <c r="Q275">
+        <v>4.34</v>
+      </c>
+      <c r="R275">
+        <v>1.81</v>
+      </c>
+      <c r="S275">
         <v>1.62</v>
       </c>
-      <c r="O275">
-        <v>3.5</v>
-      </c>
-      <c r="P275">
-        <v>5.25</v>
-      </c>
-      <c r="Q275">
-        <v>2.25</v>
-      </c>
-      <c r="R275">
-        <v>1.98</v>
-      </c>
-      <c r="S275">
-        <v>1.43</v>
-      </c>
       <c r="T275">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="U275">
-        <v>3.1</v>
+        <v>4.25</v>
       </c>
       <c r="V275">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="W275">
         <v>1.03</v>
       </c>
       <c r="X275">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y275">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Z275">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
       <c r="AA275">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AB275">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC275">
-        <v>4.33</v>
+        <v>6.65</v>
       </c>
       <c r="AD275">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AE275">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF275">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="AG275">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AK275">
-        <v>2.15</v>
+        <v>1.27</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,61 +45297,61 @@
         </is>
       </c>
       <c r="N276">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O276">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P276">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q276">
-        <v>4.34</v>
+        <v>2.5</v>
       </c>
       <c r="R276">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S276">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="T276">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U276">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="V276">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W276">
+        <v>1.01</v>
+      </c>
+      <c r="X276">
+        <v>1.13</v>
+      </c>
+      <c r="Y276">
+        <v>1.63</v>
+      </c>
+      <c r="Z276">
+        <v>2.24</v>
+      </c>
+      <c r="AA276">
+        <v>2.95</v>
+      </c>
+      <c r="AB276">
+        <v>1.36</v>
+      </c>
+      <c r="AC276">
+        <v>6</v>
+      </c>
+      <c r="AD276">
+        <v>1.06</v>
+      </c>
+      <c r="AE276">
         <v>1.03</v>
       </c>
-      <c r="X276">
-        <v>1.08</v>
-      </c>
-      <c r="Y276">
-        <v>1.67</v>
-      </c>
-      <c r="Z276">
-        <v>2.04</v>
-      </c>
-      <c r="AA276">
-        <v>3.4</v>
-      </c>
-      <c r="AB276">
-        <v>1.33</v>
-      </c>
-      <c r="AC276">
-        <v>6.65</v>
-      </c>
-      <c r="AD276">
-        <v>1.05</v>
-      </c>
-      <c r="AE276">
-        <v>1.02</v>
-      </c>
       <c r="AF276">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AG276">
         <v>1.49</v>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AK276">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q277">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R277">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="S277">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="T277">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="U277">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="V277">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="W277">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X277">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y277">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="Z277">
-        <v>2.24</v>
+        <v>2.95</v>
       </c>
       <c r="AA277">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB277">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC277">
-        <v>6</v>
+        <v>3.72</v>
       </c>
       <c r="AD277">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AE277">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF277">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AG277">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>1.97</v>
       </c>
       <c r="AD281">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE281">
         <v>1.33</v>
@@ -46314,10 +46314,10 @@
         <v>3.44</v>
       </c>
       <c r="AA282">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB282">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC282">
         <v>3</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="O284">
         <v>2.9</v>
       </c>
       <c r="P284">
-        <v>3.75</v>
+        <v>3.91</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46806,7 +46806,7 @@
         <v>2.88</v>
       </c>
       <c r="AB285">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC285">
         <v>5.85</v>
@@ -46939,68 +46939,68 @@
         <v>1.57</v>
       </c>
       <c r="R286">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S286">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T286">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="U286">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="V286">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W286">
+        <v>1.06</v>
+      </c>
+      <c r="X286">
+        <v>1.01</v>
+      </c>
+      <c r="Y286">
+        <v>1.23</v>
+      </c>
+      <c r="Z286">
+        <v>3.3</v>
+      </c>
+      <c r="AA286">
+        <v>1.82</v>
+      </c>
+      <c r="AB286">
+        <v>1.85</v>
+      </c>
+      <c r="AC286">
+        <v>3.05</v>
+      </c>
+      <c r="AD286">
+        <v>1.28</v>
+      </c>
+      <c r="AE286">
+        <v>1.07</v>
+      </c>
+      <c r="AF286">
+        <v>2.7</v>
+      </c>
+      <c r="AG286">
+        <v>1.4</v>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ286">
         <v>1.08</v>
       </c>
-      <c r="X286">
-        <v>1.03</v>
-      </c>
-      <c r="Y286">
-        <v>1.18</v>
-      </c>
-      <c r="Z286">
-        <v>3.52</v>
-      </c>
-      <c r="AA286">
-        <v>1.68</v>
-      </c>
-      <c r="AB286">
-        <v>2.02</v>
-      </c>
-      <c r="AC286">
-        <v>2.7</v>
-      </c>
-      <c r="AD286">
-        <v>1.36</v>
-      </c>
-      <c r="AE286">
-        <v>1.1</v>
-      </c>
-      <c r="AF286">
-        <v>2.45</v>
-      </c>
-      <c r="AG286">
-        <v>1.5</v>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI286" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ286">
-        <v>1.06</v>
-      </c>
       <c r="AK286">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47253,7 +47253,7 @@
         </is>
       </c>
       <c r="N288">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O288">
         <v>5.15</v>
@@ -47905,34 +47905,34 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="O292">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="P292">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Q292">
         <v>1.92</v>
       </c>
       <c r="R292">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="S292">
         <v>1.09</v>
       </c>
       <c r="T292">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="U292">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V292">
         <v>2.2</v>
       </c>
       <c r="W292">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X292">
         <v>1</v>
@@ -47947,19 +47947,19 @@
         <v>1.14</v>
       </c>
       <c r="AB292">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AC292">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD292">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AE292">
         <v>1.71</v>
       </c>
       <c r="AF292">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AG292">
         <v>3.4</v>
@@ -47978,7 +47978,7 @@
         <v>1.2</v>
       </c>
       <c r="AK292">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48729,55 +48729,55 @@
         <v>4.58</v>
       </c>
       <c r="Q297">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R297">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T297">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U297">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V297">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W297">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X297">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z297">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA297">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB297">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC297">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD297">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE297">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF297">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG297">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK297">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48907,7 +48907,7 @@
         <v>2.42</v>
       </c>
       <c r="V298">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W298">
         <v>1.13</v>
@@ -48922,16 +48922,16 @@
         <v>4.25</v>
       </c>
       <c r="AA298">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB298">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC298">
         <v>2.52</v>
       </c>
       <c r="AD298">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE298">
         <v>1.12</v>
@@ -48940,7 +48940,7 @@
         <v>1.55</v>
       </c>
       <c r="AG298">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>1.22</v>
       </c>
       <c r="AK298">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="O299">
-        <v>8.35</v>
+        <v>5.8</v>
       </c>
       <c r="P299">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q299">
         <v>1.52</v>
@@ -49067,13 +49067,13 @@
         <v>4</v>
       </c>
       <c r="U299">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V299">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W299">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X299">
         <v>1.01</v>
@@ -49085,25 +49085,25 @@
         <v>5.75</v>
       </c>
       <c r="AA299">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB299">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AC299">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AD299">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE299">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF299">
         <v>1.91</v>
       </c>
       <c r="AG299">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AK299">
-        <v>3.69</v>
+        <v>3.96</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O302">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P302">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q302">
         <v>2.37</v>
@@ -49562,10 +49562,10 @@
         <v>1.31</v>
       </c>
       <c r="W302">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X302">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y302">
         <v>1.33</v>
@@ -49574,7 +49574,7 @@
         <v>2.83</v>
       </c>
       <c r="AA302">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB302">
         <v>1.6</v>
@@ -49583,7 +49583,7 @@
         <v>3.92</v>
       </c>
       <c r="AD302">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE302">
         <v>1.02</v>
@@ -49592,7 +49592,7 @@
         <v>1.93</v>
       </c>
       <c r="AG302">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK302">
         <v>1.83</v>
@@ -49704,10 +49704,10 @@
         <v>3.4</v>
       </c>
       <c r="P303">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q303">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R303">
         <v>2.22</v>
@@ -49716,46 +49716,46 @@
         <v>1.29</v>
       </c>
       <c r="T303">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U303">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V303">
         <v>1.53</v>
       </c>
       <c r="W303">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X303">
         <v>1.01</v>
       </c>
       <c r="Y303">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z303">
         <v>4.05</v>
       </c>
       <c r="AA303">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB303">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC303">
         <v>2.65</v>
       </c>
       <c r="AD303">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE303">
         <v>1.13</v>
       </c>
       <c r="AF303">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG303">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q3">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="U3">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB3">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD3">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.13</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.45</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>2.58</v>
+        <v>4.68</v>
       </c>
       <c r="R4">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="S4">
+        <v>1.36</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>2.62</v>
+      </c>
+      <c r="V4">
         <v>1.4</v>
       </c>
-      <c r="T4">
-        <v>2.57</v>
-      </c>
-      <c r="U4">
-        <v>2.85</v>
-      </c>
-      <c r="V4">
-        <v>1.33</v>
-      </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.23</v>
+      </c>
+      <c r="Z4">
+        <v>3.42</v>
+      </c>
+      <c r="AA4">
+        <v>1.9</v>
+      </c>
+      <c r="AB4">
+        <v>1.92</v>
+      </c>
+      <c r="AC4">
+        <v>2.92</v>
+      </c>
+      <c r="AD4">
         <v>1.3</v>
       </c>
-      <c r="Z4">
-        <v>2.97</v>
-      </c>
-      <c r="AA4">
-        <v>2.09</v>
-      </c>
-      <c r="AB4">
+      <c r="AE4">
+        <v>1.08</v>
+      </c>
+      <c r="AF4">
         <v>1.73</v>
       </c>
-      <c r="AC4">
-        <v>3.42</v>
-      </c>
-      <c r="AD4">
-        <v>1.23</v>
-      </c>
-      <c r="AE4">
-        <v>1.05</v>
-      </c>
-      <c r="AF4">
-        <v>1.8</v>
-      </c>
       <c r="AG4">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U5">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z5">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB5">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
         <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="Z6">
-        <v>4.95</v>
+        <v>2.77</v>
       </c>
       <c r="AA6">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="AB6">
-        <v>2.29</v>
+        <v>1.59</v>
       </c>
       <c r="AC6">
-        <v>2.25</v>
+        <v>3.92</v>
       </c>
       <c r="AD6">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AG6">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>2.09</v>
+      </c>
+      <c r="R7">
+        <v>2.37</v>
+      </c>
+      <c r="S7">
+        <v>1.22</v>
+      </c>
+      <c r="T7">
         <v>3.5</v>
       </c>
-      <c r="P7">
-        <v>4.6</v>
-      </c>
-      <c r="Q7">
-        <v>2.4</v>
-      </c>
-      <c r="R7">
-        <v>2.1</v>
-      </c>
-      <c r="S7">
-        <v>1.41</v>
-      </c>
-      <c r="T7">
-        <v>2.55</v>
-      </c>
       <c r="U7">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>2.7</v>
+        <v>4.95</v>
       </c>
       <c r="AA7">
-        <v>2.17</v>
+        <v>1.47</v>
       </c>
       <c r="AB7">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="AC7">
-        <v>3.92</v>
+        <v>2.27</v>
       </c>
       <c r="AD7">
+        <v>1.54</v>
+      </c>
+      <c r="AE7">
         <v>1.18</v>
       </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
       <c r="AF7">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="AG7">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.64</v>
+        <v>1.6</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>2.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q8">
-        <v>3.17</v>
+        <v>2.06</v>
       </c>
       <c r="R8">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
+        <v>1.36</v>
+      </c>
+      <c r="T8">
+        <v>2.9</v>
+      </c>
+      <c r="U8">
+        <v>2.76</v>
+      </c>
+      <c r="V8">
         <v>1.35</v>
       </c>
-      <c r="T8">
-        <v>2.77</v>
-      </c>
-      <c r="U8">
-        <v>2.69</v>
-      </c>
-      <c r="V8">
-        <v>1.37</v>
-      </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA8">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC8">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.83</v>
+      </c>
+      <c r="O9">
+        <v>3.35</v>
+      </c>
+      <c r="P9">
+        <v>3.6</v>
+      </c>
+      <c r="Q9">
+        <v>2.5</v>
+      </c>
+      <c r="R9">
+        <v>2.1</v>
+      </c>
+      <c r="S9">
+        <v>1.36</v>
+      </c>
+      <c r="T9">
+        <v>2.88</v>
+      </c>
+      <c r="U9">
+        <v>2.76</v>
+      </c>
+      <c r="V9">
+        <v>1.35</v>
+      </c>
+      <c r="W9">
+        <v>1.07</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.2</v>
+      </c>
+      <c r="AA9">
+        <v>2</v>
+      </c>
+      <c r="AB9">
+        <v>1.79</v>
+      </c>
+      <c r="AC9">
+        <v>3.2</v>
+      </c>
+      <c r="AD9">
+        <v>1.26</v>
+      </c>
+      <c r="AE9">
+        <v>1.06</v>
+      </c>
+      <c r="AF9">
         <v>1.75</v>
       </c>
-      <c r="O9">
-        <v>3.4</v>
-      </c>
-      <c r="P9">
-        <v>3.8</v>
-      </c>
-      <c r="Q9">
-        <v>2.3</v>
-      </c>
-      <c r="R9">
-        <v>2.24</v>
-      </c>
-      <c r="S9">
-        <v>1.26</v>
-      </c>
-      <c r="T9">
-        <v>3.24</v>
-      </c>
-      <c r="U9">
-        <v>2.45</v>
-      </c>
-      <c r="V9">
-        <v>1.5</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.18</v>
-      </c>
-      <c r="Z9">
-        <v>4</v>
-      </c>
-      <c r="AA9">
-        <v>1.65</v>
-      </c>
-      <c r="AB9">
-        <v>2.06</v>
-      </c>
-      <c r="AC9">
-        <v>2.59</v>
-      </c>
-      <c r="AD9">
-        <v>1.39</v>
-      </c>
-      <c r="AE9">
-        <v>1.14</v>
-      </c>
-      <c r="AF9">
-        <v>1.62</v>
-      </c>
       <c r="AG9">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.85</v>
+        <v>4.33</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>3.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q10">
+        <v>5</v>
+      </c>
+      <c r="R10">
+        <v>2.3</v>
+      </c>
+      <c r="S10">
+        <v>1.33</v>
+      </c>
+      <c r="T10">
+        <v>3.1</v>
+      </c>
+      <c r="U10">
         <v>2.5</v>
       </c>
-      <c r="R10">
-        <v>2.1</v>
-      </c>
-      <c r="S10">
-        <v>1.36</v>
-      </c>
-      <c r="T10">
-        <v>2.72</v>
-      </c>
-      <c r="U10">
-        <v>2.76</v>
-      </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
         <v>1.04</v>
       </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
+        <v>1.78</v>
+      </c>
+      <c r="AB10">
         <v>1.89</v>
       </c>
-      <c r="AB10">
-        <v>1.79</v>
-      </c>
       <c r="AC10">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="AD10">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>2.01</v>
       </c>
       <c r="AK10">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.33</v>
+        <v>1.76</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>1.64</v>
+        <v>3.8</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S11">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AC11">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,13 +2268,13 @@
         <v>2.41</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P12">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R12">
         <v>2.17</v>
@@ -2283,16 +2283,16 @@
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="U12">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -2301,25 +2301,25 @@
         <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
         <v>2.15</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R13">
         <v>2.08</v>
@@ -2449,10 +2449,10 @@
         <v>2.85</v>
       </c>
       <c r="U13">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.04</v>
@@ -2464,28 +2464,28 @@
         <v>1.23</v>
       </c>
       <c r="Z13">
-        <v>3.42</v>
+        <v>3.53</v>
       </c>
       <c r="AA13">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB13">
         <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
         <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="O14">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -2648,7 +2648,7 @@
         <v>1.76</v>
       </c>
       <c r="AG14">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2757,31 +2757,31 @@
         <v>1.72</v>
       </c>
       <c r="O15">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>4.56</v>
+        <v>4</v>
       </c>
       <c r="Q15">
         <v>2.24</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
         <v>2.53</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.03</v>
@@ -2790,44 +2790,44 @@
         <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB15">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AC15">
         <v>2.74</v>
       </c>
       <c r="AD15">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG15">
+        <v>2.05</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.2</v>
+      </c>
+      <c r="AK15">
         <v>2.1</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>2.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O16">
-        <v>5.28</v>
+        <v>4.8</v>
       </c>
       <c r="P16">
-        <v>9.1</v>
+        <v>8.25</v>
       </c>
       <c r="Q16">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="R16">
         <v>2.47</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="U16">
         <v>2.38</v>
@@ -2953,16 +2953,16 @@
         <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>3.82</v>
+        <v>4.17</v>
       </c>
       <c r="AA16">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC16">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD16">
         <v>1.38</v>
@@ -2971,7 +2971,7 @@
         <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
         <v>1.68</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AK16">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.16</v>
+        <v>2.89</v>
       </c>
       <c r="Q17">
         <v>2.68</v>
@@ -3116,7 +3116,7 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA17">
         <v>1.81</v>
@@ -3128,10 +3128,10 @@
         <v>2.81</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE17">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.44</v>
+        <v>2.29</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P18">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="Q18">
-        <v>4.64</v>
+        <v>2.67</v>
       </c>
       <c r="R18">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
         <v>2.88</v>
       </c>
       <c r="U18">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA18">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD18">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.78</v>
+        <v>3.44</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>3.75</v>
+        <v>1.99</v>
       </c>
       <c r="Q19">
-        <v>2.33</v>
+        <v>4.33</v>
       </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AB19">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
+        <v>1.95</v>
+      </c>
+      <c r="AK19">
         <v>1.2</v>
-      </c>
-      <c r="AK19">
-        <v>1.85</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="Q20">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4076,10 +4076,10 @@
         <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -4088,13 +4088,13 @@
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="AA23">
         <v>1.71</v>
@@ -4106,7 +4106,7 @@
         <v>2.62</v>
       </c>
       <c r="AD23">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE23">
         <v>1.11</v>
@@ -4115,7 +4115,7 @@
         <v>1.56</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
+        <v>4.6</v>
+      </c>
+      <c r="O47">
+        <v>4</v>
+      </c>
+      <c r="P47">
+        <v>1.53</v>
+      </c>
+      <c r="Q47">
         <v>4.9</v>
       </c>
-      <c r="O47">
-        <v>4.2</v>
-      </c>
-      <c r="P47">
-        <v>1.5</v>
-      </c>
-      <c r="Q47">
-        <v>4.95</v>
-      </c>
       <c r="R47">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S47">
         <v>1.17</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U47">
         <v>2.06</v>
@@ -8006,22 +8006,22 @@
         <v>1.09</v>
       </c>
       <c r="Z47">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AA47">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB47">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AC47">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD47">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE47">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF47">
         <v>1.5</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.13</v>
+        <v>2.23</v>
       </c>
       <c r="AK47">
         <v>1.1</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q54">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -9144,22 +9144,22 @@
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9184,7 +9184,7 @@
         <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O55">
         <v>3.5</v>
       </c>
       <c r="P55">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P56">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W56">
         <v>0</v>
@@ -9470,22 +9470,22 @@
         <v>0</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O77">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q77">
         <v>3.47</v>
@@ -12902,7 +12902,7 @@
         <v>1.78</v>
       </c>
       <c r="AB77">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
         <v>2.88</v>
@@ -13853,16 +13853,16 @@
         <v>2.88</v>
       </c>
       <c r="S83">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T83">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="U83">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V83">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="W83">
         <v>1.25</v>
@@ -13871,31 +13871,31 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z83">
         <v>8.5</v>
       </c>
       <c r="AA83">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB83">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="AC83">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AD83">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AE83">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AF83">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG83">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14001,34 +14001,34 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="O84">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P84">
-        <v>5.98</v>
+        <v>6.5</v>
       </c>
       <c r="Q84">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R84">
         <v>2.38</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T84">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U84">
         <v>2.38</v>
       </c>
       <c r="V84">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W84">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X84">
         <v>1.02</v>
@@ -14037,28 +14037,28 @@
         <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA84">
         <v>1.65</v>
       </c>
       <c r="AB84">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC84">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD84">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE84">
         <v>1.14</v>
       </c>
       <c r="AF84">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG84">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK84">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -18918,7 +18918,7 @@
         <v>1.53</v>
       </c>
       <c r="W114">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X114">
         <v>1.02</v>
@@ -19878,10 +19878,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Q120">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R120">
-        <v>3.51</v>
+        <v>3.24</v>
       </c>
       <c r="S120">
         <v>1.15</v>
@@ -19914,7 +19914,7 @@
         <v>4.1</v>
       </c>
       <c r="AC120">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AD120">
         <v>2.26</v>
@@ -19926,7 +19926,7 @@
         <v>1.49</v>
       </c>
       <c r="AG120">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>1.09</v>
       </c>
       <c r="AK120">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20050,7 +20050,7 @@
         <v>1.22</v>
       </c>
       <c r="T121">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="U121">
         <v>2.1</v>
@@ -20071,25 +20071,25 @@
         <v>5.25</v>
       </c>
       <c r="AA121">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB121">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC121">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD121">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE121">
         <v>1.22</v>
       </c>
       <c r="AF121">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG121">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O162">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P162">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q162">
         <v>3.04</v>
@@ -26733,13 +26733,13 @@
         <v>1.25</v>
       </c>
       <c r="T162">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U162">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V162">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W162">
         <v>1.13</v>
@@ -26757,7 +26757,7 @@
         <v>1.57</v>
       </c>
       <c r="AB162">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC162">
         <v>2.43</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G184">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O212">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="P212">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Q212">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="R212">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="S212">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T212">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U212">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="V212">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W212">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z212">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="AA212">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB212">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AC212">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AD212">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AE212">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF212">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AG212">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="AK212">
         <v>1.01</v>
@@ -36181,7 +36181,7 @@
         <v>2.02</v>
       </c>
       <c r="R220">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="S220">
         <v>1.17</v>
@@ -36190,13 +36190,13 @@
         <v>4.5</v>
       </c>
       <c r="U220">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V220">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W220">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X220">
         <v>1.01</v>
@@ -36208,16 +36208,16 @@
         <v>6.7</v>
       </c>
       <c r="AA220">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB220">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AC220">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD220">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AE220">
         <v>1.36</v>
@@ -36242,7 +36242,7 @@
         <v>1.2</v>
       </c>
       <c r="AK220">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36344,7 +36344,7 @@
         <v>3.75</v>
       </c>
       <c r="R221">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="S221">
         <v>1.15</v>
@@ -36353,7 +36353,7 @@
         <v>5</v>
       </c>
       <c r="U221">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V221">
         <v>2.05</v>
@@ -36362,7 +36362,7 @@
         <v>1.29</v>
       </c>
       <c r="X221">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y221">
         <v>1.03</v>
@@ -36380,10 +36380,10 @@
         <v>1.57</v>
       </c>
       <c r="AD221">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AE221">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AF221">
         <v>1.25</v>
@@ -36676,16 +36676,16 @@
         <v>1.22</v>
       </c>
       <c r="T223">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U223">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V223">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W223">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X223">
         <v>1.01</v>
@@ -36694,28 +36694,28 @@
         <v>1.1</v>
       </c>
       <c r="Z223">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AA223">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB223">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC223">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AD223">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE223">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF223">
         <v>1.5</v>
       </c>
       <c r="AG223">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="O228">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P228">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q228">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="R228">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="S228">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T228">
-        <v>3.84</v>
+        <v>3.28</v>
       </c>
       <c r="U228">
-        <v>2.19</v>
+        <v>2.51</v>
       </c>
       <c r="V228">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W228">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X228">
         <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z228">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA228">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB228">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="AC228">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AD228">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AE228">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF228">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG228">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AK228">
-        <v>2.46</v>
+        <v>1.7</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O229">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="P229">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Q229">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="R229">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S229">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T229">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="U229">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="V229">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="W229">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z229">
-        <v>5.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA229">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AB229">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="AC229">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AD229">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AE229">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AF229">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AG229">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK229">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.09</v>
+        <v>1.62</v>
       </c>
       <c r="O230">
-        <v>3.6</v>
+        <v>4.24</v>
       </c>
       <c r="P230">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q230">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="R230">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="S230">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T230">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U230">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="V230">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W230">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X230">
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z230">
-        <v>4.05</v>
+        <v>5.7</v>
       </c>
       <c r="AA230">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AB230">
-        <v>2.07</v>
+        <v>2.72</v>
       </c>
       <c r="AC230">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="AD230">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AE230">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AF230">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AG230">
-        <v>2.23</v>
+        <v>2.66</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK230">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G269">
@@ -44165,13 +44165,13 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R269">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S269">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T269">
         <v>2.2</v>
@@ -44183,25 +44183,25 @@
         <v>1.2</v>
       </c>
       <c r="W269">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X269">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y269">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z269">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AA269">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB269">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC269">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AD269">
         <v>1.04</v>
@@ -44210,10 +44210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AG269">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AK269">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G270">
@@ -44328,13 +44328,13 @@
         <v>0</v>
       </c>
       <c r="Q270">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R270">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S270">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T270">
         <v>2.2</v>
@@ -44346,25 +44346,25 @@
         <v>1.2</v>
       </c>
       <c r="W270">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X270">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y270">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z270">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AA270">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB270">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC270">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AD270">
         <v>1.04</v>
@@ -44373,10 +44373,10 @@
         <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AG270">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AK270">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q276">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R276">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="S276">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="T276">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="U276">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="V276">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="W276">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X276">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y276">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="Z276">
-        <v>2.24</v>
+        <v>2.95</v>
       </c>
       <c r="AA276">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB276">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC276">
-        <v>6</v>
+        <v>3.72</v>
       </c>
       <c r="AD276">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AE276">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF276">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AG276">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK276">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,80 +45460,80 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O277">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P277">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q277">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R277">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="S277">
+        <v>1.58</v>
+      </c>
+      <c r="T277">
+        <v>2.25</v>
+      </c>
+      <c r="U277">
+        <v>3.8</v>
+      </c>
+      <c r="V277">
+        <v>1.19</v>
+      </c>
+      <c r="W277">
+        <v>1.01</v>
+      </c>
+      <c r="X277">
+        <v>1.13</v>
+      </c>
+      <c r="Y277">
+        <v>1.63</v>
+      </c>
+      <c r="Z277">
+        <v>2.24</v>
+      </c>
+      <c r="AA277">
+        <v>2.95</v>
+      </c>
+      <c r="AB277">
+        <v>1.36</v>
+      </c>
+      <c r="AC277">
+        <v>6</v>
+      </c>
+      <c r="AD277">
+        <v>1.06</v>
+      </c>
+      <c r="AE277">
+        <v>1.03</v>
+      </c>
+      <c r="AF277">
+        <v>2.42</v>
+      </c>
+      <c r="AG277">
+        <v>1.49</v>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ277">
         <v>1.4</v>
       </c>
-      <c r="T277">
-        <v>2.71</v>
-      </c>
-      <c r="U277">
-        <v>3.2</v>
-      </c>
-      <c r="V277">
-        <v>1.32</v>
-      </c>
-      <c r="W277">
-        <v>1.03</v>
-      </c>
-      <c r="X277">
-        <v>1.03</v>
-      </c>
-      <c r="Y277">
-        <v>1.34</v>
-      </c>
-      <c r="Z277">
-        <v>2.95</v>
-      </c>
-      <c r="AA277">
-        <v>2.15</v>
-      </c>
-      <c r="AB277">
-        <v>1.62</v>
-      </c>
-      <c r="AC277">
-        <v>3.72</v>
-      </c>
-      <c r="AD277">
-        <v>1.2</v>
-      </c>
-      <c r="AE277">
-        <v>1.04</v>
-      </c>
-      <c r="AF277">
-        <v>2</v>
-      </c>
-      <c r="AG277">
-        <v>1.75</v>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ277">
-        <v>1.24</v>
-      </c>
       <c r="AK277">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45810,7 +45810,7 @@
         <v>2.3</v>
       </c>
       <c r="V279">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W279">
         <v>1.12</v>
@@ -45822,10 +45822,10 @@
         <v>1.14</v>
       </c>
       <c r="Z279">
-        <v>3.13</v>
+        <v>4.33</v>
       </c>
       <c r="AA279">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AB279">
         <v>1.89</v>
@@ -45834,13 +45834,13 @@
         <v>2.49</v>
       </c>
       <c r="AD279">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE279">
         <v>1.13</v>
       </c>
       <c r="AF279">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG279">
         <v>2.15</v>
@@ -49218,7 +49218,7 @@
         <v>2.94</v>
       </c>
       <c r="Q300">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R300">
         <v>2.3</v>
@@ -49227,7 +49227,7 @@
         <v>1.29</v>
       </c>
       <c r="T300">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="U300">
         <v>2.4</v>
@@ -49266,7 +49266,7 @@
         <v>1.6</v>
       </c>
       <c r="AG300">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>1.25</v>
       </c>
       <c r="AK300">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AL300">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="Q6">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="AA6">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AB6">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AC6">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="V7">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="Z7">
-        <v>4.95</v>
+        <v>2.77</v>
       </c>
       <c r="AA7">
-        <v>1.47</v>
+        <v>2.17</v>
       </c>
       <c r="AB7">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="AC7">
-        <v>2.27</v>
+        <v>3.92</v>
       </c>
       <c r="AD7">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AG7">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>2.09</v>
+      </c>
+      <c r="R8">
+        <v>2.37</v>
+      </c>
+      <c r="S8">
+        <v>1.22</v>
+      </c>
+      <c r="T8">
+        <v>3.5</v>
+      </c>
+      <c r="U8">
+        <v>2.2</v>
+      </c>
+      <c r="V8">
         <v>1.6</v>
       </c>
-      <c r="O8">
-        <v>3.6</v>
-      </c>
-      <c r="P8">
-        <v>4.6</v>
-      </c>
-      <c r="Q8">
-        <v>2.06</v>
-      </c>
-      <c r="R8">
-        <v>2.15</v>
-      </c>
-      <c r="S8">
-        <v>1.36</v>
-      </c>
-      <c r="T8">
-        <v>2.9</v>
-      </c>
-      <c r="U8">
-        <v>2.76</v>
-      </c>
-      <c r="V8">
-        <v>1.35</v>
-      </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z8">
-        <v>3.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA8">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AB8">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK8">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="O18">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2.82</v>
+        <v>1.99</v>
       </c>
       <c r="Q18">
-        <v>2.67</v>
+        <v>4.33</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
         <v>2.88</v>
       </c>
       <c r="U18">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
         <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA18">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB18">
+        <v>1.8</v>
+      </c>
+      <c r="AC18">
+        <v>3.34</v>
+      </c>
+      <c r="AD18">
+        <v>1.24</v>
+      </c>
+      <c r="AE18">
+        <v>1.05</v>
+      </c>
+      <c r="AF18">
         <v>1.79</v>
       </c>
-      <c r="AC18">
-        <v>3.14</v>
-      </c>
-      <c r="AD18">
-        <v>1.31</v>
-      </c>
-      <c r="AE18">
-        <v>1.07</v>
-      </c>
-      <c r="AF18">
-        <v>1.7</v>
-      </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AK18">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.44</v>
+        <v>1.78</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>1.99</v>
+        <v>3.75</v>
       </c>
       <c r="Q19">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AA19">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC19">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,58 +3569,58 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P20">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q20">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z20">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB20">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC20">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
         <v>3.5</v>
       </c>
       <c r="P21">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q21">
         <v>3.94</v>
@@ -4278,7 +4278,7 @@
         <v>1.44</v>
       </c>
       <c r="AG24">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4547,43 +4547,43 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA26">
         <v>1.8</v>
@@ -4592,19 +4592,19 @@
         <v>2</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5365,40 +5365,40 @@
         <v>1.91</v>
       </c>
       <c r="O31">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA31">
         <v>1.61</v>
@@ -5407,19 +5407,19 @@
         <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="Q32">
-        <v>4.68</v>
+        <v>3.52</v>
       </c>
       <c r="R32">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="U32">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA32">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="O33">
+        <v>3.68</v>
+      </c>
+      <c r="P33">
+        <v>1.57</v>
+      </c>
+      <c r="Q33">
+        <v>4.68</v>
+      </c>
+      <c r="R33">
+        <v>2.36</v>
+      </c>
+      <c r="S33">
+        <v>1.3</v>
+      </c>
+      <c r="T33">
         <v>3.25</v>
       </c>
-      <c r="P33">
-        <v>2.25</v>
-      </c>
-      <c r="Q33">
-        <v>3.52</v>
-      </c>
-      <c r="R33">
-        <v>2.07</v>
-      </c>
-      <c r="S33">
-        <v>1.33</v>
-      </c>
-      <c r="T33">
-        <v>2.85</v>
-      </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
         <v>2.88</v>
       </c>
       <c r="AD33">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,61 +5854,61 @@
         <v>1.8</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7336,7 +7336,7 @@
         <v>1.38</v>
       </c>
       <c r="T43">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="U43">
         <v>2.82</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA50">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P51">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA51">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB51">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8812,10 +8812,10 @@
         <v>1.53</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.14</v>
@@ -8824,10 +8824,10 @@
         <v>4.33</v>
       </c>
       <c r="AA52">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB52">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AC52">
         <v>2.43</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
         <v>3.3</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,61 +9277,61 @@
         <v>1.8</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O56">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P56">
         <v>2.8</v>
       </c>
       <c r="Q56">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R56">
         <v>1.95</v>
@@ -9464,10 +9464,10 @@
         <v>1.27</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.35</v>
@@ -9476,7 +9476,7 @@
         <v>2.74</v>
       </c>
       <c r="AA56">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB56">
         <v>1.58</v>
@@ -9488,13 +9488,13 @@
         <v>1.16</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK56">
         <v>1.45</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="O60">
         <v>3.6</v>
@@ -10107,7 +10107,7 @@
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U60">
         <v>2.25</v>
@@ -11447,10 +11447,10 @@
         <v>1.27</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="O78">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="P78">
         <v>1.68</v>
@@ -13515,61 +13515,61 @@
         <v>2.1</v>
       </c>
       <c r="O81">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P81">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14206,7 +14206,7 @@
         <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AC85">
         <v>1.86</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O87">
         <v>3.5</v>
@@ -14677,7 +14677,7 @@
         <v>2</v>
       </c>
       <c r="V88">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W88">
         <v>1.17</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O89">
         <v>3.7</v>
@@ -15347,7 +15347,7 @@
         <v>1.64</v>
       </c>
       <c r="AB92">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC92">
         <v>2.41</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16449,7 +16449,7 @@
         <v>1.63</v>
       </c>
       <c r="O99">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
         <v>5.75</v>
@@ -18444,7 +18444,7 @@
         <v>2.08</v>
       </c>
       <c r="AB111">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC111">
         <v>3.7</v>
@@ -19057,7 +19057,7 @@
         <v>1.44</v>
       </c>
       <c r="O115">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="P115">
         <v>5.25</v>
@@ -19383,7 +19383,7 @@
         <v>1.67</v>
       </c>
       <c r="O117">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P117">
         <v>4</v>
@@ -19558,7 +19558,7 @@
         <v>2.62</v>
       </c>
       <c r="S118">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T118">
         <v>5.2</v>
@@ -20527,7 +20527,7 @@
         <v>4.2</v>
       </c>
       <c r="P124">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q124">
         <v>1.87</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="O126">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P126">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="Q126">
         <v>2.45</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O127">
         <v>4</v>
@@ -21197,7 +21197,7 @@
         <v>2.4</v>
       </c>
       <c r="V128">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W128">
         <v>1.1</v>
@@ -21378,7 +21378,7 @@
         <v>1.55</v>
       </c>
       <c r="AB129">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AC129">
         <v>2.33</v>
@@ -21538,7 +21538,7 @@
         <v>4.11</v>
       </c>
       <c r="AA130">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB130">
         <v>2</v>
@@ -21547,7 +21547,7 @@
         <v>3.01</v>
       </c>
       <c r="AD130">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE130">
         <v>1.11</v>
@@ -21828,7 +21828,7 @@
         <v>1.3</v>
       </c>
       <c r="O132">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P132">
         <v>7.4</v>
@@ -22151,10 +22151,10 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="O134">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P134">
         <v>15</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O137">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="P137">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q137">
         <v>3.18</v>
@@ -23485,7 +23485,7 @@
         <v>1.09</v>
       </c>
       <c r="X142">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y142">
         <v>1.22</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="O144">
-        <v>3.37</v>
+        <v>4.3</v>
       </c>
       <c r="P144">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="Q144">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="R144">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="S144">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="T144">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="U144">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="V144">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="W144">
+        <v>1.17</v>
+      </c>
+      <c r="X144">
+        <v>1.02</v>
+      </c>
+      <c r="Y144">
         <v>1.06</v>
       </c>
-      <c r="X144">
-        <v>1.03</v>
-      </c>
-      <c r="Y144">
-        <v>1.25</v>
-      </c>
       <c r="Z144">
-        <v>3.1</v>
+        <v>6.05</v>
       </c>
       <c r="AA144">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AB144">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AC144">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="AD144">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AE144">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AF144">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AG144">
-        <v>2.05</v>
+        <v>2.76</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK144">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,80 +23944,80 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="O145">
-        <v>4.3</v>
+        <v>3.37</v>
       </c>
       <c r="P145">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="Q145">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="R145">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="S145">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="T145">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="U145">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="V145">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>6.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA145">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AB145">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC145">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="AD145">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="AE145">
+        <v>1.07</v>
+      </c>
+      <c r="AF145">
+        <v>1.7</v>
+      </c>
+      <c r="AG145">
+        <v>2.05</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ145">
         <v>1.3</v>
       </c>
-      <c r="AF145">
-        <v>1.4</v>
-      </c>
-      <c r="AG145">
-        <v>2.76</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>1.17</v>
-      </c>
       <c r="AK145">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -27702,55 +27702,55 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S168">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T168">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U168">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V168">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W168">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X168">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y168">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z168">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA168">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB168">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC168">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD168">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF168">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG168">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK168">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28363,40 +28363,40 @@
         <v>1.29</v>
       </c>
       <c r="T172">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U172">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V172">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W172">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X172">
         <v>1.02</v>
       </c>
       <c r="Y172">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z172">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA172">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB172">
         <v>2.25</v>
       </c>
       <c r="AC172">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD172">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE172">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF172">
         <v>1.6</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="O173">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="P173">
-        <v>3.08</v>
+        <v>6.37</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>6.37</v>
+        <v>0</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
         <v>0</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O176">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P176">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29160,10 +29160,10 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O177">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P177">
         <v>2.25</v>
@@ -30518,10 +30518,10 @@
         <v>1.13</v>
       </c>
       <c r="AF185">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG185">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>7.5</v>
       </c>
       <c r="AA186">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB186">
         <v>2.92</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P187">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="Q187">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="R187">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S187">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T187">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U187">
         <v>2.63</v>
       </c>
       <c r="V187">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W187">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X187">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z187">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="AA187">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB187">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC187">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AD187">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE187">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF187">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG187">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK187">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O188">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P188">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q188">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="R188">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="S188">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T188">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U188">
         <v>2.63</v>
       </c>
       <c r="V188">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W188">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z188">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="AA188">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB188">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AC188">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AD188">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE188">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF188">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG188">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK188">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31158,7 +31158,7 @@
         <v>1.88</v>
       </c>
       <c r="AB189">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC189">
         <v>2.88</v>
@@ -31448,7 +31448,7 @@
         <v>4</v>
       </c>
       <c r="P191">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q191">
         <v>2.01</v>
@@ -32755,55 +32755,55 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R199">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S199">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T199">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U199">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V199">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W199">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X199">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y199">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z199">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA199">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB199">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC199">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD199">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE199">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF199">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG199">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK199">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33618,7 +33618,7 @@
         <v>1.5</v>
       </c>
       <c r="AG204">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R205">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S205">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T205">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U205">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V205">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W205">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X205">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y205">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z205">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA205">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB205">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC205">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD205">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE205">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF205">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG205">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AK205">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="O207">
-        <v>3.3</v>
+        <v>4.06</v>
       </c>
       <c r="P207">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q207">
-        <v>2.94</v>
+        <v>2.16</v>
       </c>
       <c r="R207">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="S207">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T207">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="U207">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="V207">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="W207">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z207">
-        <v>4</v>
+        <v>6.79</v>
       </c>
       <c r="AA207">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AB207">
-        <v>2.11</v>
+        <v>2.83</v>
       </c>
       <c r="AC207">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="AD207">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AE207">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AF207">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG207">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK207">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O208">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="P208">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q208">
-        <v>2.16</v>
+        <v>2.94</v>
       </c>
       <c r="R208">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="S208">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T208">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="U208">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="V208">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="W208">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z208">
-        <v>6.79</v>
+        <v>4</v>
       </c>
       <c r="AA208">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AB208">
-        <v>2.83</v>
+        <v>2.11</v>
       </c>
       <c r="AC208">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="AD208">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AE208">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AF208">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG208">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK208">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -35360,7 +35360,7 @@
         <v>3.7</v>
       </c>
       <c r="P215">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q215">
         <v>2.63</v>
@@ -35378,7 +35378,7 @@
         <v>2.13</v>
       </c>
       <c r="V215">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W215">
         <v>1.17</v>
@@ -35399,7 +35399,7 @@
         <v>2.75</v>
       </c>
       <c r="AC215">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD215">
         <v>1.71</v>
@@ -35852,55 +35852,55 @@
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R218">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S218">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T218">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U218">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V218">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W218">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y218">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z218">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA218">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB218">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC218">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD218">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE218">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF218">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG218">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK218">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36863,7 +36863,7 @@
         <v>1.61</v>
       </c>
       <c r="AB224">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC224">
         <v>2.46</v>
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O226">
         <v>4.25</v>
       </c>
       <c r="P226">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="Q226">
         <v>2.17</v>
@@ -37162,7 +37162,7 @@
         <v>2.38</v>
       </c>
       <c r="S226">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T226">
         <v>3.52</v>
@@ -37174,7 +37174,7 @@
         <v>1.5</v>
       </c>
       <c r="W226">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X226">
         <v>1.01</v>
@@ -37186,7 +37186,7 @@
         <v>4.4</v>
       </c>
       <c r="AA226">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB226">
         <v>2.3</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="O228">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P228">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="Q228">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="R228">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S228">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T228">
-        <v>3.28</v>
+        <v>3.84</v>
       </c>
       <c r="U228">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="V228">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W228">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X228">
         <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z228">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA228">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB228">
-        <v>2.07</v>
+        <v>2.54</v>
       </c>
       <c r="AC228">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AD228">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE228">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF228">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG228">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AK228">
-        <v>1.7</v>
+        <v>2.46</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O229">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="P229">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Q229">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R229">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S229">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T229">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="U229">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="V229">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="W229">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z229">
-        <v>4.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA229">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AB229">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="AC229">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AD229">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AE229">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AF229">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AG229">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK229">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="O230">
-        <v>4.24</v>
+        <v>3.6</v>
       </c>
       <c r="P230">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="Q230">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="R230">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="S230">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T230">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U230">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="V230">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W230">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X230">
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z230">
-        <v>5.7</v>
+        <v>4.05</v>
       </c>
       <c r="AA230">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AB230">
-        <v>2.72</v>
+        <v>2.07</v>
       </c>
       <c r="AC230">
-        <v>2.12</v>
+        <v>2.53</v>
       </c>
       <c r="AD230">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AE230">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AF230">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AG230">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK230">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38460,55 +38460,55 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R234">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S234">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T234">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U234">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V234">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W234">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X234">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y234">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z234">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA234">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB234">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC234">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD234">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE234">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF234">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG234">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK234">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R237">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S237">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T237">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U237">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V237">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W237">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X237">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y237">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z237">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA237">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB237">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC237">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD237">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE237">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF237">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG237">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK237">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39272,7 +39272,7 @@
         <v>3.5</v>
       </c>
       <c r="P239">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q239">
         <v>2.15</v>
@@ -39429,7 +39429,7 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O240">
         <v>3.1</v>
@@ -39785,7 +39785,7 @@
         <v>1.3</v>
       </c>
       <c r="X242">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y242">
         <v>1.01</v>
@@ -40090,55 +40090,55 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R244">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S244">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T244">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U244">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V244">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W244">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X244">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y244">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z244">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA244">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB244">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC244">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD244">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE244">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF244">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG244">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK244">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40428,7 +40428,7 @@
         <v>3.4</v>
       </c>
       <c r="U246">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="V246">
         <v>1.56</v>
@@ -40449,13 +40449,13 @@
         <v>1.6</v>
       </c>
       <c r="AB246">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC246">
         <v>2.36</v>
       </c>
       <c r="AD246">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE246">
         <v>1.18</v>
@@ -40570,7 +40570,7 @@
         </is>
       </c>
       <c r="N247">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O247">
         <v>3.12</v>
@@ -41222,7 +41222,7 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="O251">
         <v>4.1</v>
@@ -42242,7 +42242,7 @@
         <v>1.77</v>
       </c>
       <c r="AB257">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC257">
         <v>2.83</v>
@@ -42852,43 +42852,43 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q261">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R261">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S261">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T261">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U261">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V261">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W261">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X261">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y261">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z261">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA261">
         <v>2.15</v>
@@ -42897,19 +42897,19 @@
         <v>1.66</v>
       </c>
       <c r="AC261">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD261">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE261">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF261">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG261">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK261">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43836,7 +43836,7 @@
         <v>3.3</v>
       </c>
       <c r="P267">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q267">
         <v>3.1</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G269">
@@ -44165,13 +44165,13 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R269">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S269">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T269">
         <v>2.2</v>
@@ -44183,25 +44183,25 @@
         <v>1.2</v>
       </c>
       <c r="W269">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X269">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y269">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z269">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AA269">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB269">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC269">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AD269">
         <v>1.04</v>
@@ -44210,10 +44210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AG269">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AK269">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G270">
@@ -44328,13 +44328,13 @@
         <v>0</v>
       </c>
       <c r="Q270">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R270">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S270">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T270">
         <v>2.2</v>
@@ -44346,25 +44346,25 @@
         <v>1.2</v>
       </c>
       <c r="W270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X270">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y270">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z270">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AA270">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB270">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC270">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AD270">
         <v>1.04</v>
@@ -44373,10 +44373,10 @@
         <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AG270">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AK270">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44687,7 +44687,7 @@
         <v>2.25</v>
       </c>
       <c r="AB272">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC272">
         <v>3.94</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O275">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P275">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q275">
-        <v>4.34</v>
+        <v>2.5</v>
       </c>
       <c r="R275">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S275">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="T275">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U275">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="V275">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W275">
+        <v>1.01</v>
+      </c>
+      <c r="X275">
+        <v>1.13</v>
+      </c>
+      <c r="Y275">
+        <v>1.63</v>
+      </c>
+      <c r="Z275">
+        <v>2.24</v>
+      </c>
+      <c r="AA275">
+        <v>3.1</v>
+      </c>
+      <c r="AB275">
+        <v>1.36</v>
+      </c>
+      <c r="AC275">
+        <v>6</v>
+      </c>
+      <c r="AD275">
+        <v>1.06</v>
+      </c>
+      <c r="AE275">
         <v>1.03</v>
       </c>
-      <c r="X275">
-        <v>1.08</v>
-      </c>
-      <c r="Y275">
-        <v>1.67</v>
-      </c>
-      <c r="Z275">
-        <v>2.04</v>
-      </c>
-      <c r="AA275">
-        <v>3.4</v>
-      </c>
-      <c r="AB275">
-        <v>1.33</v>
-      </c>
-      <c r="AC275">
-        <v>6.65</v>
-      </c>
-      <c r="AD275">
-        <v>1.05</v>
-      </c>
-      <c r="AE275">
-        <v>1.02</v>
-      </c>
       <c r="AF275">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AG275">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AK275">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="O276">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P276">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q276">
-        <v>2.3</v>
+        <v>4.34</v>
       </c>
       <c r="R276">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="S276">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="T276">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="U276">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="V276">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="W276">
         <v>1.03</v>
       </c>
       <c r="X276">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y276">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="Z276">
-        <v>2.95</v>
+        <v>2.04</v>
       </c>
       <c r="AA276">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB276">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AC276">
-        <v>3.72</v>
+        <v>6.65</v>
       </c>
       <c r="AD276">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AE276">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF276">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AG276">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AK276">
-        <v>1.83</v>
+        <v>1.27</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q277">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R277">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="S277">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="T277">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="U277">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="V277">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="W277">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X277">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y277">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="Z277">
-        <v>2.24</v>
+        <v>2.95</v>
       </c>
       <c r="AA277">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB277">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC277">
-        <v>6</v>
+        <v>3.72</v>
       </c>
       <c r="AD277">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AE277">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF277">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AG277">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O281">
         <v>5</v>
       </c>
       <c r="P281">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Q281">
         <v>1.84</v>
@@ -47253,7 +47253,7 @@
         </is>
       </c>
       <c r="N288">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="O288">
         <v>5.15</v>
@@ -47911,7 +47911,7 @@
         <v>5</v>
       </c>
       <c r="P292">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q292">
         <v>1.92</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G295">
@@ -48901,7 +48901,7 @@
         <v>1.29</v>
       </c>
       <c r="T298">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U298">
         <v>2.42</v>
@@ -48956,7 +48956,7 @@
         <v>1.22</v>
       </c>
       <c r="AK298">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49088,7 +49088,7 @@
         <v>1.42</v>
       </c>
       <c r="AB299">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC299">
         <v>2.07</v>
@@ -49103,7 +49103,7 @@
         <v>1.91</v>
       </c>
       <c r="AG299">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK302">
         <v>1.83</v>
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O307">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="P307">
-        <v>5.58</v>
+        <v>4.8</v>
       </c>
       <c r="Q307">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R307">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T307">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U307">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V307">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W307">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X307">
         <v>0</v>
       </c>
       <c r="Y307">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z307">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA307">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB307">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC307">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD307">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF307">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG307">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK307">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL307">
         <v>0</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G4">
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q4">
-        <v>4.68</v>
+        <v>3.17</v>
       </c>
       <c r="R4">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U4">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
         <v>1.4</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z4">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB4">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>2.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>3.17</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
+        <v>1.36</v>
+      </c>
+      <c r="T5">
+        <v>2.9</v>
+      </c>
+      <c r="U5">
+        <v>2.76</v>
+      </c>
+      <c r="V5">
         <v>1.35</v>
       </c>
-      <c r="T5">
-        <v>2.77</v>
-      </c>
-      <c r="U5">
-        <v>2.69</v>
-      </c>
-      <c r="V5">
-        <v>1.4</v>
-      </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA5">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC5">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE5">
         <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="U6">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
+        <v>1.04</v>
+      </c>
+      <c r="X6">
         <v>1.03</v>
       </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="Z6">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="AA6">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AB6">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG6">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.83</v>
+        <v>3.8</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="AA7">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AB7">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AC7">
-        <v>3.92</v>
+        <v>2.92</v>
       </c>
       <c r="AD7">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.83</v>
+        <v>1.16</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.33</v>
+        <v>1.76</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>1.64</v>
+        <v>3.8</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="AD10">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>2.01</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
-        <v>3.8</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
+        <v>5</v>
+      </c>
+      <c r="R11">
         <v>2.3</v>
       </c>
-      <c r="R11">
-        <v>2.24</v>
-      </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
+        <v>1.05</v>
+      </c>
+      <c r="X11">
+        <v>1.04</v>
+      </c>
+      <c r="Y11">
+        <v>1.22</v>
+      </c>
+      <c r="Z11">
+        <v>3.9</v>
+      </c>
+      <c r="AA11">
+        <v>1.78</v>
+      </c>
+      <c r="AB11">
+        <v>1.89</v>
+      </c>
+      <c r="AC11">
+        <v>2.96</v>
+      </c>
+      <c r="AD11">
+        <v>1.3</v>
+      </c>
+      <c r="AE11">
+        <v>1.07</v>
+      </c>
+      <c r="AF11">
+        <v>1.75</v>
+      </c>
+      <c r="AG11">
+        <v>1.95</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>2.01</v>
+      </c>
+      <c r="AK11">
         <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.18</v>
-      </c>
-      <c r="Z11">
-        <v>4</v>
-      </c>
-      <c r="AA11">
-        <v>1.65</v>
-      </c>
-      <c r="AB11">
-        <v>2.06</v>
-      </c>
-      <c r="AC11">
-        <v>2.59</v>
-      </c>
-      <c r="AD11">
-        <v>1.39</v>
-      </c>
-      <c r="AE11">
-        <v>1.14</v>
-      </c>
-      <c r="AF11">
-        <v>1.62</v>
-      </c>
-      <c r="AG11">
-        <v>2.14</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.2</v>
-      </c>
-      <c r="AK11">
-        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>2.41</v>
       </c>
       <c r="O12">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.6</v>
@@ -2295,13 +2295,13 @@
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="AA12">
         <v>1.82</v>
@@ -2310,13 +2310,13 @@
         <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
         <v>1.65</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
         <v>1.56</v>
@@ -2440,7 +2440,7 @@
         <v>3</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2467,7 +2467,7 @@
         <v>3.53</v>
       </c>
       <c r="AA13">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB13">
         <v>1.88</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="O14">
         <v>4.1</v>
       </c>
       <c r="P14">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -2621,10 +2621,10 @@
         <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
         <v>3.58</v>
@@ -2639,10 +2639,10 @@
         <v>2.74</v>
       </c>
       <c r="AD14">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
         <v>1.76</v>
@@ -2784,28 +2784,28 @@
         <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="AA15">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB15">
         <v>2.08</v>
       </c>
       <c r="AC15">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
         <v>1.69</v>
@@ -2920,10 +2920,10 @@
         <v>1.3</v>
       </c>
       <c r="O16">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="P16">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q16">
         <v>1.76</v>
@@ -2938,10 +2938,10 @@
         <v>3.26</v>
       </c>
       <c r="U16">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
         <v>1.1</v>
@@ -2950,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
         <v>4.17</v>
@@ -2965,10 +2965,10 @@
         <v>2.83</v>
       </c>
       <c r="AD16">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
         <v>2.05</v>
@@ -3086,7 +3086,7 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="Q17">
         <v>2.68</v>
@@ -3110,22 +3110,22 @@
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AA17">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB17">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC17">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="AD17">
         <v>1.39</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.44</v>
+        <v>1.78</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>1.99</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AA18">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC18">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD18">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF18">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,58 +3406,58 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P19">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA19">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB19">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC19">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="O20">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>1.99</v>
       </c>
       <c r="Q20">
-        <v>2.67</v>
+        <v>4.33</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
         <v>2.88</v>
       </c>
       <c r="U20">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
         <v>1.26</v>
       </c>
       <c r="Z20">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA20">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
+        <v>1.8</v>
+      </c>
+      <c r="AC20">
+        <v>3.34</v>
+      </c>
+      <c r="AD20">
+        <v>1.24</v>
+      </c>
+      <c r="AE20">
+        <v>1.05</v>
+      </c>
+      <c r="AF20">
         <v>1.79</v>
       </c>
-      <c r="AC20">
-        <v>3.14</v>
-      </c>
-      <c r="AD20">
-        <v>1.31</v>
-      </c>
-      <c r="AE20">
-        <v>1.07</v>
-      </c>
-      <c r="AF20">
-        <v>1.7</v>
-      </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4067,10 +4067,10 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="R23">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="S23">
         <v>1.28</v>
@@ -4097,7 +4097,7 @@
         <v>4.06</v>
       </c>
       <c r="AA23">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB23">
         <v>2.12</v>
@@ -4230,10 +4230,10 @@
         <v>3.95</v>
       </c>
       <c r="Q24">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4254,31 +4254,31 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AA24">
         <v>1.5</v>
       </c>
       <c r="AB24">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AC24">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD24">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF24">
         <v>1.44</v>
       </c>
       <c r="AG24">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>1.21</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
         <v>1.88</v>
@@ -4556,55 +4556,55 @@
         <v>1.91</v>
       </c>
       <c r="Q26">
-        <v>4.02</v>
+        <v>3.75</v>
       </c>
       <c r="R26">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U26">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z26">
-        <v>3.72</v>
+        <v>2.93</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AB26">
         <v>2</v>
       </c>
       <c r="AC26">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="AD26">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5371,34 +5371,34 @@
         <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="R31">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
         <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="AA31">
         <v>1.61</v>
@@ -5407,19 +5407,19 @@
         <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG31">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="O32">
+        <v>3.68</v>
+      </c>
+      <c r="P32">
+        <v>1.57</v>
+      </c>
+      <c r="Q32">
+        <v>4.68</v>
+      </c>
+      <c r="R32">
+        <v>2.36</v>
+      </c>
+      <c r="S32">
+        <v>1.3</v>
+      </c>
+      <c r="T32">
         <v>3.25</v>
       </c>
-      <c r="P32">
-        <v>2.25</v>
-      </c>
-      <c r="Q32">
-        <v>3.52</v>
-      </c>
-      <c r="R32">
-        <v>2.07</v>
-      </c>
-      <c r="S32">
-        <v>1.33</v>
-      </c>
-      <c r="T32">
-        <v>2.85</v>
-      </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O33">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>4.68</v>
+        <v>3.52</v>
       </c>
       <c r="R33">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="U33">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>2.88</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,25 +5860,25 @@
         <v>3.8</v>
       </c>
       <c r="Q34">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R34">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5896,19 +5896,19 @@
         <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD34">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG34">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6026,7 +6026,7 @@
         <v>2.89</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="S35">
         <v>1.42</v>
@@ -6044,7 +6044,7 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
         <v>1.35</v>
@@ -6053,19 +6053,19 @@
         <v>2.95</v>
       </c>
       <c r="AA35">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AB35">
         <v>1.79</v>
       </c>
       <c r="AC35">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD35">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
         <v>1.83</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="R36">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V36">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W36">
+        <v>1.05</v>
+      </c>
+      <c r="X36">
         <v>1.03</v>
       </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
       <c r="Y36">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="Z36">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AA36">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="AB36">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC36">
-        <v>4.35</v>
+        <v>3.86</v>
       </c>
       <c r="AD36">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6355,10 +6355,10 @@
         <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U37">
         <v>2.88</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AK43">
         <v>1.29</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.9</v>
+      </c>
+      <c r="O50">
+        <v>3.1</v>
+      </c>
+      <c r="P50">
+        <v>2.2</v>
+      </c>
+      <c r="Q50">
+        <v>3.5</v>
+      </c>
+      <c r="R50">
         <v>2</v>
       </c>
-      <c r="O50">
-        <v>3.4</v>
-      </c>
-      <c r="P50">
-        <v>3.1</v>
-      </c>
-      <c r="Q50">
-        <v>2.67</v>
-      </c>
-      <c r="R50">
-        <v>2.12</v>
-      </c>
       <c r="S50">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T50">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="U50">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="Z50">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="AA50">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC50">
-        <v>2.92</v>
+        <v>4.15</v>
       </c>
       <c r="AD50">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF50">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AG50">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q51">
-        <v>3.76</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>2.78</v>
+        <v>3.74</v>
       </c>
       <c r="AA51">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AB51">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC51">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD51">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
+        <v>2.1</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.19</v>
+      </c>
+      <c r="AK51">
         <v>1.83</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.26</v>
-      </c>
-      <c r="AK51">
-        <v>1.31</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
+        <v>3.1</v>
+      </c>
+      <c r="Q52">
+        <v>2.5</v>
+      </c>
+      <c r="R52">
+        <v>2.2</v>
+      </c>
+      <c r="S52">
+        <v>1.33</v>
+      </c>
+      <c r="T52">
+        <v>3</v>
+      </c>
+      <c r="U52">
         <v>2.75</v>
       </c>
-      <c r="Q52">
-        <v>2.7</v>
-      </c>
-      <c r="R52">
-        <v>2.28</v>
-      </c>
-      <c r="S52">
-        <v>1.23</v>
-      </c>
-      <c r="T52">
-        <v>3.46</v>
-      </c>
-      <c r="U52">
-        <v>2.22</v>
-      </c>
       <c r="V52">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="AA52">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AB52">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC52">
-        <v>2.43</v>
+        <v>3.04</v>
       </c>
       <c r="AD52">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O54">
         <v>3.6</v>
       </c>
       <c r="P54">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q54">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="R54">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T54">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U54">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="V54">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z54">
-        <v>4.05</v>
+        <v>2.81</v>
       </c>
       <c r="AA54">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB54">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AC54">
-        <v>2.46</v>
+        <v>3.58</v>
       </c>
       <c r="AD54">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF54">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AG54">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK54">
         <v>1.73</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="O55">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P55">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q55">
-        <v>2.41</v>
+        <v>2.86</v>
       </c>
       <c r="R55">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="T55">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="U55">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
+        <v>1.07</v>
+      </c>
+      <c r="Y55">
+        <v>1.47</v>
+      </c>
+      <c r="Z55">
+        <v>2.54</v>
+      </c>
+      <c r="AA55">
+        <v>2.25</v>
+      </c>
+      <c r="AB55">
+        <v>1.53</v>
+      </c>
+      <c r="AC55">
+        <v>4.4</v>
+      </c>
+      <c r="AD55">
+        <v>1.14</v>
+      </c>
+      <c r="AE55">
         <v>1.01</v>
       </c>
-      <c r="Y55">
-        <v>1.23</v>
-      </c>
-      <c r="Z55">
-        <v>3.42</v>
-      </c>
-      <c r="AA55">
-        <v>1.79</v>
-      </c>
-      <c r="AB55">
-        <v>1.88</v>
-      </c>
-      <c r="AC55">
-        <v>2.92</v>
-      </c>
-      <c r="AD55">
-        <v>1.31</v>
-      </c>
-      <c r="AE55">
-        <v>1.09</v>
-      </c>
       <c r="AF55">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AG55">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="O56">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q56">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="R56">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T56">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="U56">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="Z56">
+        <v>3.82</v>
+      </c>
+      <c r="AA56">
+        <v>1.65</v>
+      </c>
+      <c r="AB56">
+        <v>2.2</v>
+      </c>
+      <c r="AC56">
         <v>2.74</v>
       </c>
-      <c r="AA56">
-        <v>2.25</v>
-      </c>
-      <c r="AB56">
-        <v>1.58</v>
-      </c>
-      <c r="AC56">
-        <v>4.15</v>
-      </c>
       <c r="AD56">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF56">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AG56">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9630,13 +9630,13 @@
         <v>1.1</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z57">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA57">
         <v>1.8</v>
@@ -9645,10 +9645,10 @@
         <v>1.91</v>
       </c>
       <c r="AC57">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD57">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE57">
         <v>1.11</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="O60">
         <v>3.6</v>
@@ -10104,10 +10104,10 @@
         <v>2.49</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U60">
         <v>2.25</v>
@@ -10116,22 +10116,22 @@
         <v>1.6</v>
       </c>
       <c r="W60">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y60">
         <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>4.65</v>
+        <v>5.05</v>
       </c>
       <c r="AA60">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AB60">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC60">
         <v>2.35</v>
@@ -10140,7 +10140,7 @@
         <v>1.62</v>
       </c>
       <c r="AE60">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF60">
         <v>1.44</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O67">
         <v>3.8</v>
       </c>
       <c r="P67">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="Q67">
         <v>2.04</v>
@@ -11423,7 +11423,7 @@
         <v>1.17</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y68">
         <v>1.1</v>
@@ -11432,10 +11432,10 @@
         <v>5.55</v>
       </c>
       <c r="AA68">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB68">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AC68">
         <v>2.11</v>
@@ -11444,7 +11444,7 @@
         <v>1.76</v>
       </c>
       <c r="AE68">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AF68">
         <v>1.65</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
         <v>1.25</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="O78">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="P78">
         <v>1.68</v>
@@ -13038,19 +13038,19 @@
         <v>2.36</v>
       </c>
       <c r="S78">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T78">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U78">
         <v>2.21</v>
       </c>
       <c r="V78">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X78">
         <v>1.01</v>
@@ -13521,22 +13521,22 @@
         <v>3</v>
       </c>
       <c r="Q81">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S81">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T81">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U81">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W81">
         <v>1.08</v>
@@ -13551,7 +13551,7 @@
         <v>3.42</v>
       </c>
       <c r="AA81">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB81">
         <v>1.95</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="O85">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="P85">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="Q85">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="R85">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="S85">
         <v>1.2</v>
@@ -14197,13 +14197,13 @@
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA85">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB85">
         <v>3.1</v>
@@ -14221,7 +14221,7 @@
         <v>1.35</v>
       </c>
       <c r="AG85">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>1.6</v>
       </c>
       <c r="Q86">
-        <v>3.95</v>
+        <v>4.44</v>
       </c>
       <c r="R86">
         <v>2.54</v>
@@ -14348,13 +14348,13 @@
         <v>3.9</v>
       </c>
       <c r="U86">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V86">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X86">
         <v>1.01</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
+        <v>2.48</v>
+      </c>
+      <c r="O87">
+        <v>3.83</v>
+      </c>
+      <c r="P87">
         <v>2.25</v>
       </c>
-      <c r="O87">
-        <v>3.5</v>
-      </c>
-      <c r="P87">
-        <v>2.75</v>
-      </c>
       <c r="Q87">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="R87">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="S87">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="U87">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V87">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="AA87">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AB87">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AC87">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AD87">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE87">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AF87">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="O88">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
+        <v>2.75</v>
+      </c>
+      <c r="Q88">
+        <v>2.76</v>
+      </c>
+      <c r="R88">
         <v>2.25</v>
       </c>
-      <c r="Q88">
-        <v>3.1</v>
-      </c>
-      <c r="R88">
-        <v>2.56</v>
-      </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T88">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="V88">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>5.7</v>
+        <v>4.35</v>
       </c>
       <c r="AA88">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AB88">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AC88">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD88">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AE88">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK88">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14837,13 +14837,13 @@
         <v>3.32</v>
       </c>
       <c r="U89">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V89">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
         <v>1.02</v>
@@ -14982,22 +14982,22 @@
         <v>2.3</v>
       </c>
       <c r="O90">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
         <v>2.5</v>
       </c>
       <c r="Q90">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="R90">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T90">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="U90">
         <v>2.13</v>
@@ -15009,7 +15009,7 @@
         <v>1.14</v>
       </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
         <v>1.13</v>
@@ -15024,10 +15024,10 @@
         <v>2.3</v>
       </c>
       <c r="AC90">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD90">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE90">
         <v>1.19</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15335,7 +15335,7 @@
         <v>1.13</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y92">
         <v>1.15</v>
@@ -15350,13 +15350,13 @@
         <v>2.28</v>
       </c>
       <c r="AC92">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AD92">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE92">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF92">
         <v>1.53</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15661,28 +15661,28 @@
         <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y94">
         <v>1.3</v>
       </c>
       <c r="Z94">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="AA94">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB94">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC94">
-        <v>3.48</v>
+        <v>3.63</v>
       </c>
       <c r="AD94">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF94">
         <v>1.85</v>
@@ -15990,10 +15990,10 @@
         <v>1.04</v>
       </c>
       <c r="Y96">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z96">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA96">
         <v>2.19</v>
@@ -16289,7 +16289,7 @@
         <v>3.3</v>
       </c>
       <c r="P98">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="Q98">
         <v>2.55</v>
@@ -16298,10 +16298,10 @@
         <v>1.87</v>
       </c>
       <c r="S98">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T98">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U98">
         <v>3.5</v>
@@ -16313,25 +16313,25 @@
         <v>1.04</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y98">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Z98">
         <v>2.39</v>
       </c>
       <c r="AA98">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AB98">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC98">
-        <v>4.65</v>
+        <v>4.82</v>
       </c>
       <c r="AD98">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE98">
         <v>1.02</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16467,10 +16467,10 @@
         <v>2.76</v>
       </c>
       <c r="U99">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V99">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W99">
         <v>1.05</v>
@@ -16479,10 +16479,10 @@
         <v>1.05</v>
       </c>
       <c r="Y99">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z99">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="AA99">
         <v>2.29</v>
@@ -16491,13 +16491,13 @@
         <v>1.64</v>
       </c>
       <c r="AC99">
-        <v>3.8</v>
+        <v>4.38</v>
       </c>
       <c r="AD99">
         <v>1.21</v>
       </c>
       <c r="AE99">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF99">
         <v>2.21</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK99">
         <v>2.2</v>
@@ -16772,16 +16772,16 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="O101">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="P101">
         <v>2.19</v>
       </c>
       <c r="Q101">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R101">
         <v>2.23</v>
@@ -16805,10 +16805,10 @@
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="AA101">
         <v>1.77</v>
@@ -16817,13 +16817,13 @@
         <v>2.22</v>
       </c>
       <c r="AC101">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AD101">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE101">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF101">
         <v>1.56</v>
@@ -16965,13 +16965,13 @@
         <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="AA102">
         <v>1.86</v>
@@ -16980,10 +16980,10 @@
         <v>1.81</v>
       </c>
       <c r="AC102">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD102">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
         <v>1.07</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
         <v>1.82</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O111">
         <v>3.1</v>
       </c>
       <c r="P111">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q111">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R111">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S111">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T111">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="U111">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V111">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z111">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AA111">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB111">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC111">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD111">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE111">
         <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG111">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK111">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18574,16 +18574,16 @@
         <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="R112">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S112">
         <v>1.28</v>
       </c>
       <c r="T112">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U112">
         <v>2.63</v>
@@ -18592,37 +18592,37 @@
         <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
         <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z112">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA112">
         <v>1.72</v>
       </c>
       <c r="AB112">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC112">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD112">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG112">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18737,16 +18737,16 @@
         <v>0</v>
       </c>
       <c r="Q113">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="R113">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S113">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="U113">
         <v>3</v>
@@ -18755,37 +18755,37 @@
         <v>1.33</v>
       </c>
       <c r="W113">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z113">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA113">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AB113">
         <v>1.72</v>
       </c>
       <c r="AC113">
-        <v>3.82</v>
+        <v>3.34</v>
       </c>
       <c r="AD113">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE113">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK113">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK114">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19084,7 +19084,7 @@
         <v>1.14</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y115">
         <v>1.11</v>
@@ -19099,7 +19099,7 @@
         <v>2.68</v>
       </c>
       <c r="AC115">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD115">
         <v>1.7</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,7 +19389,7 @@
         <v>4</v>
       </c>
       <c r="Q117">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="R117">
         <v>2.38</v>
@@ -19453,7 +19453,7 @@
         <v>1.22</v>
       </c>
       <c r="AK117">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19573,13 +19573,13 @@
         <v>1.24</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z118">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AA118">
         <v>1.24</v>
@@ -19594,7 +19594,7 @@
         <v>2.12</v>
       </c>
       <c r="AE118">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AF118">
         <v>1.3</v>
@@ -19721,10 +19721,10 @@
         <v>2.46</v>
       </c>
       <c r="S119">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T119">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="U119">
         <v>2</v>
@@ -19733,16 +19733,16 @@
         <v>1.73</v>
       </c>
       <c r="W119">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y119">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z119">
-        <v>5.55</v>
+        <v>5.69</v>
       </c>
       <c r="AA119">
         <v>1.4</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
+        <v>2.19</v>
+      </c>
+      <c r="O120">
+        <v>3.45</v>
+      </c>
+      <c r="P120">
+        <v>2.67</v>
+      </c>
+      <c r="Q120">
+        <v>2.7</v>
+      </c>
+      <c r="R120">
+        <v>2.5</v>
+      </c>
+      <c r="S120">
+        <v>1.22</v>
+      </c>
+      <c r="T120">
+        <v>3.56</v>
+      </c>
+      <c r="U120">
+        <v>2.1</v>
+      </c>
+      <c r="V120">
+        <v>1.62</v>
+      </c>
+      <c r="W120">
         <v>1.18</v>
       </c>
-      <c r="O120">
-        <v>6.4</v>
-      </c>
-      <c r="P120">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q120">
-        <v>1.5</v>
-      </c>
-      <c r="R120">
-        <v>3.24</v>
-      </c>
-      <c r="S120">
-        <v>1.15</v>
-      </c>
-      <c r="T120">
-        <v>5</v>
-      </c>
-      <c r="U120">
-        <v>1.7</v>
-      </c>
-      <c r="V120">
-        <v>2.1</v>
-      </c>
-      <c r="W120">
-        <v>1.3</v>
-      </c>
       <c r="X120">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Z120">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="AA120">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AB120">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC120">
-        <v>1.51</v>
+        <v>2.27</v>
       </c>
       <c r="AD120">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AE120">
+        <v>1.22</v>
+      </c>
+      <c r="AF120">
+        <v>1.42</v>
+      </c>
+      <c r="AG120">
+        <v>2.66</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>1.22</v>
+      </c>
+      <c r="AK120">
         <v>1.57</v>
-      </c>
-      <c r="AF120">
-        <v>1.49</v>
-      </c>
-      <c r="AG120">
-        <v>2.44</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.09</v>
-      </c>
-      <c r="AK120">
-        <v>4.2</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.19</v>
+        <v>1.18</v>
       </c>
       <c r="O121">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="P121">
-        <v>2.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q121">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="R121">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="S121">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T121">
-        <v>3.56</v>
+        <v>5</v>
       </c>
       <c r="U121">
+        <v>1.7</v>
+      </c>
+      <c r="V121">
         <v>2.1</v>
       </c>
-      <c r="V121">
-        <v>1.62</v>
-      </c>
       <c r="W121">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X121">
+        <v>1</v>
+      </c>
+      <c r="Y121">
         <v>1.02</v>
       </c>
-      <c r="Y121">
-        <v>1.13</v>
-      </c>
       <c r="Z121">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="AA121">
+        <v>1.16</v>
+      </c>
+      <c r="AB121">
+        <v>4.1</v>
+      </c>
+      <c r="AC121">
+        <v>1.51</v>
+      </c>
+      <c r="AD121">
+        <v>2.26</v>
+      </c>
+      <c r="AE121">
+        <v>1.57</v>
+      </c>
+      <c r="AF121">
         <v>1.49</v>
       </c>
-      <c r="AB121">
-        <v>2.45</v>
-      </c>
-      <c r="AC121">
-        <v>2.27</v>
-      </c>
-      <c r="AD121">
-        <v>1.62</v>
-      </c>
-      <c r="AE121">
-        <v>1.22</v>
-      </c>
-      <c r="AF121">
-        <v>1.42</v>
-      </c>
       <c r="AG121">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK121">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,10 +20204,10 @@
         <v>3.05</v>
       </c>
       <c r="Q122">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="R122">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S122">
         <v>1.38</v>
@@ -20225,19 +20225,19 @@
         <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z122">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA122">
         <v>2.1</v>
       </c>
       <c r="AB122">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC122">
         <v>3.58</v>
@@ -20268,7 +20268,7 @@
         <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20542,7 +20542,7 @@
         <v>3.7</v>
       </c>
       <c r="U124">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V124">
         <v>1.6</v>
@@ -20702,13 +20702,13 @@
         <v>1.27</v>
       </c>
       <c r="T125">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U125">
         <v>2.35</v>
       </c>
       <c r="V125">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W125">
         <v>1.13</v>
@@ -20720,7 +20720,7 @@
         <v>1.14</v>
       </c>
       <c r="Z125">
-        <v>4.65</v>
+        <v>4.83</v>
       </c>
       <c r="AA125">
         <v>1.5</v>
@@ -20729,13 +20729,13 @@
         <v>2.4</v>
       </c>
       <c r="AC125">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AD125">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE125">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF125">
         <v>1.48</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK125">
         <v>1.75</v>
@@ -20862,7 +20862,7 @@
         <v>2.49</v>
       </c>
       <c r="S126">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T126">
         <v>3.5</v>
@@ -20883,22 +20883,22 @@
         <v>1.15</v>
       </c>
       <c r="Z126">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="AA126">
         <v>1.57</v>
       </c>
       <c r="AB126">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC126">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AD126">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE126">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF126">
         <v>1.53</v>
@@ -20920,7 +20920,7 @@
         <v>1.29</v>
       </c>
       <c r="AK126">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21022,10 +21022,10 @@
         <v>4.75</v>
       </c>
       <c r="R127">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T127">
         <v>3.6</v>
@@ -21040,7 +21040,7 @@
         <v>1.08</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y127">
         <v>1.18</v>
@@ -21055,13 +21055,13 @@
         <v>2.2</v>
       </c>
       <c r="AC127">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AD127">
         <v>1.44</v>
       </c>
       <c r="AE127">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF127">
         <v>1.6</v>
@@ -21185,16 +21185,16 @@
         <v>3.1</v>
       </c>
       <c r="R128">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S128">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T128">
         <v>3.6</v>
       </c>
       <c r="U128">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V128">
         <v>1.55</v>
@@ -21203,7 +21203,7 @@
         <v>1.1</v>
       </c>
       <c r="X128">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y128">
         <v>1.15</v>
@@ -21218,13 +21218,13 @@
         <v>2.19</v>
       </c>
       <c r="AC128">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD128">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE128">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF128">
         <v>1.5</v>
@@ -21517,7 +21517,7 @@
         <v>1.37</v>
       </c>
       <c r="T130">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="U130">
         <v>2.55</v>
@@ -21532,25 +21532,25 @@
         <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z130">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="AA130">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB130">
         <v>2</v>
       </c>
       <c r="AC130">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AD130">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE130">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF130">
         <v>1.65</v>
@@ -21864,7 +21864,7 @@
         <v>5.4</v>
       </c>
       <c r="AA132">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB132">
         <v>2.52</v>
@@ -22166,10 +22166,10 @@
         <v>2.89</v>
       </c>
       <c r="S134">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T134">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U134">
         <v>2.15</v>
@@ -22178,7 +22178,7 @@
         <v>1.6</v>
       </c>
       <c r="W134">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X134">
         <v>1.02</v>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK134">
         <v>5.95</v>
@@ -22498,7 +22498,7 @@
         <v>2.68</v>
       </c>
       <c r="U136">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V136">
         <v>1.4</v>
@@ -22643,10 +22643,10 @@
         <v>3.1</v>
       </c>
       <c r="O137">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P137">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q137">
         <v>3.18</v>
@@ -22655,10 +22655,10 @@
         <v>2.23</v>
       </c>
       <c r="S137">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T137">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U137">
         <v>2.26</v>
@@ -22667,7 +22667,7 @@
         <v>1.55</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X137">
         <v>1.02</v>
@@ -22682,7 +22682,7 @@
         <v>1.65</v>
       </c>
       <c r="AB137">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AC137">
         <v>2.41</v>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O141">
         <v>3.45</v>
@@ -23464,7 +23464,7 @@
         <v>1.56</v>
       </c>
       <c r="Q142">
-        <v>5.51</v>
+        <v>5.45</v>
       </c>
       <c r="R142">
         <v>2.2</v>
@@ -23627,10 +23627,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q143">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="R143">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S143">
         <v>1.29</v>
@@ -23691,7 +23691,7 @@
         <v>1.13</v>
       </c>
       <c r="AK143">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="O144">
-        <v>4.3</v>
+        <v>3.37</v>
       </c>
       <c r="P144">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="Q144">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="R144">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="S144">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="T144">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="U144">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="V144">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="W144">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>6.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA144">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AB144">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC144">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="AD144">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="AE144">
+        <v>1.07</v>
+      </c>
+      <c r="AF144">
+        <v>1.7</v>
+      </c>
+      <c r="AG144">
+        <v>2.05</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
         <v>1.3</v>
       </c>
-      <c r="AF144">
-        <v>1.4</v>
-      </c>
-      <c r="AG144">
-        <v>2.76</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.17</v>
-      </c>
       <c r="AK144">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="O145">
-        <v>3.37</v>
+        <v>4.3</v>
       </c>
       <c r="P145">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="Q145">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="R145">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="S145">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="T145">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="U145">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="V145">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="W145">
+        <v>1.17</v>
+      </c>
+      <c r="X145">
+        <v>1</v>
+      </c>
+      <c r="Y145">
         <v>1.06</v>
       </c>
-      <c r="X145">
-        <v>1.03</v>
-      </c>
-      <c r="Y145">
-        <v>1.25</v>
-      </c>
       <c r="Z145">
-        <v>3.1</v>
+        <v>6.05</v>
       </c>
       <c r="AA145">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AB145">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AC145">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="AD145">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AE145">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="AF145">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AG145">
-        <v>2.05</v>
+        <v>2.76</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24463,19 +24463,19 @@
         <v>1.2</v>
       </c>
       <c r="X148">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y148">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z148">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="AA148">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AB148">
-        <v>2.98</v>
+        <v>3.07</v>
       </c>
       <c r="AC148">
         <v>2</v>
@@ -24484,7 +24484,7 @@
         <v>1.89</v>
       </c>
       <c r="AE148">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF148">
         <v>1.32</v>
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>13.1</v>
+        <v>11.9</v>
       </c>
       <c r="O161">
-        <v>7.3</v>
+        <v>7.11</v>
       </c>
       <c r="P161">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Q161">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="R161">
         <v>3</v>
       </c>
       <c r="S161">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T161">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U161">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V161">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W161">
         <v>1.17</v>
       </c>
       <c r="X161">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z161">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA161">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB161">
         <v>2.75</v>
       </c>
       <c r="AC161">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AD161">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE161">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AF161">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG161">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>4.56</v>
+        <v>1.11</v>
       </c>
       <c r="AK161">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G167">
@@ -27702,55 +27702,55 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G171">
@@ -28354,55 +28354,55 @@
         <v>1.62</v>
       </c>
       <c r="Q172">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="R172">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="S172">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T172">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="U172">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="V172">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W172">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X172">
         <v>1.02</v>
       </c>
       <c r="Y172">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z172">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA172">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB172">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC172">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AD172">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE172">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF172">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG172">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK172">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28864,7 +28864,7 @@
         <v>1.07</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
         <v>1.2</v>
@@ -29181,7 +29181,7 @@
         <v>3.5</v>
       </c>
       <c r="U177">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V177">
         <v>1.53</v>
@@ -29196,7 +29196,7 @@
         <v>1.18</v>
       </c>
       <c r="Z177">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="AA177">
         <v>1.6</v>
@@ -29205,7 +29205,7 @@
         <v>2.25</v>
       </c>
       <c r="AC177">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AD177">
         <v>1.45</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G184">
@@ -30473,55 +30473,55 @@
         <v>1.41</v>
       </c>
       <c r="Q185">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="R185">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S185">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T185">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="U185">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V185">
         <v>1.5</v>
       </c>
       <c r="W185">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X185">
         <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z185">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA185">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB185">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AC185">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD185">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE185">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF185">
         <v>1.85</v>
       </c>
       <c r="AG185">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AK185">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30654,22 +30654,22 @@
         <v>1.82</v>
       </c>
       <c r="W186">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X186">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y186">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z186">
         <v>7.5</v>
       </c>
       <c r="AA186">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB186">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="AC186">
         <v>1.92</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O187">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P187">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q187">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="R187">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="S187">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T187">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U187">
         <v>2.63</v>
       </c>
       <c r="V187">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W187">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y187">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z187">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="AA187">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB187">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AC187">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AD187">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE187">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF187">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG187">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK187">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O188">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P188">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="Q188">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="R188">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S188">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T188">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U188">
         <v>2.63</v>
       </c>
       <c r="V188">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W188">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X188">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y188">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z188">
-        <v>3.92</v>
+        <v>3.56</v>
       </c>
       <c r="AA188">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB188">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC188">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AD188">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE188">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF188">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG188">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK188">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31146,7 +31146,7 @@
         <v>1.11</v>
       </c>
       <c r="X189">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y189">
         <v>1.27</v>
@@ -31158,22 +31158,22 @@
         <v>1.88</v>
       </c>
       <c r="AB189">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC189">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AD189">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE189">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF189">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG189">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31288,16 +31288,16 @@
         <v>2.45</v>
       </c>
       <c r="Q190">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="R190">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S190">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T190">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U190">
         <v>2.88</v>
@@ -31306,7 +31306,7 @@
         <v>1.36</v>
       </c>
       <c r="W190">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X190">
         <v>1.02</v>
@@ -31352,7 +31352,7 @@
         <v>1.31</v>
       </c>
       <c r="AK190">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31614,7 +31614,7 @@
         <v>7.48</v>
       </c>
       <c r="Q192">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R192">
         <v>2.6</v>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK192">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31771,7 +31771,7 @@
         <v>3.4</v>
       </c>
       <c r="O193">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P193">
         <v>1.91</v>
@@ -31949,7 +31949,7 @@
         <v>1.3</v>
       </c>
       <c r="T194">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U194">
         <v>2.48</v>
@@ -32004,7 +32004,7 @@
         <v>1.31</v>
       </c>
       <c r="AK194">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O196">
         <v>5.4</v>
       </c>
       <c r="P196">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q196">
         <v>1.69</v>
@@ -32287,7 +32287,7 @@
         <v>1.09</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y196">
         <v>1.21</v>
@@ -32296,19 +32296,19 @@
         <v>4.31</v>
       </c>
       <c r="AA196">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AB196">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AC196">
         <v>2.59</v>
       </c>
       <c r="AD196">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE196">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF196">
         <v>2.09</v>
@@ -32589,7 +32589,7 @@
         <v>3.45</v>
       </c>
       <c r="P198">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q198">
         <v>2.45</v>
@@ -32613,25 +32613,25 @@
         <v>1.05</v>
       </c>
       <c r="X198">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y198">
         <v>1.25</v>
       </c>
       <c r="Z198">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="AA198">
         <v>1.84</v>
       </c>
       <c r="AB198">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AC198">
         <v>3.2</v>
       </c>
       <c r="AD198">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE198">
         <v>1.07</v>
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK198">
         <v>1.83</v>
@@ -32755,55 +32755,55 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T199">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V199">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W199">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X199">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z199">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC199">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD199">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG199">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK199">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33265,7 +33265,7 @@
         <v>1.2</v>
       </c>
       <c r="X202">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y202">
         <v>1.07</v>
@@ -33286,7 +33286,7 @@
         <v>1.91</v>
       </c>
       <c r="AE202">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AF202">
         <v>1.4</v>
@@ -33570,34 +33570,34 @@
         <v>3</v>
       </c>
       <c r="Q204">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R204">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S204">
         <v>1.28</v>
       </c>
       <c r="T204">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U204">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V204">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W204">
         <v>1.1</v>
       </c>
       <c r="X204">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y204">
         <v>1.15</v>
       </c>
       <c r="Z204">
-        <v>4.3</v>
+        <v>4.44</v>
       </c>
       <c r="AA204">
         <v>1.6</v>
@@ -33606,10 +33606,10 @@
         <v>2.2</v>
       </c>
       <c r="AC204">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AD204">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE204">
         <v>1.16</v>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33917,7 +33917,7 @@
         <v>1.08</v>
       </c>
       <c r="X206">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y206">
         <v>1.15</v>
@@ -33932,13 +33932,13 @@
         <v>2.08</v>
       </c>
       <c r="AC206">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AD206">
         <v>1.48</v>
       </c>
       <c r="AE206">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF206">
         <v>1.57</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O207">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="P207">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q207">
-        <v>2.16</v>
+        <v>2.94</v>
       </c>
       <c r="R207">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="S207">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T207">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="U207">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="V207">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="W207">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X207">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y207">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z207">
-        <v>6.79</v>
+        <v>4</v>
       </c>
       <c r="AA207">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AB207">
-        <v>2.83</v>
+        <v>2.11</v>
       </c>
       <c r="AC207">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="AD207">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AE207">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AF207">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG207">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK207">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G208">
@@ -34216,77 +34216,77 @@
         <v>2.2</v>
       </c>
       <c r="O208">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P208">
+        <v>2.6</v>
+      </c>
+      <c r="Q208">
         <v>2.75</v>
       </c>
-      <c r="Q208">
-        <v>2.94</v>
-      </c>
       <c r="R208">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="S208">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T208">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="U208">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="V208">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="W208">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X208">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y208">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z208">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AA208">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AB208">
-        <v>2.11</v>
+        <v>2.68</v>
       </c>
       <c r="AC208">
-        <v>2.88</v>
+        <v>2.07</v>
       </c>
       <c r="AD208">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AE208">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AF208">
+        <v>1.38</v>
+      </c>
+      <c r="AG208">
+        <v>2.76</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ208">
+        <v>1.38</v>
+      </c>
+      <c r="AK208">
         <v>1.57</v>
-      </c>
-      <c r="AG208">
-        <v>2.25</v>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ208">
-        <v>1.3</v>
-      </c>
-      <c r="AK208">
-        <v>1.53</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="O209">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="P209">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q209">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R209">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S209">
         <v>1.2</v>
       </c>
       <c r="T209">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U209">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V209">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W209">
         <v>1.17</v>
       </c>
       <c r="X209">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y209">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z209">
-        <v>5.75</v>
+        <v>6.79</v>
       </c>
       <c r="AA209">
+        <v>1.33</v>
+      </c>
+      <c r="AB209">
+        <v>2.83</v>
+      </c>
+      <c r="AC209">
+        <v>1.99</v>
+      </c>
+      <c r="AD209">
+        <v>1.83</v>
+      </c>
+      <c r="AE209">
+        <v>1.31</v>
+      </c>
+      <c r="AF209">
         <v>1.4</v>
       </c>
-      <c r="AB209">
-        <v>2.75</v>
-      </c>
-      <c r="AC209">
-        <v>2.07</v>
-      </c>
-      <c r="AD209">
-        <v>1.78</v>
-      </c>
-      <c r="AE209">
-        <v>1.33</v>
-      </c>
-      <c r="AF209">
-        <v>1.38</v>
-      </c>
       <c r="AG209">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AK209">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34557,7 +34557,7 @@
         <v>1.3</v>
       </c>
       <c r="T210">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="U210">
         <v>2.42</v>
@@ -35852,55 +35852,55 @@
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36830,55 +36830,55 @@
         <v>7.55</v>
       </c>
       <c r="Q224">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R224">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S224">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T224">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="U224">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="V224">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W224">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X224">
         <v>1.01</v>
       </c>
       <c r="Y224">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z224">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AA224">
         <v>1.61</v>
       </c>
       <c r="AB224">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AC224">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD224">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE224">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF224">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AG224">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AK224">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36999,10 +36999,10 @@
         <v>2.2</v>
       </c>
       <c r="S225">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T225">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U225">
         <v>2.75</v>
@@ -37023,10 +37023,10 @@
         <v>3.58</v>
       </c>
       <c r="AA225">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB225">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AC225">
         <v>3</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="O226">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="P226">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="Q226">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="R226">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="S226">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T226">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="U226">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V226">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W226">
+        <v>1.22</v>
+      </c>
+      <c r="X226">
+        <v>1</v>
+      </c>
+      <c r="Y226">
         <v>1.11</v>
       </c>
-      <c r="X226">
-        <v>1.01</v>
-      </c>
-      <c r="Y226">
-        <v>1.16</v>
-      </c>
       <c r="Z226">
-        <v>4.4</v>
+        <v>5.87</v>
       </c>
       <c r="AA226">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AB226">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AC226">
-        <v>2.61</v>
+        <v>2.12</v>
       </c>
       <c r="AD226">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="AE226">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF226">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AG226">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK226">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="O227">
-        <v>3.26</v>
+        <v>4.25</v>
       </c>
       <c r="P227">
-        <v>2.23</v>
+        <v>4.45</v>
       </c>
       <c r="Q227">
-        <v>3.68</v>
+        <v>2.17</v>
       </c>
       <c r="R227">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S227">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T227">
-        <v>2.72</v>
+        <v>3.52</v>
       </c>
       <c r="U227">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V227">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W227">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X227">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z227">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="AA227">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AB227">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AC227">
-        <v>3.34</v>
+        <v>2.61</v>
       </c>
       <c r="AD227">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AE227">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AF227">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG227">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK227">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37494,7 +37494,7 @@
         <v>3.84</v>
       </c>
       <c r="U228">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V228">
         <v>1.63</v>
@@ -37524,7 +37524,7 @@
         <v>1.49</v>
       </c>
       <c r="AE228">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF228">
         <v>1.6</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="O229">
-        <v>4.24</v>
+        <v>3.6</v>
       </c>
       <c r="P229">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="Q229">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="R229">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="S229">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T229">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U229">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="V229">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W229">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z229">
-        <v>5.7</v>
+        <v>4.14</v>
       </c>
       <c r="AA229">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AB229">
-        <v>2.72</v>
+        <v>2.07</v>
       </c>
       <c r="AC229">
-        <v>2.12</v>
+        <v>2.53</v>
       </c>
       <c r="AD229">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AE229">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AF229">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AG229">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK229">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="O230">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P230">
-        <v>3.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q230">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="R230">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S230">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="T230">
-        <v>3.28</v>
+        <v>2.72</v>
       </c>
       <c r="U230">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="V230">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W230">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X230">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z230">
-        <v>4.05</v>
+        <v>3.21</v>
       </c>
       <c r="AA230">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AB230">
-        <v>2.07</v>
+        <v>1.76</v>
       </c>
       <c r="AC230">
-        <v>2.53</v>
+        <v>3.34</v>
       </c>
       <c r="AD230">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE230">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF230">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG230">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK230">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37971,7 +37971,7 @@
         <v>2.37</v>
       </c>
       <c r="Q231">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="R231">
         <v>2.1</v>
@@ -37992,7 +37992,7 @@
         <v>1.04</v>
       </c>
       <c r="X231">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y231">
         <v>1.38</v>
@@ -38007,10 +38007,10 @@
         <v>1.72</v>
       </c>
       <c r="AC231">
-        <v>3.64</v>
+        <v>3.76</v>
       </c>
       <c r="AD231">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE231">
         <v>1.04</v>
@@ -38134,34 +38134,34 @@
         <v>15.5</v>
       </c>
       <c r="Q232">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="R232">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="S232">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T232">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="U232">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V232">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W232">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X232">
         <v>1.02</v>
       </c>
       <c r="Y232">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z232">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="AA232">
         <v>1.66</v>
@@ -38170,35 +38170,35 @@
         <v>2.15</v>
       </c>
       <c r="AC232">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AD232">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE232">
+        <v>1.14</v>
+      </c>
+      <c r="AF232">
+        <v>2.25</v>
+      </c>
+      <c r="AG232">
+        <v>1.57</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ232">
         <v>1.11</v>
       </c>
-      <c r="AF232">
-        <v>2.79</v>
-      </c>
-      <c r="AG232">
-        <v>1.38</v>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ232">
-        <v>1.04</v>
-      </c>
       <c r="AK232">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38460,55 +38460,55 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38626,22 +38626,22 @@
         <v>3.1</v>
       </c>
       <c r="R235">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S235">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T235">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U235">
         <v>2.35</v>
       </c>
       <c r="V235">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W235">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X235">
         <v>1.01</v>
@@ -38684,7 +38684,7 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK235">
         <v>1.44</v>
@@ -38831,10 +38831,10 @@
         <v>1.05</v>
       </c>
       <c r="AF236">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG236">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O238">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P238">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q238">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R238">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S238">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T238">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="U238">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V238">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W238">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X238">
         <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z238">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA238">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB238">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC238">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AD238">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE238">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF238">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG238">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK238">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="O239">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P239">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q239">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="R239">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="S239">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T239">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U239">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V239">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W239">
         <v>1.06</v>
       </c>
       <c r="X239">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y239">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z239">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA239">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AB239">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC239">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD239">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE239">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF239">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG239">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK239">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39429,43 +39429,43 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O240">
         <v>3.1</v>
       </c>
       <c r="P240">
+        <v>2.8</v>
+      </c>
+      <c r="Q240">
+        <v>3.1</v>
+      </c>
+      <c r="R240">
+        <v>1.96</v>
+      </c>
+      <c r="S240">
+        <v>1.42</v>
+      </c>
+      <c r="T240">
+        <v>2.51</v>
+      </c>
+      <c r="U240">
         <v>3</v>
       </c>
-      <c r="Q240">
-        <v>2.88</v>
-      </c>
-      <c r="R240">
-        <v>2.01</v>
-      </c>
-      <c r="S240">
-        <v>1.39</v>
-      </c>
-      <c r="T240">
-        <v>2.61</v>
-      </c>
-      <c r="U240">
-        <v>2.94</v>
-      </c>
       <c r="V240">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W240">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X240">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z240">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AA240">
         <v>2.05</v>
@@ -39474,19 +39474,19 @@
         <v>1.75</v>
       </c>
       <c r="AC240">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AD240">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE240">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF240">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG240">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK240">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39592,64 +39592,64 @@
         </is>
       </c>
       <c r="N241">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O241">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P241">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q241">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R241">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="S241">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T241">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="U241">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="V241">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W241">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X241">
         <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z241">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA241">
         <v>1.9</v>
       </c>
       <c r="AB241">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC241">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="AD241">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE241">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF241">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG241">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK241">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39767,13 +39767,13 @@
         <v>5.5</v>
       </c>
       <c r="R242">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="S242">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T242">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U242">
         <v>1.77</v>
@@ -39785,19 +39785,19 @@
         <v>1.3</v>
       </c>
       <c r="X242">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y242">
         <v>1.01</v>
       </c>
       <c r="Z242">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AA242">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AB242">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="AC242">
         <v>1.65</v>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK242">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39933,7 +39933,7 @@
         <v>2.4</v>
       </c>
       <c r="S243">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T243">
         <v>3.5</v>
@@ -39945,7 +39945,7 @@
         <v>1.56</v>
       </c>
       <c r="W243">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X243">
         <v>1.02</v>
@@ -39988,7 +39988,7 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK243">
         <v>2.38</v>
@@ -40090,55 +40090,55 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,19 +40244,19 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O245">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P245">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="Q245">
         <v>1.8</v>
       </c>
       <c r="R245">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S245">
         <v>1.17</v>
@@ -40268,7 +40268,7 @@
         <v>2</v>
       </c>
       <c r="V245">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W245">
         <v>1.2</v>
@@ -40280,28 +40280,28 @@
         <v>1.08</v>
       </c>
       <c r="Z245">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AA245">
         <v>1.4</v>
       </c>
       <c r="AB245">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AC245">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AD245">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE245">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF245">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG245">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK245">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40446,7 +40446,7 @@
         <v>4.5</v>
       </c>
       <c r="AA246">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB246">
         <v>2.3</v>
@@ -40570,7 +40570,7 @@
         </is>
       </c>
       <c r="N247">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O247">
         <v>3.12</v>
@@ -40905,55 +40905,55 @@
         <v>2.52</v>
       </c>
       <c r="Q249">
-        <v>3.24</v>
+        <v>3.82</v>
       </c>
       <c r="R249">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S249">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T249">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="U249">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="V249">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W249">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X249">
         <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z249">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="AA249">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB249">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AC249">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="AD249">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AE249">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF249">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AG249">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK249">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41062,7 +41062,7 @@
         <v>6.9</v>
       </c>
       <c r="O250">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="P250">
         <v>1.48</v>
@@ -41092,10 +41092,10 @@
         <v>1.01</v>
       </c>
       <c r="Y250">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z250">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="AA250">
         <v>1.92</v>
@@ -41252,7 +41252,7 @@
         <v>1.13</v>
       </c>
       <c r="X251">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y251">
         <v>1.18</v>
@@ -41400,10 +41400,10 @@
         <v>2.14</v>
       </c>
       <c r="S252">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T252">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U252">
         <v>2.88</v>
@@ -41554,7 +41554,7 @@
         <v>4.05</v>
       </c>
       <c r="P253">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q253">
         <v>2.2</v>
@@ -41581,22 +41581,22 @@
         <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z253">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA253">
         <v>1.57</v>
       </c>
       <c r="AB253">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC253">
         <v>2.55</v>
       </c>
       <c r="AD253">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE253">
         <v>1.13</v>
@@ -41621,7 +41621,7 @@
         <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41717,7 +41717,7 @@
         <v>3.2</v>
       </c>
       <c r="P254">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q254">
         <v>3.04</v>
@@ -41747,7 +41747,7 @@
         <v>1.28</v>
       </c>
       <c r="Z254">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AA254">
         <v>1.93</v>
@@ -41756,13 +41756,13 @@
         <v>1.81</v>
       </c>
       <c r="AC254">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AD254">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE254">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF254">
         <v>1.75</v>
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O255">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P255">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
       <c r="Q255">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R255">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S255">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T255">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U255">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V255">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W255">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X255">
         <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z255">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="AA255">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB255">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC255">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD255">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE255">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF255">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AG255">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>1.22</v>
       </c>
       <c r="AK255">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42212,13 +42212,13 @@
         <v>3.8</v>
       </c>
       <c r="R257">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S257">
         <v>1.32</v>
       </c>
       <c r="T257">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U257">
         <v>2.63</v>
@@ -42270,7 +42270,7 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK257">
         <v>1.17</v>
@@ -42544,7 +42544,7 @@
         <v>1.3</v>
       </c>
       <c r="T259">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="U259">
         <v>2.67</v>
@@ -42861,34 +42861,34 @@
         <v>3.6</v>
       </c>
       <c r="Q261">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="R261">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S261">
+        <v>1.44</v>
+      </c>
+      <c r="T261">
+        <v>2.63</v>
+      </c>
+      <c r="U261">
+        <v>3.2</v>
+      </c>
+      <c r="V261">
+        <v>1.3</v>
+      </c>
+      <c r="W261">
+        <v>1.05</v>
+      </c>
+      <c r="X261">
+        <v>1.05</v>
+      </c>
+      <c r="Y261">
         <v>1.38</v>
       </c>
-      <c r="T261">
-        <v>2.65</v>
-      </c>
-      <c r="U261">
-        <v>2.9</v>
-      </c>
-      <c r="V261">
-        <v>1.32</v>
-      </c>
-      <c r="W261">
-        <v>1.04</v>
-      </c>
-      <c r="X261">
-        <v>1.03</v>
-      </c>
-      <c r="Y261">
-        <v>1.33</v>
-      </c>
       <c r="Z261">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AA261">
         <v>2.15</v>
@@ -42897,19 +42897,19 @@
         <v>1.66</v>
       </c>
       <c r="AC261">
-        <v>3.78</v>
+        <v>4.15</v>
       </c>
       <c r="AD261">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE261">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF261">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG261">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK261">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43214,7 +43214,7 @@
         <v>1.25</v>
       </c>
       <c r="Z263">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="AA263">
         <v>1.89</v>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK263">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43356,7 +43356,7 @@
         <v>2.05</v>
       </c>
       <c r="S264">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T264">
         <v>2.56</v>
@@ -43377,7 +43377,7 @@
         <v>1.35</v>
       </c>
       <c r="Z264">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA264">
         <v>2.13</v>
@@ -43528,13 +43528,13 @@
         <v>2.1</v>
       </c>
       <c r="V265">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W265">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X265">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y265">
         <v>1.09</v>
@@ -43555,7 +43555,7 @@
         <v>1.75</v>
       </c>
       <c r="AE265">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AF265">
         <v>1.54</v>
@@ -43577,7 +43577,7 @@
         <v>1.16</v>
       </c>
       <c r="AK265">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43836,7 +43836,7 @@
         <v>3.3</v>
       </c>
       <c r="P267">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="Q267">
         <v>3.1</v>
@@ -44023,19 +44023,19 @@
         <v>1.17</v>
       </c>
       <c r="X268">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y268">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z268">
-        <v>5.3</v>
+        <v>5.43</v>
       </c>
       <c r="AA268">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB268">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC268">
         <v>2.18</v>
@@ -44044,7 +44044,7 @@
         <v>1.7</v>
       </c>
       <c r="AE268">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF268">
         <v>1.73</v>
@@ -44165,7 +44165,7 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R269">
         <v>1.8</v>
@@ -44226,7 +44226,7 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK269">
         <v>1.44</v>
@@ -44328,7 +44328,7 @@
         <v>0</v>
       </c>
       <c r="Q270">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R270">
         <v>1.81</v>
@@ -44358,7 +44358,7 @@
         <v>2.04</v>
       </c>
       <c r="AA270">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB270">
         <v>1.28</v>
@@ -44555,7 +44555,7 @@
         <v>1.2</v>
       </c>
       <c r="AK271">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="O272">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P272">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="Q272">
         <v>2.57</v>
@@ -44660,22 +44660,22 @@
         <v>1.98</v>
       </c>
       <c r="S272">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T272">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="U272">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V272">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W272">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X272">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y272">
         <v>1.36</v>
@@ -44696,7 +44696,7 @@
         <v>1.17</v>
       </c>
       <c r="AE272">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF272">
         <v>1.95</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,80 +44971,80 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q274">
+        <v>2.5</v>
+      </c>
+      <c r="R274">
+        <v>1.79</v>
+      </c>
+      <c r="S274">
+        <v>1.58</v>
+      </c>
+      <c r="T274">
         <v>2.25</v>
       </c>
-      <c r="R274">
-        <v>1.98</v>
-      </c>
-      <c r="S274">
-        <v>1.43</v>
-      </c>
-      <c r="T274">
-        <v>2.48</v>
-      </c>
       <c r="U274">
+        <v>3.8</v>
+      </c>
+      <c r="V274">
+        <v>1.19</v>
+      </c>
+      <c r="W274">
+        <v>1.01</v>
+      </c>
+      <c r="X274">
+        <v>1.13</v>
+      </c>
+      <c r="Y274">
+        <v>1.63</v>
+      </c>
+      <c r="Z274">
+        <v>2.24</v>
+      </c>
+      <c r="AA274">
         <v>3.1</v>
       </c>
-      <c r="V274">
-        <v>1.28</v>
-      </c>
-      <c r="W274">
+      <c r="AB274">
+        <v>1.36</v>
+      </c>
+      <c r="AC274">
+        <v>6</v>
+      </c>
+      <c r="AD274">
+        <v>1.06</v>
+      </c>
+      <c r="AE274">
         <v>1.03</v>
       </c>
-      <c r="X274">
-        <v>1.04</v>
-      </c>
-      <c r="Y274">
+      <c r="AF274">
+        <v>2.42</v>
+      </c>
+      <c r="AG274">
+        <v>1.49</v>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ274">
         <v>1.4</v>
       </c>
-      <c r="Z274">
-        <v>2.57</v>
-      </c>
-      <c r="AA274">
-        <v>2.35</v>
-      </c>
-      <c r="AB274">
-        <v>1.53</v>
-      </c>
-      <c r="AC274">
-        <v>4.33</v>
-      </c>
-      <c r="AD274">
-        <v>1.14</v>
-      </c>
-      <c r="AE274">
-        <v>1.01</v>
-      </c>
-      <c r="AF274">
-        <v>2.21</v>
-      </c>
-      <c r="AG274">
-        <v>1.58</v>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ274">
-        <v>1.3</v>
-      </c>
       <c r="AK274">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q275">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R275">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="S275">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="T275">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="U275">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="V275">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="W275">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X275">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="Z275">
-        <v>2.24</v>
+        <v>2.95</v>
       </c>
       <c r="AA275">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB275">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC275">
-        <v>6</v>
+        <v>3.72</v>
       </c>
       <c r="AD275">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AE275">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF275">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AG275">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK275">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="O276">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="P276">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q276">
-        <v>4.34</v>
+        <v>2.25</v>
       </c>
       <c r="R276">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="S276">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="T276">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="U276">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="V276">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="W276">
         <v>1.03</v>
       </c>
       <c r="X276">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y276">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="Z276">
-        <v>2.04</v>
+        <v>2.57</v>
       </c>
       <c r="AA276">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB276">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC276">
-        <v>6.65</v>
+        <v>4.33</v>
       </c>
       <c r="AD276">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AE276">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF276">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AG276">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AK276">
-        <v>1.27</v>
+        <v>2.15</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="O277">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P277">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q277">
-        <v>2.3</v>
+        <v>4.34</v>
       </c>
       <c r="R277">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="S277">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="T277">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="U277">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="V277">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="W277">
         <v>1.03</v>
       </c>
       <c r="X277">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y277">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="Z277">
-        <v>2.95</v>
+        <v>2.04</v>
       </c>
       <c r="AA277">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB277">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AC277">
-        <v>3.72</v>
+        <v>6.65</v>
       </c>
       <c r="AD277">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AE277">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF277">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AG277">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AK277">
-        <v>1.83</v>
+        <v>1.27</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45629,7 +45629,7 @@
         <v>3.45</v>
       </c>
       <c r="P278">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="Q278">
         <v>2.3</v>
@@ -45979,16 +45979,16 @@
         <v>1.15</v>
       </c>
       <c r="X280">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y280">
         <v>1.15</v>
       </c>
       <c r="Z280">
-        <v>5.15</v>
+        <v>5.52</v>
       </c>
       <c r="AA280">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AB280">
         <v>2.63</v>
@@ -46124,13 +46124,13 @@
         <v>1.84</v>
       </c>
       <c r="R281">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="S281">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T281">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U281">
         <v>2</v>
@@ -46142,13 +46142,13 @@
         <v>1.2</v>
       </c>
       <c r="X281">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y281">
         <v>1.07</v>
       </c>
       <c r="Z281">
-        <v>5.8</v>
+        <v>5.97</v>
       </c>
       <c r="AA281">
         <v>1.36</v>
@@ -46305,7 +46305,7 @@
         <v>1.07</v>
       </c>
       <c r="X282">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y282">
         <v>1.25</v>
@@ -46320,10 +46320,10 @@
         <v>2</v>
       </c>
       <c r="AC282">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AD282">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE282">
         <v>1.08</v>
@@ -46444,7 +46444,7 @@
         <v>2.9</v>
       </c>
       <c r="P283">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB283">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46773,10 +46773,10 @@
         <v>4.1</v>
       </c>
       <c r="Q285">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R285">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S285">
         <v>1.5</v>
@@ -46936,7 +46936,7 @@
         <v>10.5</v>
       </c>
       <c r="Q286">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R286">
         <v>2.4</v>
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="O287">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P287">
-        <v>5.32</v>
+        <v>5.06</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="O288">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="P288">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O290">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P290">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="O292">
         <v>5</v>
@@ -47944,7 +47944,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AA292">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AB292">
         <v>4.55</v>
@@ -47962,7 +47962,7 @@
         <v>1.24</v>
       </c>
       <c r="AG292">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK292">
         <v>2.38</v>
@@ -48892,10 +48892,10 @@
         <v>1.95</v>
       </c>
       <c r="Q298">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="R298">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S298">
         <v>1.29</v>
@@ -48953,7 +48953,7 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK298">
         <v>1.25</v>
@@ -49067,16 +49067,16 @@
         <v>4</v>
       </c>
       <c r="U299">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V299">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W299">
         <v>1.18</v>
       </c>
       <c r="X299">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y299">
         <v>1.1</v>
@@ -49085,7 +49085,7 @@
         <v>5.75</v>
       </c>
       <c r="AA299">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AB299">
         <v>2.6</v>
@@ -49740,7 +49740,7 @@
         <v>1.68</v>
       </c>
       <c r="AB303">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC303">
         <v>2.65</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -638,7 +638,7 @@
         <v>2.21</v>
       </c>
       <c r="O2">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
         <v>3.05</v>
@@ -665,10 +665,10 @@
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
         <v>3.96</v>
@@ -677,16 +677,16 @@
         <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AC2">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
         <v>1.6</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="P3">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="Q3">
         <v>2.58</v>
@@ -813,10 +813,10 @@
         <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="U3">
         <v>2.9</v>
@@ -825,7 +825,7 @@
         <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -852,7 +852,7 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
         <v>1.9</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O4">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q4">
         <v>3.17</v>
@@ -1000,7 +1000,7 @@
         <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB4">
         <v>1.75</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
+        <v>1.79</v>
+      </c>
+      <c r="Q5">
         <v>4.6</v>
-      </c>
-      <c r="Q5">
-        <v>2.06</v>
       </c>
       <c r="R5">
         <v>2.15</v>
@@ -1142,46 +1142,46 @@
         <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AC5">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD5">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>2.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1314,7 +1314,7 @@
         <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1341,10 +1341,10 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG6">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>1.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q7">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA7">
+        <v>1.95</v>
+      </c>
+      <c r="AB7">
+        <v>1.81</v>
+      </c>
+      <c r="AC7">
+        <v>3.2</v>
+      </c>
+      <c r="AD7">
+        <v>1.26</v>
+      </c>
+      <c r="AE7">
+        <v>1.06</v>
+      </c>
+      <c r="AF7">
         <v>1.9</v>
       </c>
-      <c r="AB7">
-        <v>1.92</v>
-      </c>
-      <c r="AC7">
-        <v>2.92</v>
-      </c>
-      <c r="AD7">
-        <v>1.3</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
-      <c r="AF7">
-        <v>1.73</v>
-      </c>
       <c r="AG7">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>3.8</v>
+        <v>1.64</v>
       </c>
       <c r="Q10">
+        <v>5</v>
+      </c>
+      <c r="R10">
         <v>2.3</v>
       </c>
-      <c r="R10">
-        <v>2.24</v>
-      </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.22</v>
+      </c>
+      <c r="Z10">
+        <v>3.9</v>
+      </c>
+      <c r="AA10">
+        <v>1.78</v>
+      </c>
+      <c r="AB10">
+        <v>1.89</v>
+      </c>
+      <c r="AC10">
+        <v>2.96</v>
+      </c>
+      <c r="AD10">
+        <v>1.3</v>
+      </c>
+      <c r="AE10">
+        <v>1.07</v>
+      </c>
+      <c r="AF10">
+        <v>1.75</v>
+      </c>
+      <c r="AG10">
+        <v>1.95</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>2.01</v>
+      </c>
+      <c r="AK10">
         <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.18</v>
-      </c>
-      <c r="Z10">
-        <v>4</v>
-      </c>
-      <c r="AA10">
-        <v>1.65</v>
-      </c>
-      <c r="AB10">
-        <v>2.06</v>
-      </c>
-      <c r="AC10">
-        <v>2.59</v>
-      </c>
-      <c r="AD10">
-        <v>1.39</v>
-      </c>
-      <c r="AE10">
-        <v>1.14</v>
-      </c>
-      <c r="AF10">
-        <v>1.62</v>
-      </c>
-      <c r="AG10">
-        <v>2.14</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.2</v>
-      </c>
-      <c r="AK10">
-        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.33</v>
+        <v>1.76</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>1.64</v>
+        <v>3.8</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AC11">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.01</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="S12">
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
         <v>1.11</v>
@@ -2301,28 +2301,28 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.69</v>
+        <v>4.16</v>
       </c>
       <c r="AA12">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AC12">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2446,10 +2446,10 @@
         <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U13">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="V13">
         <v>1.4</v>
@@ -2464,7 +2464,7 @@
         <v>1.23</v>
       </c>
       <c r="Z13">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="AA13">
         <v>1.94</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
         <v>1.67</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="O14">
         <v>4.1</v>
       </c>
       <c r="P14">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q14">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="R14">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
         <v>1.3</v>
@@ -2630,10 +2630,10 @@
         <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC14">
         <v>2.74</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,13 +2757,13 @@
         <v>1.72</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Q15">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
         <v>2.25</v>
@@ -2793,10 +2793,10 @@
         <v>4.25</v>
       </c>
       <c r="AA15">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB15">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
         <v>2.62</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="O16">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="P16">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="Q16">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R16">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2938,10 +2938,10 @@
         <v>3.26</v>
       </c>
       <c r="U16">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.1</v>
@@ -2956,7 +2956,7 @@
         <v>4.17</v>
       </c>
       <c r="AA16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
         <v>2.13</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK16">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,25 +3086,25 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="R17">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="S17">
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
         <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
         <v>1.08</v>
@@ -3122,7 +3122,7 @@
         <v>1.8</v>
       </c>
       <c r="AB17">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC17">
         <v>2.92</v>
@@ -3134,10 +3134,10 @@
         <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,58 +3243,58 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P18">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U18">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA18">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB18">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD18">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE18">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
         <v>1.7</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="O19">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.82</v>
+        <v>1.99</v>
       </c>
       <c r="Q19">
-        <v>2.67</v>
+        <v>4.33</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
         <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB19">
+        <v>1.8</v>
+      </c>
+      <c r="AC19">
+        <v>3.34</v>
+      </c>
+      <c r="AD19">
+        <v>1.24</v>
+      </c>
+      <c r="AE19">
+        <v>1.05</v>
+      </c>
+      <c r="AF19">
         <v>1.79</v>
       </c>
-      <c r="AC19">
-        <v>3.14</v>
-      </c>
-      <c r="AD19">
-        <v>1.31</v>
-      </c>
-      <c r="AE19">
-        <v>1.07</v>
-      </c>
-      <c r="AF19">
-        <v>1.7</v>
-      </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.44</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>1.99</v>
+        <v>3.75</v>
       </c>
       <c r="Q20">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R20">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD20">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>4.06</v>
       </c>
       <c r="AA23">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB23">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
         <v>2.62</v>
@@ -4435,7 +4435,7 @@
         <v>1.21</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
         <v>1.88</v>
@@ -4568,28 +4568,28 @@
         <v>2.75</v>
       </c>
       <c r="U26">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z26">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="AA26">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
         <v>3.58</v>
@@ -4601,10 +4601,10 @@
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
         <v>1.18</v>
@@ -5416,10 +5416,10 @@
         <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5564,10 +5564,10 @@
         <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
@@ -5905,10 +5905,10 @@
         <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>3.15</v>
       </c>
       <c r="Q35">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="R35">
         <v>1.96</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6195,7 +6195,7 @@
         <v>1.4</v>
       </c>
       <c r="T36">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U36">
         <v>3.2</v>
@@ -6204,7 +6204,7 @@
         <v>1.3</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1.03</v>
@@ -6216,10 +6216,10 @@
         <v>2.78</v>
       </c>
       <c r="AA36">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB36">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC36">
         <v>3.86</v>
@@ -6382,7 +6382,7 @@
         <v>2.01</v>
       </c>
       <c r="AB37">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
         <v>3.65</v>
@@ -7336,7 +7336,7 @@
         <v>1.38</v>
       </c>
       <c r="T43">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U43">
         <v>2.82</v>
@@ -7357,7 +7357,7 @@
         <v>3.1</v>
       </c>
       <c r="AA43">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB43">
         <v>1.7</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="O50">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q50">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="Z50">
-        <v>2.65</v>
+        <v>3.74</v>
       </c>
       <c r="AA50">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AB50">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC50">
-        <v>4.15</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG50">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q51">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="AA51">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AB51">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
+        <v>2.9</v>
+      </c>
+      <c r="O52">
+        <v>3.1</v>
+      </c>
+      <c r="P52">
+        <v>2.2</v>
+      </c>
+      <c r="Q52">
+        <v>3.5</v>
+      </c>
+      <c r="R52">
         <v>2</v>
       </c>
-      <c r="O52">
-        <v>3.4</v>
-      </c>
-      <c r="P52">
-        <v>3.1</v>
-      </c>
-      <c r="Q52">
-        <v>2.5</v>
-      </c>
-      <c r="R52">
+      <c r="S52">
+        <v>1.44</v>
+      </c>
+      <c r="T52">
+        <v>2.63</v>
+      </c>
+      <c r="U52">
+        <v>3.2</v>
+      </c>
+      <c r="V52">
+        <v>1.3</v>
+      </c>
+      <c r="W52">
+        <v>1.05</v>
+      </c>
+      <c r="X52">
+        <v>1.04</v>
+      </c>
+      <c r="Y52">
+        <v>1.43</v>
+      </c>
+      <c r="Z52">
+        <v>2.65</v>
+      </c>
+      <c r="AA52">
         <v>2.2</v>
       </c>
-      <c r="S52">
-        <v>1.33</v>
-      </c>
-      <c r="T52">
-        <v>3</v>
-      </c>
-      <c r="U52">
-        <v>2.75</v>
-      </c>
-      <c r="V52">
-        <v>1.4</v>
-      </c>
-      <c r="W52">
-        <v>1.07</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.25</v>
-      </c>
-      <c r="Z52">
-        <v>3.28</v>
-      </c>
-      <c r="AA52">
-        <v>1.85</v>
-      </c>
       <c r="AB52">
+        <v>1.65</v>
+      </c>
+      <c r="AC52">
+        <v>4.15</v>
+      </c>
+      <c r="AD52">
+        <v>1.16</v>
+      </c>
+      <c r="AE52">
+        <v>1.03</v>
+      </c>
+      <c r="AF52">
         <v>1.95</v>
       </c>
-      <c r="AC52">
-        <v>3.04</v>
-      </c>
-      <c r="AD52">
-        <v>1.29</v>
-      </c>
-      <c r="AE52">
-        <v>1.08</v>
-      </c>
-      <c r="AF52">
-        <v>1.73</v>
-      </c>
       <c r="AG52">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q54">
-        <v>2.6</v>
+        <v>3.02</v>
       </c>
       <c r="R54">
+        <v>1.87</v>
+      </c>
+      <c r="S54">
+        <v>1.44</v>
+      </c>
+      <c r="T54">
+        <v>2.5</v>
+      </c>
+      <c r="U54">
+        <v>3.3</v>
+      </c>
+      <c r="V54">
+        <v>1.29</v>
+      </c>
+      <c r="W54">
+        <v>1.05</v>
+      </c>
+      <c r="X54">
+        <v>1.07</v>
+      </c>
+      <c r="Y54">
+        <v>1.47</v>
+      </c>
+      <c r="Z54">
+        <v>2.53</v>
+      </c>
+      <c r="AA54">
+        <v>2.25</v>
+      </c>
+      <c r="AB54">
+        <v>1.49</v>
+      </c>
+      <c r="AC54">
+        <v>4.6</v>
+      </c>
+      <c r="AD54">
+        <v>1.13</v>
+      </c>
+      <c r="AE54">
+        <v>1.01</v>
+      </c>
+      <c r="AF54">
         <v>2</v>
       </c>
-      <c r="S54">
-        <v>1.4</v>
-      </c>
-      <c r="T54">
-        <v>2.75</v>
-      </c>
-      <c r="U54">
-        <v>3</v>
-      </c>
-      <c r="V54">
-        <v>1.33</v>
-      </c>
-      <c r="W54">
-        <v>1.06</v>
-      </c>
-      <c r="X54">
-        <v>1.04</v>
-      </c>
-      <c r="Y54">
-        <v>1.38</v>
-      </c>
-      <c r="Z54">
-        <v>2.81</v>
-      </c>
-      <c r="AA54">
-        <v>2.1</v>
-      </c>
-      <c r="AB54">
-        <v>1.61</v>
-      </c>
-      <c r="AC54">
-        <v>3.58</v>
-      </c>
-      <c r="AD54">
-        <v>1.21</v>
-      </c>
-      <c r="AE54">
-        <v>1.04</v>
-      </c>
-      <c r="AF54">
-        <v>1.86</v>
-      </c>
       <c r="AG54">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="O55">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q55">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R55">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="S55">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T55">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U55">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="V55">
+        <v>1.5</v>
+      </c>
+      <c r="W55">
+        <v>1.11</v>
+      </c>
+      <c r="X55">
+        <v>1.01</v>
+      </c>
+      <c r="Y55">
+        <v>1.19</v>
+      </c>
+      <c r="Z55">
+        <v>3.82</v>
+      </c>
+      <c r="AA55">
+        <v>1.65</v>
+      </c>
+      <c r="AB55">
+        <v>2.2</v>
+      </c>
+      <c r="AC55">
+        <v>2.74</v>
+      </c>
+      <c r="AD55">
+        <v>1.41</v>
+      </c>
+      <c r="AE55">
+        <v>1.12</v>
+      </c>
+      <c r="AF55">
+        <v>1.62</v>
+      </c>
+      <c r="AG55">
+        <v>2.2</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
         <v>1.25</v>
       </c>
-      <c r="W55">
-        <v>1.02</v>
-      </c>
-      <c r="X55">
-        <v>1.07</v>
-      </c>
-      <c r="Y55">
-        <v>1.47</v>
-      </c>
-      <c r="Z55">
-        <v>2.54</v>
-      </c>
-      <c r="AA55">
-        <v>2.25</v>
-      </c>
-      <c r="AB55">
-        <v>1.53</v>
-      </c>
-      <c r="AC55">
-        <v>4.4</v>
-      </c>
-      <c r="AD55">
-        <v>1.14</v>
-      </c>
-      <c r="AE55">
-        <v>1.01</v>
-      </c>
-      <c r="AF55">
-        <v>1.97</v>
-      </c>
-      <c r="AG55">
-        <v>1.73</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.3</v>
-      </c>
       <c r="AK55">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
         <v>3.6</v>
       </c>
       <c r="P56">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q56">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T56">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U56">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="Z56">
-        <v>3.82</v>
+        <v>2.86</v>
       </c>
       <c r="AA56">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="AB56">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC56">
-        <v>2.74</v>
+        <v>3.58</v>
       </c>
       <c r="AD56">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AE56">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG56">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK56">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>3.8</v>
       </c>
       <c r="AA57">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB57">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC57">
         <v>3.2</v>
@@ -9965,10 +9965,10 @@
         <v>4.8</v>
       </c>
       <c r="AA59">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB59">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AC59">
         <v>2.23</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q60">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="R60">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="S60">
         <v>1.25</v>
@@ -10122,31 +10122,31 @@
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>5.05</v>
+        <v>4.89</v>
       </c>
       <c r="AA60">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB60">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC60">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD60">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE60">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG60">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.26</v>
       </c>
       <c r="AK60">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10454,7 +10454,7 @@
         <v>2.97</v>
       </c>
       <c r="AA62">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB62">
         <v>1.71</v>
@@ -11106,7 +11106,7 @@
         <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB66">
         <v>1.74</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O67">
         <v>3.8</v>
       </c>
       <c r="P67">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q67">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="R67">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S67">
         <v>1.33</v>
@@ -11284,10 +11284,10 @@
         <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG67">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA68">
         <v>1.45</v>
@@ -11438,13 +11438,13 @@
         <v>2.75</v>
       </c>
       <c r="AC68">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD68">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE68">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF68">
         <v>1.65</v>
@@ -12250,7 +12250,7 @@
         <v>1.9</v>
       </c>
       <c r="AB73">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC73">
         <v>2.97</v>
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O74">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P74">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="Q74">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="R74">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
         <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U74">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V74">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W74">
         <v>1.13</v>
@@ -12404,31 +12404,31 @@
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z74">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA74">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB74">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AC74">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AD74">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK74">
         <v>1.25</v>
@@ -13056,7 +13056,7 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z78">
         <v>5</v>
@@ -13195,16 +13195,16 @@
         <v>1.03</v>
       </c>
       <c r="Q79">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R79">
         <v>3.55</v>
       </c>
       <c r="S79">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T79">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U79">
         <v>1.82</v>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="AA79">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AB79">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AC79">
         <v>1.7</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13841,10 +13841,10 @@
         <v>5.7</v>
       </c>
       <c r="O83">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="P83">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="Q83">
         <v>5.92</v>
@@ -13859,7 +13859,7 @@
         <v>5.05</v>
       </c>
       <c r="U83">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="V83">
         <v>1.9</v>
@@ -13877,10 +13877,10 @@
         <v>8.5</v>
       </c>
       <c r="AA83">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB83">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AC83">
         <v>1.68</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O85">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P85">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R85">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S85">
         <v>1.2</v>
@@ -14203,7 +14203,7 @@
         <v>5.95</v>
       </c>
       <c r="AA85">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AB85">
         <v>3.1</v>
@@ -14237,7 +14237,7 @@
         <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14339,7 +14339,7 @@
         <v>4.44</v>
       </c>
       <c r="R86">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="S86">
         <v>1.2</v>
@@ -14369,19 +14369,19 @@
         <v>1.37</v>
       </c>
       <c r="AB86">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="AC86">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AD86">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AE86">
         <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG86">
         <v>2.5</v>
@@ -14514,10 +14514,10 @@
         <v>2</v>
       </c>
       <c r="V87">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14656,7 +14656,7 @@
         <v>2.25</v>
       </c>
       <c r="O88">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P88">
         <v>2.75</v>
@@ -14668,10 +14668,10 @@
         <v>2.25</v>
       </c>
       <c r="S88">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U88">
         <v>2.19</v>
@@ -14837,13 +14837,13 @@
         <v>3.32</v>
       </c>
       <c r="U89">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W89">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
         <v>1.02</v>
@@ -14861,10 +14861,10 @@
         <v>2.33</v>
       </c>
       <c r="AC89">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD89">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE89">
         <v>1.22</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P90">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q90">
         <v>2.83</v>
@@ -14994,10 +14994,10 @@
         <v>2.27</v>
       </c>
       <c r="S90">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U90">
         <v>2.13</v>
@@ -15018,10 +15018,10 @@
         <v>4.6</v>
       </c>
       <c r="AA90">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB90">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC90">
         <v>2.24</v>
@@ -15151,16 +15151,16 @@
         <v>3.18</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U91">
         <v>0</v>
@@ -15175,16 +15175,16 @@
         <v>0</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15196,10 +15196,10 @@
         <v>0</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O95">
         <v>3.9</v>
@@ -15839,10 +15839,10 @@
         <v>2.81</v>
       </c>
       <c r="AC95">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD95">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE95">
         <v>1.3</v>
@@ -15851,7 +15851,7 @@
         <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -16455,10 +16455,10 @@
         <v>5.75</v>
       </c>
       <c r="Q99">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="R99">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S99">
         <v>1.43</v>
@@ -16612,10 +16612,10 @@
         <v>2.25</v>
       </c>
       <c r="O100">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P100">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O103">
         <v>4.33</v>
@@ -17110,7 +17110,7 @@
         <v>1.9</v>
       </c>
       <c r="R103">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="S103">
         <v>1.22</v>
@@ -17122,7 +17122,7 @@
         <v>2.12</v>
       </c>
       <c r="V103">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W103">
         <v>1.18</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK103">
         <v>2.64</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="O104">
         <v>4.25</v>
       </c>
       <c r="P104">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q104">
         <v>4.4</v>
@@ -17303,7 +17303,7 @@
         <v>1.43</v>
       </c>
       <c r="AB104">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC104">
         <v>2.04</v>
@@ -17922,22 +17922,22 @@
         <v>6.41</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W108">
         <v>0</v>
@@ -17946,16 +17946,16 @@
         <v>0</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -17967,10 +17967,10 @@
         <v>0</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,16 +18085,16 @@
         <v>2.63</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U109">
         <v>0</v>
@@ -18109,16 +18109,16 @@
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18130,10 +18130,10 @@
         <v>0</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,22 +18248,22 @@
         <v>10.7</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W110">
         <v>0</v>
@@ -18272,31 +18272,31 @@
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE110">
         <v>0</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>0</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18417,13 +18417,13 @@
         <v>2.05</v>
       </c>
       <c r="S111">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T111">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="U111">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V111">
         <v>1.35</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>3.48</v>
+        <v>2.94</v>
       </c>
       <c r="R112">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S112">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T112">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U112">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V112">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W112">
         <v>1.08</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z112">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA112">
+        <v>1.93</v>
+      </c>
+      <c r="AB112">
         <v>1.72</v>
       </c>
-      <c r="AB112">
-        <v>1.9</v>
-      </c>
       <c r="AC112">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD112">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF112">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG112">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK112">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q113">
-        <v>2.85</v>
+        <v>3.48</v>
       </c>
       <c r="R113">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="U113">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V113">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
         <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y113">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z113">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA113">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB113">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC113">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD113">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF113">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG113">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK113">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O115">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="P115">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q115">
         <v>1.92</v>
@@ -19069,7 +19069,7 @@
         <v>2.38</v>
       </c>
       <c r="S115">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T115">
         <v>4.1</v>
@@ -19078,10 +19078,10 @@
         <v>2.1</v>
       </c>
       <c r="V115">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W115">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X115">
         <v>1</v>
@@ -19090,19 +19090,19 @@
         <v>1.11</v>
       </c>
       <c r="Z115">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA115">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB115">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AC115">
         <v>2.2</v>
       </c>
       <c r="AD115">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE115">
         <v>1.22</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK115">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P116">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q116">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="R116">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S116">
         <v>1.35</v>
@@ -19238,43 +19238,43 @@
         <v>2.77</v>
       </c>
       <c r="U116">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V116">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W116">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y116">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z116">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AA116">
         <v>2.05</v>
       </c>
       <c r="AB116">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC116">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD116">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE116">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG116">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK116">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19561,7 +19561,7 @@
         <v>1.15</v>
       </c>
       <c r="T118">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="U118">
         <v>1.81</v>
@@ -19582,7 +19582,7 @@
         <v>8</v>
       </c>
       <c r="AA118">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AB118">
         <v>3.6</v>
@@ -19712,7 +19712,7 @@
         <v>3.8</v>
       </c>
       <c r="P119">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="Q119">
         <v>2.65</v>
@@ -19742,7 +19742,7 @@
         <v>1.11</v>
       </c>
       <c r="Z119">
-        <v>5.69</v>
+        <v>6.34</v>
       </c>
       <c r="AA119">
         <v>1.4</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="O120">
         <v>3.45</v>
       </c>
       <c r="P120">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -19911,7 +19911,7 @@
         <v>1.49</v>
       </c>
       <c r="AB120">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC120">
         <v>2.27</v>
@@ -20035,10 +20035,10 @@
         <v>1.18</v>
       </c>
       <c r="O121">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="P121">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q121">
         <v>1.5</v>
@@ -20062,7 +20062,7 @@
         <v>1.3</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
         <v>1.02</v>
@@ -20237,7 +20237,7 @@
         <v>2.1</v>
       </c>
       <c r="AB122">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC122">
         <v>3.58</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O123">
         <v>3.58</v>
@@ -20431,7 +20431,7 @@
         <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="O124">
         <v>4.2</v>
       </c>
       <c r="P124">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="Q124">
         <v>1.87</v>
@@ -20594,7 +20594,7 @@
         <v>1.16</v>
       </c>
       <c r="AK124">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20711,7 +20711,7 @@
         <v>1.68</v>
       </c>
       <c r="W125">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X125">
         <v>1.01</v>
@@ -20726,13 +20726,13 @@
         <v>1.5</v>
       </c>
       <c r="AB125">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC125">
         <v>2.44</v>
       </c>
       <c r="AD125">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE125">
         <v>1.21</v>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O126">
         <v>3.6</v>
@@ -20856,10 +20856,10 @@
         <v>3.01</v>
       </c>
       <c r="Q126">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R126">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S126">
         <v>1.3</v>
@@ -20883,7 +20883,7 @@
         <v>1.15</v>
       </c>
       <c r="Z126">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="AA126">
         <v>1.57</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="O127">
         <v>4</v>
       </c>
       <c r="P127">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q127">
         <v>4.75</v>
@@ -21025,7 +21025,7 @@
         <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T127">
         <v>3.6</v>
@@ -21064,10 +21064,10 @@
         <v>1.17</v>
       </c>
       <c r="AF127">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG127">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O128">
         <v>3.7</v>
       </c>
       <c r="P128">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q128">
         <v>3.1</v>
       </c>
       <c r="R128">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S128">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T128">
         <v>3.6</v>
       </c>
       <c r="U128">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="V128">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W128">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
         <v>1</v>
@@ -21215,7 +21215,7 @@
         <v>1.69</v>
       </c>
       <c r="AB128">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AC128">
         <v>2.52</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O129">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P129">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -21378,7 +21378,7 @@
         <v>1.55</v>
       </c>
       <c r="AB129">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AC129">
         <v>2.33</v>
@@ -21499,19 +21499,19 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O130">
         <v>3.5</v>
       </c>
       <c r="P130">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q130">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R130">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S130">
         <v>1.37</v>
@@ -21520,25 +21520,25 @@
         <v>3.13</v>
       </c>
       <c r="U130">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V130">
         <v>1.43</v>
       </c>
       <c r="W130">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X130">
         <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z130">
         <v>4.13</v>
       </c>
       <c r="AA130">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB130">
         <v>2</v>
@@ -21547,16 +21547,16 @@
         <v>3</v>
       </c>
       <c r="AD130">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE130">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF130">
         <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>1.35</v>
       </c>
       <c r="AK130">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O132">
         <v>5</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="O134">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P134">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q134">
         <v>1.46</v>
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="O135">
         <v>4.4</v>
       </c>
       <c r="P135">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="Q135">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R135">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S135">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U135">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="V135">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA135">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB135">
         <v>2.1</v>
       </c>
       <c r="AC135">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="AD135">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE135">
+        <v>1.1</v>
+      </c>
+      <c r="AF135">
+        <v>1.95</v>
+      </c>
+      <c r="AG135">
+        <v>1.73</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
         <v>1.11</v>
       </c>
-      <c r="AF135">
-        <v>1.93</v>
-      </c>
-      <c r="AG135">
-        <v>1.75</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.1</v>
-      </c>
       <c r="AK135">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22504,7 +22504,7 @@
         <v>1.4</v>
       </c>
       <c r="W136">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X136">
         <v>1.01</v>
@@ -22516,7 +22516,7 @@
         <v>3.08</v>
       </c>
       <c r="AA136">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB136">
         <v>1.78</v>
@@ -22550,7 +22550,7 @@
         <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22643,7 +22643,7 @@
         <v>3.1</v>
       </c>
       <c r="O137">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P137">
         <v>2.15</v>
@@ -22682,7 +22682,7 @@
         <v>1.65</v>
       </c>
       <c r="AB137">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC137">
         <v>2.41</v>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O141">
         <v>3.45</v>
@@ -23464,7 +23464,7 @@
         <v>1.56</v>
       </c>
       <c r="Q142">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="R142">
         <v>2.2</v>
@@ -23781,7 +23781,7 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O144">
         <v>3.37</v>
@@ -23790,55 +23790,55 @@
         <v>3.08</v>
       </c>
       <c r="Q144">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="R144">
         <v>2.11</v>
       </c>
       <c r="S144">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T144">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U144">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="V144">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W144">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X144">
         <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z144">
+        <v>3.05</v>
+      </c>
+      <c r="AA144">
+        <v>2.04</v>
+      </c>
+      <c r="AB144">
+        <v>1.9</v>
+      </c>
+      <c r="AC144">
         <v>3.1</v>
       </c>
-      <c r="AA144">
-        <v>1.9</v>
-      </c>
-      <c r="AB144">
-        <v>1.98</v>
-      </c>
-      <c r="AC144">
-        <v>3</v>
-      </c>
       <c r="AD144">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE144">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG144">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.3</v>
       </c>
       <c r="AK144">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23965,7 +23965,7 @@
         <v>4.5</v>
       </c>
       <c r="U145">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V145">
         <v>1.74</v>
@@ -23983,10 +23983,10 @@
         <v>6.05</v>
       </c>
       <c r="AA145">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB145">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AC145">
         <v>2.07</v>
@@ -24279,16 +24279,16 @@
         <v>2.92</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U147">
         <v>0</v>
@@ -24303,16 +24303,16 @@
         <v>0</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC147">
         <v>0</v>
@@ -24324,10 +24324,10 @@
         <v>0</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>11.9</v>
+        <v>9.65</v>
       </c>
       <c r="O161">
-        <v>7.11</v>
+        <v>6.32</v>
       </c>
       <c r="P161">
+        <v>1.26</v>
+      </c>
+      <c r="Q161">
+        <v>6.5</v>
+      </c>
+      <c r="R161">
+        <v>2.88</v>
+      </c>
+      <c r="S161">
         <v>1.2</v>
       </c>
-      <c r="Q161">
-        <v>8.5</v>
-      </c>
-      <c r="R161">
-        <v>3</v>
-      </c>
-      <c r="S161">
-        <v>1.14</v>
-      </c>
       <c r="T161">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U161">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V161">
         <v>1.75</v>
       </c>
       <c r="W161">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X161">
         <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z161">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AA161">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB161">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AC161">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD161">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AE161">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AF161">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG161">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.11</v>
+        <v>3.74</v>
       </c>
       <c r="AK161">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27702,55 +27702,55 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S168">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T168">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U168">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V168">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W168">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X168">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y168">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z168">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA168">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB168">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC168">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD168">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF168">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG168">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK168">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -29160,19 +29160,19 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O177">
         <v>3.3</v>
       </c>
       <c r="P177">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q177">
         <v>3.01</v>
       </c>
       <c r="R177">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S177">
         <v>1.26</v>
@@ -29196,22 +29196,22 @@
         <v>1.18</v>
       </c>
       <c r="Z177">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="AA177">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB177">
         <v>2.25</v>
       </c>
       <c r="AC177">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AD177">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE177">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF177">
         <v>1.53</v>
@@ -29362,7 +29362,7 @@
         <v>3.92</v>
       </c>
       <c r="AA178">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB178">
         <v>2.05</v>
@@ -29396,7 +29396,7 @@
         <v>1.4</v>
       </c>
       <c r="AK178">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -30476,7 +30476,7 @@
         <v>6</v>
       </c>
       <c r="R185">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S185">
         <v>1.3</v>
@@ -30491,7 +30491,7 @@
         <v>1.5</v>
       </c>
       <c r="W185">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X185">
         <v>1.01</v>
@@ -30512,7 +30512,7 @@
         <v>2.56</v>
       </c>
       <c r="AD185">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE185">
         <v>1.12</v>
@@ -30521,7 +30521,7 @@
         <v>1.85</v>
       </c>
       <c r="AG185">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O187">
         <v>3.5</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O191">
         <v>4</v>
       </c>
       <c r="P191">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q191">
         <v>2.01</v>
@@ -31614,7 +31614,7 @@
         <v>7.48</v>
       </c>
       <c r="Q192">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R192">
         <v>2.6</v>
@@ -31647,7 +31647,7 @@
         <v>1.47</v>
       </c>
       <c r="AB192">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AC192">
         <v>2.05</v>
@@ -31777,55 +31777,55 @@
         <v>1.91</v>
       </c>
       <c r="Q193">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="R193">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S193">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T193">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="U193">
         <v>2.5</v>
       </c>
       <c r="V193">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W193">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X193">
         <v>1</v>
       </c>
       <c r="Y193">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z193">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA193">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB193">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AC193">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AD193">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE193">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF193">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG193">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>1.56</v>
       </c>
       <c r="AB195">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC195">
         <v>2.33</v>
@@ -32151,7 +32151,7 @@
         <v>1.62</v>
       </c>
       <c r="AG195">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>1.69</v>
       </c>
       <c r="R196">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="S196">
         <v>1.31</v>
@@ -32420,19 +32420,19 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O197">
         <v>4.5</v>
       </c>
       <c r="P197">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q197">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R197">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="S197">
         <v>1.17</v>
@@ -32444,40 +32444,40 @@
         <v>2.08</v>
       </c>
       <c r="V197">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W197">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z197">
-        <v>5.55</v>
+        <v>6.78</v>
       </c>
       <c r="AA197">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB197">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC197">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AD197">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AE197">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF197">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG197">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>1.07</v>
       </c>
       <c r="AF198">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG198">
         <v>1.97</v>
@@ -32755,55 +32755,55 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R199">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S199">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T199">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U199">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V199">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W199">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X199">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y199">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z199">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AA199">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB199">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC199">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD199">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE199">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF199">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG199">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK199">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33241,7 +33241,7 @@
         <v>4.45</v>
       </c>
       <c r="P202">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q202">
         <v>4.03</v>
@@ -33277,7 +33277,7 @@
         <v>1.32</v>
       </c>
       <c r="AB202">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC202">
         <v>1.93</v>
@@ -33564,7 +33564,7 @@
         <v>2.15</v>
       </c>
       <c r="O204">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P204">
         <v>3</v>
@@ -33603,7 +33603,7 @@
         <v>1.6</v>
       </c>
       <c r="AB204">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC204">
         <v>2.48</v>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R205">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S205">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T205">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U205">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="V205">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W205">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X205">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y205">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z205">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA205">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB205">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC205">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD205">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE205">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF205">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG205">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AK205">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33929,7 +33929,7 @@
         <v>1.67</v>
       </c>
       <c r="AB206">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC206">
         <v>2.66</v>
@@ -34059,7 +34059,7 @@
         <v>2.75</v>
       </c>
       <c r="Q207">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R207">
         <v>2.17</v>
@@ -34071,10 +34071,10 @@
         <v>3.25</v>
       </c>
       <c r="U207">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V207">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W207">
         <v>1.08</v>
@@ -34086,7 +34086,7 @@
         <v>1.19</v>
       </c>
       <c r="Z207">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA207">
         <v>1.72</v>
@@ -34252,10 +34252,10 @@
         <v>5.75</v>
       </c>
       <c r="AA208">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB208">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AC208">
         <v>2.07</v>
@@ -34415,7 +34415,7 @@
         <v>6.79</v>
       </c>
       <c r="AA209">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB209">
         <v>2.83</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35396,7 +35396,7 @@
         <v>1.4</v>
       </c>
       <c r="AB215">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC215">
         <v>2.15</v>
@@ -35852,55 +35852,55 @@
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R218">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S218">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T218">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U218">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V218">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W218">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X218">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y218">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z218">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA218">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB218">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC218">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD218">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE218">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF218">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG218">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK218">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.52</v>
+        <v>4.23</v>
       </c>
       <c r="O220">
-        <v>4.15</v>
+        <v>4.52</v>
       </c>
       <c r="P220">
-        <v>4.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q220">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="R220">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="S220">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T220">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U220">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="V220">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="W220">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X220">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z220">
-        <v>6.7</v>
+        <v>8.6</v>
       </c>
       <c r="AA220">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AB220">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="AC220">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AD220">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AE220">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AF220">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AG220">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK220">
-        <v>2.34</v>
+        <v>1.22</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>4.23</v>
+        <v>1.8</v>
       </c>
       <c r="O221">
-        <v>4.52</v>
+        <v>3.85</v>
       </c>
       <c r="P221">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q221">
-        <v>3.75</v>
+        <v>2.21</v>
       </c>
       <c r="R221">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="S221">
         <v>1.15</v>
       </c>
       <c r="T221">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U221">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V221">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="W221">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X221">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y221">
         <v>1.03</v>
       </c>
       <c r="Z221">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="AA221">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AB221">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC221">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD221">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AE221">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AF221">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AG221">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK221">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O222">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P222">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q222">
+        <v>2.18</v>
+      </c>
+      <c r="R222">
+        <v>2.4</v>
+      </c>
+      <c r="S222">
+        <v>1.22</v>
+      </c>
+      <c r="T222">
+        <v>3.55</v>
+      </c>
+      <c r="U222">
         <v>2.2</v>
       </c>
-      <c r="R222">
-        <v>2.7</v>
-      </c>
-      <c r="S222">
-        <v>1.15</v>
-      </c>
-      <c r="T222">
-        <v>4.8</v>
-      </c>
-      <c r="U222">
-        <v>1.73</v>
-      </c>
       <c r="V222">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="W222">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="X222">
         <v>1.01</v>
       </c>
       <c r="Y222">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z222">
-        <v>7.3</v>
+        <v>4.91</v>
       </c>
       <c r="AA222">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AB222">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="AC222">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AD222">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AE222">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AF222">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG222">
-        <v>3.14</v>
+        <v>2.44</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK222">
         <v>1.91</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="O223">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="P223">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="Q223">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="R223">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="S223">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T223">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="U223">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="V223">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="W223">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="X223">
         <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z223">
-        <v>4.91</v>
+        <v>6.7</v>
       </c>
       <c r="AA223">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB223">
-        <v>2.29</v>
+        <v>3.08</v>
       </c>
       <c r="AC223">
-        <v>2.23</v>
+        <v>1.82</v>
       </c>
       <c r="AD223">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AE223">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AF223">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG223">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.2</v>
       </c>
       <c r="AK223">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36833,52 +36833,52 @@
         <v>1.67</v>
       </c>
       <c r="R224">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="S224">
         <v>1.25</v>
       </c>
       <c r="T224">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U224">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V224">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W224">
         <v>1.14</v>
       </c>
       <c r="X224">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y224">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z224">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AA224">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB224">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AC224">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD224">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AE224">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF224">
         <v>1.85</v>
       </c>
       <c r="AG224">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK224">
         <v>3.6</v>
@@ -36987,7 +36987,7 @@
         <v>2.17</v>
       </c>
       <c r="O225">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P225">
         <v>3</v>
@@ -36999,7 +36999,7 @@
         <v>2.2</v>
       </c>
       <c r="S225">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T225">
         <v>3.12</v>
@@ -37023,7 +37023,7 @@
         <v>3.58</v>
       </c>
       <c r="AA225">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB225">
         <v>1.9</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,65 +37147,65 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="O226">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="P226">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="Q226">
+        <v>2.17</v>
+      </c>
+      <c r="R226">
+        <v>2.38</v>
+      </c>
+      <c r="S226">
+        <v>1.25</v>
+      </c>
+      <c r="T226">
+        <v>3.52</v>
+      </c>
+      <c r="U226">
+        <v>2.38</v>
+      </c>
+      <c r="V226">
+        <v>1.5</v>
+      </c>
+      <c r="W226">
+        <v>1.11</v>
+      </c>
+      <c r="X226">
+        <v>1.01</v>
+      </c>
+      <c r="Y226">
+        <v>1.19</v>
+      </c>
+      <c r="Z226">
+        <v>4.5</v>
+      </c>
+      <c r="AA226">
+        <v>1.61</v>
+      </c>
+      <c r="AB226">
+        <v>2.3</v>
+      </c>
+      <c r="AC226">
+        <v>2.61</v>
+      </c>
+      <c r="AD226">
+        <v>1.54</v>
+      </c>
+      <c r="AE226">
+        <v>1.21</v>
+      </c>
+      <c r="AF226">
+        <v>1.65</v>
+      </c>
+      <c r="AG226">
         <v>2.2</v>
       </c>
-      <c r="R226">
-        <v>2.52</v>
-      </c>
-      <c r="S226">
-        <v>1.2</v>
-      </c>
-      <c r="T226">
-        <v>4</v>
-      </c>
-      <c r="U226">
-        <v>2</v>
-      </c>
-      <c r="V226">
-        <v>1.75</v>
-      </c>
-      <c r="W226">
-        <v>1.22</v>
-      </c>
-      <c r="X226">
-        <v>1</v>
-      </c>
-      <c r="Y226">
-        <v>1.11</v>
-      </c>
-      <c r="Z226">
-        <v>5.87</v>
-      </c>
-      <c r="AA226">
-        <v>1.43</v>
-      </c>
-      <c r="AB226">
-        <v>2.8</v>
-      </c>
-      <c r="AC226">
-        <v>2.12</v>
-      </c>
-      <c r="AD226">
-        <v>1.78</v>
-      </c>
-      <c r="AE226">
-        <v>1.28</v>
-      </c>
-      <c r="AF226">
-        <v>1.43</v>
-      </c>
-      <c r="AG226">
-        <v>2.66</v>
-      </c>
       <c r="AH226" t="inlineStr">
         <is>
           <t>[]</t>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK226">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="O227">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P227">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="Q227">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="R227">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="S227">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T227">
-        <v>3.52</v>
+        <v>3.28</v>
       </c>
       <c r="U227">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V227">
         <v>1.5</v>
       </c>
       <c r="W227">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X227">
         <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z227">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="AA227">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB227">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC227">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="AD227">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AE227">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AF227">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG227">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK227">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37473,7 +37473,7 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O228">
         <v>4.2</v>
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK228">
         <v>2.46</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="O229">
-        <v>3.6</v>
+        <v>4.24</v>
       </c>
       <c r="P229">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="Q229">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="R229">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="S229">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T229">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U229">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="V229">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W229">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X229">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y229">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z229">
-        <v>4.14</v>
+        <v>5.87</v>
       </c>
       <c r="AA229">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AB229">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="AC229">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="AD229">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="AE229">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AF229">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AG229">
-        <v>2.23</v>
+        <v>2.66</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK229">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37971,22 +37971,22 @@
         <v>2.37</v>
       </c>
       <c r="Q231">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="R231">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S231">
         <v>1.4</v>
       </c>
       <c r="T231">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="U231">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="V231">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W231">
         <v>1.04</v>
@@ -37995,16 +37995,16 @@
         <v>1.04</v>
       </c>
       <c r="Y231">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z231">
-        <v>3.16</v>
+        <v>2.78</v>
       </c>
       <c r="AA231">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB231">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC231">
         <v>3.76</v>
@@ -38016,10 +38016,10 @@
         <v>1.04</v>
       </c>
       <c r="AF231">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG231">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK231">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38146,10 +38146,10 @@
         <v>3.38</v>
       </c>
       <c r="U232">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V232">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W232">
         <v>1.12</v>
@@ -38460,55 +38460,55 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R234">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S234">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T234">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U234">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V234">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W234">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X234">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y234">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z234">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA234">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB234">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC234">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD234">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE234">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF234">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG234">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK234">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38626,7 +38626,7 @@
         <v>3.1</v>
       </c>
       <c r="R235">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S235">
         <v>1.29</v>
@@ -38656,7 +38656,7 @@
         <v>1.7</v>
       </c>
       <c r="AB235">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC235">
         <v>2.56</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O236">
         <v>3.25</v>
       </c>
       <c r="P236">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q236">
         <v>2.57</v>
@@ -38795,7 +38795,7 @@
         <v>1.35</v>
       </c>
       <c r="T236">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U236">
         <v>2.73</v>
@@ -38819,7 +38819,7 @@
         <v>1.93</v>
       </c>
       <c r="AB236">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC236">
         <v>3.34</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R237">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S237">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T237">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U237">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V237">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W237">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X237">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y237">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z237">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA237">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB237">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC237">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD237">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE237">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF237">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG237">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK237">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,10 +39103,10 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O238">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P238">
         <v>3</v>
@@ -39142,7 +39142,7 @@
         <v>2.88</v>
       </c>
       <c r="AA238">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB238">
         <v>1.6</v>
@@ -39157,10 +39157,10 @@
         <v>1.03</v>
       </c>
       <c r="AF238">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG238">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39266,31 +39266,31 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="O239">
         <v>3.25</v>
       </c>
       <c r="P239">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q239">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R239">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S239">
         <v>1.4</v>
       </c>
       <c r="T239">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U239">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V239">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W239">
         <v>1.06</v>
@@ -39302,19 +39302,19 @@
         <v>1.37</v>
       </c>
       <c r="Z239">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AA239">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AB239">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC239">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AD239">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE239">
         <v>1.04</v>
@@ -39323,7 +39323,7 @@
         <v>1.91</v>
       </c>
       <c r="AG239">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK239">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39444,10 +39444,10 @@
         <v>1.96</v>
       </c>
       <c r="S240">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T240">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="U240">
         <v>3</v>
@@ -39456,7 +39456,7 @@
         <v>1.33</v>
       </c>
       <c r="W240">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X240">
         <v>1.02</v>
@@ -39502,7 +39502,7 @@
         <v>1.26</v>
       </c>
       <c r="AK240">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39598,25 +39598,25 @@
         <v>3.3</v>
       </c>
       <c r="P241">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q241">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="R241">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S241">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T241">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="U241">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V241">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W241">
         <v>1.05</v>
@@ -39631,16 +39631,16 @@
         <v>3.7</v>
       </c>
       <c r="AA241">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB241">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AC241">
         <v>2.88</v>
       </c>
       <c r="AD241">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE241">
         <v>1.08</v>
@@ -39767,7 +39767,7 @@
         <v>5.5</v>
       </c>
       <c r="R242">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="S242">
         <v>1.11</v>
@@ -39933,7 +39933,7 @@
         <v>2.4</v>
       </c>
       <c r="S243">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T243">
         <v>3.5</v>
@@ -39945,7 +39945,7 @@
         <v>1.56</v>
       </c>
       <c r="W243">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X243">
         <v>1.02</v>
@@ -39972,7 +39972,7 @@
         <v>1.18</v>
       </c>
       <c r="AF243">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG243">
         <v>2.18</v>
@@ -40090,55 +40090,55 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R244">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S244">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T244">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U244">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V244">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W244">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X244">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y244">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z244">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA244">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB244">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC244">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD244">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE244">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF244">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG244">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK244">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40256,13 +40256,13 @@
         <v>1.8</v>
       </c>
       <c r="R245">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S245">
         <v>1.17</v>
       </c>
       <c r="T245">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U245">
         <v>2</v>
@@ -40298,7 +40298,7 @@
         <v>1.28</v>
       </c>
       <c r="AF245">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG245">
         <v>2.34</v>
@@ -40317,7 +40317,7 @@
         <v>1.11</v>
       </c>
       <c r="AK245">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40446,7 +40446,7 @@
         <v>4.5</v>
       </c>
       <c r="AA246">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB246">
         <v>2.3</v>
@@ -40570,10 +40570,10 @@
         </is>
       </c>
       <c r="N247">
-        <v>3.75</v>
+        <v>3.99</v>
       </c>
       <c r="O247">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="P247">
         <v>1.9</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="O248">
         <v>3.5</v>
       </c>
       <c r="P248">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q248">
         <v>2.88</v>
@@ -40923,7 +40923,7 @@
         <v>1.5</v>
       </c>
       <c r="W249">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X249">
         <v>1.01</v>
@@ -40950,10 +40950,10 @@
         <v>1.12</v>
       </c>
       <c r="AF249">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG249">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O251">
         <v>4.1</v>
       </c>
       <c r="P251">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q251">
         <v>1.94</v>
@@ -41267,10 +41267,10 @@
         <v>2.08</v>
       </c>
       <c r="AC251">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD251">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE251">
         <v>1.17</v>
@@ -41385,7 +41385,7 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O252">
         <v>3.6</v>
@@ -41427,7 +41427,7 @@
         <v>1.92</v>
       </c>
       <c r="AB252">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC252">
         <v>3.2</v>
@@ -41554,7 +41554,7 @@
         <v>4.05</v>
       </c>
       <c r="P253">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q253">
         <v>2.2</v>
@@ -41587,7 +41587,7 @@
         <v>4.55</v>
       </c>
       <c r="AA253">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB253">
         <v>2.25</v>
@@ -41596,7 +41596,7 @@
         <v>2.55</v>
       </c>
       <c r="AD253">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE253">
         <v>1.13</v>
@@ -41753,7 +41753,7 @@
         <v>1.93</v>
       </c>
       <c r="AB254">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC254">
         <v>3.6</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O255">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P255">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q255">
         <v>2.2</v>
@@ -41916,7 +41916,7 @@
         <v>1.65</v>
       </c>
       <c r="AB255">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC255">
         <v>2.7</v>
@@ -41928,10 +41928,10 @@
         <v>1.11</v>
       </c>
       <c r="AF255">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AG255">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -42046,55 +42046,55 @@
         <v>2.97</v>
       </c>
       <c r="Q256">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R256">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S256">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T256">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="U256">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V256">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W256">
         <v>1.06</v>
       </c>
       <c r="X256">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y256">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z256">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA256">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AB256">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AC256">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AD256">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE256">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF256">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AG256">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>1.25</v>
       </c>
       <c r="AK256">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42209,7 +42209,7 @@
         <v>1.95</v>
       </c>
       <c r="Q257">
-        <v>3.8</v>
+        <v>4.28</v>
       </c>
       <c r="R257">
         <v>2.3</v>
@@ -42873,7 +42873,7 @@
         <v>2.63</v>
       </c>
       <c r="U261">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V261">
         <v>1.3</v>
@@ -42897,7 +42897,7 @@
         <v>1.66</v>
       </c>
       <c r="AC261">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD261">
         <v>1.16</v>
@@ -42906,10 +42906,10 @@
         <v>1.02</v>
       </c>
       <c r="AF261">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG261">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>5.5</v>
       </c>
       <c r="AA262">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB262">
         <v>2.5</v>
@@ -43510,7 +43510,7 @@
         <v>4.2</v>
       </c>
       <c r="P265">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q265">
         <v>1.88</v>
@@ -43522,7 +43522,7 @@
         <v>1.2</v>
       </c>
       <c r="T265">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U265">
         <v>2.1</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,22 +44156,22 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q269">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="R269">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S269">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T269">
         <v>2.2</v>
@@ -44183,25 +44183,25 @@
         <v>1.2</v>
       </c>
       <c r="W269">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X269">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y269">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z269">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AA269">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB269">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC269">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AD269">
         <v>1.04</v>
@@ -44210,10 +44210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AG269">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK269">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,22 +44319,22 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q270">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="R270">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S270">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T270">
         <v>2.2</v>
@@ -44346,25 +44346,25 @@
         <v>1.2</v>
       </c>
       <c r="W270">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X270">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y270">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z270">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AA270">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB270">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC270">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AD270">
         <v>1.04</v>
@@ -44373,10 +44373,10 @@
         <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AG270">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK270">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44497,7 +44497,7 @@
         <v>2.43</v>
       </c>
       <c r="S271">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T271">
         <v>3.9</v>
@@ -44524,7 +44524,7 @@
         <v>1.36</v>
       </c>
       <c r="AB271">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC271">
         <v>1.99</v>
@@ -44539,7 +44539,7 @@
         <v>1.29</v>
       </c>
       <c r="AG271">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44654,22 +44654,22 @@
         <v>4.8</v>
       </c>
       <c r="Q272">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="R272">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S272">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T272">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="U272">
         <v>3.2</v>
       </c>
       <c r="V272">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W272">
         <v>1.07</v>
@@ -44678,22 +44678,22 @@
         <v>1.06</v>
       </c>
       <c r="Y272">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z272">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AA272">
         <v>2.25</v>
       </c>
       <c r="AB272">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC272">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="AD272">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE272">
         <v>1.07</v>
@@ -44702,7 +44702,7 @@
         <v>1.95</v>
       </c>
       <c r="AG272">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK272">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q274">
         <v>2.5</v>
@@ -45134,7 +45134,7 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O275">
         <v>3.4</v>
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O276">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P276">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q276">
         <v>2.25</v>
@@ -45336,7 +45336,7 @@
         <v>2.57</v>
       </c>
       <c r="AA276">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AB276">
         <v>1.53</v>
@@ -45463,7 +45463,7 @@
         <v>3.2</v>
       </c>
       <c r="O277">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P277">
         <v>2.3</v>
@@ -45665,7 +45665,7 @@
         <v>2.18</v>
       </c>
       <c r="AB278">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC278">
         <v>3.98</v>
@@ -45988,10 +45988,10 @@
         <v>5.52</v>
       </c>
       <c r="AA280">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB280">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC280">
         <v>2.17</v>
@@ -46003,7 +46003,7 @@
         <v>1.25</v>
       </c>
       <c r="AF280">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG280">
         <v>2.75</v>
@@ -46118,7 +46118,7 @@
         <v>5</v>
       </c>
       <c r="P281">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q281">
         <v>1.84</v>
@@ -46127,10 +46127,10 @@
         <v>2.7</v>
       </c>
       <c r="S281">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T281">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U281">
         <v>2</v>
@@ -46284,7 +46284,7 @@
         <v>1.53</v>
       </c>
       <c r="Q282">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="R282">
         <v>2.26</v>
@@ -46296,7 +46296,7 @@
         <v>3.2</v>
       </c>
       <c r="U282">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="V282">
         <v>1.43</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O283">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="P283">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="O284">
         <v>2.9</v>
       </c>
       <c r="P284">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46803,7 +46803,7 @@
         <v>2.1</v>
       </c>
       <c r="AA285">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB285">
         <v>1.32</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="O286">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="P286">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Q286">
         <v>1.62</v>
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O287">
         <v>4.1</v>
       </c>
       <c r="P287">
-        <v>5.06</v>
+        <v>4.95</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47129,10 +47129,10 @@
         <v>0</v>
       </c>
       <c r="AA287">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB287">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC287">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB288">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47911,7 +47911,7 @@
         <v>5</v>
       </c>
       <c r="P292">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q292">
         <v>1.92</v>
@@ -47944,7 +47944,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AA292">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AB292">
         <v>4.55</v>
@@ -47962,7 +47962,7 @@
         <v>1.24</v>
       </c>
       <c r="AG292">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK292">
         <v>2.38</v>
@@ -48759,10 +48759,10 @@
         <v>3.85</v>
       </c>
       <c r="AA297">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB297">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC297">
         <v>2.62</v>
@@ -48901,13 +48901,13 @@
         <v>1.29</v>
       </c>
       <c r="T298">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="U298">
         <v>2.42</v>
       </c>
       <c r="V298">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W298">
         <v>1.13</v>
@@ -49085,7 +49085,7 @@
         <v>5.75</v>
       </c>
       <c r="AA299">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB299">
         <v>2.6</v>
@@ -49103,7 +49103,7 @@
         <v>1.91</v>
       </c>
       <c r="AG299">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK299">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49577,7 +49577,7 @@
         <v>2.16</v>
       </c>
       <c r="AB302">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC302">
         <v>3.92</v>
@@ -49740,7 +49740,7 @@
         <v>1.68</v>
       </c>
       <c r="AB303">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC303">
         <v>2.65</v>
@@ -49755,7 +49755,7 @@
         <v>1.5</v>
       </c>
       <c r="AG303">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O307">
         <v>4.2</v>
       </c>
       <c r="P307">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q307">
         <v>1.96</v>
@@ -50420,7 +50420,7 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK307">
         <v>2.4</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G4">
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>3.17</v>
+        <v>4.6</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V4">
         <v>1.4</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA4">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC4">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
         <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="Z5">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AB5">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="AC5">
-        <v>2.92</v>
+        <v>3.92</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.16</v>
+        <v>1.83</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="Q6">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="R6">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
+        <v>1.03</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.29</v>
+      </c>
+      <c r="Z6">
+        <v>3.4</v>
+      </c>
+      <c r="AA6">
+        <v>1.95</v>
+      </c>
+      <c r="AB6">
+        <v>1.81</v>
+      </c>
+      <c r="AC6">
+        <v>3.2</v>
+      </c>
+      <c r="AD6">
+        <v>1.26</v>
+      </c>
+      <c r="AE6">
         <v>1.06</v>
       </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
-        <v>1.41</v>
-      </c>
-      <c r="Z6">
-        <v>2.77</v>
-      </c>
-      <c r="AA6">
-        <v>2.17</v>
-      </c>
-      <c r="AB6">
-        <v>1.59</v>
-      </c>
-      <c r="AC6">
-        <v>3.92</v>
-      </c>
-      <c r="AD6">
-        <v>1.18</v>
-      </c>
-      <c r="AE6">
-        <v>1.03</v>
-      </c>
       <c r="AF6">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>2.09</v>
+      </c>
+      <c r="R7">
+        <v>2.37</v>
+      </c>
+      <c r="S7">
+        <v>1.22</v>
+      </c>
+      <c r="T7">
+        <v>3.5</v>
+      </c>
+      <c r="U7">
+        <v>2.2</v>
+      </c>
+      <c r="V7">
         <v>1.6</v>
       </c>
-      <c r="O7">
-        <v>3.6</v>
-      </c>
-      <c r="P7">
-        <v>4.6</v>
-      </c>
-      <c r="Q7">
-        <v>2.15</v>
-      </c>
-      <c r="R7">
-        <v>2.2</v>
-      </c>
-      <c r="S7">
-        <v>1.36</v>
-      </c>
-      <c r="T7">
-        <v>2.9</v>
-      </c>
-      <c r="U7">
-        <v>2.76</v>
-      </c>
-      <c r="V7">
-        <v>1.35</v>
-      </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>3.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AB7">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AG7">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q8">
-        <v>2.09</v>
+        <v>3.17</v>
       </c>
       <c r="R8">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>4.95</v>
+        <v>3.14</v>
       </c>
       <c r="AA8">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="AB8">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>2.27</v>
+        <v>3.28</v>
       </c>
       <c r="AD8">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
         <v>3.6</v>
@@ -1797,10 +1797,10 @@
         <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1821,7 +1821,7 @@
         <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD9">
         <v>1.26</v>
@@ -1945,13 +1945,13 @@
         <v>3.7</v>
       </c>
       <c r="P10">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1978,13 +1978,13 @@
         <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AD10">
         <v>1.3</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P11">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
         <v>2.45</v>
@@ -2132,34 +2132,34 @@
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="AD11">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>3.4</v>
       </c>
       <c r="AA18">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB18">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC18">
         <v>3.14</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.44</v>
+        <v>1.78</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>1.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q19">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AA19">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC19">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
+        <v>2</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.22</v>
+      </c>
+      <c r="AK19">
         <v>1.87</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.95</v>
-      </c>
-      <c r="AK19">
-        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.78</v>
+        <v>3.44</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>3.75</v>
+        <v>1.99</v>
       </c>
       <c r="Q20">
-        <v>2.3</v>
+        <v>4.36</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
+        <v>1.86</v>
+      </c>
+      <c r="AB20">
         <v>1.8</v>
       </c>
-      <c r="AB20">
-        <v>1.89</v>
-      </c>
       <c r="AC20">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AK20">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="O24">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P24">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="Q24">
         <v>2.46</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
         <v>1.73</v>
@@ -4556,10 +4556,10 @@
         <v>1.91</v>
       </c>
       <c r="Q26">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S26">
         <v>1.4</v>
@@ -4598,7 +4598,7 @@
         <v>1.21</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
         <v>1.85</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.3</v>
@@ -5902,7 +5902,7 @@
         <v>1.32</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
@@ -6361,10 +6361,10 @@
         <v>2.77</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
         <v>1.05</v>
@@ -6382,7 +6382,7 @@
         <v>2.01</v>
       </c>
       <c r="AB37">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC37">
         <v>3.65</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>2.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK47">
         <v>1.1</v>
@@ -9132,25 +9132,25 @@
         <v>2.5</v>
       </c>
       <c r="U54">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W54">
         <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y54">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z54">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AA54">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB54">
         <v>1.49</v>
@@ -9162,7 +9162,7 @@
         <v>1.13</v>
       </c>
       <c r="AE54">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF54">
         <v>2</v>
@@ -9325,7 +9325,7 @@
         <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF55">
         <v>1.62</v>
@@ -9449,37 +9449,37 @@
         <v>2.6</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S56">
         <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U56">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V56">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W56">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y56">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z56">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="AA56">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AB56">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC56">
         <v>3.58</v>
@@ -9488,7 +9488,7 @@
         <v>1.21</v>
       </c>
       <c r="AE56">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF56">
         <v>1.91</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
         <v>1.73</v>
@@ -9630,13 +9630,13 @@
         <v>1.1</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA57">
         <v>1.87</v>
@@ -9645,10 +9645,10 @@
         <v>1.9</v>
       </c>
       <c r="AC57">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
         <v>1.11</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P60">
         <v>2.75</v>
@@ -10107,13 +10107,13 @@
         <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U60">
         <v>2.25</v>
       </c>
       <c r="V60">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W60">
         <v>1.15</v>
@@ -10143,7 +10143,7 @@
         <v>1.23</v>
       </c>
       <c r="AF60">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
         <v>2.55</v>
@@ -11073,7 +11073,7 @@
         <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q66">
         <v>3.02</v>
@@ -11106,7 +11106,7 @@
         <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB66">
         <v>1.74</v>
@@ -11260,7 +11260,7 @@
         <v>1.04</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.24</v>
@@ -11396,10 +11396,10 @@
         <v>1.25</v>
       </c>
       <c r="O68">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="P68">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q68">
         <v>1.77</v>
@@ -12543,55 +12543,55 @@
         <v>2.6</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>3.19</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12899,7 +12899,7 @@
         <v>3.48</v>
       </c>
       <c r="AA77">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
         <v>1.95</v>
@@ -13542,7 +13542,7 @@
         <v>1.08</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
         <v>1.23</v>
@@ -13563,7 +13563,7 @@
         <v>1.31</v>
       </c>
       <c r="AE81">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF81">
         <v>1.65</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="O84">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P84">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q84">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S84">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U84">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V84">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W84">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z84">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="AA84">
         <v>1.65</v>
       </c>
       <c r="AB84">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC84">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD84">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE84">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG84">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK84">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O92">
         <v>3.75</v>
@@ -17641,10 +17641,10 @@
         <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG106">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>2.94</v>
+        <v>3.48</v>
       </c>
       <c r="R112">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="S112">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="U112">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V112">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
         <v>1.08</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z112">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA112">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB112">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC112">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD112">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE112">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG112">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>3.48</v>
+        <v>2.94</v>
       </c>
       <c r="R113">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S113">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U113">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V113">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
         <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z113">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA113">
+        <v>1.93</v>
+      </c>
+      <c r="AB113">
         <v>1.72</v>
       </c>
-      <c r="AB113">
-        <v>1.9</v>
-      </c>
       <c r="AC113">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD113">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE113">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK113">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18912,7 +18912,7 @@
         <v>3.38</v>
       </c>
       <c r="U114">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V114">
         <v>1.53</v>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="O115">
-        <v>4.74</v>
+        <v>4.35</v>
       </c>
       <c r="P115">
         <v>5</v>
@@ -19127,7 +19127,7 @@
         <v>1.19</v>
       </c>
       <c r="AK115">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O118">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P118">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="Q118">
         <v>2.35</v>
@@ -19561,7 +19561,7 @@
         <v>1.15</v>
       </c>
       <c r="T118">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="U118">
         <v>1.81</v>
@@ -19570,7 +19570,7 @@
         <v>2.01</v>
       </c>
       <c r="W118">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X118">
         <v>1</v>
@@ -19585,7 +19585,7 @@
         <v>1.3</v>
       </c>
       <c r="AB118">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC118">
         <v>1.76</v>
@@ -19721,19 +19721,19 @@
         <v>2.46</v>
       </c>
       <c r="S119">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T119">
         <v>4.15</v>
       </c>
       <c r="U119">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V119">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W119">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X119">
         <v>1</v>
@@ -19748,7 +19748,7 @@
         <v>1.4</v>
       </c>
       <c r="AB119">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC119">
         <v>2.08</v>
@@ -20234,7 +20234,7 @@
         <v>2.88</v>
       </c>
       <c r="AA122">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB122">
         <v>1.7</v>
@@ -23464,7 +23464,7 @@
         <v>1.56</v>
       </c>
       <c r="Q142">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="R142">
         <v>2.2</v>
@@ -23485,7 +23485,7 @@
         <v>1.09</v>
       </c>
       <c r="X142">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y142">
         <v>1.22</v>
@@ -23657,10 +23657,10 @@
         <v>4.15</v>
       </c>
       <c r="AA143">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB143">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC143">
         <v>2.55</v>
@@ -23784,10 +23784,10 @@
         <v>2.1</v>
       </c>
       <c r="O144">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="Q144">
         <v>2.78</v>
@@ -23796,10 +23796,10 @@
         <v>2.11</v>
       </c>
       <c r="S144">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T144">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U144">
         <v>2.74</v>
@@ -23808,7 +23808,7 @@
         <v>1.41</v>
       </c>
       <c r="W144">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X144">
         <v>1.03</v>
@@ -23947,7 +23947,7 @@
         <v>1.77</v>
       </c>
       <c r="O145">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P145">
         <v>3.9</v>
@@ -23977,10 +23977,10 @@
         <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z145">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AA145">
         <v>1.4</v>
@@ -24466,10 +24466,10 @@
         <v>1</v>
       </c>
       <c r="Y148">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z148">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA148">
         <v>1.37</v>
@@ -24478,10 +24478,10 @@
         <v>3.07</v>
       </c>
       <c r="AC148">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD148">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AE148">
         <v>1.38</v>
@@ -26715,80 +26715,80 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O162">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P162">
+        <v>2.4</v>
+      </c>
+      <c r="Q162">
+        <v>3</v>
+      </c>
+      <c r="R162">
         <v>2.3</v>
       </c>
-      <c r="Q162">
-        <v>3.04</v>
-      </c>
-      <c r="R162">
-        <v>2.24</v>
-      </c>
       <c r="S162">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U162">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="V162">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W162">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X162">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y162">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z162">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA162">
         <v>1.57</v>
       </c>
       <c r="AB162">
+        <v>2.35</v>
+      </c>
+      <c r="AC162">
+        <v>2.74</v>
+      </c>
+      <c r="AD162">
+        <v>1.35</v>
+      </c>
+      <c r="AE162">
+        <v>1.1</v>
+      </c>
+      <c r="AF162">
+        <v>1.6</v>
+      </c>
+      <c r="AG162">
         <v>2.2</v>
       </c>
-      <c r="AC162">
-        <v>2.43</v>
-      </c>
-      <c r="AD162">
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ162">
+        <v>1.45</v>
+      </c>
+      <c r="AK162">
         <v>1.44</v>
-      </c>
-      <c r="AE162">
-        <v>1.14</v>
-      </c>
-      <c r="AF162">
-        <v>1.48</v>
-      </c>
-      <c r="AG162">
-        <v>2.41</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ162">
-        <v>1.2</v>
-      </c>
-      <c r="AK162">
-        <v>1.4</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>7.18</v>
+        <v>5.6</v>
       </c>
       <c r="O185">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P185">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q185">
         <v>6</v>
@@ -30494,7 +30494,7 @@
         <v>1.11</v>
       </c>
       <c r="X185">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y185">
         <v>1.16</v>
@@ -30630,7 +30630,7 @@
         <v>1.25</v>
       </c>
       <c r="O186">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="P186">
         <v>6.5</v>
@@ -30651,7 +30651,7 @@
         <v>1.85</v>
       </c>
       <c r="V186">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="W186">
         <v>1.23</v>
@@ -30666,7 +30666,7 @@
         <v>7.5</v>
       </c>
       <c r="AA186">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB186">
         <v>3.02</v>
@@ -32755,55 +32755,55 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T199">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V199">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W199">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X199">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z199">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC199">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD199">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG199">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK199">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O202">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="P202">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q202">
         <v>4.03</v>
@@ -33250,13 +33250,13 @@
         <v>2.54</v>
       </c>
       <c r="S202">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T202">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="U202">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V202">
         <v>1.75</v>
@@ -33274,19 +33274,19 @@
         <v>7</v>
       </c>
       <c r="AA202">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB202">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC202">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD202">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AE202">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AF202">
         <v>1.4</v>
@@ -33440,7 +33440,7 @@
         <v>1.57</v>
       </c>
       <c r="AB203">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AC203">
         <v>2.41</v>
@@ -33887,7 +33887,7 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="O206">
         <v>3.5</v>
@@ -33926,10 +33926,10 @@
         <v>4.25</v>
       </c>
       <c r="AA206">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB206">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC206">
         <v>2.66</v>
@@ -34089,10 +34089,10 @@
         <v>3.9</v>
       </c>
       <c r="AA207">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB207">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC207">
         <v>2.88</v>
@@ -34252,10 +34252,10 @@
         <v>5.75</v>
       </c>
       <c r="AA208">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB208">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC208">
         <v>2.07</v>
@@ -34865,31 +34865,31 @@
         </is>
       </c>
       <c r="N212">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="O212">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="P212">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q212">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="R212">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="S212">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T212">
         <v>4.2</v>
       </c>
       <c r="U212">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V212">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W212">
         <v>1.19</v>
@@ -34901,28 +34901,28 @@
         <v>1.08</v>
       </c>
       <c r="Z212">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AA212">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB212">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AC212">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AD212">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE212">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF212">
         <v>2.15</v>
       </c>
       <c r="AG212">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AK212">
         <v>1.01</v>
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O221">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P221">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q221">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="R221">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="S221">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T221">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="U221">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="V221">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="W221">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="X221">
         <v>1.01</v>
       </c>
       <c r="Y221">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z221">
-        <v>7.3</v>
+        <v>4.91</v>
       </c>
       <c r="AA221">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AB221">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="AC221">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AD221">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AE221">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AF221">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG221">
-        <v>3.14</v>
+        <v>2.44</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK221">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="O222">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="P222">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="Q222">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="R222">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="S222">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T222">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="U222">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="V222">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="W222">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="X222">
         <v>1.01</v>
       </c>
       <c r="Y222">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z222">
-        <v>4.91</v>
+        <v>6.7</v>
       </c>
       <c r="AA222">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB222">
-        <v>2.29</v>
+        <v>3.08</v>
       </c>
       <c r="AC222">
-        <v>2.23</v>
+        <v>1.82</v>
       </c>
       <c r="AD222">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AE222">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AF222">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG222">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>1.2</v>
       </c>
       <c r="AK222">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="O223">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P223">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q223">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="R223">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="S223">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T223">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U223">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V223">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="W223">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X223">
         <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z223">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="AA223">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB223">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AC223">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AD223">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AE223">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF223">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG223">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK223">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="O224">
-        <v>4.55</v>
+        <v>5.3</v>
       </c>
       <c r="P224">
-        <v>7.55</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q224">
         <v>1.67</v>
@@ -36860,10 +36860,10 @@
         <v>4.65</v>
       </c>
       <c r="AA224">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB224">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AC224">
         <v>2.25</v>
@@ -36894,7 +36894,7 @@
         <v>1.01</v>
       </c>
       <c r="AK224">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.45</v>
+        <v>2.7</v>
       </c>
       <c r="O228">
-        <v>4.2</v>
+        <v>3.26</v>
       </c>
       <c r="P228">
-        <v>5.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q228">
-        <v>2.04</v>
+        <v>3.68</v>
       </c>
       <c r="R228">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S228">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T228">
-        <v>3.84</v>
+        <v>2.72</v>
       </c>
       <c r="U228">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="V228">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="W228">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X228">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z228">
-        <v>4.75</v>
+        <v>3.21</v>
       </c>
       <c r="AA228">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="AB228">
-        <v>2.54</v>
+        <v>1.76</v>
       </c>
       <c r="AC228">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD228">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AE228">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AF228">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG228">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK228">
-        <v>2.46</v>
+        <v>1.41</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.7</v>
+        <v>1.45</v>
       </c>
       <c r="O230">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="P230">
-        <v>2.23</v>
+        <v>5.25</v>
       </c>
       <c r="Q230">
-        <v>3.68</v>
+        <v>2.04</v>
       </c>
       <c r="R230">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S230">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T230">
-        <v>2.72</v>
+        <v>3.84</v>
       </c>
       <c r="U230">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="V230">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="W230">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X230">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z230">
-        <v>3.21</v>
+        <v>4.75</v>
       </c>
       <c r="AA230">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AB230">
-        <v>1.76</v>
+        <v>2.54</v>
       </c>
       <c r="AC230">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD230">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AE230">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF230">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG230">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK230">
-        <v>1.41</v>
+        <v>2.46</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39121,10 +39121,10 @@
         <v>1.4</v>
       </c>
       <c r="T238">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U238">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="V238">
         <v>1.33</v>
@@ -39160,7 +39160,7 @@
         <v>1.91</v>
       </c>
       <c r="AG238">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39429,22 +39429,22 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O240">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P240">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q240">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="R240">
         <v>1.96</v>
       </c>
       <c r="S240">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T240">
         <v>2.62</v>
@@ -39502,7 +39502,7 @@
         <v>1.26</v>
       </c>
       <c r="AK240">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39592,31 +39592,31 @@
         </is>
       </c>
       <c r="N241">
+        <v>3.25</v>
+      </c>
+      <c r="O241">
         <v>3.4</v>
       </c>
-      <c r="O241">
-        <v>3.3</v>
-      </c>
       <c r="P241">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q241">
-        <v>4.28</v>
+        <v>3.91</v>
       </c>
       <c r="R241">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S241">
         <v>1.34</v>
       </c>
       <c r="T241">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="U241">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V241">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W241">
         <v>1.05</v>
@@ -39625,19 +39625,19 @@
         <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z241">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA241">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AB241">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AC241">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD241">
         <v>1.37</v>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="AK241">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39755,7 +39755,7 @@
         </is>
       </c>
       <c r="N242">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="O242">
         <v>5.7</v>
@@ -39767,7 +39767,7 @@
         <v>5.5</v>
       </c>
       <c r="R242">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="S242">
         <v>1.11</v>
@@ -39788,25 +39788,25 @@
         <v>1</v>
       </c>
       <c r="Y242">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z242">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="AA242">
         <v>1.24</v>
       </c>
       <c r="AB242">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="AC242">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AD242">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AE242">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AF242">
         <v>1.39</v>
@@ -40576,7 +40576,7 @@
         <v>3.18</v>
       </c>
       <c r="P247">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O249">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="P249">
-        <v>2.52</v>
+        <v>1.94</v>
       </c>
       <c r="Q249">
         <v>3.82</v>
@@ -41104,10 +41104,10 @@
         <v>1.99</v>
       </c>
       <c r="AC250">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="AD250">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE250">
         <v>1.09</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="O254">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P254">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q254">
         <v>3.04</v>
@@ -43510,7 +43510,7 @@
         <v>4.2</v>
       </c>
       <c r="P265">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="Q265">
         <v>1.88</v>
@@ -43577,7 +43577,7 @@
         <v>1.16</v>
       </c>
       <c r="AK265">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43996,10 +43996,10 @@
         <v>1.32</v>
       </c>
       <c r="O268">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P268">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q268">
         <v>1.67</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,22 +44156,22 @@
         </is>
       </c>
       <c r="N269">
-        <v>1.61</v>
+        <v>2.37</v>
       </c>
       <c r="O269">
+        <v>2.6</v>
+      </c>
+      <c r="P269">
         <v>3.1</v>
       </c>
-      <c r="P269">
-        <v>5.5</v>
-      </c>
       <c r="Q269">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="R269">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S269">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T269">
         <v>2.2</v>
@@ -44183,25 +44183,25 @@
         <v>1.2</v>
       </c>
       <c r="W269">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X269">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y269">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z269">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AA269">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB269">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC269">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AD269">
         <v>1.04</v>
@@ -44210,10 +44210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AG269">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK269">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,22 +44319,22 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.37</v>
+        <v>1.61</v>
       </c>
       <c r="O270">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P270">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q270">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="R270">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S270">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T270">
         <v>2.2</v>
@@ -44346,25 +44346,25 @@
         <v>1.2</v>
       </c>
       <c r="W270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X270">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y270">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z270">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AA270">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB270">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC270">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AD270">
         <v>1.04</v>
@@ -44373,10 +44373,10 @@
         <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AG270">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK270">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -45949,31 +45949,31 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O280">
         <v>3.9</v>
       </c>
       <c r="P280">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q280">
         <v>2.6</v>
       </c>
       <c r="R280">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S280">
         <v>1.21</v>
       </c>
       <c r="T280">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U280">
         <v>2.14</v>
       </c>
       <c r="V280">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W280">
         <v>1.15</v>
@@ -45982,10 +45982,10 @@
         <v>1</v>
       </c>
       <c r="Y280">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z280">
-        <v>5.52</v>
+        <v>6.28</v>
       </c>
       <c r="AA280">
         <v>1.47</v>
@@ -46275,7 +46275,7 @@
         </is>
       </c>
       <c r="N282">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="O282">
         <v>3.93</v>
@@ -46314,10 +46314,10 @@
         <v>3.44</v>
       </c>
       <c r="AA282">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB282">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC282">
         <v>3.12</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G4">
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="Q4">
-        <v>4.6</v>
+        <v>3.17</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U4">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
         <v>1.4</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z4">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB4">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
+        <v>1.79</v>
+      </c>
+      <c r="Q6">
         <v>4.6</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>2.15</v>
-      </c>
-      <c r="R6">
-        <v>2.2</v>
       </c>
       <c r="S6">
         <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>2.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>2.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q8">
-        <v>3.17</v>
+        <v>2.15</v>
       </c>
       <c r="R8">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
+        <v>1.36</v>
+      </c>
+      <c r="T8">
+        <v>2.9</v>
+      </c>
+      <c r="U8">
+        <v>2.76</v>
+      </c>
+      <c r="V8">
         <v>1.35</v>
       </c>
-      <c r="T8">
-        <v>2.77</v>
-      </c>
-      <c r="U8">
-        <v>2.69</v>
-      </c>
-      <c r="V8">
-        <v>1.4</v>
-      </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA8">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC8">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="P10">
-        <v>1.61</v>
+        <v>3.17</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>2.32</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
         <v>1.04</v>
@@ -1975,28 +1975,28 @@
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>2.01</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="O11">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
-        <v>3.17</v>
+        <v>1.61</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2138,28 +2138,28 @@
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA11">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>2.01</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4387,61 +4387,61 @@
         <v>3.55</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P25">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q25">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="R25">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S25">
+        <v>1.37</v>
+      </c>
+      <c r="T25">
+        <v>2.82</v>
+      </c>
+      <c r="U25">
+        <v>2.9</v>
+      </c>
+      <c r="V25">
         <v>1.38</v>
       </c>
-      <c r="T25">
-        <v>2.75</v>
-      </c>
-      <c r="U25">
-        <v>2.88</v>
-      </c>
-      <c r="V25">
-        <v>1.34</v>
-      </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>3.43</v>
       </c>
       <c r="AA25">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AB25">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AD25">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG25">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         <v>2.68</v>
       </c>
       <c r="U30">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V30">
         <v>1.32</v>
@@ -5250,7 +5250,7 @@
         <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
         <v>1.83</v>
@@ -5531,7 +5531,7 @@
         <v>3.68</v>
       </c>
       <c r="P32">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q32">
         <v>4.68</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="P33">
         <v>2.25</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
         <v>3.15</v>
       </c>
       <c r="Q35">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="R35">
         <v>1.96</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK35">
         <v>1.54</v>
@@ -7324,7 +7324,7 @@
         <v>3.3</v>
       </c>
       <c r="P43">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q43">
         <v>4.2</v>
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8510,7 +8510,7 @@
         <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
         <v>1.7</v>
@@ -8631,7 +8631,7 @@
         <v>3.1</v>
       </c>
       <c r="Q51">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
         <v>2.2</v>
@@ -8652,7 +8652,7 @@
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.25</v>
@@ -8673,7 +8673,7 @@
         <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
         <v>1.75</v>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8815,7 +8815,7 @@
         <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y52">
         <v>1.43</v>
@@ -8836,7 +8836,7 @@
         <v>1.16</v>
       </c>
       <c r="AE52">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
         <v>1.95</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -12262,7 +12262,7 @@
         <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG73">
         <v>2.01</v>
@@ -12428,7 +12428,7 @@
         <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="O78">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P78">
         <v>1.68</v>
@@ -13065,7 +13065,7 @@
         <v>1.47</v>
       </c>
       <c r="AB78">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC78">
         <v>2.29</v>
@@ -13853,10 +13853,10 @@
         <v>2.88</v>
       </c>
       <c r="S83">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T83">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="U83">
         <v>1.83</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O85">
         <v>3.75</v>
@@ -14206,7 +14206,7 @@
         <v>1.33</v>
       </c>
       <c r="AB85">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC85">
         <v>1.86</v>
@@ -14333,7 +14333,7 @@
         <v>4.33</v>
       </c>
       <c r="P86">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q86">
         <v>4.44</v>
@@ -14372,13 +14372,13 @@
         <v>2.87</v>
       </c>
       <c r="AC86">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AD86">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE86">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF86">
         <v>1.44</v>
@@ -14496,7 +14496,7 @@
         <v>3.83</v>
       </c>
       <c r="P87">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -14529,10 +14529,10 @@
         <v>5.7</v>
       </c>
       <c r="AA87">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB87">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AC87">
         <v>2.21</v>
@@ -14656,10 +14656,10 @@
         <v>2.25</v>
       </c>
       <c r="O88">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P88">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q88">
         <v>2.76</v>
@@ -14692,10 +14692,10 @@
         <v>4.35</v>
       </c>
       <c r="AA88">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB88">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AC88">
         <v>2.33</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O89">
         <v>3.7</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q89">
         <v>2.63</v>
@@ -14855,10 +14855,10 @@
         <v>4.55</v>
       </c>
       <c r="AA89">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB89">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AC89">
         <v>2.31</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O90">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="Q90">
         <v>2.83</v>
@@ -15009,7 +15009,7 @@
         <v>1.14</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.13</v>
@@ -15670,10 +15670,10 @@
         <v>3.31</v>
       </c>
       <c r="AA94">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB94">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC94">
         <v>3.63</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O98">
         <v>3.3</v>
       </c>
       <c r="P98">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="Q98">
         <v>2.55</v>
@@ -16322,10 +16322,10 @@
         <v>2.39</v>
       </c>
       <c r="AA98">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AB98">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC98">
         <v>4.82</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="O99">
         <v>3.7</v>
@@ -16455,10 +16455,10 @@
         <v>5.75</v>
       </c>
       <c r="Q99">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R99">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S99">
         <v>1.43</v>
@@ -16491,13 +16491,13 @@
         <v>1.64</v>
       </c>
       <c r="AC99">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AD99">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE99">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF99">
         <v>2.21</v>
@@ -16609,16 +16609,16 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O100">
-        <v>3.53</v>
+        <v>3.32</v>
       </c>
       <c r="P100">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q100">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="R100">
         <v>2.32</v>
@@ -16642,16 +16642,16 @@
         <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z100">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA100">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC100">
         <v>2.74</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="O101">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P101">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O111">
         <v>3.1</v>
@@ -18574,7 +18574,7 @@
         <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="R112">
         <v>2.13</v>
@@ -18770,7 +18770,7 @@
         <v>1.93</v>
       </c>
       <c r="AB113">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC113">
         <v>3.34</v>
@@ -19380,16 +19380,16 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="O117">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P117">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="Q117">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R117">
         <v>2.38</v>
@@ -19914,10 +19914,10 @@
         <v>2.5</v>
       </c>
       <c r="AC120">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AD120">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE120">
         <v>1.22</v>
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="O121">
         <v>7</v>
@@ -20062,7 +20062,7 @@
         <v>1.3</v>
       </c>
       <c r="X121">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y121">
         <v>1.02</v>
@@ -20074,7 +20074,7 @@
         <v>1.16</v>
       </c>
       <c r="AB121">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AC121">
         <v>1.51</v>
@@ -20358,10 +20358,10 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="O123">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P123">
         <v>3.2</v>
@@ -20400,7 +20400,7 @@
         <v>1.66</v>
       </c>
       <c r="AB123">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC123">
         <v>2.6</v>
@@ -20530,7 +20530,7 @@
         <v>5.6</v>
       </c>
       <c r="Q124">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R124">
         <v>2.5</v>
@@ -20690,7 +20690,7 @@
         <v>3.7</v>
       </c>
       <c r="P125">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -20717,7 +20717,7 @@
         <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z125">
         <v>4.83</v>
@@ -20726,13 +20726,13 @@
         <v>1.5</v>
       </c>
       <c r="AB125">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC125">
         <v>2.44</v>
       </c>
       <c r="AD125">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE125">
         <v>1.21</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O126">
         <v>3.6</v>
       </c>
       <c r="P126">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="Q126">
         <v>2.5</v>
@@ -20880,7 +20880,7 @@
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z126">
         <v>4.46</v>
@@ -20889,7 +20889,7 @@
         <v>1.57</v>
       </c>
       <c r="AB126">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC126">
         <v>2.51</v>
@@ -21049,7 +21049,7 @@
         <v>4.25</v>
       </c>
       <c r="AA127">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB127">
         <v>2.2</v>
@@ -21182,10 +21182,10 @@
         <v>2.37</v>
       </c>
       <c r="Q128">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R128">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S128">
         <v>1.25</v>
@@ -21194,10 +21194,10 @@
         <v>3.6</v>
       </c>
       <c r="U128">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V128">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W128">
         <v>1.11</v>
@@ -21206,16 +21206,16 @@
         <v>1</v>
       </c>
       <c r="Y128">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z128">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA128">
         <v>1.69</v>
       </c>
       <c r="AB128">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AC128">
         <v>2.52</v>
@@ -21227,10 +21227,10 @@
         <v>1.18</v>
       </c>
       <c r="AF128">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG128">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21529,13 +21529,13 @@
         <v>1.1</v>
       </c>
       <c r="X130">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z130">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="AA130">
         <v>1.77</v>
@@ -21988,22 +21988,22 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O133">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q133">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R133">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S133">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T133">
         <v>3.4</v>
@@ -22018,34 +22018,34 @@
         <v>1.11</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
         <v>1.18</v>
       </c>
       <c r="Z133">
-        <v>4.66</v>
+        <v>4.4</v>
       </c>
       <c r="AA133">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB133">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC133">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD133">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE133">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF133">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG133">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK133">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22163,7 +22163,7 @@
         <v>1.46</v>
       </c>
       <c r="R134">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="S134">
         <v>1.22</v>
@@ -22172,7 +22172,7 @@
         <v>3.56</v>
       </c>
       <c r="U134">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V134">
         <v>1.6</v>
@@ -22196,10 +22196,10 @@
         <v>2.3</v>
       </c>
       <c r="AC134">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AD134">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE134">
         <v>1.22</v>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK134">
         <v>5.95</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="O136">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="P136">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="Q136">
         <v>3.5</v>
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O146">
         <v>3.44</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>9.65</v>
+        <v>7.1</v>
       </c>
       <c r="O161">
         <v>6.32</v>
       </c>
       <c r="P161">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q161">
         <v>6.5</v>
@@ -26567,13 +26567,13 @@
         <v>2.88</v>
       </c>
       <c r="S161">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T161">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U161">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V161">
         <v>1.75</v>
@@ -26591,10 +26591,10 @@
         <v>7.2</v>
       </c>
       <c r="AA161">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB161">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AC161">
         <v>1.94</v>
@@ -27702,55 +27702,55 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="O172">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P172">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q172">
         <v>4.45</v>
@@ -28843,10 +28843,10 @@
         <v>3.02</v>
       </c>
       <c r="Q175">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="R175">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S175">
         <v>1.32</v>
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O177">
         <v>3.3</v>
@@ -30790,10 +30790,10 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P187">
         <v>2.62</v>
@@ -30832,7 +30832,7 @@
         <v>1.75</v>
       </c>
       <c r="AB187">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC187">
         <v>2.62</v>
@@ -30959,7 +30959,7 @@
         <v>3.45</v>
       </c>
       <c r="P188">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q188">
         <v>2.3</v>
@@ -31122,19 +31122,19 @@
         <v>3.4</v>
       </c>
       <c r="P189">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q189">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="R189">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S189">
         <v>1.33</v>
       </c>
       <c r="T189">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="U189">
         <v>2.56</v>
@@ -31143,13 +31143,13 @@
         <v>1.44</v>
       </c>
       <c r="W189">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X189">
         <v>1</v>
       </c>
       <c r="Y189">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z189">
         <v>3.56</v>
@@ -31158,16 +31158,16 @@
         <v>1.88</v>
       </c>
       <c r="AB189">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC189">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="AD189">
         <v>1.4</v>
       </c>
       <c r="AE189">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF189">
         <v>1.64</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="O190">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P190">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="Q190">
         <v>3.51</v>
@@ -31318,7 +31318,7 @@
         <v>3.08</v>
       </c>
       <c r="AA190">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB190">
         <v>1.77</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O191">
         <v>4</v>
       </c>
       <c r="P191">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q191">
         <v>2.01</v>
@@ -31466,7 +31466,7 @@
         <v>1.9</v>
       </c>
       <c r="V191">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W191">
         <v>1.2</v>
@@ -31647,7 +31647,7 @@
         <v>1.47</v>
       </c>
       <c r="AB192">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AC192">
         <v>2.05</v>
@@ -31792,10 +31792,10 @@
         <v>2.5</v>
       </c>
       <c r="V193">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W193">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X193">
         <v>1</v>
@@ -31810,7 +31810,7 @@
         <v>1.86</v>
       </c>
       <c r="AB193">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC193">
         <v>3.04</v>
@@ -31973,7 +31973,7 @@
         <v>1.77</v>
       </c>
       <c r="AB194">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC194">
         <v>2.92</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>5.05</v>
+        <v>5.45</v>
       </c>
       <c r="O195">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="P195">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q195">
         <v>4.53</v>
@@ -32115,10 +32115,10 @@
         <v>3.56</v>
       </c>
       <c r="U195">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="V195">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W195">
         <v>1.13</v>
@@ -32130,25 +32130,25 @@
         <v>1.13</v>
       </c>
       <c r="Z195">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA195">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB195">
         <v>2.35</v>
       </c>
       <c r="AC195">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AD195">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE195">
         <v>1.18</v>
       </c>
       <c r="AF195">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG195">
         <v>2.15</v>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK195">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,16 +32257,16 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="O196">
         <v>5.4</v>
       </c>
       <c r="P196">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q196">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R196">
         <v>2.42</v>
@@ -32278,7 +32278,7 @@
         <v>3.32</v>
       </c>
       <c r="U196">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="V196">
         <v>1.51</v>
@@ -32293,13 +32293,13 @@
         <v>1.21</v>
       </c>
       <c r="Z196">
-        <v>4.31</v>
+        <v>4.34</v>
       </c>
       <c r="AA196">
         <v>1.65</v>
       </c>
       <c r="AB196">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AC196">
         <v>2.59</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK196">
         <v>3.64</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O198">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="P198">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q198">
         <v>2.45</v>
@@ -32622,10 +32622,10 @@
         <v>3.54</v>
       </c>
       <c r="AA198">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB198">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC198">
         <v>3.2</v>
@@ -33600,10 +33600,10 @@
         <v>4.44</v>
       </c>
       <c r="AA204">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB204">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC204">
         <v>2.48</v>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34539,16 +34539,16 @@
         </is>
       </c>
       <c r="N210">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="O210">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="P210">
         <v>1.34</v>
       </c>
       <c r="Q210">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="R210">
         <v>2.5</v>
@@ -34560,7 +34560,7 @@
         <v>3.12</v>
       </c>
       <c r="U210">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="V210">
         <v>1.5</v>
@@ -34572,10 +34572,10 @@
         <v>1.02</v>
       </c>
       <c r="Y210">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z210">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA210">
         <v>1.65</v>
@@ -34584,19 +34584,19 @@
         <v>2.2</v>
       </c>
       <c r="AC210">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD210">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE210">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF210">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG210">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK210">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35037,55 +35037,55 @@
         <v>0</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35200,7 +35200,7 @@
         <v>3.59</v>
       </c>
       <c r="Q214">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R214">
         <v>2.24</v>
@@ -35218,10 +35218,10 @@
         <v>1.45</v>
       </c>
       <c r="W214">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X214">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y214">
         <v>1.16</v>
@@ -35261,7 +35261,7 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK214">
         <v>1.81</v>
@@ -35719,10 +35719,10 @@
         <v>3.8</v>
       </c>
       <c r="AA217">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB217">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC217">
         <v>3</v>
@@ -36190,13 +36190,13 @@
         <v>5</v>
       </c>
       <c r="U220">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V220">
         <v>2.05</v>
       </c>
       <c r="W220">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X220">
         <v>1</v>
@@ -36217,7 +36217,7 @@
         <v>1.57</v>
       </c>
       <c r="AD220">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AE220">
         <v>1.54</v>
@@ -36347,7 +36347,7 @@
         <v>2.4</v>
       </c>
       <c r="S221">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T221">
         <v>3.55</v>
@@ -36371,7 +36371,7 @@
         <v>4.91</v>
       </c>
       <c r="AA221">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB221">
         <v>2.29</v>
@@ -36537,7 +36537,7 @@
         <v>1.33</v>
       </c>
       <c r="AB222">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AC222">
         <v>1.82</v>
@@ -36697,7 +36697,7 @@
         <v>7.3</v>
       </c>
       <c r="AA223">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB223">
         <v>3.5</v>
@@ -36990,7 +36990,7 @@
         <v>3.45</v>
       </c>
       <c r="P225">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="Q225">
         <v>2.54</v>
@@ -36999,10 +36999,10 @@
         <v>2.2</v>
       </c>
       <c r="S225">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T225">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="U225">
         <v>2.75</v>
@@ -37023,7 +37023,7 @@
         <v>3.58</v>
       </c>
       <c r="AA225">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB225">
         <v>1.9</v>
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O226">
         <v>4.25</v>
       </c>
       <c r="P226">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="Q226">
         <v>2.17</v>
@@ -37180,7 +37180,7 @@
         <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z226">
         <v>4.5</v>
@@ -37198,7 +37198,7 @@
         <v>1.54</v>
       </c>
       <c r="AE226">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF226">
         <v>1.65</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="O227">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P227">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q227">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="R227">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S227">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="T227">
-        <v>3.28</v>
+        <v>2.72</v>
       </c>
       <c r="U227">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="V227">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W227">
+        <v>1.06</v>
+      </c>
+      <c r="X227">
+        <v>1.02</v>
+      </c>
+      <c r="Y227">
+        <v>1.3</v>
+      </c>
+      <c r="Z227">
+        <v>3.21</v>
+      </c>
+      <c r="AA227">
+        <v>2.08</v>
+      </c>
+      <c r="AB227">
+        <v>1.76</v>
+      </c>
+      <c r="AC227">
+        <v>3.5</v>
+      </c>
+      <c r="AD227">
+        <v>1.29</v>
+      </c>
+      <c r="AE227">
         <v>1.08</v>
       </c>
-      <c r="X227">
-        <v>1.01</v>
-      </c>
-      <c r="Y227">
-        <v>1.22</v>
-      </c>
-      <c r="Z227">
-        <v>4.14</v>
-      </c>
-      <c r="AA227">
-        <v>1.65</v>
-      </c>
-      <c r="AB227">
-        <v>2.07</v>
-      </c>
-      <c r="AC227">
-        <v>2.53</v>
-      </c>
-      <c r="AD227">
-        <v>1.49</v>
-      </c>
-      <c r="AE227">
-        <v>1.12</v>
-      </c>
       <c r="AF227">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG227">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK227">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O228">
-        <v>3.26</v>
+        <v>4.24</v>
       </c>
       <c r="P228">
-        <v>2.23</v>
+        <v>3.81</v>
       </c>
       <c r="Q228">
-        <v>3.68</v>
+        <v>2.2</v>
       </c>
       <c r="R228">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="S228">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="T228">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="U228">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="V228">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="W228">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X228">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y228">
+        <v>1.1</v>
+      </c>
+      <c r="Z228">
+        <v>6.5</v>
+      </c>
+      <c r="AA228">
+        <v>1.43</v>
+      </c>
+      <c r="AB228">
+        <v>2.8</v>
+      </c>
+      <c r="AC228">
+        <v>2.12</v>
+      </c>
+      <c r="AD228">
+        <v>1.75</v>
+      </c>
+      <c r="AE228">
         <v>1.3</v>
       </c>
-      <c r="Z228">
-        <v>3.21</v>
-      </c>
-      <c r="AA228">
-        <v>2.08</v>
-      </c>
-      <c r="AB228">
-        <v>1.76</v>
-      </c>
-      <c r="AC228">
-        <v>3.34</v>
-      </c>
-      <c r="AD228">
-        <v>1.27</v>
-      </c>
-      <c r="AE228">
-        <v>1.06</v>
-      </c>
       <c r="AF228">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AG228">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK228">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="O229">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="P229">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Q229">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="R229">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S229">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T229">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U229">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="V229">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W229">
+        <v>1.15</v>
+      </c>
+      <c r="X229">
+        <v>1.01</v>
+      </c>
+      <c r="Y229">
+        <v>1.14</v>
+      </c>
+      <c r="Z229">
+        <v>5.5</v>
+      </c>
+      <c r="AA229">
+        <v>1.49</v>
+      </c>
+      <c r="AB229">
+        <v>2.48</v>
+      </c>
+      <c r="AC229">
+        <v>2.3</v>
+      </c>
+      <c r="AD229">
+        <v>1.6</v>
+      </c>
+      <c r="AE229">
         <v>1.22</v>
       </c>
-      <c r="X229">
-        <v>1</v>
-      </c>
-      <c r="Y229">
-        <v>1.11</v>
-      </c>
-      <c r="Z229">
-        <v>5.87</v>
-      </c>
-      <c r="AA229">
-        <v>1.43</v>
-      </c>
-      <c r="AB229">
-        <v>2.8</v>
-      </c>
-      <c r="AC229">
-        <v>2.12</v>
-      </c>
-      <c r="AD229">
-        <v>1.78</v>
-      </c>
-      <c r="AE229">
-        <v>1.28</v>
-      </c>
       <c r="AF229">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AG229">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK229">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="O230">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P230">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q230">
-        <v>2.04</v>
+        <v>2.61</v>
       </c>
       <c r="R230">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S230">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T230">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="U230">
-        <v>2.17</v>
+        <v>2.51</v>
       </c>
       <c r="V230">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W230">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X230">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z230">
-        <v>4.75</v>
+        <v>4.29</v>
       </c>
       <c r="AA230">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AB230">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="AC230">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AD230">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE230">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF230">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG230">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AK230">
-        <v>2.46</v>
+        <v>1.7</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37965,7 +37965,7 @@
         <v>3</v>
       </c>
       <c r="O231">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P231">
         <v>2.37</v>
@@ -37983,10 +37983,10 @@
         <v>2.59</v>
       </c>
       <c r="U231">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="V231">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W231">
         <v>1.04</v>
@@ -37995,22 +37995,22 @@
         <v>1.04</v>
       </c>
       <c r="Y231">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z231">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AA231">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AB231">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC231">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AD231">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE231">
         <v>1.04</v>
@@ -38035,7 +38035,7 @@
         <v>1.33</v>
       </c>
       <c r="AK231">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38155,7 +38155,7 @@
         <v>1.12</v>
       </c>
       <c r="X232">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y232">
         <v>1.15</v>
@@ -38164,10 +38164,10 @@
         <v>4.2</v>
       </c>
       <c r="AA232">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB232">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC232">
         <v>2.49</v>
@@ -38460,55 +38460,55 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38614,7 +38614,7 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O235">
         <v>3.3</v>
@@ -38656,7 +38656,7 @@
         <v>1.7</v>
       </c>
       <c r="AB235">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC235">
         <v>2.56</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O236">
         <v>3.25</v>
@@ -39921,7 +39921,7 @@
         <v>1.53</v>
       </c>
       <c r="O243">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P243">
         <v>4.8</v>
@@ -40090,55 +40090,55 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,10 +40244,10 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O245">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P245">
         <v>6</v>
@@ -40256,7 +40256,7 @@
         <v>1.8</v>
       </c>
       <c r="R245">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S245">
         <v>1.17</v>
@@ -40286,7 +40286,7 @@
         <v>1.4</v>
       </c>
       <c r="AB245">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AC245">
         <v>1.94</v>
@@ -40416,7 +40416,7 @@
         <v>5.5</v>
       </c>
       <c r="Q246">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R246">
         <v>2.45</v>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O251">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P251">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q251">
         <v>1.94</v>
@@ -41258,19 +41258,19 @@
         <v>1.18</v>
       </c>
       <c r="Z251">
-        <v>4.18</v>
+        <v>4.4</v>
       </c>
       <c r="AA251">
         <v>1.7</v>
       </c>
       <c r="AB251">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AC251">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AD251">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE251">
         <v>1.17</v>
@@ -41388,10 +41388,10 @@
         <v>1.53</v>
       </c>
       <c r="O252">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="P252">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q252">
         <v>2.2</v>
@@ -41427,7 +41427,7 @@
         <v>1.92</v>
       </c>
       <c r="AB252">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC252">
         <v>3.2</v>
@@ -41551,7 +41551,7 @@
         <v>1.69</v>
       </c>
       <c r="O253">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P253">
         <v>4.33</v>
@@ -41621,7 +41621,7 @@
         <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41916,7 +41916,7 @@
         <v>1.65</v>
       </c>
       <c r="AB255">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC255">
         <v>2.7</v>
@@ -41928,10 +41928,10 @@
         <v>1.11</v>
       </c>
       <c r="AF255">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG255">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -42046,34 +42046,34 @@
         <v>2.97</v>
       </c>
       <c r="Q256">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="R256">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S256">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T256">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="U256">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V256">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W256">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X256">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y256">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z256">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA256">
         <v>2.07</v>
@@ -42082,19 +42082,19 @@
         <v>1.72</v>
       </c>
       <c r="AC256">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD256">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE256">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF256">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG256">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK256">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42206,7 +42206,7 @@
         <v>3.3</v>
       </c>
       <c r="P257">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q257">
         <v>4.28</v>
@@ -42233,13 +42233,13 @@
         <v>1</v>
       </c>
       <c r="Y257">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z257">
         <v>3.77</v>
       </c>
       <c r="AA257">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB257">
         <v>1.97</v>
@@ -42251,7 +42251,7 @@
         <v>1.33</v>
       </c>
       <c r="AE257">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF257">
         <v>1.7</v>
@@ -42565,7 +42565,7 @@
         <v>3.5</v>
       </c>
       <c r="AA259">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB259">
         <v>1.92</v>
@@ -42861,7 +42861,7 @@
         <v>3.6</v>
       </c>
       <c r="Q261">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R261">
         <v>2</v>
@@ -42870,10 +42870,10 @@
         <v>1.44</v>
       </c>
       <c r="T261">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="U261">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V261">
         <v>1.3</v>
@@ -42882,31 +42882,31 @@
         <v>1.05</v>
       </c>
       <c r="X261">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y261">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="Z261">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="AA261">
         <v>2.15</v>
       </c>
       <c r="AB261">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AC261">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD261">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE261">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF261">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG261">
         <v>1.65</v>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK261">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="O263">
         <v>4.12</v>
       </c>
       <c r="P263">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q263">
         <v>5.8</v>
@@ -43251,7 +43251,7 @@
         <v>1.2</v>
       </c>
       <c r="AK263">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43670,10 +43670,10 @@
         <v>4.8</v>
       </c>
       <c r="O266">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P266">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q266">
         <v>5.5</v>
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="O267">
         <v>3.3</v>
       </c>
       <c r="P267">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q267">
         <v>3.1</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,22 +44156,22 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.37</v>
+        <v>1.61</v>
       </c>
       <c r="O269">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P269">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q269">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="R269">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S269">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T269">
         <v>2.2</v>
@@ -44183,25 +44183,25 @@
         <v>1.2</v>
       </c>
       <c r="W269">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X269">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y269">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z269">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AA269">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB269">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC269">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AD269">
         <v>1.04</v>
@@ -44210,10 +44210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AG269">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK269">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,22 +44319,22 @@
         </is>
       </c>
       <c r="N270">
-        <v>1.61</v>
+        <v>2.45</v>
       </c>
       <c r="O270">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P270">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q270">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="R270">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S270">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T270">
         <v>2.2</v>
@@ -44346,25 +44346,25 @@
         <v>1.2</v>
       </c>
       <c r="W270">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X270">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y270">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z270">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AA270">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB270">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC270">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AD270">
         <v>1.04</v>
@@ -44373,10 +44373,10 @@
         <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AG270">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK270">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44524,7 +44524,7 @@
         <v>1.36</v>
       </c>
       <c r="AB271">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC271">
         <v>1.99</v>
@@ -44536,10 +44536,10 @@
         <v>1.27</v>
       </c>
       <c r="AF271">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AG271">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44654,46 +44654,46 @@
         <v>4.8</v>
       </c>
       <c r="Q272">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="R272">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S272">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T272">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="U272">
         <v>3.2</v>
       </c>
       <c r="V272">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W272">
         <v>1.07</v>
       </c>
       <c r="X272">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y272">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z272">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA272">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB272">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC272">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AD272">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE272">
         <v>1.07</v>
@@ -44702,7 +44702,7 @@
         <v>1.95</v>
       </c>
       <c r="AG272">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK272">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -45013,7 +45013,7 @@
         <v>3.1</v>
       </c>
       <c r="AB274">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC274">
         <v>6</v>
@@ -45173,7 +45173,7 @@
         <v>2.95</v>
       </c>
       <c r="AA275">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB275">
         <v>1.62</v>
@@ -45502,7 +45502,7 @@
         <v>3.4</v>
       </c>
       <c r="AB277">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC277">
         <v>6.65</v>
@@ -45665,7 +45665,7 @@
         <v>2.18</v>
       </c>
       <c r="AB278">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC278">
         <v>3.98</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O284">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P284">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -47253,10 +47253,10 @@
         </is>
       </c>
       <c r="N288">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="O288">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="P288">
         <v>1.34</v>
@@ -47911,7 +47911,7 @@
         <v>5</v>
       </c>
       <c r="P292">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q292">
         <v>1.92</v>
@@ -48729,55 +48729,55 @@
         <v>4.58</v>
       </c>
       <c r="Q297">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="R297">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="S297">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T297">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U297">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V297">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W297">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X297">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y297">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z297">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA297">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB297">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC297">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AD297">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE297">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF297">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG297">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK297">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48922,16 +48922,16 @@
         <v>4.25</v>
       </c>
       <c r="AA298">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB298">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC298">
         <v>2.52</v>
       </c>
       <c r="AD298">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE298">
         <v>1.12</v>
@@ -49049,10 +49049,10 @@
         <v>1.24</v>
       </c>
       <c r="O299">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="P299">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q299">
         <v>1.52</v>
@@ -49731,25 +49731,25 @@
         <v>1.01</v>
       </c>
       <c r="Y303">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z303">
         <v>4.05</v>
       </c>
       <c r="AA303">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB303">
         <v>2.25</v>
       </c>
       <c r="AC303">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AD303">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE303">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF303">
         <v>1.5</v>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK303">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="O307">
         <v>4.2</v>
       </c>
       <c r="P307">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q307">
         <v>1.96</v>
@@ -50368,7 +50368,7 @@
         <v>1.15</v>
       </c>
       <c r="T307">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U307">
         <v>1.97</v>

--- a/jogos_2026-10-25.xlsx
+++ b/jogos_2026-10-25.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>2.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>3.17</v>
+        <v>2.15</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
+        <v>1.36</v>
+      </c>
+      <c r="T4">
+        <v>2.9</v>
+      </c>
+      <c r="U4">
+        <v>2.76</v>
+      </c>
+      <c r="V4">
         <v>1.35</v>
       </c>
-      <c r="T4">
-        <v>2.77</v>
-      </c>
-      <c r="U4">
-        <v>2.69</v>
-      </c>
-      <c r="V4">
-        <v>1.4</v>
-      </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA4">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>4.6</v>
+        <v>2.09</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z6">
-        <v>3.42</v>
+        <v>4.95</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AB6">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>2.27</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK6">
-        <v>1.16</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>2.09</v>
+        <v>4.6</v>
       </c>
       <c r="R7">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>4.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA7">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AB7">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AC7">
-        <v>2.27</v>
+        <v>2.92</v>
       </c>
       <c r="AD7">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
+        <v>1.25</v>
+      </c>
+      <c r="AK7">
         <v>1.16</v>
-      </c>
-      <c r="AK7">
-        <v>2.05</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.6</v>
+        <v>2.65</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>4.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q8">
-        <v>2.15</v>
+        <v>3.17</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U8">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB8">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="O10">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>3.17</v>
+        <v>1.61</v>
       </c>
       <c r="Q10">
-        <v>2.32</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.04</v>
@@ -1975,28 +1975,28 @@
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>2.01</v>
       </c>
       <c r="AK10">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="P11">
-        <v>1.61</v>
+        <v>3.17</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2138,28 +2138,28 @@
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.01</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.78</v>
+        <v>3.44</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>3.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>4.36</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
+        <v>1.86</v>
+      </c>
+      <c r="AB19">
         <v>1.8</v>
       </c>
-      <c r="AB19">
-        <v>1.89</v>
-      </c>
       <c r="AC19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AK19">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.44</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>1.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q20">
-        <v>4.36</v>
+        <v>2.45</v>
       </c>
       <c r="R20">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD20">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4568,13 +4568,13 @@
         <v>2.75</v>
       </c>
       <c r="U26">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.03</v>
@@ -4598,7 +4598,7 @@
         <v>1.21</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
         <v>1.85</v>
@@ -5208,10 +5208,10 @@
         <v>4.21</v>
       </c>
       <c r="Q30">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
         <v>1.37</v>
@@ -5250,7 +5250,7 @@
         <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
         <v>1.83</v>
@@ -5528,7 +5528,7 @@
         <v>3.75</v>
       </c>
       <c r="O32">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
         <v>1.75</v>
@@ -5691,7 +5691,7 @@
         <v>2.38</v>
       </c>
       <c r="O33">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
         <v>2.25</v>
@@ -5902,7 +5902,7 @@
         <v>1.32</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
@@ -6017,7 +6017,7 @@
         <v>2.25</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P35">
         <v>3.15</v>
@@ -6198,10 +6198,10 @@
         <v>2.7</v>
       </c>
       <c r="U36">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V36">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
         <v>1.07</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AK43">
         <v>1.29</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q48">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="AB48">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="AC48">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA49">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AB49">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,10 +8468,10 @@
         <v>2.75</v>
       </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
         <v>1.3</v>
@@ -8510,7 +8510,7 @@
         <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
         <v>1.7</v>
@@ -8631,13 +8631,13 @@
         <v>3.1</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
         <v>2.9</v>
@@ -8652,7 +8652,7 @@
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.25</v>
@@ -8673,7 +8673,7 @@
         <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
         <v>1.75</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
         <v>1.83</v>
@@ -8815,7 +8815,7 @@
         <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
         <v>1.43</v>
@@ -8836,7 +8836,7 @@
         <v>1.16</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF52">
         <v>1.95</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK52">
         <v>1.36</v>
@@ -9141,7 +9141,7 @@
         <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y54">
         <v>1.44</v>
@@ -9162,7 +9162,7 @@
         <v>1.13</v>
       </c>
       <c r="AE54">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF54">
         <v>2</v>
@@ -9313,10 +9313,10 @@
         <v>3.82</v>
       </c>
       <c r="AA55">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB55">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC55">
         <v>2.74</v>
@@ -9325,7 +9325,7 @@
         <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF55">
         <v>1.62</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
         <v>1.67</v>
@@ -9467,7 +9467,7 @@
         <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
         <v>1.36</v>
@@ -9488,7 +9488,7 @@
         <v>1.21</v>
       </c>
       <c r="AE56">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
         <v>1.91</v>
@@ -10092,7 +10092,7 @@
         <v>2.33</v>
       </c>
       <c r="O60">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
         <v>2.75</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q67">
         <v>2.03</v>
@@ -11260,7 +11260,7 @@
         <v>1.04</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y67">
         <v>1.24</v>
@@ -11396,7 +11396,7 @@
         <v>1.25</v>
       </c>
       <c r="O68">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="P68">
         <v>7.1</v>
@@ -11414,10 +11414,10 @@
         <v>4.5</v>
       </c>
       <c r="U68">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V68">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W68">
         <v>1.17</v>
@@ -12214,7 +12214,7 @@
         <v>3.1</v>
       </c>
       <c r="P73">
-        <v>3.77</v>
+        <v>3.51</v>
       </c>
       <c r="Q73">
         <v>2.7</v>
@@ -12226,7 +12226,7 @@
         <v>1.42</v>
       </c>
       <c r="T73">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U73">
         <v>2.73</v>
@@ -12235,28 +12235,28 @@
         <v>1.38</v>
       </c>
       <c r="W73">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
         <v>1.28</v>
       </c>
       <c r="Z73">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AA73">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB73">
         <v>1.8</v>
       </c>
       <c r="AC73">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD73">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE73">
         <v>1.08</v>
@@ -12265,7 +12265,7 @@
         <v>1.8</v>
       </c>
       <c r="AG73">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12377,7 +12377,7 @@
         <v>3.6</v>
       </c>
       <c r="P74">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -12389,16 +12389,16 @@
         <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U74">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V74">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W74">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
         <v>1.03</v>
@@ -12407,19 +12407,19 @@
         <v>1.15</v>
       </c>
       <c r="Z74">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA74">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB74">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AC74">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD74">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE74">
         <v>1.17</v>
@@ -12428,7 +12428,7 @@
         <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
         <v>1.25</v>
@@ -13035,7 +13035,7 @@
         <v>3.79</v>
       </c>
       <c r="R78">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="S78">
         <v>1.25</v>
@@ -13065,7 +13065,7 @@
         <v>1.47</v>
       </c>
       <c r="AB78">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC78">
         <v>2.29</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>2.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>1.08</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
         <v>1.23</v>
@@ -13563,7 +13563,7 @@
         <v>1.31</v>
       </c>
       <c r="AE81">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF81">
         <v>1.65</v>
@@ -14351,10 +14351,10 @@
         <v>2.05</v>
       </c>
       <c r="V86">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.01</v>
@@ -14369,7 +14369,7 @@
         <v>1.37</v>
       </c>
       <c r="AB86">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="AC86">
         <v>1.73</v>
@@ -14381,7 +14381,7 @@
         <v>1.25</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG86">
         <v>2.5</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
         <v>1.4</v>
@@ -14665,7 +14665,7 @@
         <v>2.76</v>
       </c>
       <c r="R88">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S88">
         <v>1.25</v>
@@ -14704,7 +14704,7 @@
         <v>1.48</v>
       </c>
       <c r="AE88">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF88">
         <v>1.5</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
         <v>3.7</v>
@@ -14840,7 +14840,7 @@
         <v>2.29</v>
       </c>
       <c r="V89">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
         <v>1.1</v>
@@ -15009,7 +15009,7 @@
         <v>1.14</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
         <v>1.13</v>
@@ -15308,16 +15308,16 @@
         <v>1.7</v>
       </c>
       <c r="O92">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P92">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="Q92">
         <v>2.24</v>
       </c>
       <c r="R92">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S92">
         <v>1.25</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK92">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15848,7 +15848,7 @@
         <v>1.3</v>
       </c>
       <c r="AF95">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG95">
         <v>2.75</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O98">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P98">
         <v>4.05</v>
@@ -16449,16 +16449,16 @@
         <v>1.48</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P99">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q99">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R99">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S99">
         <v>1.43</v>
@@ -16467,10 +16467,10 @@
         <v>2.76</v>
       </c>
       <c r="U99">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V99">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W99">
         <v>1.05</v>
@@ -16485,10 +16485,10 @@
         <v>2.82</v>
       </c>
       <c r="AA99">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AB99">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC99">
         <v>4.33</v>
@@ -16500,10 +16500,10 @@
         <v>1.06</v>
       </c>
       <c r="AF99">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG99">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16612,13 +16612,13 @@
         <v>2.29</v>
       </c>
       <c r="O100">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P100">
         <v>2.87</v>
       </c>
       <c r="Q100">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="R100">
         <v>2.32</v>
@@ -16663,10 +16663,10 @@
         <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG100">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16775,10 +16775,10 @@
         <v>2.6</v>
       </c>
       <c r="O101">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="P101">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -17641,10 +17641,10 @@
         <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>2.19</v>
       </c>
       <c r="Q112">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="R112">
         <v>2.13</v>
@@ -18616,7 +18616,7 @@
         <v>1.32</v>
       </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF112">
         <v>1.65</v>
@@ -19090,16 +19090,16 @@
         <v>1.11</v>
       </c>
       <c r="Z115">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="AA115">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB115">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AC115">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AD115">
         <v>1.69</v>
@@ -19383,7 +19383,7 @@
         <v>1.74</v>
       </c>
       <c r="O117">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="P117">
         <v>4.22</v>
@@ -19546,13 +19546,13 @@
         <v>2</v>
       </c>
       <c r="O118">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P118">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="Q118">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R118">
         <v>2.62</v>
@@ -19564,10 +19564,10 @@
         <v>5.2</v>
       </c>
       <c r="U118">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V118">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="W118">
         <v>1.29</v>
@@ -19754,7 +19754,7 @@
         <v>2.08</v>
       </c>
       <c r="AD119">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE119">
         <v>1.33</v>
@@ -19779,7 +19779,7 @@
         <v>1.21</v>
       </c>
       <c r="AK119">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20237,7 +20237,7 @@
         <v>2.05</v>
       </c>
       <c r="AB122">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC122">
         <v>3.58</v>
@@ -20358,10 +20358,10 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="O123">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P123">
         <v>3.2</v>
@@ -20400,7 +20400,7 @@
         <v>1.66</v>
       </c>
       <c r="AB123">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC123">
         <v>2.6</v>
@@ -20575,7 +20575,7 @@
         <v>1.21</v>
       </c>
       <c r="AF124">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG124">
         <v>2.05</v>
@@ -20690,7 +20690,7 @@
         <v>3.7</v>
       </c>
       <c r="P125">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -20726,7 +20726,7 @@
         <v>1.5</v>
       </c>
       <c r="AB125">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC125">
         <v>2.44</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O126">
         <v>3.6</v>
       </c>
       <c r="P126">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="Q126">
         <v>2.5</v>
@@ -20904,7 +20904,7 @@
         <v>1.53</v>
       </c>
       <c r="AG126">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T127">
         <v>3.6</v>
@@ -21037,7 +21037,7 @@
         <v>1.51</v>
       </c>
       <c r="W127">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X127">
         <v>1</v>
@@ -21064,10 +21064,10 @@
         <v>1.17</v>
       </c>
       <c r="AF127">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG127">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O128">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P128">
         <v>2.37</v>
       </c>
       <c r="Q128">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R128">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S128">
         <v>1.25</v>
@@ -21194,10 +21194,10 @@
         <v>3.6</v>
       </c>
       <c r="U128">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V128">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W128">
         <v>1.11</v>
@@ -21209,7 +21209,7 @@
         <v>1.17</v>
       </c>
       <c r="Z128">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA128">
         <v>1.69</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21505,7 +21505,7 @@
         <v>3.5</v>
       </c>
       <c r="P130">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q130">
         <v>2.68</v>
@@ -21532,10 +21532,10 @@
         <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z130">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA130">
         <v>1.77</v>
@@ -21831,13 +21831,13 @@
         <v>5</v>
       </c>
       <c r="P132">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q132">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R132">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="S132">
         <v>1.2</v>
@@ -21846,7 +21846,7 @@
         <v>4</v>
       </c>
       <c r="U132">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V132">
         <v>1.68</v>
@@ -21870,13 +21870,13 @@
         <v>2.52</v>
       </c>
       <c r="AC132">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD132">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE132">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF132">
         <v>1.73</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P133">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q133">
         <v>2.63</v>
@@ -22160,10 +22160,10 @@
         <v>23</v>
       </c>
       <c r="Q134">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R134">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="S134">
         <v>1.22</v>
@@ -22172,7 +22172,7 @@
         <v>3.56</v>
       </c>
       <c r="U134">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="V134">
         <v>1.6</v>
@@ -22649,10 +22649,10 @@
         <v>2.15</v>
       </c>
       <c r="Q137">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="R137">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="S137">
         <v>1.27</v>
@@ -23301,7 +23301,7 @@
         <v>3.6</v>
       </c>
       <c r="Q141">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R141">
         <v>2.11</v>
@@ -23365,7 +23365,7 @@
         <v>1.18</v>
       </c>
       <c r="AK141">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23787,7 +23787,7 @@
         <v>3.4</v>
       </c>
       <c r="P144">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="Q144">
         <v>2.78</v>
@@ -23796,10 +23796,10 @@
         <v>2.11</v>
       </c>
       <c r="S144">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U144">
         <v>2.74</v>
@@ -23808,7 +23808,7 @@
         <v>1.41</v>
       </c>
       <c r="W144">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
         <v>1.03</v>
@@ -23944,10 +23944,10 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O145">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P145">
         <v>3.9</v>
@@ -24466,10 +24466,10 @@
         <v>1</v>
       </c>
       <c r="Y148">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z148">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA148">
         <v>1.37</v>
@@ -24478,10 +24478,10 @@
         <v>3.07</v>
       </c>
       <c r="AC148">
+        <v>1.87</v>
+      </c>
+      <c r="AD148">
         <v>1.9</v>
-      </c>
-      <c r="AD148">
-        <v>1.87</v>
       </c>
       <c r="AE148">
         <v>1.38</v>
@@ -29199,10 +29199,10 @@
         <v>4.54</v>
       </c>
       <c r="AA177">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB177">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC177">
         <v>2.47</v>
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AK177">
         <v>1.35</v>
@@ -30494,7 +30494,7 @@
         <v>1.11</v>
       </c>
       <c r="X185">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y185">
         <v>1.16</v>
@@ -30639,7 +30639,7 @@
         <v>1.71</v>
       </c>
       <c r="R186">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="S186">
         <v>1.18</v>
@@ -30681,7 +30681,7 @@
         <v>1.36</v>
       </c>
       <c r="AF186">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG186">
         <v>2.3</v>
@@ -30799,10 +30799,10 @@
         <v>2.62</v>
       </c>
       <c r="Q187">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R187">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S187">
         <v>1.3</v>
@@ -30863,7 +30863,7 @@
         <v>1.29</v>
       </c>
       <c r="AK187">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31004,7 +31004,7 @@
         <v>1.33</v>
       </c>
       <c r="AE188">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF188">
         <v>1.71</v>
@@ -31125,7 +31125,7 @@
         <v>2.25</v>
       </c>
       <c r="Q189">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="R189">
         <v>2.27</v>
@@ -31134,7 +31134,7 @@
         <v>1.33</v>
       </c>
       <c r="T189">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="U189">
         <v>2.56</v>
@@ -31158,7 +31158,7 @@
         <v>1.88</v>
       </c>
       <c r="AB189">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC189">
         <v>2.88</v>
@@ -31282,7 +31282,7 @@
         <v>2.63</v>
       </c>
       <c r="O190">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P190">
         <v>2.23</v>
@@ -31321,7 +31321,7 @@
         <v>2.05</v>
       </c>
       <c r="AB190">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC190">
         <v>3.2</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="O191">
         <v>4</v>
       </c>
       <c r="P191">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q191">
         <v>2.01</v>
@@ -31792,7 +31792,7 @@
         <v>2.5</v>
       </c>
       <c r="V193">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W193">
         <v>1.1</v>
@@ -32001,7 +32001,7 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK194">
         <v>1.65</v>
@@ -32100,7 +32100,7 @@
         <v>4.45</v>
       </c>
       <c r="P195">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q195">
         <v>4.53</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="O198">
         <v>3.66</v>
@@ -32616,22 +32616,22 @@
         <v>1</v>
       </c>
       <c r="Y198">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z198">
         <v>3.54</v>
       </c>
       <c r="AA198">
+        <v>1.9</v>
+      </c>
+      <c r="AB198">
         <v>1.87</v>
       </c>
-      <c r="AB198">
-        <v>1.9</v>
-      </c>
       <c r="AC198">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="AD198">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE198">
         <v>1.07</v>
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK198">
         <v>1.83</v>
@@ -32776,7 +32776,7 @@
         <v>1.06</v>
       </c>
       <c r="X199">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y199">
         <v>1.33</v>
@@ -32797,7 +32797,7 @@
         <v>1.21</v>
       </c>
       <c r="AE199">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF199">
         <v>1.83</v>
@@ -33244,10 +33244,10 @@
         <v>1.53</v>
       </c>
       <c r="Q202">
-        <v>4.03</v>
+        <v>4.12</v>
       </c>
       <c r="R202">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S202">
         <v>1.14</v>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK202">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33573,7 +33573,7 @@
         <v>2.5</v>
       </c>
       <c r="R204">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S204">
         <v>1.28</v>
@@ -33742,7 +33742,7 @@
         <v>1.5</v>
       </c>
       <c r="T205">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="U205">
         <v>3.38</v>
@@ -33751,10 +33751,10 @@
         <v>1.24</v>
       </c>
       <c r="W205">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X205">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y205">
         <v>1.49</v>
@@ -33775,10 +33775,10 @@
         <v>1.14</v>
       </c>
       <c r="AE205">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF205">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AG205">
         <v>1.65</v>
@@ -33941,7 +33941,7 @@
         <v>1.15</v>
       </c>
       <c r="AF206">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG206">
         <v>2.3</v>
@@ -34059,7 +34059,7 @@
         <v>2.75</v>
       </c>
       <c r="Q207">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R207">
         <v>2.17</v>
@@ -34123,7 +34123,7 @@
         <v>1.3</v>
       </c>
       <c r="AK207">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34388,7 +34388,7 @@
         <v>2.3</v>
       </c>
       <c r="R209">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="S209">
         <v>1.2</v>
@@ -34542,13 +34542,13 @@
         <v>6.5</v>
       </c>
       <c r="O210">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P210">
         <v>1.34</v>
       </c>
       <c r="Q210">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R210">
         <v>2.5</v>
@@ -34557,10 +34557,10 @@
         <v>1.3</v>
       </c>
       <c r="T210">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U210">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V210">
         <v>1.5</v>
@@ -34572,47 +34572,47 @@
         <v>1.02</v>
       </c>
       <c r="Y210">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z210">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA210">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB210">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC210">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD210">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE210">
+        <v>1.15</v>
+      </c>
+      <c r="AF210">
+        <v>1.88</v>
+      </c>
+      <c r="AG210">
+        <v>1.85</v>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ210">
         <v>1.14</v>
       </c>
-      <c r="AF210">
-        <v>1.85</v>
-      </c>
-      <c r="AG210">
-        <v>1.83</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ210">
-        <v>1.17</v>
-      </c>
       <c r="AK210">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35043,7 +35043,7 @@
         <v>2.15</v>
       </c>
       <c r="S213">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T213">
         <v>2.77</v>
@@ -35058,7 +35058,7 @@
         <v>1.07</v>
       </c>
       <c r="X213">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y213">
         <v>1.29</v>
@@ -35079,7 +35079,7 @@
         <v>1.21</v>
       </c>
       <c r="AE213">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF213">
         <v>1.89</v>
@@ -35221,7 +35221,7 @@
         <v>1.1</v>
       </c>
       <c r="X214">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
         <v>1.16</v>
@@ -35725,7 +35725,7 @@
         <v>2</v>
       </c>
       <c r="AC217">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD217">
         <v>1.33</v>
@@ -35737,7 +35737,7 @@
         <v>1.6</v>
       </c>
       <c r="AG217">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>1.28</v>
       </c>
       <c r="AE218">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF218">
         <v>1.91</v>
@@ -36863,7 +36863,7 @@
         <v>1.53</v>
       </c>
       <c r="AB224">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AC224">
         <v>2.25</v>
@@ -36894,7 +36894,7 @@
         <v>1.01</v>
       </c>
       <c r="AK224">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36990,7 +36990,7 @@
         <v>3.45</v>
       </c>
       <c r="P225">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="Q225">
         <v>2.54</v>
@@ -37147,16 +37147,16 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="O226">
         <v>4.25</v>
       </c>
       <c r="P226">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q226">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="R226">
         <v>2.38</v>
@@ -37168,7 +37168,7 @@
         <v>3.52</v>
       </c>
       <c r="U226">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V226">
         <v>1.5</v>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK226">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,80 +37310,80 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.7</v>
+        <v>1.56</v>
       </c>
       <c r="O227">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P227">
+        <v>5.25</v>
+      </c>
+      <c r="Q227">
+        <v>2.01</v>
+      </c>
+      <c r="R227">
+        <v>2.5</v>
+      </c>
+      <c r="S227">
+        <v>1.25</v>
+      </c>
+      <c r="T227">
+        <v>3.94</v>
+      </c>
+      <c r="U227">
+        <v>2.3</v>
+      </c>
+      <c r="V227">
+        <v>1.67</v>
+      </c>
+      <c r="W227">
+        <v>1.15</v>
+      </c>
+      <c r="X227">
+        <v>1.01</v>
+      </c>
+      <c r="Y227">
+        <v>1.14</v>
+      </c>
+      <c r="Z227">
+        <v>5.5</v>
+      </c>
+      <c r="AA227">
+        <v>1.49</v>
+      </c>
+      <c r="AB227">
+        <v>2.48</v>
+      </c>
+      <c r="AC227">
+        <v>2.39</v>
+      </c>
+      <c r="AD227">
+        <v>1.59</v>
+      </c>
+      <c r="AE227">
+        <v>1.22</v>
+      </c>
+      <c r="AF227">
+        <v>1.57</v>
+      </c>
+      <c r="AG227">
+        <v>2.3</v>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ227">
+        <v>1.17</v>
+      </c>
+      <c r="AK227">
         <v>2.4</v>
-      </c>
-      <c r="Q227">
-        <v>3.68</v>
-      </c>
-      <c r="R227">
-        <v>2.05</v>
-      </c>
-      <c r="S227">
-        <v>1.44</v>
-      </c>
-      <c r="T227">
-        <v>2.72</v>
-      </c>
-      <c r="U227">
-        <v>2.88</v>
-      </c>
-      <c r="V227">
-        <v>1.36</v>
-      </c>
-      <c r="W227">
-        <v>1.06</v>
-      </c>
-      <c r="X227">
-        <v>1.02</v>
-      </c>
-      <c r="Y227">
-        <v>1.3</v>
-      </c>
-      <c r="Z227">
-        <v>3.21</v>
-      </c>
-      <c r="AA227">
-        <v>2.08</v>
-      </c>
-      <c r="AB227">
-        <v>1.76</v>
-      </c>
-      <c r="AC227">
-        <v>3.5</v>
-      </c>
-      <c r="AD227">
-        <v>1.29</v>
-      </c>
-      <c r="AE227">
-        <v>1.08</v>
-      </c>
-      <c r="AF227">
-        <v>1.75</v>
-      </c>
-      <c r="AG227">
-        <v>2</v>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ227">
-        <v>1.36</v>
-      </c>
-      <c r="AK227">
-        <v>1.41</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="O228">
-        <v>4.24</v>
+        <v>3.6</v>
       </c>
       <c r="P228">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="Q228">
+        <v>2.61</v>
+      </c>
+      <c r="R228">
+        <v>2.25</v>
+      </c>
+      <c r="S228">
+        <v>1.31</v>
+      </c>
+      <c r="T228">
+        <v>3.35</v>
+      </c>
+      <c r="U228">
+        <v>2.51</v>
+      </c>
+      <c r="V228">
+        <v>1.5</v>
+      </c>
+      <c r="W228">
+        <v>1.1</v>
+      </c>
+      <c r="X228">
+        <v>1.02</v>
+      </c>
+      <c r="Y228">
+        <v>1.2</v>
+      </c>
+      <c r="Z228">
+        <v>4.29</v>
+      </c>
+      <c r="AA228">
+        <v>1.69</v>
+      </c>
+      <c r="AB228">
         <v>2.2</v>
       </c>
-      <c r="R228">
-        <v>2.52</v>
-      </c>
-      <c r="S228">
-        <v>1.2</v>
-      </c>
-      <c r="T228">
-        <v>4</v>
-      </c>
-      <c r="U228">
-        <v>2</v>
-      </c>
-      <c r="V228">
-        <v>1.75</v>
-      </c>
-      <c r="W228">
-        <v>1.22</v>
-      </c>
-      <c r="X228">
-        <v>1</v>
-      </c>
-      <c r="Y228">
-        <v>1.1</v>
-      </c>
-      <c r="Z228">
-        <v>6.5</v>
-      </c>
-      <c r="AA228">
+      <c r="AC228">
+        <v>2.58</v>
+      </c>
+      <c r="AD228">
         <v>1.43</v>
       </c>
-      <c r="AB228">
-        <v>2.8</v>
-      </c>
-      <c r="AC228">
-        <v>2.12</v>
-      </c>
-      <c r="AD228">
-        <v>1.75</v>
-      </c>
       <c r="AE228">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AF228">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AG228">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK228">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="O229">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="P229">
-        <v>5.25</v>
+        <v>3.81</v>
       </c>
       <c r="Q229">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="R229">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S229">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T229">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="U229">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V229">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W229">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X229">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y229">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z229">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA229">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AB229">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AC229">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AD229">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AE229">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF229">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AG229">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK229">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="O230">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P230">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q230">
-        <v>2.61</v>
+        <v>3.68</v>
       </c>
       <c r="R230">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S230">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T230">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="U230">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="V230">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W230">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X230">
         <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z230">
-        <v>4.29</v>
+        <v>3.21</v>
       </c>
       <c r="AA230">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="AB230">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC230">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD230">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AE230">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF230">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG230">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK230">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37965,7 +37965,7 @@
         <v>3</v>
       </c>
       <c r="O231">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P231">
         <v>2.37</v>
@@ -37983,7 +37983,7 @@
         <v>2.59</v>
       </c>
       <c r="U231">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="V231">
         <v>1.3</v>
@@ -37995,13 +37995,13 @@
         <v>1.04</v>
       </c>
       <c r="Y231">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z231">
         <v>3.1</v>
       </c>
       <c r="AA231">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB231">
         <v>1.77</v>
@@ -38155,7 +38155,7 @@
         <v>1.12</v>
       </c>
       <c r="X232">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y232">
         <v>1.15</v>
@@ -38644,7 +38644,7 @@
         <v>1.08</v>
       </c>
       <c r="X235">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y235">
         <v>1.2</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O236">
         <v>3.25</v>
@@ -39106,7 +39106,7 @@
         <v>2.25</v>
       </c>
       <c r="O238">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P238">
         <v>3</v>
@@ -39323,7 +39323,7 @@
         <v>1.91</v>
       </c>
       <c r="AG239">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39432,16 +39432,16 @@
         <v>2.37</v>
       </c>
       <c r="O240">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P240">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q240">
         <v>3.06</v>
       </c>
       <c r="R240">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S240">
         <v>1.42</v>
@@ -39474,7 +39474,7 @@
         <v>1.75</v>
       </c>
       <c r="AC240">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="AD240">
         <v>1.18</v>
@@ -39595,16 +39595,16 @@
         <v>3.25</v>
       </c>
       <c r="O241">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P241">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q241">
         <v>3.91</v>
       </c>
       <c r="R241">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="S241">
         <v>1.34</v>
@@ -39619,7 +39619,7 @@
         <v>1.39</v>
       </c>
       <c r="W241">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X241">
         <v>1.01</v>
@@ -39634,7 +39634,7 @@
         <v>1.81</v>
       </c>
       <c r="AB241">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC241">
         <v>2.92</v>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AK241">
         <v>1.3</v>
@@ -39764,7 +39764,7 @@
         <v>1.37</v>
       </c>
       <c r="Q242">
-        <v>5.5</v>
+        <v>4.52</v>
       </c>
       <c r="R242">
         <v>3</v>
@@ -39812,7 +39812,7 @@
         <v>1.39</v>
       </c>
       <c r="AG242">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>4.3</v>
       </c>
       <c r="P243">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q243">
         <v>2</v>
@@ -40090,28 +40090,28 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R244">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S244">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T244">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="U244">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V244">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W244">
         <v>1.08</v>
       </c>
       <c r="X244">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y244">
         <v>1.34</v>
@@ -40120,25 +40120,25 @@
         <v>3.05</v>
       </c>
       <c r="AA244">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB244">
         <v>1.79</v>
       </c>
       <c r="AC244">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD244">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE244">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF244">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG244">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK244">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,10 +40244,10 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="O245">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="P245">
         <v>6</v>
@@ -40286,7 +40286,7 @@
         <v>1.4</v>
       </c>
       <c r="AB245">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC245">
         <v>1.94</v>
@@ -40419,43 +40419,43 @@
         <v>1.91</v>
       </c>
       <c r="R246">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="S246">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T246">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U246">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V246">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W246">
+        <v>1.14</v>
+      </c>
+      <c r="X246">
+        <v>1.02</v>
+      </c>
+      <c r="Y246">
         <v>1.12</v>
       </c>
-      <c r="X246">
-        <v>1.03</v>
-      </c>
-      <c r="Y246">
-        <v>1.13</v>
-      </c>
       <c r="Z246">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA246">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB246">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC246">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AD246">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AE246">
         <v>1.18</v>
@@ -40464,7 +40464,7 @@
         <v>1.7</v>
       </c>
       <c r="AG246">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>1.09</v>
       </c>
       <c r="AK246">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -41249,7 +41249,7 @@
         <v>1.55</v>
       </c>
       <c r="W251">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X251">
         <v>1</v>
@@ -41385,7 +41385,7 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O252">
         <v>3.78</v>
@@ -41397,7 +41397,7 @@
         <v>2.2</v>
       </c>
       <c r="R252">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S252">
         <v>1.36</v>
@@ -41548,19 +41548,19 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="O253">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P253">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q253">
         <v>2.2</v>
       </c>
       <c r="R253">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S253">
         <v>1.25</v>
@@ -41584,22 +41584,22 @@
         <v>1.15</v>
       </c>
       <c r="Z253">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AA253">
         <v>1.61</v>
       </c>
       <c r="AB253">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC253">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AD253">
         <v>1.51</v>
       </c>
       <c r="AE253">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF253">
         <v>1.6</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="O254">
         <v>3.25</v>
       </c>
       <c r="P254">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q254">
         <v>3.04</v>
@@ -41738,7 +41738,7 @@
         <v>1.37</v>
       </c>
       <c r="W254">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X254">
         <v>1.03</v>
@@ -41913,7 +41913,7 @@
         <v>3.68</v>
       </c>
       <c r="AA255">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB255">
         <v>2.1</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="O256">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P256">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="Q256">
         <v>2.75</v>
@@ -42206,7 +42206,7 @@
         <v>3.3</v>
       </c>
       <c r="P257">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q257">
         <v>4.28</v>
@@ -42233,25 +42233,25 @@
         <v>1</v>
       </c>
       <c r="Y257">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z257">
         <v>3.77</v>
       </c>
       <c r="AA257">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB257">
         <v>1.97</v>
       </c>
       <c r="AC257">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD257">
         <v>1.33</v>
       </c>
       <c r="AE257">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF257">
         <v>1.7</v>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK257">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42867,7 +42867,7 @@
         <v>2</v>
       </c>
       <c r="S261">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T261">
         <v>2.43</v>
@@ -42882,7 +42882,7 @@
         <v>1.05</v>
       </c>
       <c r="X261">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y261">
         <v>1.46</v>
@@ -42903,7 +42903,7 @@
         <v>1.15</v>
       </c>
       <c r="AE261">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF261">
         <v>2.11</v>
@@ -43178,7 +43178,7 @@
         </is>
       </c>
       <c r="N263">
-        <v>5.95</v>
+        <v>5.4</v>
       </c>
       <c r="O263">
         <v>4.12</v>
@@ -43356,7 +43356,7 @@
         <v>2.05</v>
       </c>
       <c r="S264">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T264">
         <v>2.56</v>
@@ -43411,7 +43411,7 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="AK264">
         <v>1.25</v>
@@ -43510,7 +43510,7 @@
         <v>4.2</v>
       </c>
       <c r="P265">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q265">
         <v>1.88</v>
@@ -43546,7 +43546,7 @@
         <v>1.4</v>
       </c>
       <c r="AB265">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC265">
         <v>2.02</v>
@@ -43884,7 +43884,7 @@
         <v>1.15</v>
       </c>
       <c r="AF267">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG267">
         <v>2.4</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,22 +44156,22 @@
         </is>
       </c>
       <c r="N269">
-        <v>1.61</v>
+        <v>2.45</v>
       </c>
       <c r="O269">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P269">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q269">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="R269">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S269">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T269">
         <v>2.2</v>
@@ -44183,25 +44183,25 @@
         <v>1.2</v>
       </c>
       <c r="W269">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X269">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y269">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z269">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AA269">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB269">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC269">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AD269">
         <v>1.04</v>
@@ -44210,10 +44210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF269">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AG269">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK269">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,22 +44319,22 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="O270">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P270">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="Q270">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="R270">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S270">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T270">
         <v>2.2</v>
@@ -44346,25 +44346,25 @@
         <v>1.2</v>
       </c>
       <c r="W270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X270">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y270">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z270">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AA270">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB270">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC270">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AD270">
         <v>1.04</v>
@@ -44373,10 +44373,10 @@
         <v>1.02</v>
       </c>
       <c r="AF270">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AG270">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK270">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -45013,7 +45013,7 @@
         <v>3.1</v>
       </c>
       <c r="AB274">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC274">
         <v>6</v>
@@ -45460,19 +45460,19 @@
         </is>
       </c>
       <c r="N277">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O277">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P277">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q277">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="R277">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S277">
         <v>1.67</v>
@@ -45490,13 +45490,13 @@
         <v>1.03</v>
       </c>
       <c r="X277">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y277">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Z277">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AA277">
         <v>3.4</v>
@@ -45505,7 +45505,7 @@
         <v>1.32</v>
       </c>
       <c r="AC277">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="AD277">
         <v>1.05</v>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AK277">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45629,7 +45629,7 @@
         <v>3.45</v>
       </c>
       <c r="P278">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q278">
         <v>2.3</v>
@@ -45665,7 +45665,7 @@
         <v>2.18</v>
       </c>
       <c r="AB278">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC278">
         <v>3.98</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O280">
         <v>3.9</v>
       </c>
       <c r="P280">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q280">
         <v>2.6</v>
@@ -45982,16 +45982,16 @@
         <v>1</v>
       </c>
       <c r="Y280">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z280">
-        <v>6.28</v>
+        <v>6.21</v>
       </c>
       <c r="AA280">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB280">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC280">
         <v>2.17</v>
@@ -46112,7 +46112,7 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="O281">
         <v>5</v>
@@ -46127,10 +46127,10 @@
         <v>2.7</v>
       </c>
       <c r="S281">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T281">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U281">
         <v>2</v>
@@ -46284,7 +46284,7 @@
         <v>1.53</v>
       </c>
       <c r="Q282">
-        <v>5.21</v>
+        <v>5.07</v>
       </c>
       <c r="R282">
         <v>2.26</v>
@@ -46296,10 +46296,10 @@
         <v>3.2</v>
       </c>
       <c r="U282">
-        <v>2.8